--- a/交易管理系统不贪婪版.xlsx
+++ b/交易管理系统不贪婪版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14060"/>
+    <workbookView windowWidth="29400" windowHeight="13460"/>
   </bookViews>
   <sheets>
     <sheet name="单次交易" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="_TrackRule">持仓跟踪!$AC$2:$AC$157</definedName>
     <definedName name="_TrackTradeId">持仓跟踪!$B$2:$B$157</definedName>
     <definedName name="_TrackType">持仓跟踪!$A$2:$A$157</definedName>
-    <definedName name="_TradeIds">单次交易!$A$2:$A$98</definedName>
+    <definedName name="_TradeIds">单次交易!$A$2:$A$102</definedName>
     <definedName name="技术指标列表">技术指标!$A$2:$A$201</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="320">
   <si>
     <t>交易编号</t>
   </si>
@@ -825,6 +825,9 @@
     <t>放大，然后持有</t>
   </si>
   <si>
+    <t>是不是放到6.5更合适</t>
+  </si>
+  <si>
     <t>指标</t>
   </si>
   <si>
@@ -1239,7 +1242,7 @@
     <numFmt numFmtId="176" formatCode="\¥#,##0.00;[Red]\-\¥#,##0.00"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1261,13 +1264,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1779,13 +1775,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1794,122 +1793,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1953,13 +1949,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1969,55 +1962,37 @@
     <xf numFmtId="177" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2105,8 +2080,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TradeRecords" displayName="TradeRecords" ref="A1:AR98">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AR98" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TradeRecords" displayName="TradeRecords" ref="A1:AR102">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AR102" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="44">
     <tableColumn id="1" name="交易编号"/>
     <tableColumn id="2" name="股票代码"/>
@@ -2206,7 +2181,7 @@
     <tableColumn id="1" name="记录类型"/>
     <tableColumn id="2" name="交易编号"/>
     <tableColumn id="3" name="股票代码">
-      <calculatedColumnFormula>IF(B2="","",IFERROR(LOOKUP(2,1/(单次交易!$A$2:$A$98=B2),单次交易!$B$2:$B$98),""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(B2="","",IFERROR(LOOKUP(2,1/(单次交易!$A$2:$A$102=B2),单次交易!$B$2:$B$102),""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" name="止损阶段序号"/>
     <tableColumn id="5" name="激活价"/>
@@ -2219,7 +2194,7 @@
     <tableColumn id="12" name="当前阶段"/>
     <tableColumn id="13" name="阶段判断理由"/>
     <tableColumn id="14" name="初始止损">
-      <calculatedColumnFormula>IF(B2="","",IFERROR(LOOKUP(2,1/(单次交易!$A$2:$A$98=B2),单次交易!$N$2:$N$98),""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(B2="","",IFERROR(LOOKUP(2,1/(单次交易!$A$2:$A$102=B2),单次交易!$N$2:$N$102),""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" name="历史最高收盘价">
       <calculatedColumnFormula>IF(A2&lt;&gt;"每日跟踪","",IF(OR(B2="",H2="",I2=""),"",IFERROR(SUMPRODUCT(MAX((($A$2:$A$497="每日跟踪")*($B$2:$B$497=B2)*($H$2:$H$497&lt;=H2))*$I$2:$I$497)),"")))</calculatedColumnFormula>
@@ -2249,14 +2224,14 @@
     <tableColumn id="24" name="卖出动作"/>
     <tableColumn id="25" name="实际卖出价"/>
     <tableColumn id="26" name="实际卖出股数">
-      <calculatedColumnFormula>IF(X2&lt;&gt;"执行卖出","",IFERROR(LOOKUP(2,1/(单次交易!$A$2:$A$98=B2),单次交易!$AP$2:$AP$98),""))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(X2&lt;&gt;"执行卖出","",IFERROR(LOOKUP(2,1/(单次交易!$A$2:$A$102=B2),单次交易!$AP$2:$AP$102),""))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="27" name="卖出费用"/>
     <tableColumn id="28" name="执行检查">
       <calculatedColumnFormula>IF(A2&lt;&gt;"每日跟踪","",IF(OR(B2="",H2="",I2="",J2="",K2="",L2="",M2=""),"待补充每日记录",IF(W2="触发止损：应全部卖出",IF(X2&lt;&gt;"执行卖出","违规：触发止损但未执行",IF(Y2="","待补充实际卖出价","卖出记录完整")),IF(X2="","待选择卖出动作",IF(X2="执行卖出",IF(Y2="","待补充实际卖出价","卖出记录完整"),"正常")))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="29" name="规则检查">
-      <calculatedColumnFormula>IF(A2="","",IF(A2="止损计划",IF(OR(B2="",D2="",E2="",F2="",G2=""),"计划不完整",IF(OR(D2&lt;1,D2&lt;&gt;INT(D2)),"阶段序号无效",IF(COUNTIFS($A$2:$A$497,"止损计划",$B$2:$B$497,B2,$D$2:$D$497,D2)&gt;1,"阶段序号重复",IF(E2&lt;=IFERROR(LOOKUP(2,1/(单次交易!$A$2:$A$98=B2),单次交易!$E$2:$E$98),0),"激活价须高于买入价",IF(F2&lt;N2,"止损价不得低于初始止损",IF(F2&gt;E2,"止损价不得高于激活价",IF(AND(COUNTIFS($A$2:$A$497,"止损计划",$B$2:$B$497,B2,$D$2:$D$497,"&lt;"&amp;D2)&gt;0,OR(E2&lt;=SUMPRODUCT(MAX((($A$2:$A$497="止损计划")*($B$2:$B$497=B2)*($D$2:$D$497&lt;D2))*$E$2:$E$497)),F2&lt;SUMPRODUCT(MAX((($A$2:$A$497="止损计划")*($B$2:$B$497=B2)*($D$2:$D$497&lt;D2))*$F$2:$F$497)))),"阶段价格必须逐级提高","计划有效"))))))),IF(A2="每日跟踪",IF(OR(B2="",H2="",I2="",J2=""),"每日数据不完整",IF(COUNTIFS($A$2:$A$497,"每日跟踪",$B$2:$B$497,B2,$H$2:$H$497,H2)&gt;1,"同一交易日期重复",IF(AND(R2&lt;&gt;"",R2&lt;S2),"人工止损无效：不能下调","跟踪有效"))),"记录类型无效")))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(A2="","",IF(A2="止损计划",IF(OR(B2="",D2="",E2="",F2="",G2=""),"计划不完整",IF(OR(D2&lt;1,D2&lt;&gt;INT(D2)),"阶段序号无效",IF(COUNTIFS($A$2:$A$497,"止损计划",$B$2:$B$497,B2,$D$2:$D$497,D2)&gt;1,"阶段序号重复",IF(E2&lt;=IFERROR(LOOKUP(2,1/(单次交易!$A$2:$A$102=B2),单次交易!$E$2:$E$102),0),"激活价须高于买入价",IF(F2&lt;N2,"止损价不得低于初始止损",IF(F2&gt;E2,"止损价不得高于激活价",IF(AND(COUNTIFS($A$2:$A$497,"止损计划",$B$2:$B$497,B2,$D$2:$D$497,"&lt;"&amp;D2)&gt;0,OR(E2&lt;=SUMPRODUCT(MAX((($A$2:$A$497="止损计划")*($B$2:$B$497=B2)*($D$2:$D$497&lt;D2))*$E$2:$E$497)),F2&lt;SUMPRODUCT(MAX((($A$2:$A$497="止损计划")*($B$2:$B$497=B2)*($D$2:$D$497&lt;D2))*$F$2:$F$497)))),"阶段价格必须逐级提高","计划有效"))))))),IF(A2="每日跟踪",IF(OR(B2="",H2="",I2="",J2=""),"每日数据不完整",IF(COUNTIFS($A$2:$A$497,"每日跟踪",$B$2:$B$497,B2,$H$2:$H$497,H2)&gt;1,"同一交易日期重复",IF(AND(R2&lt;&gt;"",R2&lt;S2),"人工止损无效：不能下调","跟踪有效"))),"记录类型无效")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2710,40 +2685,40 @@
       <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="16" t="s">
+      <c r="AG1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="16" t="s">
+      <c r="AH1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="16" t="s">
+      <c r="AI1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="16" t="s">
+      <c r="AJ1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="16" t="s">
+      <c r="AK1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="16" t="s">
+      <c r="AL1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="16" t="s">
+      <c r="AM1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="16" t="s">
+      <c r="AN1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="16" t="s">
+      <c r="AO1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="16" t="s">
+      <c r="AP1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="16" t="s">
+      <c r="AQ1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="16" t="s">
+      <c r="AR1" s="15" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2786,7 +2761,7 @@
       <c r="L2" s="8">
         <v>5000</v>
       </c>
-      <c r="M2" s="18">
+      <c r="M2" s="17">
         <f>IF(A2="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A2)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42578</v>
       </c>
@@ -2810,7 +2785,7 @@
         <f>IF(OR(AO2="",N2="",AO2&lt;=0),"",(AO2-N2)/AO2)</f>
         <v>0.0512820512820512</v>
       </c>
-      <c r="W2" s="19">
+      <c r="W2" s="18">
         <f>IF(OR(U2="",V2="",V2&lt;=0),"",U2/V2)</f>
         <v>0.500000000000001</v>
       </c>
@@ -2824,7 +2799,7 @@
       </c>
       <c r="Z2" s="7">
         <f>IF(OR(AE2="",多次统计数据!$B$8=""),"",AE2-多次统计数据!$B$8)</f>
-        <v>-0.083548626922961</v>
+        <v>-0.0829438248745022</v>
       </c>
       <c r="AA2" s="11">
         <f>IF(OR(I2="",M2="",M2&lt;I2),"",M2-I2)</f>
@@ -2832,7 +2807,7 @@
       </c>
       <c r="AB2" s="7">
         <f>IF(OR(A2="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC2" s="8" t="str">
         <f>IF(OR(AB2="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB2,"低于上限","达到或超过上限"))</f>
@@ -2875,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="AR2" s="8" t="str">
-        <f ca="1">IF(A2="","",IF(OR(E2="",H2=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK2="",AL2&lt;&gt;""),AND(AK2&lt;&gt;"",AL2="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM2="",AN2&lt;&gt;""),AND(AM2&lt;&gt;"",AN2="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM2&lt;&gt;"",AN2&lt;&gt;""),OR(AK2="",AL2="")),"违规：必须先完成第二批",IF(OR(H2&lt;=0,H2&lt;&gt;INT(H2),MOD(H2,100)&lt;&gt;0,AND(AL2&lt;&gt;"",OR(AL2&lt;=0,AL2&lt;&gt;INT(AL2),MOD(AL2,100)&lt;&gt;0)),AND(AN2&lt;&gt;"",OR(AN2&lt;=0,AN2&lt;&gt;INT(AN2),MOD(AN2,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL2&lt;&gt;"",AN2&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ2&gt;C2*D2,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A2="","",IF(OR(E2="",H2=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK2="",AL2&lt;&gt;""),AND(AK2&lt;&gt;"",AL2="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM2="",AN2&lt;&gt;""),AND(AM2&lt;&gt;"",AN2="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM2&lt;&gt;"",AN2&lt;&gt;""),OR(AK2="",AL2="")),"违规：必须先完成第二批",IF(OR(H2&lt;=0,H2&lt;&gt;INT(H2),MOD(H2,100)&lt;&gt;0,AND(AL2&lt;&gt;"",OR(AL2&lt;=0,AL2&lt;&gt;INT(AL2),MOD(AL2,100)&lt;&gt;0)),AND(AN2&lt;&gt;"",OR(AN2&lt;=0,AN2&lt;&gt;INT(AN2),MOD(AN2,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL2&lt;&gt;"",AN2&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ2&gt;C2*D2,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -2918,7 +2893,7 @@
       <c r="L3" s="8">
         <v>9800</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="17">
         <f>IF(A3="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A3)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42663</v>
       </c>
@@ -2942,7 +2917,7 @@
         <f>IF(OR(AO3="",N3="",AO3&lt;=0),"",(AO3-N3)/AO3)</f>
         <v>0.0540540540540541</v>
       </c>
-      <c r="W3" s="19">
+      <c r="W3" s="18">
         <f>IF(OR(U3="",V3="",V3&lt;=0),"",U3/V3)</f>
         <v>1.5</v>
       </c>
@@ -2956,7 +2931,7 @@
       </c>
       <c r="Z3" s="7">
         <f>IF(OR(AE3="",多次统计数据!$B$8=""),"",AE3-多次统计数据!$B$8)</f>
-        <v>-0.0210218321807972</v>
+        <v>-0.0204170301323384</v>
       </c>
       <c r="AA3" s="11">
         <f>IF(OR(I3="",M3="",M3&lt;I3),"",M3-I3)</f>
@@ -2964,7 +2939,7 @@
       </c>
       <c r="AB3" s="7">
         <f>IF(OR(A3="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC3" s="8" t="str">
         <f>IF(OR(AB3="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB3,"低于上限","达到或超过上限"))</f>
@@ -3007,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="AR3" s="8" t="str">
-        <f ca="1">IF(A3="","",IF(OR(E3="",H3=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK3="",AL3&lt;&gt;""),AND(AK3&lt;&gt;"",AL3="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM3="",AN3&lt;&gt;""),AND(AM3&lt;&gt;"",AN3="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM3&lt;&gt;"",AN3&lt;&gt;""),OR(AK3="",AL3="")),"违规：必须先完成第二批",IF(OR(H3&lt;=0,H3&lt;&gt;INT(H3),MOD(H3,100)&lt;&gt;0,AND(AL3&lt;&gt;"",OR(AL3&lt;=0,AL3&lt;&gt;INT(AL3),MOD(AL3,100)&lt;&gt;0)),AND(AN3&lt;&gt;"",OR(AN3&lt;=0,AN3&lt;&gt;INT(AN3),MOD(AN3,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL3&lt;&gt;"",AN3&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ3&gt;C3*D3,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A3="","",IF(OR(E3="",H3=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK3="",AL3&lt;&gt;""),AND(AK3&lt;&gt;"",AL3="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM3="",AN3&lt;&gt;""),AND(AM3&lt;&gt;"",AN3="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM3&lt;&gt;"",AN3&lt;&gt;""),OR(AK3="",AL3="")),"违规：必须先完成第二批",IF(OR(H3&lt;=0,H3&lt;&gt;INT(H3),MOD(H3,100)&lt;&gt;0,AND(AL3&lt;&gt;"",OR(AL3&lt;=0,AL3&lt;&gt;INT(AL3),MOD(AL3,100)&lt;&gt;0)),AND(AN3&lt;&gt;"",OR(AN3&lt;=0,AN3&lt;&gt;INT(AN3),MOD(AN3,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL3&lt;&gt;"",AN3&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ3&gt;C3*D3,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -3052,7 +3027,7 @@
         <f>IF(A4="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A4)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>9000</v>
       </c>
-      <c r="M4" s="18">
+      <c r="M4" s="17">
         <f>IF(A4="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A4)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42716</v>
       </c>
@@ -3076,7 +3051,7 @@
         <f>IF(OR(AO4="",N4="",AO4&lt;=0),"",(AO4-N4)/AO4)</f>
         <v>0.0585241730279898</v>
       </c>
-      <c r="W4" s="19">
+      <c r="W4" s="18">
         <f>IF(OR(U4="",V4="",V4&lt;=0),"",U4/V4)</f>
         <v>2.47826086956522</v>
       </c>
@@ -3090,7 +3065,7 @@
       </c>
       <c r="Z4" s="7">
         <f>IF(OR(AE4="",多次统计数据!$B$8=""),"",AE4-多次统计数据!$B$8)</f>
-        <v>-0.0933186565394847</v>
+        <v>-0.0927138544910259</v>
       </c>
       <c r="AA4" s="11">
         <f>IF(OR(I4="",M4="",M4&lt;I4),"",M4-I4)</f>
@@ -3098,7 +3073,7 @@
       </c>
       <c r="AB4" s="7">
         <f>IF(OR(A4="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC4" s="8" t="str">
         <f>IF(OR(AB4="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB4,"低于上限","达到或超过上限"))</f>
@@ -3141,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="AR4" s="8" t="str">
-        <f ca="1">IF(A4="","",IF(OR(E4="",H4=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK4="",AL4&lt;&gt;""),AND(AK4&lt;&gt;"",AL4="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM4="",AN4&lt;&gt;""),AND(AM4&lt;&gt;"",AN4="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM4&lt;&gt;"",AN4&lt;&gt;""),OR(AK4="",AL4="")),"违规：必须先完成第二批",IF(OR(H4&lt;=0,H4&lt;&gt;INT(H4),MOD(H4,100)&lt;&gt;0,AND(AL4&lt;&gt;"",OR(AL4&lt;=0,AL4&lt;&gt;INT(AL4),MOD(AL4,100)&lt;&gt;0)),AND(AN4&lt;&gt;"",OR(AN4&lt;=0,AN4&lt;&gt;INT(AN4),MOD(AN4,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL4&lt;&gt;"",AN4&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ4&gt;C4*D4,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A4="","",IF(OR(E4="",H4=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK4="",AL4&lt;&gt;""),AND(AK4&lt;&gt;"",AL4="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM4="",AN4&lt;&gt;""),AND(AM4&lt;&gt;"",AN4="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM4&lt;&gt;"",AN4&lt;&gt;""),OR(AK4="",AL4="")),"违规：必须先完成第二批",IF(OR(H4&lt;=0,H4&lt;&gt;INT(H4),MOD(H4,100)&lt;&gt;0,AND(AL4&lt;&gt;"",OR(AL4&lt;=0,AL4&lt;&gt;INT(AL4),MOD(AL4,100)&lt;&gt;0)),AND(AN4&lt;&gt;"",OR(AN4&lt;=0,AN4&lt;&gt;INT(AN4),MOD(AN4,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL4&lt;&gt;"",AN4&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ4&gt;C4*D4,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -3185,7 +3160,7 @@
         <f>IF(A5="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A5)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>10100</v>
       </c>
-      <c r="M5" s="18">
+      <c r="M5" s="17">
         <f>IF(A5="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A5)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42838</v>
       </c>
@@ -3209,7 +3184,7 @@
         <f>IF(OR(AO5="",N5="",AO5&lt;=0),"",(AO5-N5)/AO5)</f>
         <v>0.0588235294117646</v>
       </c>
-      <c r="W5" s="19">
+      <c r="W5" s="18">
         <f>IF(OR(U5="",V5="",V5&lt;=0),"",U5/V5)</f>
         <v>1.5</v>
       </c>
@@ -3223,7 +3198,7 @@
       </c>
       <c r="Z5" s="7">
         <f>IF(OR(AE5="",多次统计数据!$B$8=""),"",AE5-多次统计数据!$B$8)</f>
-        <v>-0.0636225104219201</v>
+        <v>-0.0630177083734613</v>
       </c>
       <c r="AA5" s="11">
         <f>IF(OR(I5="",M5="",M5&lt;I5),"",M5-I5)</f>
@@ -3231,7 +3206,7 @@
       </c>
       <c r="AB5" s="7">
         <f>IF(OR(A5="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC5" s="8" t="str">
         <f>IF(OR(AB5="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB5,"低于上限","达到或超过上限"))</f>
@@ -3274,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="AR5" s="8" t="str">
-        <f ca="1">IF(A5="","",IF(OR(E5="",H5=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK5="",AL5&lt;&gt;""),AND(AK5&lt;&gt;"",AL5="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM5="",AN5&lt;&gt;""),AND(AM5&lt;&gt;"",AN5="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM5&lt;&gt;"",AN5&lt;&gt;""),OR(AK5="",AL5="")),"违规：必须先完成第二批",IF(OR(H5&lt;=0,H5&lt;&gt;INT(H5),MOD(H5,100)&lt;&gt;0,AND(AL5&lt;&gt;"",OR(AL5&lt;=0,AL5&lt;&gt;INT(AL5),MOD(AL5,100)&lt;&gt;0)),AND(AN5&lt;&gt;"",OR(AN5&lt;=0,AN5&lt;&gt;INT(AN5),MOD(AN5,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL5&lt;&gt;"",AN5&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ5&gt;C5*D5,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A5="","",IF(OR(E5="",H5=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK5="",AL5&lt;&gt;""),AND(AK5&lt;&gt;"",AL5="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM5="",AN5&lt;&gt;""),AND(AM5&lt;&gt;"",AN5="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM5&lt;&gt;"",AN5&lt;&gt;""),OR(AK5="",AL5="")),"违规：必须先完成第二批",IF(OR(H5&lt;=0,H5&lt;&gt;INT(H5),MOD(H5,100)&lt;&gt;0,AND(AL5&lt;&gt;"",OR(AL5&lt;=0,AL5&lt;&gt;INT(AL5),MOD(AL5,100)&lt;&gt;0)),AND(AN5&lt;&gt;"",OR(AN5&lt;=0,AN5&lt;&gt;INT(AN5),MOD(AN5,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL5&lt;&gt;"",AN5&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ5&gt;C5*D5,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -3317,7 +3292,7 @@
       <c r="L6" s="8">
         <v>17100</v>
       </c>
-      <c r="M6" s="18">
+      <c r="M6" s="17">
         <f>IF(A6="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A6)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43074</v>
       </c>
@@ -3341,7 +3316,7 @@
         <f>IF(OR(AO6="",N6="",AO6&lt;=0),"",(AO6-N6)/AO6)</f>
         <v>0.0418118466898955</v>
       </c>
-      <c r="W6" s="19">
+      <c r="W6" s="18">
         <f>IF(OR(U6="",V6="",V6&lt;=0),"",U6/V6)</f>
         <v>2.75</v>
       </c>
@@ -3355,7 +3330,7 @@
       </c>
       <c r="Z6" s="7">
         <f>IF(OR(AE6="",多次统计数据!$B$8=""),"",AE6-多次统计数据!$B$8)</f>
-        <v>-0.0941847162703744</v>
+        <v>-0.0935799142219156</v>
       </c>
       <c r="AA6" s="11">
         <f>IF(OR(I6="",M6="",M6&lt;I6),"",M6-I6)</f>
@@ -3363,7 +3338,7 @@
       </c>
       <c r="AB6" s="7">
         <f>IF(OR(A6="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC6" s="8" t="str">
         <f>IF(OR(AB6="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB6,"低于上限","达到或超过上限"))</f>
@@ -3406,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="AR6" s="8" t="str">
-        <f ca="1">IF(A6="","",IF(OR(E6="",H6=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK6="",AL6&lt;&gt;""),AND(AK6&lt;&gt;"",AL6="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM6="",AN6&lt;&gt;""),AND(AM6&lt;&gt;"",AN6="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM6&lt;&gt;"",AN6&lt;&gt;""),OR(AK6="",AL6="")),"违规：必须先完成第二批",IF(OR(H6&lt;=0,H6&lt;&gt;INT(H6),MOD(H6,100)&lt;&gt;0,AND(AL6&lt;&gt;"",OR(AL6&lt;=0,AL6&lt;&gt;INT(AL6),MOD(AL6,100)&lt;&gt;0)),AND(AN6&lt;&gt;"",OR(AN6&lt;=0,AN6&lt;&gt;INT(AN6),MOD(AN6,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL6&lt;&gt;"",AN6&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ6&gt;C6*D6,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A6="","",IF(OR(E6="",H6=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK6="",AL6&lt;&gt;""),AND(AK6&lt;&gt;"",AL6="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM6="",AN6&lt;&gt;""),AND(AM6&lt;&gt;"",AN6="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM6&lt;&gt;"",AN6&lt;&gt;""),OR(AK6="",AL6="")),"违规：必须先完成第二批",IF(OR(H6&lt;=0,H6&lt;&gt;INT(H6),MOD(H6,100)&lt;&gt;0,AND(AL6&lt;&gt;"",OR(AL6&lt;=0,AL6&lt;&gt;INT(AL6),MOD(AL6,100)&lt;&gt;0)),AND(AN6&lt;&gt;"",OR(AN6&lt;=0,AN6&lt;&gt;INT(AN6),MOD(AN6,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL6&lt;&gt;"",AN6&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ6&gt;C6*D6,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -3451,7 +3426,7 @@
         <f>IF(A7="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A7)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>11800</v>
       </c>
-      <c r="M7" s="18">
+      <c r="M7" s="17">
         <f>IF(A7="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A7)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43182</v>
       </c>
@@ -3475,7 +3450,7 @@
         <f>IF(OR(AO7="",N7="",AO7&lt;=0),"",(AO7-N7)/AO7)</f>
         <v>0.066147859922179</v>
       </c>
-      <c r="W7" s="19">
+      <c r="W7" s="18">
         <f>IF(OR(U7="",V7="",V7&lt;=0),"",U7/V7)</f>
         <v>2.52941176470588</v>
       </c>
@@ -3489,7 +3464,7 @@
       </c>
       <c r="Z7" s="7">
         <f>IF(OR(AE7="",多次统计数据!$B$8=""),"",AE7-多次统计数据!$B$8)</f>
-        <v>-0.0948522022597031</v>
+        <v>-0.0942474002112444</v>
       </c>
       <c r="AA7" s="11">
         <f>IF(OR(I7="",M7="",M7&lt;I7),"",M7-I7)</f>
@@ -3497,7 +3472,7 @@
       </c>
       <c r="AB7" s="7">
         <f>IF(OR(A7="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC7" s="8" t="str">
         <f>IF(OR(AB7="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB7,"低于上限","达到或超过上限"))</f>
@@ -3540,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="AR7" s="8" t="str">
-        <f ca="1">IF(A7="","",IF(OR(E7="",H7=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK7="",AL7&lt;&gt;""),AND(AK7&lt;&gt;"",AL7="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM7="",AN7&lt;&gt;""),AND(AM7&lt;&gt;"",AN7="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM7&lt;&gt;"",AN7&lt;&gt;""),OR(AK7="",AL7="")),"违规：必须先完成第二批",IF(OR(H7&lt;=0,H7&lt;&gt;INT(H7),MOD(H7,100)&lt;&gt;0,AND(AL7&lt;&gt;"",OR(AL7&lt;=0,AL7&lt;&gt;INT(AL7),MOD(AL7,100)&lt;&gt;0)),AND(AN7&lt;&gt;"",OR(AN7&lt;=0,AN7&lt;&gt;INT(AN7),MOD(AN7,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL7&lt;&gt;"",AN7&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ7&gt;C7*D7,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A7="","",IF(OR(E7="",H7=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK7="",AL7&lt;&gt;""),AND(AK7&lt;&gt;"",AL7="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM7="",AN7&lt;&gt;""),AND(AM7&lt;&gt;"",AN7="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM7&lt;&gt;"",AN7&lt;&gt;""),OR(AK7="",AL7="")),"违规：必须先完成第二批",IF(OR(H7&lt;=0,H7&lt;&gt;INT(H7),MOD(H7,100)&lt;&gt;0,AND(AL7&lt;&gt;"",OR(AL7&lt;=0,AL7&lt;&gt;INT(AL7),MOD(AL7,100)&lt;&gt;0)),AND(AN7&lt;&gt;"",OR(AN7&lt;=0,AN7&lt;&gt;INT(AN7),MOD(AN7,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL7&lt;&gt;"",AN7&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ7&gt;C7*D7,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -3584,7 +3559,7 @@
         <f>IF(A8="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A8)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>32700</v>
       </c>
-      <c r="M8" s="18">
+      <c r="M8" s="17">
         <v>44391</v>
       </c>
       <c r="N8" s="10">
@@ -3607,7 +3582,7 @@
         <f>IF(OR(AO8="",N8="",AO8&lt;=0),"",(AO8-N8)/AO8)</f>
         <v>0.0314136125654449</v>
       </c>
-      <c r="W8" s="19">
+      <c r="W8" s="18">
         <f>IF(OR(U8="",V8="",V8&lt;=0),"",U8/V8)</f>
         <v>1.50000000000001</v>
       </c>
@@ -3621,7 +3596,7 @@
       </c>
       <c r="Z8" s="7">
         <f>IF(OR(AE8="",多次统计数据!$B$8=""),"",AE8-多次统计数据!$B$8)</f>
-        <v>0.00397762460329057</v>
+        <v>0.00458242665174934</v>
       </c>
       <c r="AA8" s="11">
         <f>IF(OR(I8="",M8="",M8&lt;I8),"",M8-I8)</f>
@@ -3629,7 +3604,7 @@
       </c>
       <c r="AB8" s="7">
         <f>IF(OR(A8="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC8" s="8" t="str">
         <f>IF(OR(AB8="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB8,"低于上限","达到或超过上限"))</f>
@@ -3675,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="AR8" s="8" t="str">
-        <f ca="1">IF(A8="","",IF(OR(E8="",H8=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK8="",AL8&lt;&gt;""),AND(AK8&lt;&gt;"",AL8="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM8="",AN8&lt;&gt;""),AND(AM8&lt;&gt;"",AN8="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM8&lt;&gt;"",AN8&lt;&gt;""),OR(AK8="",AL8="")),"违规：必须先完成第二批",IF(OR(H8&lt;=0,H8&lt;&gt;INT(H8),MOD(H8,100)&lt;&gt;0,AND(AL8&lt;&gt;"",OR(AL8&lt;=0,AL8&lt;&gt;INT(AL8),MOD(AL8,100)&lt;&gt;0)),AND(AN8&lt;&gt;"",OR(AN8&lt;=0,AN8&lt;&gt;INT(AN8),MOD(AN8,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL8&lt;&gt;"",AN8&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ8&gt;C8*D8,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A8="","",IF(OR(E8="",H8=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK8="",AL8&lt;&gt;""),AND(AK8&lt;&gt;"",AL8="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM8="",AN8&lt;&gt;""),AND(AM8&lt;&gt;"",AN8="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM8&lt;&gt;"",AN8&lt;&gt;""),OR(AK8="",AL8="")),"违规：必须先完成第二批",IF(OR(H8&lt;=0,H8&lt;&gt;INT(H8),MOD(H8,100)&lt;&gt;0,AND(AL8&lt;&gt;"",OR(AL8&lt;=0,AL8&lt;&gt;INT(AL8),MOD(AL8,100)&lt;&gt;0)),AND(AN8&lt;&gt;"",OR(AN8&lt;=0,AN8&lt;&gt;INT(AN8),MOD(AN8,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL8&lt;&gt;"",AN8&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ8&gt;C8*D8,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -3720,7 +3695,7 @@
         <f>IF(A9="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A9)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>6400</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="17">
         <f>IF(A9="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A9)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44914</v>
       </c>
@@ -3744,7 +3719,7 @@
         <f>IF(OR(AO9="",N9="",AO9&lt;=0),"",(AO9-N9)/AO9)</f>
         <v>0.0861618798955614</v>
       </c>
-      <c r="W9" s="19">
+      <c r="W9" s="18">
         <f>IF(OR(U9="",V9="",V9&lt;=0),"",U9/V9)</f>
         <v>2.03030303030303</v>
       </c>
@@ -3758,7 +3733,7 @@
       </c>
       <c r="Z9" s="7">
         <f>IF(OR(AE9="",多次统计数据!$B$8=""),"",AE9-多次统计数据!$B$8)</f>
-        <v>-0.0943253587118855</v>
+        <v>-0.0937205566634267</v>
       </c>
       <c r="AA9" s="11">
         <f>IF(OR(I9="",M9="",M9&lt;I9),"",M9-I9)</f>
@@ -3766,7 +3741,7 @@
       </c>
       <c r="AB9" s="7">
         <f>IF(OR(A9="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC9" s="8" t="str">
         <f>IF(OR(AB9="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB9,"低于上限","达到或超过上限"))</f>
@@ -3809,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="AR9" s="8" t="str">
-        <f ca="1">IF(A9="","",IF(OR(E9="",H9=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK9="",AL9&lt;&gt;""),AND(AK9&lt;&gt;"",AL9="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM9="",AN9&lt;&gt;""),AND(AM9&lt;&gt;"",AN9="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM9&lt;&gt;"",AN9&lt;&gt;""),OR(AK9="",AL9="")),"违规：必须先完成第二批",IF(OR(H9&lt;=0,H9&lt;&gt;INT(H9),MOD(H9,100)&lt;&gt;0,AND(AL9&lt;&gt;"",OR(AL9&lt;=0,AL9&lt;&gt;INT(AL9),MOD(AL9,100)&lt;&gt;0)),AND(AN9&lt;&gt;"",OR(AN9&lt;=0,AN9&lt;&gt;INT(AN9),MOD(AN9,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL9&lt;&gt;"",AN9&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ9&gt;C9*D9,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A9="","",IF(OR(E9="",H9=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK9="",AL9&lt;&gt;""),AND(AK9&lt;&gt;"",AL9="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM9="",AN9&lt;&gt;""),AND(AM9&lt;&gt;"",AN9="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM9&lt;&gt;"",AN9&lt;&gt;""),OR(AK9="",AL9="")),"违规：必须先完成第二批",IF(OR(H9&lt;=0,H9&lt;&gt;INT(H9),MOD(H9,100)&lt;&gt;0,AND(AL9&lt;&gt;"",OR(AL9&lt;=0,AL9&lt;&gt;INT(AL9),MOD(AL9,100)&lt;&gt;0)),AND(AN9&lt;&gt;"",OR(AN9&lt;=0,AN9&lt;&gt;INT(AN9),MOD(AN9,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL9&lt;&gt;"",AN9&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ9&gt;C9*D9,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -3854,7 +3829,7 @@
         <f>IF(A10="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A10)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>11400</v>
       </c>
-      <c r="M10" s="18">
+      <c r="M10" s="17">
         <f>IF(A10="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A10)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45041</v>
       </c>
@@ -3878,7 +3853,7 @@
         <f>IF(OR(AO10="",N10="",AO10&lt;=0),"",(AO10-N10)/AO10)</f>
         <v>0.0489130434782609</v>
       </c>
-      <c r="W10" s="19">
+      <c r="W10" s="18">
         <f>IF(OR(U10="",V10="",V10&lt;=0),"",U10/V10)</f>
         <v>1.77777777777778</v>
       </c>
@@ -3892,7 +3867,7 @@
       </c>
       <c r="Z10" s="7">
         <f>IF(OR(AE10="",多次统计数据!$B$8=""),"",AE10-多次统计数据!$B$8)</f>
-        <v>-0.0967812133747422</v>
+        <v>-0.0961764113262834</v>
       </c>
       <c r="AA10" s="11">
         <f>IF(OR(I10="",M10="",M10&lt;I10),"",M10-I10)</f>
@@ -3900,7 +3875,7 @@
       </c>
       <c r="AB10" s="7">
         <f>IF(OR(A10="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC10" s="8" t="str">
         <f>IF(OR(AB10="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB10,"低于上限","达到或超过上限"))</f>
@@ -3941,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="AR10" s="8" t="str">
-        <f ca="1">IF(A10="","",IF(OR(E10="",H10=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK10="",AL10&lt;&gt;""),AND(AK10&lt;&gt;"",AL10="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM10="",AN10&lt;&gt;""),AND(AM10&lt;&gt;"",AN10="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM10&lt;&gt;"",AN10&lt;&gt;""),OR(AK10="",AL10="")),"违规：必须先完成第二批",IF(OR(H10&lt;=0,H10&lt;&gt;INT(H10),MOD(H10,100)&lt;&gt;0,AND(AL10&lt;&gt;"",OR(AL10&lt;=0,AL10&lt;&gt;INT(AL10),MOD(AL10,100)&lt;&gt;0)),AND(AN10&lt;&gt;"",OR(AN10&lt;=0,AN10&lt;&gt;INT(AN10),MOD(AN10,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL10&lt;&gt;"",AN10&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ10&gt;C10*D10,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A10="","",IF(OR(E10="",H10=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK10="",AL10&lt;&gt;""),AND(AK10&lt;&gt;"",AL10="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM10="",AN10&lt;&gt;""),AND(AM10&lt;&gt;"",AN10="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM10&lt;&gt;"",AN10&lt;&gt;""),OR(AK10="",AL10="")),"违规：必须先完成第二批",IF(OR(H10&lt;=0,H10&lt;&gt;INT(H10),MOD(H10,100)&lt;&gt;0,AND(AL10&lt;&gt;"",OR(AL10&lt;=0,AL10&lt;&gt;INT(AL10),MOD(AL10,100)&lt;&gt;0)),AND(AN10&lt;&gt;"",OR(AN10&lt;=0,AN10&lt;&gt;INT(AN10),MOD(AN10,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL10&lt;&gt;"",AN10&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ10&gt;C10*D10,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -3986,7 +3961,7 @@
         <f>IF(A11="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A11)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>18300</v>
       </c>
-      <c r="M11" s="18">
+      <c r="M11" s="17">
         <f>IF(A11="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A11)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45373</v>
       </c>
@@ -4010,7 +3985,7 @@
         <f>IF(OR(AO11="",N11="",AO11&lt;=0),"",(AO11-N11)/AO11)</f>
         <v>0.0384615384615384</v>
       </c>
-      <c r="W11" s="19">
+      <c r="W11" s="18">
         <f>IF(OR(U11="",V11="",V11&lt;=0),"",U11/V11)</f>
         <v>1.27272727272728</v>
       </c>
@@ -4024,7 +3999,7 @@
       </c>
       <c r="Z11" s="7">
         <f>IF(OR(AE11="",多次统计数据!$B$8=""),"",AE11-多次统计数据!$B$8)</f>
-        <v>-0.0870452552686224</v>
+        <v>-0.0864404532201636</v>
       </c>
       <c r="AA11" s="11">
         <f>IF(OR(I11="",M11="",M11&lt;I11),"",M11-I11)</f>
@@ -4032,7 +4007,7 @@
       </c>
       <c r="AB11" s="7">
         <f>IF(OR(A11="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC11" s="8" t="str">
         <f>IF(OR(AB11="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB11,"低于上限","达到或超过上限"))</f>
@@ -4073,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="AR11" s="8" t="str">
-        <f ca="1">IF(A11="","",IF(OR(E11="",H11=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK11="",AL11&lt;&gt;""),AND(AK11&lt;&gt;"",AL11="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM11="",AN11&lt;&gt;""),AND(AM11&lt;&gt;"",AN11="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM11&lt;&gt;"",AN11&lt;&gt;""),OR(AK11="",AL11="")),"违规：必须先完成第二批",IF(OR(H11&lt;=0,H11&lt;&gt;INT(H11),MOD(H11,100)&lt;&gt;0,AND(AL11&lt;&gt;"",OR(AL11&lt;=0,AL11&lt;&gt;INT(AL11),MOD(AL11,100)&lt;&gt;0)),AND(AN11&lt;&gt;"",OR(AN11&lt;=0,AN11&lt;&gt;INT(AN11),MOD(AN11,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL11&lt;&gt;"",AN11&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ11&gt;C11*D11,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A11="","",IF(OR(E11="",H11=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK11="",AL11&lt;&gt;""),AND(AK11&lt;&gt;"",AL11="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM11="",AN11&lt;&gt;""),AND(AM11&lt;&gt;"",AN11="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM11&lt;&gt;"",AN11&lt;&gt;""),OR(AK11="",AL11="")),"违规：必须先完成第二批",IF(OR(H11&lt;=0,H11&lt;&gt;INT(H11),MOD(H11,100)&lt;&gt;0,AND(AL11&lt;&gt;"",OR(AL11&lt;=0,AL11&lt;&gt;INT(AL11),MOD(AL11,100)&lt;&gt;0)),AND(AN11&lt;&gt;"",OR(AN11&lt;=0,AN11&lt;&gt;INT(AN11),MOD(AN11,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL11&lt;&gt;"",AN11&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ11&gt;C11*D11,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -4118,7 +4093,7 @@
         <f>IF(A12="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A12)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1900</v>
       </c>
-      <c r="M12" s="18">
+      <c r="M12" s="17">
         <f>IF(A12="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A12)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43059</v>
       </c>
@@ -4142,7 +4117,7 @@
         <f>IF(OR(AO12="",N12="",AO12&lt;=0),"",(AO12-N12)/AO12)</f>
         <v>0.0487804878048781</v>
       </c>
-      <c r="W12" s="19">
+      <c r="W12" s="18">
         <f>IF(OR(U12="",V12="",V12&lt;=0),"",U12/V12)</f>
         <v>2.5</v>
       </c>
@@ -4156,7 +4131,7 @@
       </c>
       <c r="Z12" s="7">
         <f>IF(OR(AE12="",多次统计数据!$B$8=""),"",AE12-多次统计数据!$B$8)</f>
-        <v>0.0944948294950245</v>
+        <v>0.0950996315434832</v>
       </c>
       <c r="AA12" s="11">
         <f>IF(OR(I12="",M12="",M12&lt;I12),"",M12-I12)</f>
@@ -4164,7 +4139,7 @@
       </c>
       <c r="AB12" s="7">
         <f>IF(OR(A12="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC12" s="8" t="str">
         <f>IF(OR(AB12="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB12,"低于上限","达到或超过上限"))</f>
@@ -4205,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="AR12" s="8" t="str">
-        <f ca="1">IF(A12="","",IF(OR(E12="",H12=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK12="",AL12&lt;&gt;""),AND(AK12&lt;&gt;"",AL12="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM12="",AN12&lt;&gt;""),AND(AM12&lt;&gt;"",AN12="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM12&lt;&gt;"",AN12&lt;&gt;""),OR(AK12="",AL12="")),"违规：必须先完成第二批",IF(OR(H12&lt;=0,H12&lt;&gt;INT(H12),MOD(H12,100)&lt;&gt;0,AND(AL12&lt;&gt;"",OR(AL12&lt;=0,AL12&lt;&gt;INT(AL12),MOD(AL12,100)&lt;&gt;0)),AND(AN12&lt;&gt;"",OR(AN12&lt;=0,AN12&lt;&gt;INT(AN12),MOD(AN12,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL12&lt;&gt;"",AN12&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ12&gt;C12*D12,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A12="","",IF(OR(E12="",H12=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK12="",AL12&lt;&gt;""),AND(AK12&lt;&gt;"",AL12="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM12="",AN12&lt;&gt;""),AND(AM12&lt;&gt;"",AN12="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM12&lt;&gt;"",AN12&lt;&gt;""),OR(AK12="",AL12="")),"违规：必须先完成第二批",IF(OR(H12&lt;=0,H12&lt;&gt;INT(H12),MOD(H12,100)&lt;&gt;0,AND(AL12&lt;&gt;"",OR(AL12&lt;=0,AL12&lt;&gt;INT(AL12),MOD(AL12,100)&lt;&gt;0)),AND(AN12&lt;&gt;"",OR(AN12&lt;=0,AN12&lt;&gt;INT(AN12),MOD(AN12,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL12&lt;&gt;"",AN12&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ12&gt;C12*D12,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -4249,7 +4224,7 @@
         <f>IF(A13="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A13)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1200</v>
       </c>
-      <c r="M13" s="18">
+      <c r="M13" s="17">
         <f>IF(A13="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A13)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43311</v>
       </c>
@@ -4273,7 +4248,7 @@
         <f>IF(OR(AO13="",N13="",AO13&lt;=0),"",(AO13-N13)/AO13)</f>
         <v>0.059855844562833</v>
       </c>
-      <c r="W13" s="19">
+      <c r="W13" s="18">
         <f>IF(OR(U13="",V13="",V13&lt;=0),"",U13/V13)</f>
         <v>1.61780104712042</v>
       </c>
@@ -4287,7 +4262,7 @@
       </c>
       <c r="Z13" s="7">
         <f>IF(OR(AE13="",多次统计数据!$B$8=""),"",AE13-多次统计数据!$B$8)</f>
-        <v>-0.0996170728979932</v>
+        <v>-0.0990122708495345</v>
       </c>
       <c r="AA13" s="11">
         <f>IF(OR(I13="",M13="",M13&lt;I13),"",M13-I13)</f>
@@ -4295,7 +4270,7 @@
       </c>
       <c r="AB13" s="7">
         <f>IF(OR(A13="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC13" s="8" t="str">
         <f>IF(OR(AB13="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB13,"低于上限","达到或超过上限"))</f>
@@ -4334,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="AR13" s="8" t="str">
-        <f ca="1">IF(A13="","",IF(OR(E13="",H13=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK13="",AL13&lt;&gt;""),AND(AK13&lt;&gt;"",AL13="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM13="",AN13&lt;&gt;""),AND(AM13&lt;&gt;"",AN13="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM13&lt;&gt;"",AN13&lt;&gt;""),OR(AK13="",AL13="")),"违规：必须先完成第二批",IF(OR(H13&lt;=0,H13&lt;&gt;INT(H13),MOD(H13,100)&lt;&gt;0,AND(AL13&lt;&gt;"",OR(AL13&lt;=0,AL13&lt;&gt;INT(AL13),MOD(AL13,100)&lt;&gt;0)),AND(AN13&lt;&gt;"",OR(AN13&lt;=0,AN13&lt;&gt;INT(AN13),MOD(AN13,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL13&lt;&gt;"",AN13&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ13&gt;C13*D13,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A13="","",IF(OR(E13="",H13=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK13="",AL13&lt;&gt;""),AND(AK13&lt;&gt;"",AL13="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM13="",AN13&lt;&gt;""),AND(AM13&lt;&gt;"",AN13="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM13&lt;&gt;"",AN13&lt;&gt;""),OR(AK13="",AL13="")),"违规：必须先完成第二批",IF(OR(H13&lt;=0,H13&lt;&gt;INT(H13),MOD(H13,100)&lt;&gt;0,AND(AL13&lt;&gt;"",OR(AL13&lt;=0,AL13&lt;&gt;INT(AL13),MOD(AL13,100)&lt;&gt;0)),AND(AN13&lt;&gt;"",OR(AN13&lt;=0,AN13&lt;&gt;INT(AN13),MOD(AN13,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL13&lt;&gt;"",AN13&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ13&gt;C13*D13,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -4377,7 +4352,7 @@
       <c r="L14" s="8">
         <v>700</v>
       </c>
-      <c r="M14" s="20">
+      <c r="M14" s="19">
         <v>43311</v>
       </c>
       <c r="N14" s="10">
@@ -4400,7 +4375,7 @@
         <f>IF(OR(AO14="",N14="",AO14&lt;=0),"",(AO14-N14)/AO14)</f>
         <v>0.0694345025053686</v>
       </c>
-      <c r="W14" s="19">
+      <c r="W14" s="18">
         <f>IF(OR(U14="",V14="",V14&lt;=0),"",U14/V14)</f>
         <v>2.78006872852234</v>
       </c>
@@ -4414,7 +4389,7 @@
       </c>
       <c r="Z14" s="7">
         <f>IF(OR(AE14="",多次统计数据!$B$8=""),"",AE14-多次统计数据!$B$8)</f>
-        <v>-0.0937333427787562</v>
+        <v>-0.0931285407302974</v>
       </c>
       <c r="AA14" s="11">
         <f>IF(OR(I14="",M14="",M14&lt;I14),"",M14-I14)</f>
@@ -4422,7 +4397,7 @@
       </c>
       <c r="AB14" s="7">
         <f>IF(OR(A14="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC14" s="8" t="str">
         <f>IF(OR(AB14="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB14,"低于上限","达到或超过上限"))</f>
@@ -4461,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="AR14" s="8" t="str">
-        <f ca="1">IF(A14="","",IF(OR(E14="",H14=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK14="",AL14&lt;&gt;""),AND(AK14&lt;&gt;"",AL14="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM14="",AN14&lt;&gt;""),AND(AM14&lt;&gt;"",AN14="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM14&lt;&gt;"",AN14&lt;&gt;""),OR(AK14="",AL14="")),"违规：必须先完成第二批",IF(OR(H14&lt;=0,H14&lt;&gt;INT(H14),MOD(H14,100)&lt;&gt;0,AND(AL14&lt;&gt;"",OR(AL14&lt;=0,AL14&lt;&gt;INT(AL14),MOD(AL14,100)&lt;&gt;0)),AND(AN14&lt;&gt;"",OR(AN14&lt;=0,AN14&lt;&gt;INT(AN14),MOD(AN14,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL14&lt;&gt;"",AN14&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ14&gt;C14*D14,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A14="","",IF(OR(E14="",H14=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK14="",AL14&lt;&gt;""),AND(AK14&lt;&gt;"",AL14="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM14="",AN14&lt;&gt;""),AND(AM14&lt;&gt;"",AN14="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM14&lt;&gt;"",AN14&lt;&gt;""),OR(AK14="",AL14="")),"违规：必须先完成第二批",IF(OR(H14&lt;=0,H14&lt;&gt;INT(H14),MOD(H14,100)&lt;&gt;0,AND(AL14&lt;&gt;"",OR(AL14&lt;=0,AL14&lt;&gt;INT(AL14),MOD(AL14,100)&lt;&gt;0)),AND(AN14&lt;&gt;"",OR(AN14&lt;=0,AN14&lt;&gt;INT(AN14),MOD(AN14,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL14&lt;&gt;"",AN14&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ14&gt;C14*D14,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -4505,7 +4480,7 @@
         <f>IF(A15="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A15)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>700</v>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="17">
         <f>IF(A15="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A15)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43577</v>
       </c>
@@ -4529,7 +4504,7 @@
         <f>IF(OR(AO15="",N15="",AO15&lt;=0),"",(AO15-N15)/AO15)</f>
         <v>0.072753209700428</v>
       </c>
-      <c r="W15" s="19">
+      <c r="W15" s="18">
         <f>IF(OR(U15="",V15="",V15&lt;=0),"",U15/V15)</f>
         <v>1.94117647058823</v>
       </c>
@@ -4543,7 +4518,7 @@
       </c>
       <c r="Z15" s="7">
         <f>IF(OR(AE15="",多次统计数据!$B$8=""),"",AE15-多次统计数据!$B$8)</f>
-        <v>-0.0734978910172726</v>
+        <v>-0.0728930889688139</v>
       </c>
       <c r="AA15" s="11">
         <f>IF(OR(I15="",M15="",M15&lt;I15),"",M15-I15)</f>
@@ -4551,7 +4526,7 @@
       </c>
       <c r="AB15" s="7">
         <f>IF(OR(A15="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC15" s="8" t="str">
         <f>IF(OR(AB15="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB15,"低于上限","达到或超过上限"))</f>
@@ -4590,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="AR15" s="8" t="str">
-        <f ca="1">IF(A15="","",IF(OR(E15="",H15=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK15="",AL15&lt;&gt;""),AND(AK15&lt;&gt;"",AL15="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM15="",AN15&lt;&gt;""),AND(AM15&lt;&gt;"",AN15="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM15&lt;&gt;"",AN15&lt;&gt;""),OR(AK15="",AL15="")),"违规：必须先完成第二批",IF(OR(H15&lt;=0,H15&lt;&gt;INT(H15),MOD(H15,100)&lt;&gt;0,AND(AL15&lt;&gt;"",OR(AL15&lt;=0,AL15&lt;&gt;INT(AL15),MOD(AL15,100)&lt;&gt;0)),AND(AN15&lt;&gt;"",OR(AN15&lt;=0,AN15&lt;&gt;INT(AN15),MOD(AN15,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL15&lt;&gt;"",AN15&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ15&gt;C15*D15,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A15="","",IF(OR(E15="",H15=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK15="",AL15&lt;&gt;""),AND(AK15&lt;&gt;"",AL15="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM15="",AN15&lt;&gt;""),AND(AM15&lt;&gt;"",AN15="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM15&lt;&gt;"",AN15&lt;&gt;""),OR(AK15="",AL15="")),"违规：必须先完成第二批",IF(OR(H15&lt;=0,H15&lt;&gt;INT(H15),MOD(H15,100)&lt;&gt;0,AND(AL15&lt;&gt;"",OR(AL15&lt;=0,AL15&lt;&gt;INT(AL15),MOD(AL15,100)&lt;&gt;0)),AND(AN15&lt;&gt;"",OR(AN15&lt;=0,AN15&lt;&gt;INT(AN15),MOD(AN15,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL15&lt;&gt;"",AN15&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ15&gt;C15*D15,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -4635,7 +4610,7 @@
         <f>IF(A16="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A16)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1600</v>
       </c>
-      <c r="M16" s="18">
+      <c r="M16" s="17">
         <f>IF(A16="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A16)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43798</v>
       </c>
@@ -4659,7 +4634,7 @@
         <f>IF(OR(AO16="",N16="",AO16&lt;=0),"",(AO16-N16)/AO16)</f>
         <v>0.0278346295538273</v>
       </c>
-      <c r="W16" s="19">
+      <c r="W16" s="18">
         <f>IF(OR(U16="",V16="",V16&lt;=0),"",U16/V16)</f>
         <v>0.838235294117648</v>
       </c>
@@ -4673,7 +4648,7 @@
       </c>
       <c r="Z16" s="7">
         <f>IF(OR(AE16="",多次统计数据!$B$8=""),"",AE16-多次统计数据!$B$8)</f>
-        <v>0.0657231567649502</v>
+        <v>0.066327958813409</v>
       </c>
       <c r="AA16" s="11">
         <f>IF(OR(I16="",M16="",M16&lt;I16),"",M16-I16)</f>
@@ -4681,7 +4656,7 @@
       </c>
       <c r="AB16" s="7">
         <f>IF(OR(A16="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC16" s="8" t="str">
         <f>IF(OR(AB16="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB16,"低于上限","达到或超过上限"))</f>
@@ -4722,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="AR16" s="8" t="str">
-        <f ca="1">IF(A16="","",IF(OR(E16="",H16=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK16="",AL16&lt;&gt;""),AND(AK16&lt;&gt;"",AL16="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM16="",AN16&lt;&gt;""),AND(AM16&lt;&gt;"",AN16="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM16&lt;&gt;"",AN16&lt;&gt;""),OR(AK16="",AL16="")),"违规：必须先完成第二批",IF(OR(H16&lt;=0,H16&lt;&gt;INT(H16),MOD(H16,100)&lt;&gt;0,AND(AL16&lt;&gt;"",OR(AL16&lt;=0,AL16&lt;&gt;INT(AL16),MOD(AL16,100)&lt;&gt;0)),AND(AN16&lt;&gt;"",OR(AN16&lt;=0,AN16&lt;&gt;INT(AN16),MOD(AN16,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL16&lt;&gt;"",AN16&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ16&gt;C16*D16,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A16="","",IF(OR(E16="",H16=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK16="",AL16&lt;&gt;""),AND(AK16&lt;&gt;"",AL16="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM16="",AN16&lt;&gt;""),AND(AM16&lt;&gt;"",AN16="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM16&lt;&gt;"",AN16&lt;&gt;""),OR(AK16="",AL16="")),"违规：必须先完成第二批",IF(OR(H16&lt;=0,H16&lt;&gt;INT(H16),MOD(H16,100)&lt;&gt;0,AND(AL16&lt;&gt;"",OR(AL16&lt;=0,AL16&lt;&gt;INT(AL16),MOD(AL16,100)&lt;&gt;0)),AND(AN16&lt;&gt;"",OR(AN16&lt;=0,AN16&lt;&gt;INT(AN16),MOD(AN16,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL16&lt;&gt;"",AN16&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ16&gt;C16*D16,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -4767,7 +4742,7 @@
         <f>IF(A17="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A17)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1100</v>
       </c>
-      <c r="M17" s="18">
+      <c r="M17" s="17">
         <f>IF(A17="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A17)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43887</v>
       </c>
@@ -4791,7 +4766,7 @@
         <f>IF(OR(AO17="",N17="",AO17&lt;=0),"",(AO17-N17)/AO17)</f>
         <v>0.0362993896562801</v>
       </c>
-      <c r="W17" s="19">
+      <c r="W17" s="18">
         <f>IF(OR(U17="",V17="",V17&lt;=0),"",U17/V17)</f>
         <v>3.42477876106195</v>
       </c>
@@ -4805,7 +4780,7 @@
       </c>
       <c r="Z17" s="7">
         <f>IF(OR(AE17="",多次统计数据!$B$8=""),"",AE17-多次统计数据!$B$8)</f>
-        <v>-0.101494384433674</v>
+        <v>-0.100889582385215</v>
       </c>
       <c r="AA17" s="11">
         <f>IF(OR(I17="",M17="",M17&lt;I17),"",M17-I17)</f>
@@ -4813,7 +4788,7 @@
       </c>
       <c r="AB17" s="7">
         <f>IF(OR(A17="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC17" s="8" t="str">
         <f>IF(OR(AB17="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB17,"低于上限","达到或超过上限"))</f>
@@ -4854,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="AR17" s="8" t="str">
-        <f ca="1">IF(A17="","",IF(OR(E17="",H17=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK17="",AL17&lt;&gt;""),AND(AK17&lt;&gt;"",AL17="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM17="",AN17&lt;&gt;""),AND(AM17&lt;&gt;"",AN17="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM17&lt;&gt;"",AN17&lt;&gt;""),OR(AK17="",AL17="")),"违规：必须先完成第二批",IF(OR(H17&lt;=0,H17&lt;&gt;INT(H17),MOD(H17,100)&lt;&gt;0,AND(AL17&lt;&gt;"",OR(AL17&lt;=0,AL17&lt;&gt;INT(AL17),MOD(AL17,100)&lt;&gt;0)),AND(AN17&lt;&gt;"",OR(AN17&lt;=0,AN17&lt;&gt;INT(AN17),MOD(AN17,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL17&lt;&gt;"",AN17&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ17&gt;C17*D17,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A17="","",IF(OR(E17="",H17=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK17="",AL17&lt;&gt;""),AND(AK17&lt;&gt;"",AL17="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM17="",AN17&lt;&gt;""),AND(AM17&lt;&gt;"",AN17="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM17&lt;&gt;"",AN17&lt;&gt;""),OR(AK17="",AL17="")),"违规：必须先完成第二批",IF(OR(H17&lt;=0,H17&lt;&gt;INT(H17),MOD(H17,100)&lt;&gt;0,AND(AL17&lt;&gt;"",OR(AL17&lt;=0,AL17&lt;&gt;INT(AL17),MOD(AL17,100)&lt;&gt;0)),AND(AN17&lt;&gt;"",OR(AN17&lt;=0,AN17&lt;&gt;INT(AN17),MOD(AN17,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL17&lt;&gt;"",AN17&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ17&gt;C17*D17,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -4899,7 +4874,7 @@
         <f>IF(A18="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A18)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1200</v>
       </c>
-      <c r="M18" s="18">
+      <c r="M18" s="17">
         <f>IF(A18="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A18)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43950</v>
       </c>
@@ -4923,7 +4898,7 @@
         <f>IF(OR(AO18="",N18="",AO18&lt;=0),"",(AO18-N18)/AO18)</f>
         <v>0.0292004280691025</v>
       </c>
-      <c r="W18" s="19">
+      <c r="W18" s="18">
         <f>IF(OR(U18="",V18="",V18&lt;=0),"",U18/V18)</f>
         <v>2.40314136125655</v>
       </c>
@@ -4937,7 +4912,7 @@
       </c>
       <c r="Z18" s="7">
         <f>IF(OR(AE18="",多次统计数据!$B$8=""),"",AE18-多次统计数据!$B$8)</f>
-        <v>-0.0901933792429191</v>
+        <v>-0.0895885771944604</v>
       </c>
       <c r="AA18" s="11">
         <f>IF(OR(I18="",M18="",M18&lt;I18),"",M18-I18)</f>
@@ -4945,7 +4920,7 @@
       </c>
       <c r="AB18" s="7">
         <f>IF(OR(A18="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC18" s="8" t="str">
         <f>IF(OR(AB18="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB18,"低于上限","达到或超过上限"))</f>
@@ -4984,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="AR18" s="8" t="str">
-        <f ca="1">IF(A18="","",IF(OR(E18="",H18=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK18="",AL18&lt;&gt;""),AND(AK18&lt;&gt;"",AL18="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM18="",AN18&lt;&gt;""),AND(AM18&lt;&gt;"",AN18="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM18&lt;&gt;"",AN18&lt;&gt;""),OR(AK18="",AL18="")),"违规：必须先完成第二批",IF(OR(H18&lt;=0,H18&lt;&gt;INT(H18),MOD(H18,100)&lt;&gt;0,AND(AL18&lt;&gt;"",OR(AL18&lt;=0,AL18&lt;&gt;INT(AL18),MOD(AL18,100)&lt;&gt;0)),AND(AN18&lt;&gt;"",OR(AN18&lt;=0,AN18&lt;&gt;INT(AN18),MOD(AN18,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL18&lt;&gt;"",AN18&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ18&gt;C18*D18,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A18="","",IF(OR(E18="",H18=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK18="",AL18&lt;&gt;""),AND(AK18&lt;&gt;"",AL18="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM18="",AN18&lt;&gt;""),AND(AM18&lt;&gt;"",AN18="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM18&lt;&gt;"",AN18&lt;&gt;""),OR(AK18="",AL18="")),"违规：必须先完成第二批",IF(OR(H18&lt;=0,H18&lt;&gt;INT(H18),MOD(H18,100)&lt;&gt;0,AND(AL18&lt;&gt;"",OR(AL18&lt;=0,AL18&lt;&gt;INT(AL18),MOD(AL18,100)&lt;&gt;0)),AND(AN18&lt;&gt;"",OR(AN18&lt;=0,AN18&lt;&gt;INT(AN18),MOD(AN18,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL18&lt;&gt;"",AN18&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ18&gt;C18*D18,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -5029,7 +5004,7 @@
         <f>IF(A19="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A19)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>500</v>
       </c>
-      <c r="M19" s="18">
+      <c r="M19" s="17">
         <f>IF(A19="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A19)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44028</v>
       </c>
@@ -5053,7 +5028,7 @@
         <f>IF(OR(AO19="",N19="",AO19&lt;=0),"",(AO19-N19)/AO19)</f>
         <v>0.0196078431372549</v>
       </c>
-      <c r="W19" s="19">
+      <c r="W19" s="18">
         <f>IF(OR(U19="",V19="",V19&lt;=0),"",U19/V19)</f>
         <v>7.82352941176471</v>
       </c>
@@ -5067,7 +5042,7 @@
       </c>
       <c r="Z19" s="7">
         <f>IF(OR(AE19="",多次统计数据!$B$8=""),"",AE19-多次统计数据!$B$8)</f>
-        <v>-0.031502171503162</v>
+        <v>-0.0308973694547032</v>
       </c>
       <c r="AA19" s="11">
         <f>IF(OR(I19="",M19="",M19&lt;I19),"",M19-I19)</f>
@@ -5075,7 +5050,7 @@
       </c>
       <c r="AB19" s="7">
         <f>IF(OR(A19="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC19" s="8" t="str">
         <f>IF(OR(AB19="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB19,"低于上限","达到或超过上限"))</f>
@@ -5116,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="AR19" s="8" t="str">
-        <f ca="1">IF(A19="","",IF(OR(E19="",H19=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK19="",AL19&lt;&gt;""),AND(AK19&lt;&gt;"",AL19="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM19="",AN19&lt;&gt;""),AND(AM19&lt;&gt;"",AN19="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM19&lt;&gt;"",AN19&lt;&gt;""),OR(AK19="",AL19="")),"违规：必须先完成第二批",IF(OR(H19&lt;=0,H19&lt;&gt;INT(H19),MOD(H19,100)&lt;&gt;0,AND(AL19&lt;&gt;"",OR(AL19&lt;=0,AL19&lt;&gt;INT(AL19),MOD(AL19,100)&lt;&gt;0)),AND(AN19&lt;&gt;"",OR(AN19&lt;=0,AN19&lt;&gt;INT(AN19),MOD(AN19,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL19&lt;&gt;"",AN19&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ19&gt;C19*D19,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A19="","",IF(OR(E19="",H19=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK19="",AL19&lt;&gt;""),AND(AK19&lt;&gt;"",AL19="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM19="",AN19&lt;&gt;""),AND(AM19&lt;&gt;"",AN19="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM19&lt;&gt;"",AN19&lt;&gt;""),OR(AK19="",AL19="")),"违规：必须先完成第二批",IF(OR(H19&lt;=0,H19&lt;&gt;INT(H19),MOD(H19,100)&lt;&gt;0,AND(AL19&lt;&gt;"",OR(AL19&lt;=0,AL19&lt;&gt;INT(AL19),MOD(AL19,100)&lt;&gt;0)),AND(AN19&lt;&gt;"",OR(AN19&lt;=0,AN19&lt;&gt;INT(AN19),MOD(AN19,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL19&lt;&gt;"",AN19&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ19&gt;C19*D19,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -5161,7 +5136,7 @@
         <f>IF(A20="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A20)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>300</v>
       </c>
-      <c r="M20" s="18">
+      <c r="M20" s="17">
         <f>IF(A20="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A20)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44225</v>
       </c>
@@ -5185,7 +5160,7 @@
         <f>IF(OR(AO20="",N20="",AO20&lt;=0),"",(AO20-N20)/AO20)</f>
         <v>0.0735753527954325</v>
       </c>
-      <c r="W20" s="19">
+      <c r="W20" s="18">
         <f>IF(OR(U20="",V20="",V20&lt;=0),"",U20/V20)</f>
         <v>1.0497803806735</v>
       </c>
@@ -5199,7 +5174,7 @@
       </c>
       <c r="Z20" s="7">
         <f>IF(OR(AE20="",多次统计数据!$B$8=""),"",AE20-多次统计数据!$B$8)</f>
-        <v>-0.090441366553578</v>
+        <v>-0.0898365645051192</v>
       </c>
       <c r="AA20" s="11">
         <f>IF(OR(I20="",M20="",M20&lt;I20),"",M20-I20)</f>
@@ -5207,7 +5182,7 @@
       </c>
       <c r="AB20" s="7">
         <f>IF(OR(A20="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC20" s="8" t="str">
         <f>IF(OR(AB20="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB20,"低于上限","达到或超过上限"))</f>
@@ -5246,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="AR20" s="8" t="str">
-        <f ca="1">IF(A20="","",IF(OR(E20="",H20=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK20="",AL20&lt;&gt;""),AND(AK20&lt;&gt;"",AL20="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM20="",AN20&lt;&gt;""),AND(AM20&lt;&gt;"",AN20="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM20&lt;&gt;"",AN20&lt;&gt;""),OR(AK20="",AL20="")),"违规：必须先完成第二批",IF(OR(H20&lt;=0,H20&lt;&gt;INT(H20),MOD(H20,100)&lt;&gt;0,AND(AL20&lt;&gt;"",OR(AL20&lt;=0,AL20&lt;&gt;INT(AL20),MOD(AL20,100)&lt;&gt;0)),AND(AN20&lt;&gt;"",OR(AN20&lt;=0,AN20&lt;&gt;INT(AN20),MOD(AN20,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL20&lt;&gt;"",AN20&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ20&gt;C20*D20,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A20="","",IF(OR(E20="",H20=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK20="",AL20&lt;&gt;""),AND(AK20&lt;&gt;"",AL20="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM20="",AN20&lt;&gt;""),AND(AM20&lt;&gt;"",AN20="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM20&lt;&gt;"",AN20&lt;&gt;""),OR(AK20="",AL20="")),"违规：必须先完成第二批",IF(OR(H20&lt;=0,H20&lt;&gt;INT(H20),MOD(H20,100)&lt;&gt;0,AND(AL20&lt;&gt;"",OR(AL20&lt;=0,AL20&lt;&gt;INT(AL20),MOD(AL20,100)&lt;&gt;0)),AND(AN20&lt;&gt;"",OR(AN20&lt;=0,AN20&lt;&gt;INT(AN20),MOD(AN20,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL20&lt;&gt;"",AN20&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ20&gt;C20*D20,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -5291,7 +5266,7 @@
         <f>IF(A21="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A21)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1000</v>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="17">
         <f>IF(A21="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A21)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44530</v>
       </c>
@@ -5315,7 +5290,7 @@
         <f>IF(OR(AO21="",N21="",AO21&lt;=0),"",(AO21-N21)/AO21)</f>
         <v>0.0467111534795043</v>
       </c>
-      <c r="W21" s="19">
+      <c r="W21" s="18">
         <f>IF(OR(U21="",V21="",V21&lt;=0),"",U21/V21)</f>
         <v>2.26530612244898</v>
       </c>
@@ -5329,7 +5304,7 @@
       </c>
       <c r="Z21" s="7">
         <f>IF(OR(AE21="",多次统计数据!$B$8=""),"",AE21-多次统计数据!$B$8)</f>
-        <v>-0.0986335987185852</v>
+        <v>-0.0980287966701264</v>
       </c>
       <c r="AA21" s="11">
         <f>IF(OR(I21="",M21="",M21&lt;I21),"",M21-I21)</f>
@@ -5337,7 +5312,7 @@
       </c>
       <c r="AB21" s="7">
         <f>IF(OR(A21="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC21" s="8" t="str">
         <f>IF(OR(AB21="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB21,"低于上限","达到或超过上限"))</f>
@@ -5376,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="AR21" s="8" t="str">
-        <f ca="1">IF(A21="","",IF(OR(E21="",H21=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK21="",AL21&lt;&gt;""),AND(AK21&lt;&gt;"",AL21="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM21="",AN21&lt;&gt;""),AND(AM21&lt;&gt;"",AN21="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM21&lt;&gt;"",AN21&lt;&gt;""),OR(AK21="",AL21="")),"违规：必须先完成第二批",IF(OR(H21&lt;=0,H21&lt;&gt;INT(H21),MOD(H21,100)&lt;&gt;0,AND(AL21&lt;&gt;"",OR(AL21&lt;=0,AL21&lt;&gt;INT(AL21),MOD(AL21,100)&lt;&gt;0)),AND(AN21&lt;&gt;"",OR(AN21&lt;=0,AN21&lt;&gt;INT(AN21),MOD(AN21,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL21&lt;&gt;"",AN21&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ21&gt;C21*D21,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A21="","",IF(OR(E21="",H21=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK21="",AL21&lt;&gt;""),AND(AK21&lt;&gt;"",AL21="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM21="",AN21&lt;&gt;""),AND(AM21&lt;&gt;"",AN21="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM21&lt;&gt;"",AN21&lt;&gt;""),OR(AK21="",AL21="")),"违规：必须先完成第二批",IF(OR(H21&lt;=0,H21&lt;&gt;INT(H21),MOD(H21,100)&lt;&gt;0,AND(AL21&lt;&gt;"",OR(AL21&lt;=0,AL21&lt;&gt;INT(AL21),MOD(AL21,100)&lt;&gt;0)),AND(AN21&lt;&gt;"",OR(AN21&lt;=0,AN21&lt;&gt;INT(AN21),MOD(AN21,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL21&lt;&gt;"",AN21&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ21&gt;C21*D21,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -5421,7 +5396,7 @@
         <f>IF(A22="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A22)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>2000</v>
       </c>
-      <c r="M22" s="18">
+      <c r="M22" s="17">
         <f>IF(A22="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A22)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44760</v>
       </c>
@@ -5445,7 +5420,7 @@
         <f>IF(OR(AO22="",N22="",AO22&lt;=0),"",(AO22-N22)/AO22)</f>
         <v>0.0323472491014654</v>
       </c>
-      <c r="W22" s="19">
+      <c r="W22" s="18">
         <f>IF(OR(U22="",V22="",V22&lt;=0),"",U22/V22)</f>
         <v>3.27350427350427</v>
       </c>
@@ -5459,7 +5434,7 @@
       </c>
       <c r="Z22" s="7">
         <f>IF(OR(AE22="",多次统计数据!$B$8=""),"",AE22-多次统计数据!$B$8)</f>
-        <v>-0.0554740680157327</v>
+        <v>-0.054869265967274</v>
       </c>
       <c r="AA22" s="11">
         <f>IF(OR(I22="",M22="",M22&lt;I22),"",M22-I22)</f>
@@ -5467,7 +5442,7 @@
       </c>
       <c r="AB22" s="7">
         <f>IF(OR(A22="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC22" s="8" t="str">
         <f>IF(OR(AB22="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB22,"低于上限","达到或超过上限"))</f>
@@ -5508,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="AR22" s="8" t="str">
-        <f ca="1">IF(A22="","",IF(OR(E22="",H22=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK22="",AL22&lt;&gt;""),AND(AK22&lt;&gt;"",AL22="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM22="",AN22&lt;&gt;""),AND(AM22&lt;&gt;"",AN22="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM22&lt;&gt;"",AN22&lt;&gt;""),OR(AK22="",AL22="")),"违规：必须先完成第二批",IF(OR(H22&lt;=0,H22&lt;&gt;INT(H22),MOD(H22,100)&lt;&gt;0,AND(AL22&lt;&gt;"",OR(AL22&lt;=0,AL22&lt;&gt;INT(AL22),MOD(AL22,100)&lt;&gt;0)),AND(AN22&lt;&gt;"",OR(AN22&lt;=0,AN22&lt;&gt;INT(AN22),MOD(AN22,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL22&lt;&gt;"",AN22&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ22&gt;C22*D22,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A22="","",IF(OR(E22="",H22=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK22="",AL22&lt;&gt;""),AND(AK22&lt;&gt;"",AL22="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM22="",AN22&lt;&gt;""),AND(AM22&lt;&gt;"",AN22="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM22&lt;&gt;"",AN22&lt;&gt;""),OR(AK22="",AL22="")),"违规：必须先完成第二批",IF(OR(H22&lt;=0,H22&lt;&gt;INT(H22),MOD(H22,100)&lt;&gt;0,AND(AL22&lt;&gt;"",OR(AL22&lt;=0,AL22&lt;&gt;INT(AL22),MOD(AL22,100)&lt;&gt;0)),AND(AN22&lt;&gt;"",OR(AN22&lt;=0,AN22&lt;&gt;INT(AN22),MOD(AN22,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL22&lt;&gt;"",AN22&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ22&gt;C22*D22,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -5552,7 +5527,7 @@
       <c r="L23" s="8">
         <v>1700</v>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="17">
         <f>IF(A23="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A23)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45077</v>
       </c>
@@ -5576,7 +5551,7 @@
         <f>IF(OR(AO23="",N23="",AO23&lt;=0),"",(AO23-N23)/AO23)</f>
         <v>0.0283233409137895</v>
       </c>
-      <c r="W23" s="19">
+      <c r="W23" s="18">
         <f>IF(OR(U23="",V23="",V23&lt;=0),"",U23/V23)</f>
         <v>1.18978102189781</v>
       </c>
@@ -5590,7 +5565,7 @@
       </c>
       <c r="Z23" s="7">
         <f>IF(OR(AE23="",多次统计数据!$B$8=""),"",AE23-多次统计数据!$B$8)</f>
-        <v>-0.122632566486475</v>
+        <v>-0.122027764438016</v>
       </c>
       <c r="AA23" s="11">
         <f>IF(OR(I23="",M23="",M23&lt;I23),"",M23-I23)</f>
@@ -5598,7 +5573,7 @@
       </c>
       <c r="AB23" s="7">
         <f>IF(OR(A23="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC23" s="8" t="str">
         <f>IF(OR(AB23="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB23,"低于上限","达到或超过上限"))</f>
@@ -5639,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="AR23" s="8" t="str">
-        <f ca="1">IF(A23="","",IF(OR(E23="",H23=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK23="",AL23&lt;&gt;""),AND(AK23&lt;&gt;"",AL23="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM23="",AN23&lt;&gt;""),AND(AM23&lt;&gt;"",AN23="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM23&lt;&gt;"",AN23&lt;&gt;""),OR(AK23="",AL23="")),"违规：必须先完成第二批",IF(OR(H23&lt;=0,H23&lt;&gt;INT(H23),MOD(H23,100)&lt;&gt;0,AND(AL23&lt;&gt;"",OR(AL23&lt;=0,AL23&lt;&gt;INT(AL23),MOD(AL23,100)&lt;&gt;0)),AND(AN23&lt;&gt;"",OR(AN23&lt;=0,AN23&lt;&gt;INT(AN23),MOD(AN23,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL23&lt;&gt;"",AN23&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ23&gt;C23*D23,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A23="","",IF(OR(E23="",H23=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK23="",AL23&lt;&gt;""),AND(AK23&lt;&gt;"",AL23="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM23="",AN23&lt;&gt;""),AND(AM23&lt;&gt;"",AN23="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM23&lt;&gt;"",AN23&lt;&gt;""),OR(AK23="",AL23="")),"违规：必须先完成第二批",IF(OR(H23&lt;=0,H23&lt;&gt;INT(H23),MOD(H23,100)&lt;&gt;0,AND(AL23&lt;&gt;"",OR(AL23&lt;=0,AL23&lt;&gt;INT(AL23),MOD(AL23,100)&lt;&gt;0)),AND(AN23&lt;&gt;"",OR(AN23&lt;=0,AN23&lt;&gt;INT(AN23),MOD(AN23,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL23&lt;&gt;"",AN23&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ23&gt;C23*D23,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -5684,7 +5659,7 @@
         <f>IF(A24="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A24)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1300</v>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="17">
         <f>IF(A24="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A24)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45112</v>
       </c>
@@ -5708,7 +5683,7 @@
         <f>IF(OR(AO24="",N24="",AO24&lt;=0),"",(AO24-N24)/AO24)</f>
         <v>0.0376390076988879</v>
       </c>
-      <c r="W24" s="19">
+      <c r="W24" s="18">
         <f>IF(OR(U24="",V24="",V24&lt;=0),"",U24/V24)</f>
         <v>1.84090909090909</v>
       </c>
@@ -5722,7 +5697,7 @@
       </c>
       <c r="Z24" s="7">
         <f>IF(OR(AE24="",多次统计数据!$B$8=""),"",AE24-多次统计数据!$B$8)</f>
-        <v>-0.051938733481048</v>
+        <v>-0.0513339314325893</v>
       </c>
       <c r="AA24" s="11">
         <f>IF(OR(I24="",M24="",M24&lt;I24),"",M24-I24)</f>
@@ -5730,7 +5705,7 @@
       </c>
       <c r="AB24" s="7">
         <f>IF(OR(A24="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC24" s="8" t="str">
         <f>IF(OR(AB24="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB24,"低于上限","达到或超过上限"))</f>
@@ -5771,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="AR24" s="8" t="str">
-        <f ca="1">IF(A24="","",IF(OR(E24="",H24=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK24="",AL24&lt;&gt;""),AND(AK24&lt;&gt;"",AL24="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM24="",AN24&lt;&gt;""),AND(AM24&lt;&gt;"",AN24="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM24&lt;&gt;"",AN24&lt;&gt;""),OR(AK24="",AL24="")),"违规：必须先完成第二批",IF(OR(H24&lt;=0,H24&lt;&gt;INT(H24),MOD(H24,100)&lt;&gt;0,AND(AL24&lt;&gt;"",OR(AL24&lt;=0,AL24&lt;&gt;INT(AL24),MOD(AL24,100)&lt;&gt;0)),AND(AN24&lt;&gt;"",OR(AN24&lt;=0,AN24&lt;&gt;INT(AN24),MOD(AN24,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL24&lt;&gt;"",AN24&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ24&gt;C24*D24,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A24="","",IF(OR(E24="",H24=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK24="",AL24&lt;&gt;""),AND(AK24&lt;&gt;"",AL24="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM24="",AN24&lt;&gt;""),AND(AM24&lt;&gt;"",AN24="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM24&lt;&gt;"",AN24&lt;&gt;""),OR(AK24="",AL24="")),"违规：必须先完成第二批",IF(OR(H24&lt;=0,H24&lt;&gt;INT(H24),MOD(H24,100)&lt;&gt;0,AND(AL24&lt;&gt;"",OR(AL24&lt;=0,AL24&lt;&gt;INT(AL24),MOD(AL24,100)&lt;&gt;0)),AND(AN24&lt;&gt;"",OR(AN24&lt;=0,AN24&lt;&gt;INT(AN24),MOD(AN24,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL24&lt;&gt;"",AN24&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ24&gt;C24*D24,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -5816,7 +5791,7 @@
         <f>IF(A25="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A25)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1300</v>
       </c>
-      <c r="M25" s="18">
+      <c r="M25" s="17">
         <f>IF(A25="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A25)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45132</v>
       </c>
@@ -5840,7 +5815,7 @@
         <f>IF(OR(AO25="",N25="",AO25&lt;=0),"",(AO25-N25)/AO25)</f>
         <v>0.0361961876204754</v>
       </c>
-      <c r="W25" s="19">
+      <c r="W25" s="18">
         <f>IF(OR(U25="",V25="",V25&lt;=0),"",U25/V25)</f>
         <v>1.95857988165681</v>
       </c>
@@ -5854,7 +5829,7 @@
       </c>
       <c r="Z25" s="7">
         <f>IF(OR(AE25="",多次统计数据!$B$8=""),"",AE25-多次统计数据!$B$8)</f>
-        <v>-0.0673622659488419</v>
+        <v>-0.0667574639003831</v>
       </c>
       <c r="AA25" s="11">
         <f>IF(OR(I25="",M25="",M25&lt;I25),"",M25-I25)</f>
@@ -5862,7 +5837,7 @@
       </c>
       <c r="AB25" s="7">
         <f>IF(OR(A25="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC25" s="8" t="str">
         <f>IF(OR(AB25="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB25,"低于上限","达到或超过上限"))</f>
@@ -5903,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="AR25" s="8" t="str">
-        <f ca="1">IF(A25="","",IF(OR(E25="",H25=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK25="",AL25&lt;&gt;""),AND(AK25&lt;&gt;"",AL25="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM25="",AN25&lt;&gt;""),AND(AM25&lt;&gt;"",AN25="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM25&lt;&gt;"",AN25&lt;&gt;""),OR(AK25="",AL25="")),"违规：必须先完成第二批",IF(OR(H25&lt;=0,H25&lt;&gt;INT(H25),MOD(H25,100)&lt;&gt;0,AND(AL25&lt;&gt;"",OR(AL25&lt;=0,AL25&lt;&gt;INT(AL25),MOD(AL25,100)&lt;&gt;0)),AND(AN25&lt;&gt;"",OR(AN25&lt;=0,AN25&lt;&gt;INT(AN25),MOD(AN25,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL25&lt;&gt;"",AN25&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ25&gt;C25*D25,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A25="","",IF(OR(E25="",H25=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK25="",AL25&lt;&gt;""),AND(AK25&lt;&gt;"",AL25="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM25="",AN25&lt;&gt;""),AND(AM25&lt;&gt;"",AN25="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM25&lt;&gt;"",AN25&lt;&gt;""),OR(AK25="",AL25="")),"违规：必须先完成第二批",IF(OR(H25&lt;=0,H25&lt;&gt;INT(H25),MOD(H25,100)&lt;&gt;0,AND(AL25&lt;&gt;"",OR(AL25&lt;=0,AL25&lt;&gt;INT(AL25),MOD(AL25,100)&lt;&gt;0)),AND(AN25&lt;&gt;"",OR(AN25&lt;=0,AN25&lt;&gt;INT(AN25),MOD(AN25,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL25&lt;&gt;"",AN25&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ25&gt;C25*D25,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -5948,7 +5923,7 @@
         <f>IF(A26="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A26)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1600</v>
       </c>
-      <c r="M26" s="18">
+      <c r="M26" s="17">
         <f>IF(A26="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A26)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45138</v>
       </c>
@@ -5972,7 +5947,7 @@
         <f>IF(OR(AO26="",N26="",AO26&lt;=0),"",(AO26-N26)/AO26)</f>
         <v>0.0299277605779154</v>
       </c>
-      <c r="W26" s="19">
+      <c r="W26" s="18">
         <f>IF(OR(U26="",V26="",V26&lt;=0),"",U26/V26)</f>
         <v>1.06896551724138</v>
       </c>
@@ -5986,7 +5961,7 @@
       </c>
       <c r="Z26" s="7">
         <f>IF(OR(AE26="",多次统计数据!$B$8=""),"",AE26-多次统计数据!$B$8)</f>
-        <v>-0.132943830435881</v>
+        <v>-0.132339028387422</v>
       </c>
       <c r="AA26" s="11">
         <f>IF(OR(I26="",M26="",M26&lt;I26),"",M26-I26)</f>
@@ -5994,7 +5969,7 @@
       </c>
       <c r="AB26" s="7">
         <f>IF(OR(A26="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC26" s="8" t="str">
         <f>IF(OR(AB26="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB26,"低于上限","达到或超过上限"))</f>
@@ -6035,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="AR26" s="8" t="str">
-        <f ca="1">IF(A26="","",IF(OR(E26="",H26=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK26="",AL26&lt;&gt;""),AND(AK26&lt;&gt;"",AL26="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM26="",AN26&lt;&gt;""),AND(AM26&lt;&gt;"",AN26="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM26&lt;&gt;"",AN26&lt;&gt;""),OR(AK26="",AL26="")),"违规：必须先完成第二批",IF(OR(H26&lt;=0,H26&lt;&gt;INT(H26),MOD(H26,100)&lt;&gt;0,AND(AL26&lt;&gt;"",OR(AL26&lt;=0,AL26&lt;&gt;INT(AL26),MOD(AL26,100)&lt;&gt;0)),AND(AN26&lt;&gt;"",OR(AN26&lt;=0,AN26&lt;&gt;INT(AN26),MOD(AN26,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL26&lt;&gt;"",AN26&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ26&gt;C26*D26,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A26="","",IF(OR(E26="",H26=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK26="",AL26&lt;&gt;""),AND(AK26&lt;&gt;"",AL26="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM26="",AN26&lt;&gt;""),AND(AM26&lt;&gt;"",AN26="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM26&lt;&gt;"",AN26&lt;&gt;""),OR(AK26="",AL26="")),"违规：必须先完成第二批",IF(OR(H26&lt;=0,H26&lt;&gt;INT(H26),MOD(H26,100)&lt;&gt;0,AND(AL26&lt;&gt;"",OR(AL26&lt;=0,AL26&lt;&gt;INT(AL26),MOD(AL26,100)&lt;&gt;0)),AND(AN26&lt;&gt;"",OR(AN26&lt;=0,AN26&lt;&gt;INT(AN26),MOD(AN26,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL26&lt;&gt;"",AN26&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ26&gt;C26*D26,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -6080,7 +6055,7 @@
         <f>IF(A27="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A27)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1400</v>
       </c>
-      <c r="M27" s="18">
+      <c r="M27" s="17">
         <f>IF(A27="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A27)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45215</v>
       </c>
@@ -6104,7 +6079,7 @@
         <f>IF(OR(AO27="",N27="",AO27&lt;=0),"",(AO27-N27)/AO27)</f>
         <v>0.0348837209302326</v>
       </c>
-      <c r="W27" s="19">
+      <c r="W27" s="18">
         <f>IF(OR(U27="",V27="",V27&lt;=0),"",U27/V27)</f>
         <v>1.33333333333333</v>
       </c>
@@ -6118,7 +6093,7 @@
       </c>
       <c r="Z27" s="7">
         <f>IF(OR(AE27="",多次统计数据!$B$8=""),"",AE27-多次统计数据!$B$8)</f>
-        <v>-0.0646218195749364</v>
+        <v>-0.0640170175264776</v>
       </c>
       <c r="AA27" s="11">
         <f>IF(OR(I27="",M27="",M27&lt;I27),"",M27-I27)</f>
@@ -6126,7 +6101,7 @@
       </c>
       <c r="AB27" s="7">
         <f>IF(OR(A27="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC27" s="8" t="str">
         <f>IF(OR(AB27="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB27,"低于上限","达到或超过上限"))</f>
@@ -6167,7 +6142,7 @@
         <v>0</v>
       </c>
       <c r="AR27" s="8" t="str">
-        <f ca="1">IF(A27="","",IF(OR(E27="",H27=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK27="",AL27&lt;&gt;""),AND(AK27&lt;&gt;"",AL27="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM27="",AN27&lt;&gt;""),AND(AM27&lt;&gt;"",AN27="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM27&lt;&gt;"",AN27&lt;&gt;""),OR(AK27="",AL27="")),"违规：必须先完成第二批",IF(OR(H27&lt;=0,H27&lt;&gt;INT(H27),MOD(H27,100)&lt;&gt;0,AND(AL27&lt;&gt;"",OR(AL27&lt;=0,AL27&lt;&gt;INT(AL27),MOD(AL27,100)&lt;&gt;0)),AND(AN27&lt;&gt;"",OR(AN27&lt;=0,AN27&lt;&gt;INT(AN27),MOD(AN27,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL27&lt;&gt;"",AN27&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ27&gt;C27*D27,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A27="","",IF(OR(E27="",H27=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK27="",AL27&lt;&gt;""),AND(AK27&lt;&gt;"",AL27="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM27="",AN27&lt;&gt;""),AND(AM27&lt;&gt;"",AN27="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM27&lt;&gt;"",AN27&lt;&gt;""),OR(AK27="",AL27="")),"违规：必须先完成第二批",IF(OR(H27&lt;=0,H27&lt;&gt;INT(H27),MOD(H27,100)&lt;&gt;0,AND(AL27&lt;&gt;"",OR(AL27&lt;=0,AL27&lt;&gt;INT(AL27),MOD(AL27,100)&lt;&gt;0)),AND(AN27&lt;&gt;"",OR(AN27&lt;=0,AN27&lt;&gt;INT(AN27),MOD(AN27,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL27&lt;&gt;"",AN27&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ27&gt;C27*D27,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -6212,7 +6187,7 @@
         <f>IF(A28="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A28)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>3000</v>
       </c>
-      <c r="M28" s="18">
+      <c r="M28" s="17">
         <f>IF(A28="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A28)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45264</v>
       </c>
@@ -6236,7 +6211,7 @@
         <f>IF(OR(AO28="",N28="",AO28&lt;=0),"",(AO28-N28)/AO28)</f>
         <v>0.0156216563235608</v>
       </c>
-      <c r="W28" s="19">
+      <c r="W28" s="18">
         <f>IF(OR(U28="",V28="",V28&lt;=0),"",U28/V28)</f>
         <v>4.47945205479454</v>
       </c>
@@ -6250,7 +6225,7 @@
       </c>
       <c r="Z28" s="7">
         <f>IF(OR(AE28="",多次统计数据!$B$8=""),"",AE28-多次统计数据!$B$8)</f>
-        <v>-0.10827878424231</v>
+        <v>-0.107673982193852</v>
       </c>
       <c r="AA28" s="11">
         <f>IF(OR(I28="",M28="",M28&lt;I28),"",M28-I28)</f>
@@ -6258,7 +6233,7 @@
       </c>
       <c r="AB28" s="7">
         <f>IF(OR(A28="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC28" s="8" t="str">
         <f>IF(OR(AB28="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB28,"低于上限","达到或超过上限"))</f>
@@ -6299,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="AR28" s="8" t="str">
-        <f ca="1">IF(A28="","",IF(OR(E28="",H28=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK28="",AL28&lt;&gt;""),AND(AK28&lt;&gt;"",AL28="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM28="",AN28&lt;&gt;""),AND(AM28&lt;&gt;"",AN28="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM28&lt;&gt;"",AN28&lt;&gt;""),OR(AK28="",AL28="")),"违规：必须先完成第二批",IF(OR(H28&lt;=0,H28&lt;&gt;INT(H28),MOD(H28,100)&lt;&gt;0,AND(AL28&lt;&gt;"",OR(AL28&lt;=0,AL28&lt;&gt;INT(AL28),MOD(AL28,100)&lt;&gt;0)),AND(AN28&lt;&gt;"",OR(AN28&lt;=0,AN28&lt;&gt;INT(AN28),MOD(AN28,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL28&lt;&gt;"",AN28&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ28&gt;C28*D28,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A28="","",IF(OR(E28="",H28=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK28="",AL28&lt;&gt;""),AND(AK28&lt;&gt;"",AL28="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM28="",AN28&lt;&gt;""),AND(AM28&lt;&gt;"",AN28="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM28&lt;&gt;"",AN28&lt;&gt;""),OR(AK28="",AL28="")),"违规：必须先完成第二批",IF(OR(H28&lt;=0,H28&lt;&gt;INT(H28),MOD(H28,100)&lt;&gt;0,AND(AL28&lt;&gt;"",OR(AL28&lt;=0,AL28&lt;&gt;INT(AL28),MOD(AL28,100)&lt;&gt;0)),AND(AN28&lt;&gt;"",OR(AN28&lt;=0,AN28&lt;&gt;INT(AN28),MOD(AN28,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL28&lt;&gt;"",AN28&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ28&gt;C28*D28,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -6344,7 +6319,7 @@
         <f>IF(A29="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A29)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>3800</v>
       </c>
-      <c r="M29" s="18">
+      <c r="M29" s="17">
         <f>IF(A29="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A29)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45060</v>
       </c>
@@ -6368,7 +6343,7 @@
         <f>IF(OR(AO29="",N29="",AO29&lt;=0),"",(AO29-N29)/AO29)</f>
         <v>0.0120274914089348</v>
       </c>
-      <c r="W29" s="19">
+      <c r="W29" s="18">
         <f>IF(OR(U29="",V29="",V29&lt;=0),"",U29/V29)</f>
         <v>6.14285714285711</v>
       </c>
@@ -6382,7 +6357,7 @@
       </c>
       <c r="Z29" s="7">
         <f>IF(OR(AE29="",多次统计数据!$B$8=""),"",AE29-多次统计数据!$B$8)</f>
-        <v>-0.136860103848883</v>
+        <v>-0.136255301800425</v>
       </c>
       <c r="AA29" s="11" t="str">
         <f>IF(OR(I29="",M29="",M29&lt;I29),"",M29-I29)</f>
@@ -6390,7 +6365,7 @@
       </c>
       <c r="AB29" s="7">
         <f>IF(OR(A29="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC29" s="8" t="str">
         <f>IF(OR(AB29="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB29,"低于上限","达到或超过上限"))</f>
@@ -6429,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="AR29" s="8" t="str">
-        <f ca="1">IF(A29="","",IF(OR(E29="",H29=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK29="",AL29&lt;&gt;""),AND(AK29&lt;&gt;"",AL29="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM29="",AN29&lt;&gt;""),AND(AM29&lt;&gt;"",AN29="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM29&lt;&gt;"",AN29&lt;&gt;""),OR(AK29="",AL29="")),"违规：必须先完成第二批",IF(OR(H29&lt;=0,H29&lt;&gt;INT(H29),MOD(H29,100)&lt;&gt;0,AND(AL29&lt;&gt;"",OR(AL29&lt;=0,AL29&lt;&gt;INT(AL29),MOD(AL29,100)&lt;&gt;0)),AND(AN29&lt;&gt;"",OR(AN29&lt;=0,AN29&lt;&gt;INT(AN29),MOD(AN29,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL29&lt;&gt;"",AN29&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ29&gt;C29*D29,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A29="","",IF(OR(E29="",H29=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK29="",AL29&lt;&gt;""),AND(AK29&lt;&gt;"",AL29="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM29="",AN29&lt;&gt;""),AND(AM29&lt;&gt;"",AN29="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM29&lt;&gt;"",AN29&lt;&gt;""),OR(AK29="",AL29="")),"违规：必须先完成第二批",IF(OR(H29&lt;=0,H29&lt;&gt;INT(H29),MOD(H29,100)&lt;&gt;0,AND(AL29&lt;&gt;"",OR(AL29&lt;=0,AL29&lt;&gt;INT(AL29),MOD(AL29,100)&lt;&gt;0)),AND(AN29&lt;&gt;"",OR(AN29&lt;=0,AN29&lt;&gt;INT(AN29),MOD(AN29,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL29&lt;&gt;"",AN29&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ29&gt;C29*D29,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -6474,7 +6449,7 @@
         <f>IF(A30="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A30)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>1000</v>
       </c>
-      <c r="M30" s="18">
+      <c r="M30" s="17">
         <f>IF(A30="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A30)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43061</v>
       </c>
@@ -6498,7 +6473,7 @@
         <f>IF(OR(AO30="",N30="",AO30&lt;=0),"",(AO30-N30)/AO30)</f>
         <v>0.0497624406101526</v>
       </c>
-      <c r="W30" s="19">
+      <c r="W30" s="18">
         <f>IF(OR(U30="",V30="",V30&lt;=0),"",U30/V30)</f>
         <v>2.51758793969849</v>
       </c>
@@ -6512,7 +6487,7 @@
       </c>
       <c r="Z30" s="7">
         <f>IF(OR(AE30="",多次统计数据!$B$8=""),"",AE30-多次统计数据!$B$8)</f>
-        <v>-0.0552520348457885</v>
+        <v>-0.0546472327973297</v>
       </c>
       <c r="AA30" s="11">
         <f>IF(OR(I30="",M30="",M30&lt;I30),"",M30-I30)</f>
@@ -6520,7 +6495,7 @@
       </c>
       <c r="AB30" s="7">
         <f>IF(OR(A30="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC30" s="8" t="str">
         <f>IF(OR(AB30="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB30,"低于上限","达到或超过上限"))</f>
@@ -6564,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="AR30" s="8" t="str">
-        <f ca="1">IF(A30="","",IF(OR(E30="",H30=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK30="",AL30&lt;&gt;""),AND(AK30&lt;&gt;"",AL30="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM30="",AN30&lt;&gt;""),AND(AM30&lt;&gt;"",AN30="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM30&lt;&gt;"",AN30&lt;&gt;""),OR(AK30="",AL30="")),"违规：必须先完成第二批",IF(OR(H30&lt;=0,H30&lt;&gt;INT(H30),MOD(H30,100)&lt;&gt;0,AND(AL30&lt;&gt;"",OR(AL30&lt;=0,AL30&lt;&gt;INT(AL30),MOD(AL30,100)&lt;&gt;0)),AND(AN30&lt;&gt;"",OR(AN30&lt;=0,AN30&lt;&gt;INT(AN30),MOD(AN30,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL30&lt;&gt;"",AN30&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ30&gt;C30*D30,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A30="","",IF(OR(E30="",H30=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK30="",AL30&lt;&gt;""),AND(AK30&lt;&gt;"",AL30="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM30="",AN30&lt;&gt;""),AND(AM30&lt;&gt;"",AN30="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM30&lt;&gt;"",AN30&lt;&gt;""),OR(AK30="",AL30="")),"违规：必须先完成第二批",IF(OR(H30&lt;=0,H30&lt;&gt;INT(H30),MOD(H30,100)&lt;&gt;0,AND(AL30&lt;&gt;"",OR(AL30&lt;=0,AL30&lt;&gt;INT(AL30),MOD(AL30,100)&lt;&gt;0)),AND(AN30&lt;&gt;"",OR(AN30&lt;=0,AN30&lt;&gt;INT(AN30),MOD(AN30,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL30&lt;&gt;"",AN30&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ30&gt;C30*D30,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -6609,7 +6584,7 @@
         <f>IF(A31="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A31)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>600</v>
       </c>
-      <c r="M31" s="18">
+      <c r="M31" s="17">
         <f>IF(A31="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A31)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43083</v>
       </c>
@@ -6633,7 +6608,7 @@
         <f>IF(OR(AO31="",N31="",AO31&lt;=0),"",(AO31-N31)/AO31)</f>
         <v>0.0861618798955613</v>
       </c>
-      <c r="W31" s="19">
+      <c r="W31" s="18">
         <f>IF(OR(U31="",V31="",V31&lt;=0),"",U31/V31)</f>
         <v>0.515151515151516</v>
       </c>
@@ -6647,7 +6622,7 @@
       </c>
       <c r="Z31" s="7">
         <f>IF(OR(AE31="",多次统计数据!$B$8=""),"",AE31-多次统计数据!$B$8)</f>
-        <v>-0.0362291554888374</v>
+        <v>-0.0356243534403786</v>
       </c>
       <c r="AA31" s="11">
         <f>IF(OR(I31="",M31="",M31&lt;I31),"",M31-I31)</f>
@@ -6655,7 +6630,7 @@
       </c>
       <c r="AB31" s="7">
         <f>IF(OR(A31="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC31" s="8" t="str">
         <f>IF(OR(AB31="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB31,"低于上限","达到或超过上限"))</f>
@@ -6694,11 +6669,11 @@
         <v>0</v>
       </c>
       <c r="AR31" s="8" t="str">
-        <f ca="1">IF(A31="","",IF(OR(E31="",H31=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK31="",AL31&lt;&gt;""),AND(AK31&lt;&gt;"",AL31="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM31="",AN31&lt;&gt;""),AND(AM31&lt;&gt;"",AN31="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM31&lt;&gt;"",AN31&lt;&gt;""),OR(AK31="",AL31="")),"违规：必须先完成第二批",IF(OR(H31&lt;=0,H31&lt;&gt;INT(H31),MOD(H31,100)&lt;&gt;0,AND(AL31&lt;&gt;"",OR(AL31&lt;=0,AL31&lt;&gt;INT(AL31),MOD(AL31,100)&lt;&gt;0)),AND(AN31&lt;&gt;"",OR(AN31&lt;=0,AN31&lt;&gt;INT(AN31),MOD(AN31,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL31&lt;&gt;"",AN31&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ31&gt;C31*D31,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A31="","",IF(OR(E31="",H31=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK31="",AL31&lt;&gt;""),AND(AK31&lt;&gt;"",AL31="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM31="",AN31&lt;&gt;""),AND(AM31&lt;&gt;"",AN31="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM31&lt;&gt;"",AN31&lt;&gt;""),OR(AK31="",AL31="")),"违规：必须先完成第二批",IF(OR(H31&lt;=0,H31&lt;&gt;INT(H31),MOD(H31,100)&lt;&gt;0,AND(AL31&lt;&gt;"",OR(AL31&lt;=0,AL31&lt;&gt;INT(AL31),MOD(AL31,100)&lt;&gt;0)),AND(AN31&lt;&gt;"",OR(AN31&lt;=0,AN31&lt;&gt;INT(AN31),MOD(AN31,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL31&lt;&gt;"",AN31&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ31&gt;C31*D31,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="32" ht="34" spans="1:44">
+    <row r="32" ht="17" spans="1:44">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -6739,7 +6714,7 @@
         <f>IF(A32="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A32)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>700</v>
       </c>
-      <c r="M32" s="18">
+      <c r="M32" s="17">
         <f>IF(A32="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A32)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43131</v>
       </c>
@@ -6763,7 +6738,7 @@
         <f>IF(OR(AO32="",N32="",AO32&lt;=0),"",(AO32-N32)/AO32)</f>
         <v>0.0532544378698225</v>
       </c>
-      <c r="W32" s="19">
+      <c r="W32" s="18">
         <f>IF(OR(U32="",V32="",V32&lt;=0),"",U32/V32)</f>
         <v>3.44444444444444</v>
       </c>
@@ -6777,7 +6752,7 @@
       </c>
       <c r="Z32" s="7">
         <f>IF(OR(AE32="",多次统计数据!$B$8=""),"",AE32-多次统计数据!$B$8)</f>
-        <v>-0.0494480494085231</v>
+        <v>-0.0488432473600643</v>
       </c>
       <c r="AA32" s="11">
         <f>IF(OR(I32="",M32="",M32&lt;I32),"",M32-I32)</f>
@@ -6785,7 +6760,7 @@
       </c>
       <c r="AB32" s="7">
         <f>IF(OR(A32="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC32" s="8" t="str">
         <f>IF(OR(AB32="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB32,"低于上限","达到或超过上限"))</f>
@@ -6826,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="AR32" s="8" t="str">
-        <f ca="1">IF(A32="","",IF(OR(E32="",H32=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK32="",AL32&lt;&gt;""),AND(AK32&lt;&gt;"",AL32="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM32="",AN32&lt;&gt;""),AND(AM32&lt;&gt;"",AN32="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM32&lt;&gt;"",AN32&lt;&gt;""),OR(AK32="",AL32="")),"违规：必须先完成第二批",IF(OR(H32&lt;=0,H32&lt;&gt;INT(H32),MOD(H32,100)&lt;&gt;0,AND(AL32&lt;&gt;"",OR(AL32&lt;=0,AL32&lt;&gt;INT(AL32),MOD(AL32,100)&lt;&gt;0)),AND(AN32&lt;&gt;"",OR(AN32&lt;=0,AN32&lt;&gt;INT(AN32),MOD(AN32,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL32&lt;&gt;"",AN32&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ32&gt;C32*D32,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A32="","",IF(OR(E32="",H32=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK32="",AL32&lt;&gt;""),AND(AK32&lt;&gt;"",AL32="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM32="",AN32&lt;&gt;""),AND(AM32&lt;&gt;"",AN32="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM32&lt;&gt;"",AN32&lt;&gt;""),OR(AK32="",AL32="")),"违规：必须先完成第二批",IF(OR(H32&lt;=0,H32&lt;&gt;INT(H32),MOD(H32,100)&lt;&gt;0,AND(AL32&lt;&gt;"",OR(AL32&lt;=0,AL32&lt;&gt;INT(AL32),MOD(AL32,100)&lt;&gt;0)),AND(AN32&lt;&gt;"",OR(AN32&lt;=0,AN32&lt;&gt;INT(AN32),MOD(AN32,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL32&lt;&gt;"",AN32&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ32&gt;C32*D32,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -6871,7 +6846,7 @@
         <f>IF(A33="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A33)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>900</v>
       </c>
-      <c r="M33" s="18">
+      <c r="M33" s="17">
         <f>IF(A33="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A33)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43278</v>
       </c>
@@ -6895,7 +6870,7 @@
         <f>IF(OR(AO33="",N33="",AO33&lt;=0),"",(AO33-N33)/AO33)</f>
         <v>0.0443425076452599</v>
       </c>
-      <c r="W33" s="19">
+      <c r="W33" s="18">
         <f>IF(OR(U33="",V33="",V33&lt;=0),"",U33/V33)</f>
         <v>3.31034482758621</v>
       </c>
@@ -6909,7 +6884,7 @@
       </c>
       <c r="Z33" s="7">
         <f>IF(OR(AE33="",多次统计数据!$B$8=""),"",AE33-多次统计数据!$B$8)</f>
-        <v>-0.12145449892648</v>
+        <v>-0.120849696878021</v>
       </c>
       <c r="AA33" s="11">
         <f>IF(OR(I33="",M33="",M33&lt;I33),"",M33-I33)</f>
@@ -6917,7 +6892,7 @@
       </c>
       <c r="AB33" s="7">
         <f>IF(OR(A33="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC33" s="8" t="str">
         <f>IF(OR(AB33="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB33,"低于上限","达到或超过上限"))</f>
@@ -6956,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="AR33" s="8" t="str">
-        <f ca="1">IF(A33="","",IF(OR(E33="",H33=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK33="",AL33&lt;&gt;""),AND(AK33&lt;&gt;"",AL33="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM33="",AN33&lt;&gt;""),AND(AM33&lt;&gt;"",AN33="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM33&lt;&gt;"",AN33&lt;&gt;""),OR(AK33="",AL33="")),"违规：必须先完成第二批",IF(OR(H33&lt;=0,H33&lt;&gt;INT(H33),MOD(H33,100)&lt;&gt;0,AND(AL33&lt;&gt;"",OR(AL33&lt;=0,AL33&lt;&gt;INT(AL33),MOD(AL33,100)&lt;&gt;0)),AND(AN33&lt;&gt;"",OR(AN33&lt;=0,AN33&lt;&gt;INT(AN33),MOD(AN33,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL33&lt;&gt;"",AN33&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ33&gt;C33*D33,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A33="","",IF(OR(E33="",H33=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK33="",AL33&lt;&gt;""),AND(AK33&lt;&gt;"",AL33="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM33="",AN33&lt;&gt;""),AND(AM33&lt;&gt;"",AN33="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM33&lt;&gt;"",AN33&lt;&gt;""),OR(AK33="",AL33="")),"违规：必须先完成第二批",IF(OR(H33&lt;=0,H33&lt;&gt;INT(H33),MOD(H33,100)&lt;&gt;0,AND(AL33&lt;&gt;"",OR(AL33&lt;=0,AL33&lt;&gt;INT(AL33),MOD(AL33,100)&lt;&gt;0)),AND(AN33&lt;&gt;"",OR(AN33&lt;=0,AN33&lt;&gt;INT(AN33),MOD(AN33,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL33&lt;&gt;"",AN33&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ33&gt;C33*D33,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -7001,7 +6976,7 @@
         <f>IF(A34="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A34)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>700</v>
       </c>
-      <c r="M34" s="18">
+      <c r="M34" s="17">
         <f>IF(A34="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A34)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43619</v>
       </c>
@@ -7025,7 +7000,7 @@
         <f>IF(OR(AO34="",N34="",AO34&lt;=0),"",(AO34-N34)/AO34)</f>
         <v>0.0619136960600375</v>
       </c>
-      <c r="W34" s="19">
+      <c r="W34" s="18">
         <f>IF(OR(U34="",V34="",V34&lt;=0),"",U34/V34)</f>
         <v>2.78787878787879</v>
       </c>
@@ -7039,7 +7014,7 @@
       </c>
       <c r="Z34" s="7">
         <f>IF(OR(AE34="",多次统计数据!$B$8=""),"",AE34-多次统计数据!$B$8)</f>
-        <v>0.129511281932335</v>
+        <v>0.130116083980793</v>
       </c>
       <c r="AA34" s="11">
         <f>IF(OR(I34="",M34="",M34&lt;I34),"",M34-I34)</f>
@@ -7047,7 +7022,7 @@
       </c>
       <c r="AB34" s="7">
         <f>IF(OR(A34="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC34" s="8" t="str">
         <f>IF(OR(AB34="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB34,"低于上限","达到或超过上限"))</f>
@@ -7082,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="AR34" s="8" t="str">
-        <f ca="1">IF(A34="","",IF(OR(E34="",H34=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK34="",AL34&lt;&gt;""),AND(AK34&lt;&gt;"",AL34="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM34="",AN34&lt;&gt;""),AND(AM34&lt;&gt;"",AN34="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM34&lt;&gt;"",AN34&lt;&gt;""),OR(AK34="",AL34="")),"违规：必须先完成第二批",IF(OR(H34&lt;=0,H34&lt;&gt;INT(H34),MOD(H34,100)&lt;&gt;0,AND(AL34&lt;&gt;"",OR(AL34&lt;=0,AL34&lt;&gt;INT(AL34),MOD(AL34,100)&lt;&gt;0)),AND(AN34&lt;&gt;"",OR(AN34&lt;=0,AN34&lt;&gt;INT(AN34),MOD(AN34,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL34&lt;&gt;"",AN34&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ34&gt;C34*D34,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A34="","",IF(OR(E34="",H34=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK34="",AL34&lt;&gt;""),AND(AK34&lt;&gt;"",AL34="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM34="",AN34&lt;&gt;""),AND(AM34&lt;&gt;"",AN34="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM34&lt;&gt;"",AN34&lt;&gt;""),OR(AK34="",AL34="")),"违规：必须先完成第二批",IF(OR(H34&lt;=0,H34&lt;&gt;INT(H34),MOD(H34,100)&lt;&gt;0,AND(AL34&lt;&gt;"",OR(AL34&lt;=0,AL34&lt;&gt;INT(AL34),MOD(AL34,100)&lt;&gt;0)),AND(AN34&lt;&gt;"",OR(AN34&lt;=0,AN34&lt;&gt;INT(AN34),MOD(AN34,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL34&lt;&gt;"",AN34&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ34&gt;C34*D34,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -7127,7 +7102,7 @@
         <f>IF(A35="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A35)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>900</v>
       </c>
-      <c r="M35" s="18">
+      <c r="M35" s="17">
         <f>IF(A35="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A35)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43889</v>
       </c>
@@ -7151,7 +7126,7 @@
         <f>IF(OR(AO35="",N35="",AO35&lt;=0),"",(AO35-N35)/AO35)</f>
         <v>0.0258158792011691</v>
       </c>
-      <c r="W35" s="19">
+      <c r="W35" s="18">
         <f>IF(OR(U35="",V35="",V35&lt;=0),"",U35/V35)</f>
         <v>2.77358490566037</v>
       </c>
@@ -7165,7 +7140,7 @@
       </c>
       <c r="Z35" s="7">
         <f>IF(OR(AE35="",多次统计数据!$B$8=""),"",AE35-多次统计数据!$B$8)</f>
-        <v>-0.138986593307226</v>
+        <v>-0.138381791258767</v>
       </c>
       <c r="AA35" s="11">
         <f>IF(OR(I35="",M35="",M35&lt;I35),"",M35-I35)</f>
@@ -7173,7 +7148,7 @@
       </c>
       <c r="AB35" s="7">
         <f>IF(OR(A35="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC35" s="8" t="str">
         <f>IF(OR(AB35="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB35,"低于上限","达到或超过上限"))</f>
@@ -7208,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="AR35" s="8" t="str">
-        <f ca="1">IF(A35="","",IF(OR(E35="",H35=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK35="",AL35&lt;&gt;""),AND(AK35&lt;&gt;"",AL35="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM35="",AN35&lt;&gt;""),AND(AM35&lt;&gt;"",AN35="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM35&lt;&gt;"",AN35&lt;&gt;""),OR(AK35="",AL35="")),"违规：必须先完成第二批",IF(OR(H35&lt;=0,H35&lt;&gt;INT(H35),MOD(H35,100)&lt;&gt;0,AND(AL35&lt;&gt;"",OR(AL35&lt;=0,AL35&lt;&gt;INT(AL35),MOD(AL35,100)&lt;&gt;0)),AND(AN35&lt;&gt;"",OR(AN35&lt;=0,AN35&lt;&gt;INT(AN35),MOD(AN35,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL35&lt;&gt;"",AN35&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ35&gt;C35*D35,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A35="","",IF(OR(E35="",H35=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK35="",AL35&lt;&gt;""),AND(AK35&lt;&gt;"",AL35="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM35="",AN35&lt;&gt;""),AND(AM35&lt;&gt;"",AN35="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM35&lt;&gt;"",AN35&lt;&gt;""),OR(AK35="",AL35="")),"违规：必须先完成第二批",IF(OR(H35&lt;=0,H35&lt;&gt;INT(H35),MOD(H35,100)&lt;&gt;0,AND(AL35&lt;&gt;"",OR(AL35&lt;=0,AL35&lt;&gt;INT(AL35),MOD(AL35,100)&lt;&gt;0)),AND(AN35&lt;&gt;"",OR(AN35&lt;=0,AN35&lt;&gt;INT(AN35),MOD(AN35,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL35&lt;&gt;"",AN35&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ35&gt;C35*D35,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -7253,7 +7228,7 @@
         <f>IF(A36="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A36)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>700</v>
       </c>
-      <c r="M36" s="18">
+      <c r="M36" s="17">
         <f>IF(A36="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A36)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44083</v>
       </c>
@@ -7277,7 +7252,7 @@
         <f>IF(OR(AO36="",N36="",AO36&lt;=0),"",(AO36-N36)/AO36)</f>
         <v>0.0259190242249704</v>
       </c>
-      <c r="W36" s="19">
+      <c r="W36" s="18">
         <f>IF(OR(U36="",V36="",V36&lt;=0),"",U36/V36)</f>
         <v>3.90196078431372</v>
       </c>
@@ -7291,7 +7266,7 @@
       </c>
       <c r="Z36" s="7">
         <f>IF(OR(AE36="",多次统计数据!$B$8=""),"",AE36-多次统计数据!$B$8)</f>
-        <v>0.372065621750563</v>
+        <v>0.372670423799022</v>
       </c>
       <c r="AA36" s="11">
         <f>IF(OR(I36="",M36="",M36&lt;I36),"",M36-I36)</f>
@@ -7299,7 +7274,7 @@
       </c>
       <c r="AB36" s="7">
         <f>IF(OR(A36="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC36" s="8" t="str">
         <f>IF(OR(AB36="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB36,"低于上限","达到或超过上限"))</f>
@@ -7338,7 +7313,7 @@
         <v>0</v>
       </c>
       <c r="AR36" s="8" t="str">
-        <f ca="1">IF(A36="","",IF(OR(E36="",H36=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK36="",AL36&lt;&gt;""),AND(AK36&lt;&gt;"",AL36="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM36="",AN36&lt;&gt;""),AND(AM36&lt;&gt;"",AN36="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM36&lt;&gt;"",AN36&lt;&gt;""),OR(AK36="",AL36="")),"违规：必须先完成第二批",IF(OR(H36&lt;=0,H36&lt;&gt;INT(H36),MOD(H36,100)&lt;&gt;0,AND(AL36&lt;&gt;"",OR(AL36&lt;=0,AL36&lt;&gt;INT(AL36),MOD(AL36,100)&lt;&gt;0)),AND(AN36&lt;&gt;"",OR(AN36&lt;=0,AN36&lt;&gt;INT(AN36),MOD(AN36,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL36&lt;&gt;"",AN36&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ36&gt;C36*D36,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A36="","",IF(OR(E36="",H36=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK36="",AL36&lt;&gt;""),AND(AK36&lt;&gt;"",AL36="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM36="",AN36&lt;&gt;""),AND(AM36&lt;&gt;"",AN36="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM36&lt;&gt;"",AN36&lt;&gt;""),OR(AK36="",AL36="")),"违规：必须先完成第二批",IF(OR(H36&lt;=0,H36&lt;&gt;INT(H36),MOD(H36,100)&lt;&gt;0,AND(AL36&lt;&gt;"",OR(AL36&lt;=0,AL36&lt;&gt;INT(AL36),MOD(AL36,100)&lt;&gt;0)),AND(AN36&lt;&gt;"",OR(AN36&lt;=0,AN36&lt;&gt;INT(AN36),MOD(AN36,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL36&lt;&gt;"",AN36&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ36&gt;C36*D36,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -7383,7 +7358,7 @@
         <f>IF(A37="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A37)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>300</v>
       </c>
-      <c r="M37" s="18">
+      <c r="M37" s="17">
         <f>IF(A37="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A37)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44153</v>
       </c>
@@ -7407,7 +7382,7 @@
         <f>IF(OR(AO37="",N37="",AO37&lt;=0),"",(AO37-N37)/AO37)</f>
         <v>0.0440216377541503</v>
       </c>
-      <c r="W37" s="19">
+      <c r="W37" s="18">
         <f>IF(OR(U37="",V37="",V37&lt;=0),"",U37/V37)</f>
         <v>1.64830508474576</v>
       </c>
@@ -7421,7 +7396,7 @@
       </c>
       <c r="Z37" s="7">
         <f>IF(OR(AE37="",多次统计数据!$B$8=""),"",AE37-多次统计数据!$B$8)</f>
-        <v>-0.0291871625226281</v>
+        <v>-0.0285823604741694</v>
       </c>
       <c r="AA37" s="11">
         <f>IF(OR(I37="",M37="",M37&lt;I37),"",M37-I37)</f>
@@ -7429,7 +7404,7 @@
       </c>
       <c r="AB37" s="7">
         <f>IF(OR(A37="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC37" s="8" t="str">
         <f>IF(OR(AB37="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB37,"低于上限","达到或超过上限"))</f>
@@ -7468,7 +7443,7 @@
         <v>0</v>
       </c>
       <c r="AR37" s="8" t="str">
-        <f ca="1">IF(A37="","",IF(OR(E37="",H37=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK37="",AL37&lt;&gt;""),AND(AK37&lt;&gt;"",AL37="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM37="",AN37&lt;&gt;""),AND(AM37&lt;&gt;"",AN37="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM37&lt;&gt;"",AN37&lt;&gt;""),OR(AK37="",AL37="")),"违规：必须先完成第二批",IF(OR(H37&lt;=0,H37&lt;&gt;INT(H37),MOD(H37,100)&lt;&gt;0,AND(AL37&lt;&gt;"",OR(AL37&lt;=0,AL37&lt;&gt;INT(AL37),MOD(AL37,100)&lt;&gt;0)),AND(AN37&lt;&gt;"",OR(AN37&lt;=0,AN37&lt;&gt;INT(AN37),MOD(AN37,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL37&lt;&gt;"",AN37&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ37&gt;C37*D37,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A37="","",IF(OR(E37="",H37=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK37="",AL37&lt;&gt;""),AND(AK37&lt;&gt;"",AL37="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM37="",AN37&lt;&gt;""),AND(AM37&lt;&gt;"",AN37="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM37&lt;&gt;"",AN37&lt;&gt;""),OR(AK37="",AL37="")),"违规：必须先完成第二批",IF(OR(H37&lt;=0,H37&lt;&gt;INT(H37),MOD(H37,100)&lt;&gt;0,AND(AL37&lt;&gt;"",OR(AL37&lt;=0,AL37&lt;&gt;INT(AL37),MOD(AL37,100)&lt;&gt;0)),AND(AN37&lt;&gt;"",OR(AN37&lt;=0,AN37&lt;&gt;INT(AN37),MOD(AN37,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL37&lt;&gt;"",AN37&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ37&gt;C37*D37,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -7513,7 +7488,7 @@
         <f>IF(A38="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A38)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>500</v>
       </c>
-      <c r="M38" s="18">
+      <c r="M38" s="17">
         <f>IF(A38="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A38)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44202</v>
       </c>
@@ -7537,7 +7512,7 @@
         <f>IF(OR(AO38="",N38="",AO38&lt;=0),"",(AO38-N38)/AO38)</f>
         <v>0.0273130495681269</v>
       </c>
-      <c r="W38" s="19">
+      <c r="W38" s="18">
         <f>IF(OR(U38="",V38="",V38&lt;=0),"",U38/V38)</f>
         <v>1.84900284900286</v>
       </c>
@@ -7551,7 +7526,7 @@
       </c>
       <c r="Z38" s="7">
         <f>IF(OR(AE38="",多次统计数据!$B$8=""),"",AE38-多次统计数据!$B$8)</f>
-        <v>0.0593750897258577</v>
+        <v>0.0599798917743165</v>
       </c>
       <c r="AA38" s="11">
         <f>IF(OR(I38="",M38="",M38&lt;I38),"",M38-I38)</f>
@@ -7559,7 +7534,7 @@
       </c>
       <c r="AB38" s="7">
         <f>IF(OR(A38="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC38" s="8" t="str">
         <f>IF(OR(AB38="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB38,"低于上限","达到或超过上限"))</f>
@@ -7598,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="AR38" s="8" t="str">
-        <f ca="1">IF(A38="","",IF(OR(E38="",H38=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK38="",AL38&lt;&gt;""),AND(AK38&lt;&gt;"",AL38="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM38="",AN38&lt;&gt;""),AND(AM38&lt;&gt;"",AN38="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM38&lt;&gt;"",AN38&lt;&gt;""),OR(AK38="",AL38="")),"违规：必须先完成第二批",IF(OR(H38&lt;=0,H38&lt;&gt;INT(H38),MOD(H38,100)&lt;&gt;0,AND(AL38&lt;&gt;"",OR(AL38&lt;=0,AL38&lt;&gt;INT(AL38),MOD(AL38,100)&lt;&gt;0)),AND(AN38&lt;&gt;"",OR(AN38&lt;=0,AN38&lt;&gt;INT(AN38),MOD(AN38,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL38&lt;&gt;"",AN38&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ38&gt;C38*D38,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A38="","",IF(OR(E38="",H38=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK38="",AL38&lt;&gt;""),AND(AK38&lt;&gt;"",AL38="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM38="",AN38&lt;&gt;""),AND(AM38&lt;&gt;"",AN38="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM38&lt;&gt;"",AN38&lt;&gt;""),OR(AK38="",AL38="")),"违规：必须先完成第二批",IF(OR(H38&lt;=0,H38&lt;&gt;INT(H38),MOD(H38,100)&lt;&gt;0,AND(AL38&lt;&gt;"",OR(AL38&lt;=0,AL38&lt;&gt;INT(AL38),MOD(AL38,100)&lt;&gt;0)),AND(AN38&lt;&gt;"",OR(AN38&lt;=0,AN38&lt;&gt;INT(AN38),MOD(AN38,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL38&lt;&gt;"",AN38&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ38&gt;C38*D38,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -7643,7 +7618,7 @@
         <f>IF(A39="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A39)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>500</v>
       </c>
-      <c r="M39" s="18">
+      <c r="M39" s="17">
         <f>IF(A39="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A39)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44959</v>
       </c>
@@ -7667,7 +7642,7 @@
         <f>IF(OR(AO39="",N39="",AO39&lt;=0),"",(AO39-N39)/AO39)</f>
         <v>0.0390775144138373</v>
       </c>
-      <c r="W39" s="19">
+      <c r="W39" s="18">
         <f>IF(OR(U39="",V39="",V39&lt;=0),"",U39/V39)</f>
         <v>1.2354694485842</v>
       </c>
@@ -7681,7 +7656,7 @@
       </c>
       <c r="Z39" s="7">
         <f>IF(OR(AE39="",多次统计数据!$B$8=""),"",AE39-多次统计数据!$B$8)</f>
-        <v>-0.0185771299121516</v>
+        <v>-0.0179723278636928</v>
       </c>
       <c r="AA39" s="11">
         <f>IF(OR(I39="",M39="",M39&lt;I39),"",M39-I39)</f>
@@ -7689,7 +7664,7 @@
       </c>
       <c r="AB39" s="7">
         <f>IF(OR(A39="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC39" s="8" t="str">
         <f>IF(OR(AB39="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB39,"低于上限","达到或超过上限"))</f>
@@ -7728,7 +7703,7 @@
         <v>0</v>
       </c>
       <c r="AR39" s="8" t="str">
-        <f ca="1">IF(A39="","",IF(OR(E39="",H39=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK39="",AL39&lt;&gt;""),AND(AK39&lt;&gt;"",AL39="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM39="",AN39&lt;&gt;""),AND(AM39&lt;&gt;"",AN39="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM39&lt;&gt;"",AN39&lt;&gt;""),OR(AK39="",AL39="")),"违规：必须先完成第二批",IF(OR(H39&lt;=0,H39&lt;&gt;INT(H39),MOD(H39,100)&lt;&gt;0,AND(AL39&lt;&gt;"",OR(AL39&lt;=0,AL39&lt;&gt;INT(AL39),MOD(AL39,100)&lt;&gt;0)),AND(AN39&lt;&gt;"",OR(AN39&lt;=0,AN39&lt;&gt;INT(AN39),MOD(AN39,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL39&lt;&gt;"",AN39&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ39&gt;C39*D39,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A39="","",IF(OR(E39="",H39=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK39="",AL39&lt;&gt;""),AND(AK39&lt;&gt;"",AL39="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM39="",AN39&lt;&gt;""),AND(AM39&lt;&gt;"",AN39="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM39&lt;&gt;"",AN39&lt;&gt;""),OR(AK39="",AL39="")),"违规：必须先完成第二批",IF(OR(H39&lt;=0,H39&lt;&gt;INT(H39),MOD(H39,100)&lt;&gt;0,AND(AL39&lt;&gt;"",OR(AL39&lt;=0,AL39&lt;&gt;INT(AL39),MOD(AL39,100)&lt;&gt;0)),AND(AN39&lt;&gt;"",OR(AN39&lt;=0,AN39&lt;&gt;INT(AN39),MOD(AN39,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL39&lt;&gt;"",AN39&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ39&gt;C39*D39,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -7773,7 +7748,7 @@
         <f>IF(A40="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A40)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>800</v>
       </c>
-      <c r="M40" s="18">
+      <c r="M40" s="17">
         <f>IF(A40="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A40)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45138</v>
       </c>
@@ -7797,7 +7772,7 @@
         <f>IF(OR(AO40="",N40="",AO40&lt;=0),"",(AO40-N40)/AO40)</f>
         <v>0.0300202590705383</v>
       </c>
-      <c r="W40" s="19">
+      <c r="W40" s="18">
         <f>IF(OR(U40="",V40="",V40&lt;=0),"",U40/V40)</f>
         <v>1.45398773006136</v>
       </c>
@@ -7811,7 +7786,7 @@
       </c>
       <c r="Z40" s="7">
         <f>IF(OR(AE40="",多次统计数据!$B$8=""),"",AE40-多次统计数据!$B$8)</f>
-        <v>-0.0628466106033291</v>
+        <v>-0.0622418085548703</v>
       </c>
       <c r="AA40" s="11">
         <f>IF(OR(I40="",M40="",M40&lt;I40),"",M40-I40)</f>
@@ -7819,7 +7794,7 @@
       </c>
       <c r="AB40" s="7">
         <f>IF(OR(A40="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC40" s="8" t="str">
         <f>IF(OR(AB40="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB40,"低于上限","达到或超过上限"))</f>
@@ -7858,11 +7833,11 @@
         <v>0</v>
       </c>
       <c r="AR40" s="8" t="str">
-        <f ca="1">IF(A40="","",IF(OR(E40="",H40=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK40="",AL40&lt;&gt;""),AND(AK40&lt;&gt;"",AL40="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM40="",AN40&lt;&gt;""),AND(AM40&lt;&gt;"",AN40="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM40&lt;&gt;"",AN40&lt;&gt;""),OR(AK40="",AL40="")),"违规：必须先完成第二批",IF(OR(H40&lt;=0,H40&lt;&gt;INT(H40),MOD(H40,100)&lt;&gt;0,AND(AL40&lt;&gt;"",OR(AL40&lt;=0,AL40&lt;&gt;INT(AL40),MOD(AL40,100)&lt;&gt;0)),AND(AN40&lt;&gt;"",OR(AN40&lt;=0,AN40&lt;&gt;INT(AN40),MOD(AN40,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL40&lt;&gt;"",AN40&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ40&gt;C40*D40,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A40="","",IF(OR(E40="",H40=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK40="",AL40&lt;&gt;""),AND(AK40&lt;&gt;"",AL40="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM40="",AN40&lt;&gt;""),AND(AM40&lt;&gt;"",AN40="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM40&lt;&gt;"",AN40&lt;&gt;""),OR(AK40="",AL40="")),"违规：必须先完成第二批",IF(OR(H40&lt;=0,H40&lt;&gt;INT(H40),MOD(H40,100)&lt;&gt;0,AND(AL40&lt;&gt;"",OR(AL40&lt;=0,AL40&lt;&gt;INT(AL40),MOD(AL40,100)&lt;&gt;0)),AND(AN40&lt;&gt;"",OR(AN40&lt;=0,AN40&lt;&gt;INT(AN40),MOD(AN40,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL40&lt;&gt;"",AN40&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ40&gt;C40*D40,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="41" ht="34" spans="1:44">
+    <row r="41" ht="17" spans="1:44">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -7903,7 +7878,7 @@
         <f>IF(A41="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A41)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>400</v>
       </c>
-      <c r="M41" s="18">
+      <c r="M41" s="17">
         <f>IF(A41="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A41)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45373</v>
       </c>
@@ -7927,7 +7902,7 @@
         <f>IF(OR(AO41="",N41="",AO41&lt;=0),"",(AO41-N41)/AO41)</f>
         <v>0.0670945592954699</v>
       </c>
-      <c r="W41" s="19">
+      <c r="W41" s="18">
         <f>IF(OR(U41="",V41="",V41&lt;=0),"",U41/V41)</f>
         <v>1.78086763070078</v>
       </c>
@@ -7941,7 +7916,7 @@
       </c>
       <c r="Z41" s="7">
         <f>IF(OR(AE41="",多次统计数据!$B$8=""),"",AE41-多次统计数据!$B$8)</f>
-        <v>-0.0652285435080569</v>
+        <v>-0.0646237414595981</v>
       </c>
       <c r="AA41" s="11">
         <f>IF(OR(I41="",M41="",M41&lt;I41),"",M41-I41)</f>
@@ -7949,7 +7924,7 @@
       </c>
       <c r="AB41" s="7">
         <f>IF(OR(A41="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC41" s="8" t="str">
         <f>IF(OR(AB41="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB41,"低于上限","达到或超过上限"))</f>
@@ -7984,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="AR41" s="8" t="str">
-        <f ca="1">IF(A41="","",IF(OR(E41="",H41=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK41="",AL41&lt;&gt;""),AND(AK41&lt;&gt;"",AL41="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM41="",AN41&lt;&gt;""),AND(AM41&lt;&gt;"",AN41="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM41&lt;&gt;"",AN41&lt;&gt;""),OR(AK41="",AL41="")),"违规：必须先完成第二批",IF(OR(H41&lt;=0,H41&lt;&gt;INT(H41),MOD(H41,100)&lt;&gt;0,AND(AL41&lt;&gt;"",OR(AL41&lt;=0,AL41&lt;&gt;INT(AL41),MOD(AL41,100)&lt;&gt;0)),AND(AN41&lt;&gt;"",OR(AN41&lt;=0,AN41&lt;&gt;INT(AN41),MOD(AN41,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL41&lt;&gt;"",AN41&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ41&gt;C41*D41,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A41="","",IF(OR(E41="",H41=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK41="",AL41&lt;&gt;""),AND(AK41&lt;&gt;"",AL41="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM41="",AN41&lt;&gt;""),AND(AM41&lt;&gt;"",AN41="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM41&lt;&gt;"",AN41&lt;&gt;""),OR(AK41="",AL41="")),"违规：必须先完成第二批",IF(OR(H41&lt;=0,H41&lt;&gt;INT(H41),MOD(H41,100)&lt;&gt;0,AND(AL41&lt;&gt;"",OR(AL41&lt;=0,AL41&lt;&gt;INT(AL41),MOD(AL41,100)&lt;&gt;0)),AND(AN41&lt;&gt;"",OR(AN41&lt;=0,AN41&lt;&gt;INT(AN41),MOD(AN41,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL41&lt;&gt;"",AN41&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ41&gt;C41*D41,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -8029,7 +8004,7 @@
         <f>IF(A42="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A42)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>42600</v>
       </c>
-      <c r="M42" s="18">
+      <c r="M42" s="17">
         <f>IF(A42="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A42)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41298</v>
       </c>
@@ -8053,7 +8028,7 @@
         <f>IF(OR(AO42="",N42="",AO42&lt;=0),"",(AO42-N42)/AO42)</f>
         <v>0.0571428571428572</v>
       </c>
-      <c r="W42" s="19">
+      <c r="W42" s="18">
         <f>IF(OR(U42="",V42="",V42&lt;=0),"",U42/V42)</f>
         <v>2.5</v>
       </c>
@@ -8067,7 +8042,7 @@
       </c>
       <c r="Z42" s="7">
         <f>IF(OR(AE42="",多次统计数据!$B$8=""),"",AE42-多次统计数据!$B$8)</f>
-        <v>-0.0865472467773415</v>
+        <v>-0.0859424447288828</v>
       </c>
       <c r="AA42" s="11" t="str">
         <f>IF(OR(I42="",M42="",M42&lt;I42),"",M42-I42)</f>
@@ -8075,7 +8050,7 @@
       </c>
       <c r="AB42" s="7">
         <f>IF(OR(A42="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC42" s="8" t="str">
         <f>IF(OR(AB42="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB42,"低于上限","达到或超过上限"))</f>
@@ -8110,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="AR42" s="8" t="str">
-        <f ca="1">IF(A42="","",IF(OR(E42="",H42=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK42="",AL42&lt;&gt;""),AND(AK42&lt;&gt;"",AL42="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM42="",AN42&lt;&gt;""),AND(AM42&lt;&gt;"",AN42="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM42&lt;&gt;"",AN42&lt;&gt;""),OR(AK42="",AL42="")),"违规：必须先完成第二批",IF(OR(H42&lt;=0,H42&lt;&gt;INT(H42),MOD(H42,100)&lt;&gt;0,AND(AL42&lt;&gt;"",OR(AL42&lt;=0,AL42&lt;&gt;INT(AL42),MOD(AL42,100)&lt;&gt;0)),AND(AN42&lt;&gt;"",OR(AN42&lt;=0,AN42&lt;&gt;INT(AN42),MOD(AN42,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL42&lt;&gt;"",AN42&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ42&gt;C42*D42,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A42="","",IF(OR(E42="",H42=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK42="",AL42&lt;&gt;""),AND(AK42&lt;&gt;"",AL42="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM42="",AN42&lt;&gt;""),AND(AM42&lt;&gt;"",AN42="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM42&lt;&gt;"",AN42&lt;&gt;""),OR(AK42="",AL42="")),"违规：必须先完成第二批",IF(OR(H42&lt;=0,H42&lt;&gt;INT(H42),MOD(H42,100)&lt;&gt;0,AND(AL42&lt;&gt;"",OR(AL42&lt;=0,AL42&lt;&gt;INT(AL42),MOD(AL42,100)&lt;&gt;0)),AND(AN42&lt;&gt;"",OR(AN42&lt;=0,AN42&lt;&gt;INT(AN42),MOD(AN42,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL42&lt;&gt;"",AN42&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ42&gt;C42*D42,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -8155,7 +8130,7 @@
         <f>IF(A43="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A43)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>42000</v>
       </c>
-      <c r="M43" s="18">
+      <c r="M43" s="17">
         <f>IF(A43="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A43)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41428</v>
       </c>
@@ -8179,7 +8154,7 @@
         <f>IF(OR(AO43="",N43="",AO43&lt;=0),"",(AO43-N43)/AO43)</f>
         <v>0.0555555555555556</v>
       </c>
-      <c r="W43" s="19">
+      <c r="W43" s="18">
         <f>IF(OR(U43="",V43="",V43&lt;=0),"",U43/V43)</f>
         <v>2</v>
       </c>
@@ -8193,7 +8168,7 @@
       </c>
       <c r="Z43" s="7">
         <f>IF(OR(AE43="",多次统计数据!$B$8=""),"",AE43-多次统计数据!$B$8)</f>
-        <v>-0.0545519691594028</v>
+        <v>-0.053947167110944</v>
       </c>
       <c r="AA43" s="11">
         <f>IF(OR(I43="",M43="",M43&lt;I43),"",M43-I43)</f>
@@ -8201,7 +8176,7 @@
       </c>
       <c r="AB43" s="7">
         <f>IF(OR(A43="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC43" s="8" t="str">
         <f>IF(OR(AB43="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB43,"低于上限","达到或超过上限"))</f>
@@ -8240,7 +8215,7 @@
         <v>0</v>
       </c>
       <c r="AR43" s="8" t="str">
-        <f ca="1">IF(A43="","",IF(OR(E43="",H43=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK43="",AL43&lt;&gt;""),AND(AK43&lt;&gt;"",AL43="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM43="",AN43&lt;&gt;""),AND(AM43&lt;&gt;"",AN43="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM43&lt;&gt;"",AN43&lt;&gt;""),OR(AK43="",AL43="")),"违规：必须先完成第二批",IF(OR(H43&lt;=0,H43&lt;&gt;INT(H43),MOD(H43,100)&lt;&gt;0,AND(AL43&lt;&gt;"",OR(AL43&lt;=0,AL43&lt;&gt;INT(AL43),MOD(AL43,100)&lt;&gt;0)),AND(AN43&lt;&gt;"",OR(AN43&lt;=0,AN43&lt;&gt;INT(AN43),MOD(AN43,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL43&lt;&gt;"",AN43&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ43&gt;C43*D43,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A43="","",IF(OR(E43="",H43=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK43="",AL43&lt;&gt;""),AND(AK43&lt;&gt;"",AL43="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM43="",AN43&lt;&gt;""),AND(AM43&lt;&gt;"",AN43="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM43&lt;&gt;"",AN43&lt;&gt;""),OR(AK43="",AL43="")),"违规：必须先完成第二批",IF(OR(H43&lt;=0,H43&lt;&gt;INT(H43),MOD(H43,100)&lt;&gt;0,AND(AL43&lt;&gt;"",OR(AL43&lt;=0,AL43&lt;&gt;INT(AL43),MOD(AL43,100)&lt;&gt;0)),AND(AN43&lt;&gt;"",OR(AN43&lt;=0,AN43&lt;&gt;INT(AN43),MOD(AN43,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL43&lt;&gt;"",AN43&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ43&gt;C43*D43,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -8285,7 +8260,7 @@
         <f>IF(A44="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A44)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>47500</v>
       </c>
-      <c r="M44" s="18">
+      <c r="M44" s="17">
         <f>IF(A44="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A44)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41696</v>
       </c>
@@ -8309,7 +8284,7 @@
         <f>IF(OR(AO44="",N44="",AO44&lt;=0),"",(AO44-N44)/AO44)</f>
         <v>0.0566037735849057</v>
       </c>
-      <c r="W44" s="19">
+      <c r="W44" s="18">
         <f>IF(OR(U44="",V44="",V44&lt;=0),"",U44/V44)</f>
         <v>2.33333333333333</v>
       </c>
@@ -8323,7 +8298,7 @@
       </c>
       <c r="Z44" s="7">
         <f>IF(OR(AE44="",多次统计数据!$B$8=""),"",AE44-多次统计数据!$B$8)</f>
-        <v>-0.032561535036833</v>
+        <v>-0.0319567329883742</v>
       </c>
       <c r="AA44" s="11">
         <f>IF(OR(I44="",M44="",M44&lt;I44),"",M44-I44)</f>
@@ -8331,7 +8306,7 @@
       </c>
       <c r="AB44" s="7">
         <f>IF(OR(A44="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC44" s="8" t="str">
         <f>IF(OR(AB44="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB44,"低于上限","达到或超过上限"))</f>
@@ -8370,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="AR44" s="8" t="str">
-        <f ca="1">IF(A44="","",IF(OR(E44="",H44=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK44="",AL44&lt;&gt;""),AND(AK44&lt;&gt;"",AL44="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM44="",AN44&lt;&gt;""),AND(AM44&lt;&gt;"",AN44="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM44&lt;&gt;"",AN44&lt;&gt;""),OR(AK44="",AL44="")),"违规：必须先完成第二批",IF(OR(H44&lt;=0,H44&lt;&gt;INT(H44),MOD(H44,100)&lt;&gt;0,AND(AL44&lt;&gt;"",OR(AL44&lt;=0,AL44&lt;&gt;INT(AL44),MOD(AL44,100)&lt;&gt;0)),AND(AN44&lt;&gt;"",OR(AN44&lt;=0,AN44&lt;&gt;INT(AN44),MOD(AN44,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL44&lt;&gt;"",AN44&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ44&gt;C44*D44,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A44="","",IF(OR(E44="",H44=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK44="",AL44&lt;&gt;""),AND(AK44&lt;&gt;"",AL44="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM44="",AN44&lt;&gt;""),AND(AM44&lt;&gt;"",AN44="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM44&lt;&gt;"",AN44&lt;&gt;""),OR(AK44="",AL44="")),"违规：必须先完成第二批",IF(OR(H44&lt;=0,H44&lt;&gt;INT(H44),MOD(H44,100)&lt;&gt;0,AND(AL44&lt;&gt;"",OR(AL44&lt;=0,AL44&lt;&gt;INT(AL44),MOD(AL44,100)&lt;&gt;0)),AND(AN44&lt;&gt;"",OR(AN44&lt;=0,AN44&lt;&gt;INT(AN44),MOD(AN44,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL44&lt;&gt;"",AN44&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ44&gt;C44*D44,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -8415,7 +8390,7 @@
         <f>IF(A45="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A45)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>60000</v>
       </c>
-      <c r="M45" s="18">
+      <c r="M45" s="17">
         <f>IF(A45="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A45)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41731</v>
       </c>
@@ -8439,7 +8414,7 @@
         <f>IF(OR(AO45="",N45="",AO45&lt;=0),"",(AO45-N45)/AO45)</f>
         <v>0.0178571428571429</v>
       </c>
-      <c r="W45" s="19">
+      <c r="W45" s="18">
         <f>IF(OR(U45="",V45="",V45&lt;=0),"",U45/V45)</f>
         <v>4</v>
       </c>
@@ -8453,7 +8428,7 @@
       </c>
       <c r="Z45" s="7">
         <f>IF(OR(AE45="",多次统计数据!$B$8=""),"",AE45-多次统计数据!$B$8)</f>
-        <v>-0.0914361517128373</v>
+        <v>-0.0908313496643785</v>
       </c>
       <c r="AA45" s="11">
         <f>IF(OR(I45="",M45="",M45&lt;I45),"",M45-I45)</f>
@@ -8461,7 +8436,7 @@
       </c>
       <c r="AB45" s="7">
         <f>IF(OR(A45="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC45" s="8" t="str">
         <f>IF(OR(AB45="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB45,"低于上限","达到或超过上限"))</f>
@@ -8496,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="AR45" s="8" t="str">
-        <f ca="1">IF(A45="","",IF(OR(E45="",H45=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK45="",AL45&lt;&gt;""),AND(AK45&lt;&gt;"",AL45="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM45="",AN45&lt;&gt;""),AND(AM45&lt;&gt;"",AN45="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM45&lt;&gt;"",AN45&lt;&gt;""),OR(AK45="",AL45="")),"违规：必须先完成第二批",IF(OR(H45&lt;=0,H45&lt;&gt;INT(H45),MOD(H45,100)&lt;&gt;0,AND(AL45&lt;&gt;"",OR(AL45&lt;=0,AL45&lt;&gt;INT(AL45),MOD(AL45,100)&lt;&gt;0)),AND(AN45&lt;&gt;"",OR(AN45&lt;=0,AN45&lt;&gt;INT(AN45),MOD(AN45,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL45&lt;&gt;"",AN45&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ45&gt;C45*D45,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A45="","",IF(OR(E45="",H45=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK45="",AL45&lt;&gt;""),AND(AK45&lt;&gt;"",AL45="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM45="",AN45&lt;&gt;""),AND(AM45&lt;&gt;"",AN45="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM45&lt;&gt;"",AN45&lt;&gt;""),OR(AK45="",AL45="")),"违规：必须先完成第二批",IF(OR(H45&lt;=0,H45&lt;&gt;INT(H45),MOD(H45,100)&lt;&gt;0,AND(AL45&lt;&gt;"",OR(AL45&lt;=0,AL45&lt;&gt;INT(AL45),MOD(AL45,100)&lt;&gt;0)),AND(AN45&lt;&gt;"",OR(AN45&lt;=0,AN45&lt;&gt;INT(AN45),MOD(AN45,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL45&lt;&gt;"",AN45&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ45&gt;C45*D45,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -8541,7 +8516,7 @@
         <f>IF(A46="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A46)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>87200</v>
       </c>
-      <c r="M46" s="18">
+      <c r="M46" s="17">
         <f>IF(A46="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A46)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41757</v>
       </c>
@@ -8565,7 +8540,7 @@
         <f>IF(OR(AO46="",N46="",AO46&lt;=0),"",(AO46-N46)/AO46)</f>
         <v>0.0303030303030302</v>
       </c>
-      <c r="W46" s="19">
+      <c r="W46" s="18">
         <f>IF(OR(U46="",V46="",V46&lt;=0),"",U46/V46)</f>
         <v>3.00000000000001</v>
       </c>
@@ -8579,7 +8554,7 @@
       </c>
       <c r="Z46" s="7">
         <f>IF(OR(AE46="",多次统计数据!$B$8=""),"",AE46-多次统计数据!$B$8)</f>
-        <v>-0.14848975513091</v>
+        <v>-0.147884953082451</v>
       </c>
       <c r="AA46" s="11">
         <f>IF(OR(I46="",M46="",M46&lt;I46),"",M46-I46)</f>
@@ -8587,7 +8562,7 @@
       </c>
       <c r="AB46" s="7">
         <f>IF(OR(A46="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC46" s="8" t="str">
         <f>IF(OR(AB46="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB46,"低于上限","达到或超过上限"))</f>
@@ -8627,7 +8602,7 @@
         <v>0</v>
       </c>
       <c r="AR46" s="8" t="str">
-        <f ca="1">IF(A46="","",IF(OR(E46="",H46=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK46="",AL46&lt;&gt;""),AND(AK46&lt;&gt;"",AL46="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM46="",AN46&lt;&gt;""),AND(AM46&lt;&gt;"",AN46="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM46&lt;&gt;"",AN46&lt;&gt;""),OR(AK46="",AL46="")),"违规：必须先完成第二批",IF(OR(H46&lt;=0,H46&lt;&gt;INT(H46),MOD(H46,100)&lt;&gt;0,AND(AL46&lt;&gt;"",OR(AL46&lt;=0,AL46&lt;&gt;INT(AL46),MOD(AL46,100)&lt;&gt;0)),AND(AN46&lt;&gt;"",OR(AN46&lt;=0,AN46&lt;&gt;INT(AN46),MOD(AN46,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL46&lt;&gt;"",AN46&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ46&gt;C46*D46,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A46="","",IF(OR(E46="",H46=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK46="",AL46&lt;&gt;""),AND(AK46&lt;&gt;"",AL46="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM46="",AN46&lt;&gt;""),AND(AM46&lt;&gt;"",AN46="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM46&lt;&gt;"",AN46&lt;&gt;""),OR(AK46="",AL46="")),"违规：必须先完成第二批",IF(OR(H46&lt;=0,H46&lt;&gt;INT(H46),MOD(H46,100)&lt;&gt;0,AND(AL46&lt;&gt;"",OR(AL46&lt;=0,AL46&lt;&gt;INT(AL46),MOD(AL46,100)&lt;&gt;0)),AND(AN46&lt;&gt;"",OR(AN46&lt;=0,AN46&lt;&gt;INT(AN46),MOD(AN46,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL46&lt;&gt;"",AN46&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ46&gt;C46*D46,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -8672,7 +8647,7 @@
         <f>IF(A47="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A47)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>100500</v>
       </c>
-      <c r="M47" s="18">
+      <c r="M47" s="17">
         <f>IF(A47="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A47)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41869</v>
       </c>
@@ -8696,7 +8671,7 @@
         <f>IF(OR(AO47="",N47="",AO47&lt;=0),"",(AO47-N47)/AO47)</f>
         <v>0.0243902439024389</v>
       </c>
-      <c r="W47" s="19">
+      <c r="W47" s="18">
         <f>IF(OR(U47="",V47="",V47&lt;=0),"",U47/V47)</f>
         <v>4.00000000000002</v>
       </c>
@@ -8710,7 +8685,7 @@
       </c>
       <c r="Z47" s="7">
         <f>IF(OR(AE47="",多次统计数据!$B$8=""),"",AE47-多次统计数据!$B$8)</f>
-        <v>-0.0425577286383608</v>
+        <v>-0.041952926589902</v>
       </c>
       <c r="AA47" s="11">
         <f>IF(OR(I47="",M47="",M47&lt;I47),"",M47-I47)</f>
@@ -8718,7 +8693,7 @@
       </c>
       <c r="AB47" s="7">
         <f>IF(OR(A47="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC47" s="8" t="str">
         <f>IF(OR(AB47="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB47,"低于上限","达到或超过上限"))</f>
@@ -8753,7 +8728,7 @@
         <v>0</v>
       </c>
       <c r="AR47" s="8" t="str">
-        <f ca="1">IF(A47="","",IF(OR(E47="",H47=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK47="",AL47&lt;&gt;""),AND(AK47&lt;&gt;"",AL47="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM47="",AN47&lt;&gt;""),AND(AM47&lt;&gt;"",AN47="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM47&lt;&gt;"",AN47&lt;&gt;""),OR(AK47="",AL47="")),"违规：必须先完成第二批",IF(OR(H47&lt;=0,H47&lt;&gt;INT(H47),MOD(H47,100)&lt;&gt;0,AND(AL47&lt;&gt;"",OR(AL47&lt;=0,AL47&lt;&gt;INT(AL47),MOD(AL47,100)&lt;&gt;0)),AND(AN47&lt;&gt;"",OR(AN47&lt;=0,AN47&lt;&gt;INT(AN47),MOD(AN47,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL47&lt;&gt;"",AN47&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ47&gt;C47*D47,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A47="","",IF(OR(E47="",H47=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK47="",AL47&lt;&gt;""),AND(AK47&lt;&gt;"",AL47="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM47="",AN47&lt;&gt;""),AND(AM47&lt;&gt;"",AN47="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM47&lt;&gt;"",AN47&lt;&gt;""),OR(AK47="",AL47="")),"违规：必须先完成第二批",IF(OR(H47&lt;=0,H47&lt;&gt;INT(H47),MOD(H47,100)&lt;&gt;0,AND(AL47&lt;&gt;"",OR(AL47&lt;=0,AL47&lt;&gt;INT(AL47),MOD(AL47,100)&lt;&gt;0)),AND(AN47&lt;&gt;"",OR(AN47&lt;=0,AN47&lt;&gt;INT(AN47),MOD(AN47,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL47&lt;&gt;"",AN47&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ47&gt;C47*D47,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -8798,7 +8773,7 @@
         <f>IF(A48="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A48)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>41500</v>
       </c>
-      <c r="M48" s="18">
+      <c r="M48" s="17">
         <f>IF(A48="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A48)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41982</v>
       </c>
@@ -8822,7 +8797,7 @@
         <f>IF(OR(AO48="",N48="",AO48&lt;=0),"",(AO48-N48)/AO48)</f>
         <v>0.0555555555555556</v>
       </c>
-      <c r="W48" s="19">
+      <c r="W48" s="18">
         <f>IF(OR(U48="",V48="",V48&lt;=0),"",U48/V48)</f>
         <v>2</v>
       </c>
@@ -8836,7 +8811,7 @@
       </c>
       <c r="Z48" s="7">
         <f>IF(OR(AE48="",多次统计数据!$B$8=""),"",AE48-多次统计数据!$B$8)</f>
-        <v>0.0433781855472386</v>
+        <v>0.0439829875956973</v>
       </c>
       <c r="AA48" s="11">
         <f>IF(OR(I48="",M48="",M48&lt;I48),"",M48-I48)</f>
@@ -8844,7 +8819,7 @@
       </c>
       <c r="AB48" s="7">
         <f>IF(OR(A48="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC48" s="8" t="str">
         <f>IF(OR(AB48="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB48,"低于上限","达到或超过上限"))</f>
@@ -8879,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="AR48" s="8" t="str">
-        <f ca="1">IF(A48="","",IF(OR(E48="",H48=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK48="",AL48&lt;&gt;""),AND(AK48&lt;&gt;"",AL48="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM48="",AN48&lt;&gt;""),AND(AM48&lt;&gt;"",AN48="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM48&lt;&gt;"",AN48&lt;&gt;""),OR(AK48="",AL48="")),"违规：必须先完成第二批",IF(OR(H48&lt;=0,H48&lt;&gt;INT(H48),MOD(H48,100)&lt;&gt;0,AND(AL48&lt;&gt;"",OR(AL48&lt;=0,AL48&lt;&gt;INT(AL48),MOD(AL48,100)&lt;&gt;0)),AND(AN48&lt;&gt;"",OR(AN48&lt;=0,AN48&lt;&gt;INT(AN48),MOD(AN48,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL48&lt;&gt;"",AN48&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ48&gt;C48*D48,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A48="","",IF(OR(E48="",H48=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK48="",AL48&lt;&gt;""),AND(AK48&lt;&gt;"",AL48="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM48="",AN48&lt;&gt;""),AND(AM48&lt;&gt;"",AN48="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM48&lt;&gt;"",AN48&lt;&gt;""),OR(AK48="",AL48="")),"违规：必须先完成第二批",IF(OR(H48&lt;=0,H48&lt;&gt;INT(H48),MOD(H48,100)&lt;&gt;0,AND(AL48&lt;&gt;"",OR(AL48&lt;=0,AL48&lt;&gt;INT(AL48),MOD(AL48,100)&lt;&gt;0)),AND(AN48&lt;&gt;"",OR(AN48&lt;=0,AN48&lt;&gt;INT(AN48),MOD(AN48,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL48&lt;&gt;"",AN48&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ48&gt;C48*D48,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -8924,7 +8899,7 @@
         <f>IF(A49="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A49)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>17100</v>
       </c>
-      <c r="M49" s="18">
+      <c r="M49" s="17">
         <f>IF(A49="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A49)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42016</v>
       </c>
@@ -8948,7 +8923,7 @@
         <f>IF(OR(AO49="",N49="",AO49&lt;=0),"",(AO49-N49)/AO49)</f>
         <v>0.105058365758755</v>
       </c>
-      <c r="W49" s="19">
+      <c r="W49" s="18">
         <f>IF(OR(U49="",V49="",V49&lt;=0),"",U49/V49)</f>
         <v>1.59259259259259</v>
       </c>
@@ -8962,7 +8937,7 @@
       </c>
       <c r="Z49" s="7">
         <f>IF(OR(AE49="",多次统计数据!$B$8=""),"",AE49-多次统计数据!$B$8)</f>
-        <v>-0.07328664704372</v>
+        <v>-0.0726818449952613</v>
       </c>
       <c r="AA49" s="11">
         <f>IF(OR(I49="",M49="",M49&lt;I49),"",M49-I49)</f>
@@ -8970,7 +8945,7 @@
       </c>
       <c r="AB49" s="7">
         <f>IF(OR(A49="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC49" s="8" t="str">
         <f>IF(OR(AB49="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB49,"低于上限","达到或超过上限"))</f>
@@ -9009,7 +8984,7 @@
         <v>0</v>
       </c>
       <c r="AR49" s="8" t="str">
-        <f ca="1">IF(A49="","",IF(OR(E49="",H49=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK49="",AL49&lt;&gt;""),AND(AK49&lt;&gt;"",AL49="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM49="",AN49&lt;&gt;""),AND(AM49&lt;&gt;"",AN49="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM49&lt;&gt;"",AN49&lt;&gt;""),OR(AK49="",AL49="")),"违规：必须先完成第二批",IF(OR(H49&lt;=0,H49&lt;&gt;INT(H49),MOD(H49,100)&lt;&gt;0,AND(AL49&lt;&gt;"",OR(AL49&lt;=0,AL49&lt;&gt;INT(AL49),MOD(AL49,100)&lt;&gt;0)),AND(AN49&lt;&gt;"",OR(AN49&lt;=0,AN49&lt;&gt;INT(AN49),MOD(AN49,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL49&lt;&gt;"",AN49&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ49&gt;C49*D49,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A49="","",IF(OR(E49="",H49=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK49="",AL49&lt;&gt;""),AND(AK49&lt;&gt;"",AL49="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM49="",AN49&lt;&gt;""),AND(AM49&lt;&gt;"",AN49="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM49&lt;&gt;"",AN49&lt;&gt;""),OR(AK49="",AL49="")),"违规：必须先完成第二批",IF(OR(H49&lt;=0,H49&lt;&gt;INT(H49),MOD(H49,100)&lt;&gt;0,AND(AL49&lt;&gt;"",OR(AL49&lt;=0,AL49&lt;&gt;INT(AL49),MOD(AL49,100)&lt;&gt;0)),AND(AN49&lt;&gt;"",OR(AN49&lt;=0,AN49&lt;&gt;INT(AN49),MOD(AN49,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL49&lt;&gt;"",AN49&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ49&gt;C49*D49,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -9054,7 +9029,7 @@
         <f>IF(A50="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A50)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>12800</v>
       </c>
-      <c r="M50" s="18">
+      <c r="M50" s="17">
         <f>IF(A50="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A50)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42131</v>
       </c>
@@ -9078,7 +9053,7 @@
         <f>IF(OR(AO50="",N50="",AO50&lt;=0),"",(AO50-N50)/AO50)</f>
         <v>0.0886699507389161</v>
       </c>
-      <c r="W50" s="19">
+      <c r="W50" s="18">
         <f>IF(OR(U50="",V50="",V50&lt;=0),"",U50/V50)</f>
         <v>1.22222222222223</v>
       </c>
@@ -9092,7 +9067,7 @@
       </c>
       <c r="Z50" s="7">
         <f>IF(OR(AE50="",多次统计数据!$B$8=""),"",AE50-多次统计数据!$B$8)</f>
-        <v>-0.0963209242494413</v>
+        <v>-0.0957161222009825</v>
       </c>
       <c r="AA50" s="11">
         <f>IF(OR(I50="",M50="",M50&lt;I50),"",M50-I50)</f>
@@ -9100,7 +9075,7 @@
       </c>
       <c r="AB50" s="7">
         <f>IF(OR(A50="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC50" s="8" t="str">
         <f>IF(OR(AB50="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB50,"低于上限","达到或超过上限"))</f>
@@ -9135,137 +9110,137 @@
         <v>0</v>
       </c>
       <c r="AR50" s="8" t="str">
-        <f ca="1">IF(A50="","",IF(OR(E50="",H50=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK50="",AL50&lt;&gt;""),AND(AK50&lt;&gt;"",AL50="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM50="",AN50&lt;&gt;""),AND(AM50&lt;&gt;"",AN50="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM50&lt;&gt;"",AN50&lt;&gt;""),OR(AK50="",AL50="")),"违规：必须先完成第二批",IF(OR(H50&lt;=0,H50&lt;&gt;INT(H50),MOD(H50,100)&lt;&gt;0,AND(AL50&lt;&gt;"",OR(AL50&lt;=0,AL50&lt;&gt;INT(AL50),MOD(AL50,100)&lt;&gt;0)),AND(AN50&lt;&gt;"",OR(AN50&lt;=0,AN50&lt;&gt;INT(AN50),MOD(AN50,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL50&lt;&gt;"",AN50&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ50&gt;C50*D50,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A50="","",IF(OR(E50="",H50=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK50="",AL50&lt;&gt;""),AND(AK50&lt;&gt;"",AL50="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM50="",AN50&lt;&gt;""),AND(AM50&lt;&gt;"",AN50="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM50&lt;&gt;"",AN50&lt;&gt;""),OR(AK50="",AL50="")),"违规：必须先完成第二批",IF(OR(H50&lt;=0,H50&lt;&gt;INT(H50),MOD(H50,100)&lt;&gt;0,AND(AL50&lt;&gt;"",OR(AL50&lt;=0,AL50&lt;&gt;INT(AL50),MOD(AL50,100)&lt;&gt;0)),AND(AN50&lt;&gt;"",OR(AN50&lt;=0,AN50&lt;&gt;INT(AN50),MOD(AN50,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL50&lt;&gt;"",AN50&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ50&gt;C50*D50,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="51" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A51" s="21">
+    <row r="51" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A51" s="20">
         <v>50</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="B51" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="23">
+      <c r="C51" s="21">
         <v>226026</v>
       </c>
-      <c r="D51" s="24">
+      <c r="D51" s="22">
         <v>0.02</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="21">
         <v>4.44</v>
       </c>
-      <c r="F51" s="25">
+      <c r="F51" s="23">
         <f>IF(OR(C51="",D51="",E51="",N51="",C51&lt;=0,D51&lt;=0,E51&lt;=N51),"",ROUNDDOWN((C51*D51)/(E51-N51)/100,0)*100)</f>
         <v>18800</v>
       </c>
-      <c r="G51" s="26" t="str">
+      <c r="G51" s="23" t="str">
         <f ca="1">IF(A51="","",IF(H51&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F51="",E51="",N51="",E51&lt;=N51,账户数据!$B$7=""),"",IF(OR(AG51="",AH51="",AI51=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A51,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F51*(E51-N51)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ51="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H51" s="21">
+      <c r="H51" s="20">
         <v>18800</v>
       </c>
-      <c r="I51" s="27">
+      <c r="I51" s="24">
         <v>42159</v>
       </c>
-      <c r="J51" s="23">
+      <c r="J51" s="21">
         <v>5</v>
       </c>
-      <c r="K51" s="28">
+      <c r="K51" s="25">
         <f>IF(A51="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A51)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>3.03</v>
       </c>
-      <c r="L51" s="25">
+      <c r="L51" s="23">
         <f>IF(A51="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A51)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>18800</v>
       </c>
-      <c r="M51" s="29">
+      <c r="M51" s="26">
         <f>IF(A51="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A51)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42221</v>
       </c>
-      <c r="N51" s="23">
+      <c r="N51" s="21">
         <v>4.2</v>
       </c>
-      <c r="O51" s="23"/>
-      <c r="P51" s="30" t="str">
+      <c r="O51" s="21"/>
+      <c r="P51" s="25" t="str">
         <f>IF(A51="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A51)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q51" s="21"/>
-      <c r="R51" s="21"/>
-      <c r="S51" s="21"/>
-      <c r="T51" s="21"/>
-      <c r="U51" s="31">
+      <c r="Q51" s="20"/>
+      <c r="R51" s="20"/>
+      <c r="S51" s="20"/>
+      <c r="T51" s="20"/>
+      <c r="U51" s="27">
         <f>IF(OR(AO51="",J51="",AO51&lt;=0),"",(J51-AO51)/AO51)</f>
         <v>0.126126126126126</v>
       </c>
-      <c r="V51" s="31">
+      <c r="V51" s="27">
         <f>IF(OR(AO51="",N51="",AO51&lt;=0),"",(AO51-N51)/AO51)</f>
         <v>0.0540540540540541</v>
       </c>
-      <c r="W51" s="32">
+      <c r="W51" s="28">
         <f>IF(OR(U51="",V51="",V51&lt;=0),"",U51/V51)</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="X51" s="28">
+      <c r="X51" s="25">
         <f>IF(OR(K51="",L51="",AP51=""),"",K51*L51-(E51*H51+IF(AND(AK51&lt;&gt;"",AL51&lt;&gt;""),AK51*AL51,0)+IF(AND(AM51&lt;&gt;"",AN51&lt;&gt;""),AM51*AN51,0))-IF(O51="",0,O51)-IF(P51="",0,P51))</f>
         <v>-26508</v>
       </c>
-      <c r="Y51" s="31">
+      <c r="Y51" s="27">
         <f>IF(OR(X51="",AP51=""),"",IF((E51*H51+IF(AND(AK51&lt;&gt;"",AL51&lt;&gt;""),AK51*AL51,0)+IF(AND(AM51&lt;&gt;"",AN51&lt;&gt;""),AM51*AN51,0))+IF(O51="",0,O51)&lt;=0,"",X51/((E51*H51+IF(AND(AK51&lt;&gt;"",AL51&lt;&gt;""),AK51*AL51,0)+IF(AND(AM51&lt;&gt;"",AN51&lt;&gt;""),AM51*AN51,0))+IF(O51="",0,O51))))</f>
         <v>-0.317567567567568</v>
       </c>
-      <c r="Z51" s="31">
+      <c r="Z51" s="27">
         <f>IF(OR(AE51="",多次统计数据!$B$8=""),"",AE51-多次统计数据!$B$8)</f>
-        <v>-0.18982717009941</v>
-      </c>
-      <c r="AA51" s="33">
+        <v>-0.189222368050951</v>
+      </c>
+      <c r="AA51" s="29">
         <f>IF(OR(I51="",M51="",M51&lt;I51),"",M51-I51)</f>
         <v>62</v>
       </c>
-      <c r="AB51" s="31">
+      <c r="AB51" s="27">
         <f>IF(OR(A51="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC51" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC51" s="23" t="str">
         <f>IF(OR(AB51="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB51,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD51" s="21"/>
-      <c r="AE51" s="31">
+      <c r="AD51" s="20"/>
+      <c r="AE51" s="27">
         <f>IF(OR(X51="",C51="",C51&lt;=0),"",X51/C51)</f>
         <v>-0.117278543176449</v>
       </c>
-      <c r="AG51" s="22" t="s">
+      <c r="AG51" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="AH51" s="22" t="s">
+      <c r="AH51" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="AI51" s="21"/>
-      <c r="AJ51" s="26" t="str">
+      <c r="AI51" s="20"/>
+      <c r="AJ51" s="23" t="str">
         <f>IF(OR(AG51="",AH51=""),"",IF(OR(AND(AG51="短期博反弹",OR(AH51="1～3个交易日",AH51="4～10个交易日")),AND(AG51="突破冲新高",OR(AH51="4～10个交易日",AH51="11～20个交易日")),AND(AG51="趋势波段",OR(AH51="11～20个交易日",AH51="21～60个交易日",AH51="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v>匹配</v>
       </c>
-      <c r="AK51" s="23"/>
-      <c r="AL51" s="34"/>
-      <c r="AM51" s="23"/>
-      <c r="AN51" s="34"/>
-      <c r="AO51" s="28">
+      <c r="AK51" s="21"/>
+      <c r="AL51" s="30"/>
+      <c r="AM51" s="21"/>
+      <c r="AN51" s="30"/>
+      <c r="AO51" s="25">
         <f>IF(OR(A51="",H51="",H51&lt;=0),"",(E51*H51+IF(AND(AK51&lt;&gt;"",AL51&lt;&gt;""),AK51*AL51,0)+IF(AND(AM51&lt;&gt;"",AN51&lt;&gt;""),AM51*AN51,0))/AP51)</f>
         <v>4.44</v>
       </c>
-      <c r="AP51" s="33">
+      <c r="AP51" s="29">
         <f>IF(OR(A51="",H51="",H51&lt;=0),"",H51+IF(AL51="",0,AL51)+IF(AN51="",0,AN51))</f>
         <v>18800</v>
       </c>
-      <c r="AQ51" s="28">
+      <c r="AQ51" s="25">
         <f>IF(A51="","",IF(M51&lt;&gt;"",0,IF(OR(H51="",N51=""),"",MAX(E51-MAX(N51,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A51))*持仓跟踪!$S$2:$S$157)),0)),0)*H51+IF(OR(AK51="",AL51=""),0,MAX(AK51-MAX(N51,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A51))*持仓跟踪!$S$2:$S$157)),0)),0)*AL51)+IF(OR(AM51="",AN51=""),0,MAX(AM51-MAX(N51,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A51))*持仓跟踪!$S$2:$S$157)),0)),0)*AN51))))</f>
         <v>0</v>
       </c>
-      <c r="AR51" s="26" t="str">
-        <f ca="1">IF(A51="","",IF(OR(E51="",H51=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK51="",AL51&lt;&gt;""),AND(AK51&lt;&gt;"",AL51="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM51="",AN51&lt;&gt;""),AND(AM51&lt;&gt;"",AN51="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM51&lt;&gt;"",AN51&lt;&gt;""),OR(AK51="",AL51="")),"违规：必须先完成第二批",IF(OR(H51&lt;=0,H51&lt;&gt;INT(H51),MOD(H51,100)&lt;&gt;0,AND(AL51&lt;&gt;"",OR(AL51&lt;=0,AL51&lt;&gt;INT(AL51),MOD(AL51,100)&lt;&gt;0)),AND(AN51&lt;&gt;"",OR(AN51&lt;=0,AN51&lt;&gt;INT(AN51),MOD(AN51,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL51&lt;&gt;"",AN51&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ51&gt;C51*D51,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR51" s="23" t="str">
+        <f ca="1">IF(A51="","",IF(OR(E51="",H51=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK51="",AL51&lt;&gt;""),AND(AK51&lt;&gt;"",AL51="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM51="",AN51&lt;&gt;""),AND(AM51&lt;&gt;"",AN51="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM51&lt;&gt;"",AN51&lt;&gt;""),OR(AK51="",AL51="")),"违规：必须先完成第二批",IF(OR(H51&lt;=0,H51&lt;&gt;INT(H51),MOD(H51,100)&lt;&gt;0,AND(AL51&lt;&gt;"",OR(AL51&lt;=0,AL51&lt;&gt;INT(AL51),MOD(AL51,100)&lt;&gt;0)),AND(AN51&lt;&gt;"",OR(AN51&lt;=0,AN51&lt;&gt;INT(AN51),MOD(AN51,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL51&lt;&gt;"",AN51&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ51&gt;C51*D51,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -9310,7 +9285,7 @@
         <f>IF(A52="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A52)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>44300</v>
       </c>
-      <c r="M52" s="18">
+      <c r="M52" s="17">
         <f>IF(A52="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A52)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42682</v>
       </c>
@@ -9334,7 +9309,7 @@
         <f>IF(OR(AO52="",N52="",AO52&lt;=0),"",(AO52-N52)/AO52)</f>
         <v>0.0476190476190475</v>
       </c>
-      <c r="W52" s="19">
+      <c r="W52" s="18">
         <f>IF(OR(U52="",V52="",V52&lt;=0),"",U52/V52)</f>
         <v>1.22222222222223</v>
       </c>
@@ -9348,7 +9323,7 @@
       </c>
       <c r="Z52" s="7">
         <f>IF(OR(AE52="",多次统计数据!$B$8=""),"",AE52-多次统计数据!$B$8)</f>
-        <v>-0.0414637122786683</v>
+        <v>-0.0408589102302095</v>
       </c>
       <c r="AA52" s="11">
         <f>IF(OR(I52="",M52="",M52&lt;I52),"",M52-I52)</f>
@@ -9356,7 +9331,7 @@
       </c>
       <c r="AB52" s="7">
         <f>IF(OR(A52="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC52" s="8" t="str">
         <f>IF(OR(AB52="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB52,"低于上限","达到或超过上限"))</f>
@@ -9391,7 +9366,7 @@
         <v>0</v>
       </c>
       <c r="AR52" s="8" t="str">
-        <f ca="1">IF(A52="","",IF(OR(E52="",H52=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK52="",AL52&lt;&gt;""),AND(AK52&lt;&gt;"",AL52="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM52="",AN52&lt;&gt;""),AND(AM52&lt;&gt;"",AN52="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM52&lt;&gt;"",AN52&lt;&gt;""),OR(AK52="",AL52="")),"违规：必须先完成第二批",IF(OR(H52&lt;=0,H52&lt;&gt;INT(H52),MOD(H52,100)&lt;&gt;0,AND(AL52&lt;&gt;"",OR(AL52&lt;=0,AL52&lt;&gt;INT(AL52),MOD(AL52,100)&lt;&gt;0)),AND(AN52&lt;&gt;"",OR(AN52&lt;=0,AN52&lt;&gt;INT(AN52),MOD(AN52,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL52&lt;&gt;"",AN52&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ52&gt;C52*D52,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A52="","",IF(OR(E52="",H52=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK52="",AL52&lt;&gt;""),AND(AK52&lt;&gt;"",AL52="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM52="",AN52&lt;&gt;""),AND(AM52&lt;&gt;"",AN52="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM52&lt;&gt;"",AN52&lt;&gt;""),OR(AK52="",AL52="")),"违规：必须先完成第二批",IF(OR(H52&lt;=0,H52&lt;&gt;INT(H52),MOD(H52,100)&lt;&gt;0,AND(AL52&lt;&gt;"",OR(AL52&lt;=0,AL52&lt;&gt;INT(AL52),MOD(AL52,100)&lt;&gt;0)),AND(AN52&lt;&gt;"",OR(AN52&lt;=0,AN52&lt;&gt;INT(AN52),MOD(AN52,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL52&lt;&gt;"",AN52&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ52&gt;C52*D52,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -9436,7 +9411,7 @@
         <f>IF(A53="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A53)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>34200</v>
       </c>
-      <c r="M53" s="18">
+      <c r="M53" s="17">
         <f>IF(A53="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A53)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42769</v>
       </c>
@@ -9460,7 +9435,7 @@
         <f>IF(OR(AO53="",N53="",AO53&lt;=0),"",(AO53-N53)/AO53)</f>
         <v>0.0476190476190477</v>
       </c>
-      <c r="W53" s="19">
+      <c r="W53" s="18">
         <f>IF(OR(U53="",V53="",V53&lt;=0),"",U53/V53)</f>
         <v>0.666666666666667</v>
       </c>
@@ -9474,7 +9449,7 @@
       </c>
       <c r="Z53" s="7">
         <f>IF(OR(AE53="",多次统计数据!$B$8=""),"",AE53-多次统计数据!$B$8)</f>
-        <v>-0.0625739039985977</v>
+        <v>-0.061969101950139</v>
       </c>
       <c r="AA53" s="11" t="e">
         <f>IF(OR(#REF!="",M53="",M53&lt;#REF!),"",M53-#REF!)</f>
@@ -9482,7 +9457,7 @@
       </c>
       <c r="AB53" s="7">
         <f>IF(OR(A53="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC53" s="8" t="str">
         <f>IF(OR(AB53="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB53,"低于上限","达到或超过上限"))</f>
@@ -9517,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="AR53" s="8" t="str">
-        <f ca="1">IF(A53="","",IF(OR(E53="",H53=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK53="",AL53&lt;&gt;""),AND(AK53&lt;&gt;"",AL53="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM53="",AN53&lt;&gt;""),AND(AM53&lt;&gt;"",AN53="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM53&lt;&gt;"",AN53&lt;&gt;""),OR(AK53="",AL53="")),"违规：必须先完成第二批",IF(OR(H53&lt;=0,H53&lt;&gt;INT(H53),MOD(H53,100)&lt;&gt;0,AND(AL53&lt;&gt;"",OR(AL53&lt;=0,AL53&lt;&gt;INT(AL53),MOD(AL53,100)&lt;&gt;0)),AND(AN53&lt;&gt;"",OR(AN53&lt;=0,AN53&lt;&gt;INT(AN53),MOD(AN53,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL53&lt;&gt;"",AN53&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ53&gt;C53*D53,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A53="","",IF(OR(E53="",H53=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK53="",AL53&lt;&gt;""),AND(AK53&lt;&gt;"",AL53="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM53="",AN53&lt;&gt;""),AND(AM53&lt;&gt;"",AN53="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM53&lt;&gt;"",AN53&lt;&gt;""),OR(AK53="",AL53="")),"违规：必须先完成第二批",IF(OR(H53&lt;=0,H53&lt;&gt;INT(H53),MOD(H53,100)&lt;&gt;0,AND(AL53&lt;&gt;"",OR(AL53&lt;=0,AL53&lt;&gt;INT(AL53),MOD(AL53,100)&lt;&gt;0)),AND(AN53&lt;&gt;"",OR(AN53&lt;=0,AN53&lt;&gt;INT(AN53),MOD(AN53,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL53&lt;&gt;"",AN53&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ53&gt;C53*D53,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -9562,7 +9537,7 @@
         <f>IF(A54="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A54)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>41500</v>
       </c>
-      <c r="M54" s="18">
+      <c r="M54" s="17">
         <f>IF(A54="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A54)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42810</v>
       </c>
@@ -9586,7 +9561,7 @@
         <f>IF(OR(AO54="",N54="",AO54&lt;=0),"",(AO54-N54)/AO54)</f>
         <v>0.0370370370370371</v>
       </c>
-      <c r="W54" s="19">
+      <c r="W54" s="18">
         <f>IF(OR(U54="",V54="",V54&lt;=0),"",U54/V54)</f>
         <v>2.99999999999999</v>
       </c>
@@ -9600,7 +9575,7 @@
       </c>
       <c r="Z54" s="7">
         <f>IF(OR(AE54="",多次统计数据!$B$8=""),"",AE54-多次统计数据!$B$8)</f>
-        <v>-0.0945198261220832</v>
+        <v>-0.0939150240736244</v>
       </c>
       <c r="AA54" s="11">
         <f>IF(OR(I54="",M54="",M54&lt;I54),"",M54-I54)</f>
@@ -9608,7 +9583,7 @@
       </c>
       <c r="AB54" s="7">
         <f>IF(OR(A54="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC54" s="8" t="str">
         <f>IF(OR(AB54="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB54,"低于上限","达到或超过上限"))</f>
@@ -9643,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="AR54" s="8" t="str">
-        <f ca="1">IF(A54="","",IF(OR(E54="",H54=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK54="",AL54&lt;&gt;""),AND(AK54&lt;&gt;"",AL54="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM54="",AN54&lt;&gt;""),AND(AM54&lt;&gt;"",AN54="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM54&lt;&gt;"",AN54&lt;&gt;""),OR(AK54="",AL54="")),"违规：必须先完成第二批",IF(OR(H54&lt;=0,H54&lt;&gt;INT(H54),MOD(H54,100)&lt;&gt;0,AND(AL54&lt;&gt;"",OR(AL54&lt;=0,AL54&lt;&gt;INT(AL54),MOD(AL54,100)&lt;&gt;0)),AND(AN54&lt;&gt;"",OR(AN54&lt;=0,AN54&lt;&gt;INT(AN54),MOD(AN54,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL54&lt;&gt;"",AN54&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ54&gt;C54*D54,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A54="","",IF(OR(E54="",H54=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK54="",AL54&lt;&gt;""),AND(AK54&lt;&gt;"",AL54="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM54="",AN54&lt;&gt;""),AND(AM54&lt;&gt;"",AN54="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM54&lt;&gt;"",AN54&lt;&gt;""),OR(AK54="",AL54="")),"违规：必须先完成第二批",IF(OR(H54&lt;=0,H54&lt;&gt;INT(H54),MOD(H54,100)&lt;&gt;0,AND(AL54&lt;&gt;"",OR(AL54&lt;=0,AL54&lt;&gt;INT(AL54),MOD(AL54,100)&lt;&gt;0)),AND(AN54&lt;&gt;"",OR(AN54&lt;=0,AN54&lt;&gt;INT(AN54),MOD(AN54,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL54&lt;&gt;"",AN54&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ54&gt;C54*D54,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -9688,7 +9663,7 @@
         <f>IF(A55="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A55)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>25400</v>
       </c>
-      <c r="M55" s="18">
+      <c r="M55" s="17">
         <f>IF(A55="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A55)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42866</v>
       </c>
@@ -9712,7 +9687,7 @@
         <f>IF(OR(AO55="",N55="",AO55&lt;=0),"",(AO55-N55)/AO55)</f>
         <v>0.0506329113924051</v>
       </c>
-      <c r="W55" s="19">
+      <c r="W55" s="18">
         <f>IF(OR(U55="",V55="",V55&lt;=0),"",U55/V55)</f>
         <v>2.125</v>
       </c>
@@ -9726,7 +9701,7 @@
       </c>
       <c r="Z55" s="7">
         <f>IF(OR(AE55="",多次统计数据!$B$8=""),"",AE55-多次统计数据!$B$8)</f>
-        <v>-0.0737985838634207</v>
+        <v>-0.0731937818149619</v>
       </c>
       <c r="AA55" s="11">
         <f>IF(OR(I53="",M55="",M55&lt;I53),"",M55-I53)</f>
@@ -9734,7 +9709,7 @@
       </c>
       <c r="AB55" s="7">
         <f>IF(OR(A55="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC55" s="8" t="str">
         <f>IF(OR(AB55="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB55,"低于上限","达到或超过上限"))</f>
@@ -9769,133 +9744,133 @@
         <v>0</v>
       </c>
       <c r="AR55" s="8" t="str">
-        <f ca="1">IF(A55="","",IF(OR(E55="",H55=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK55="",AL55&lt;&gt;""),AND(AK55&lt;&gt;"",AL55="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM55="",AN55&lt;&gt;""),AND(AM55&lt;&gt;"",AN55="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM55&lt;&gt;"",AN55&lt;&gt;""),OR(AK55="",AL55="")),"违规：必须先完成第二批",IF(OR(H55&lt;=0,H55&lt;&gt;INT(H55),MOD(H55,100)&lt;&gt;0,AND(AL55&lt;&gt;"",OR(AL55&lt;=0,AL55&lt;&gt;INT(AL55),MOD(AL55,100)&lt;&gt;0)),AND(AN55&lt;&gt;"",OR(AN55&lt;=0,AN55&lt;&gt;INT(AN55),MOD(AN55,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL55&lt;&gt;"",AN55&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ55&gt;C55*D55,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A55="","",IF(OR(E55="",H55=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK55="",AL55&lt;&gt;""),AND(AK55&lt;&gt;"",AL55="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM55="",AN55&lt;&gt;""),AND(AM55&lt;&gt;"",AN55="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM55&lt;&gt;"",AN55&lt;&gt;""),OR(AK55="",AL55="")),"违规：必须先完成第二批",IF(OR(H55&lt;=0,H55&lt;&gt;INT(H55),MOD(H55,100)&lt;&gt;0,AND(AL55&lt;&gt;"",OR(AL55&lt;=0,AL55&lt;&gt;INT(AL55),MOD(AL55,100)&lt;&gt;0)),AND(AN55&lt;&gt;"",OR(AN55&lt;=0,AN55&lt;&gt;INT(AN55),MOD(AN55,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL55&lt;&gt;"",AN55&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ55&gt;C55*D55,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="56" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A56" s="21">
+    <row r="56" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A56" s="20">
         <v>55</v>
       </c>
-      <c r="B56" s="22" t="s">
+      <c r="B56" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C56" s="23">
+      <c r="C56" s="21">
         <v>202953</v>
       </c>
-      <c r="D56" s="24">
+      <c r="D56" s="22">
         <v>0.02</v>
       </c>
-      <c r="E56" s="23">
+      <c r="E56" s="21">
         <v>3.54</v>
       </c>
-      <c r="F56" s="25">
+      <c r="F56" s="23">
         <f>IF(OR(C56="",D56="",E56="",N56="",C56&lt;=0,D56&lt;=0,E56&lt;=N56),"",ROUNDDOWN((C56*D56)/(E56-N56)/100,0)*100)</f>
         <v>28900</v>
       </c>
-      <c r="G56" s="26" t="str">
+      <c r="G56" s="23" t="str">
         <f ca="1">IF(A56="","",IF(H56&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F56="",E56="",N56="",E56&lt;=N56,账户数据!$B$7=""),"",IF(OR(AG56="",AH56="",AI56=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A56,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F56*(E56-N56)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ56="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H56" s="21">
+      <c r="H56" s="20">
         <v>28900</v>
       </c>
-      <c r="I56" s="27">
+      <c r="I56" s="24">
         <v>42871</v>
       </c>
-      <c r="J56" s="23">
+      <c r="J56" s="21">
         <v>4</v>
       </c>
-      <c r="K56" s="30">
+      <c r="K56" s="25">
         <f>IF(A56="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A56)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>5.52</v>
       </c>
-      <c r="L56" s="26">
+      <c r="L56" s="23">
         <f>IF(A56="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A56)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>28900</v>
       </c>
-      <c r="M56" s="35">
+      <c r="M56" s="26">
         <f>IF(A56="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A56)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43053</v>
       </c>
-      <c r="N56" s="23">
+      <c r="N56" s="21">
         <v>3.4</v>
       </c>
-      <c r="O56" s="23"/>
-      <c r="P56" s="30" t="str">
+      <c r="O56" s="21"/>
+      <c r="P56" s="25" t="str">
         <f>IF(A56="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A56)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q56" s="21"/>
-      <c r="R56" s="21"/>
-      <c r="S56" s="21"/>
-      <c r="T56" s="21"/>
-      <c r="U56" s="31">
+      <c r="Q56" s="20"/>
+      <c r="R56" s="20"/>
+      <c r="S56" s="20"/>
+      <c r="T56" s="20"/>
+      <c r="U56" s="27">
         <f>IF(OR(AO56="",J56="",AO56&lt;=0),"",(J56-AO56)/AO56)</f>
         <v>0.129943502824859</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="27">
         <f>IF(OR(AO56="",N56="",AO56&lt;=0),"",(AO56-N56)/AO56)</f>
         <v>0.0395480225988701</v>
       </c>
-      <c r="W56" s="32">
+      <c r="W56" s="28">
         <f>IF(OR(U56="",V56="",V56&lt;=0),"",U56/V56)</f>
         <v>3.28571428571428</v>
       </c>
-      <c r="X56" s="30">
+      <c r="X56" s="25">
         <f>IF(OR(K56="",L56="",AP56=""),"",K56*L56-(E56*H56+IF(AND(AK56&lt;&gt;"",AL56&lt;&gt;""),AK56*AL56,0)+IF(AND(AM56&lt;&gt;"",AN56&lt;&gt;""),AM56*AN56,0))-IF(O56="",0,O56)-IF(P56="",0,P56))</f>
         <v>57222</v>
       </c>
-      <c r="Y56" s="36">
+      <c r="Y56" s="27">
         <f>IF(OR(X56="",AP56=""),"",IF((E56*H56+IF(AND(AK56&lt;&gt;"",AL56&lt;&gt;""),AK56*AL56,0)+IF(AND(AM56&lt;&gt;"",AN56&lt;&gt;""),AM56*AN56,0))+IF(O56="",0,O56)&lt;=0,"",X56/((E56*H56+IF(AND(AK56&lt;&gt;"",AL56&lt;&gt;""),AK56*AL56,0)+IF(AND(AM56&lt;&gt;"",AN56&lt;&gt;""),AM56*AN56,0))+IF(O56="",0,O56))))</f>
         <v>0.559322033898305</v>
       </c>
-      <c r="Z56" s="36">
+      <c r="Z56" s="27">
         <f>IF(OR(AE56="",多次统计数据!$B$8=""),"",AE56-多次统计数据!$B$8)</f>
-        <v>0.209398424857501</v>
-      </c>
-      <c r="AA56" s="37">
+        <v>0.210003226905959</v>
+      </c>
+      <c r="AA56" s="29">
         <f>IF(OR(I56="",M56="",M56&lt;I56),"",M56-I56)</f>
         <v>182</v>
       </c>
-      <c r="AB56" s="31">
+      <c r="AB56" s="27">
         <f>IF(OR(A56="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC56" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC56" s="23" t="str">
         <f>IF(OR(AB56="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB56,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD56" s="21"/>
-      <c r="AE56" s="36">
+      <c r="AD56" s="20"/>
+      <c r="AE56" s="27">
         <f>IF(OR(X56="",C56="",C56&lt;=0),"",X56/C56)</f>
         <v>0.281947051780461</v>
       </c>
-      <c r="AG56" s="21"/>
-      <c r="AH56" s="21"/>
-      <c r="AI56" s="21"/>
-      <c r="AJ56" s="26" t="str">
+      <c r="AG56" s="20"/>
+      <c r="AH56" s="20"/>
+      <c r="AI56" s="20"/>
+      <c r="AJ56" s="23" t="str">
         <f>IF(OR(AG56="",AH56=""),"",IF(OR(AND(AG56="短期博反弹",OR(AH56="1～3个交易日",AH56="4～10个交易日")),AND(AG56="突破冲新高",OR(AH56="4～10个交易日",AH56="11～20个交易日")),AND(AG56="趋势波段",OR(AH56="11～20个交易日",AH56="21～60个交易日",AH56="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK56" s="23"/>
-      <c r="AL56" s="34"/>
-      <c r="AM56" s="23"/>
-      <c r="AN56" s="34"/>
-      <c r="AO56" s="28">
+      <c r="AK56" s="21"/>
+      <c r="AL56" s="30"/>
+      <c r="AM56" s="21"/>
+      <c r="AN56" s="30"/>
+      <c r="AO56" s="25">
         <f>IF(OR(A56="",H56="",H56&lt;=0),"",(E56*H56+IF(AND(AK56&lt;&gt;"",AL56&lt;&gt;""),AK56*AL56,0)+IF(AND(AM56&lt;&gt;"",AN56&lt;&gt;""),AM56*AN56,0))/AP56)</f>
         <v>3.54</v>
       </c>
-      <c r="AP56" s="33">
+      <c r="AP56" s="29">
         <f>IF(OR(A56="",H56="",H56&lt;=0),"",H56+IF(AL56="",0,AL56)+IF(AN56="",0,AN56))</f>
         <v>28900</v>
       </c>
-      <c r="AQ56" s="28">
+      <c r="AQ56" s="25">
         <f>IF(A56="","",IF(M56&lt;&gt;"",0,IF(OR(H56="",N56=""),"",MAX(E56-MAX(N56,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A56))*持仓跟踪!$S$2:$S$157)),0)),0)*H56+IF(OR(AK56="",AL56=""),0,MAX(AK56-MAX(N56,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A56))*持仓跟踪!$S$2:$S$157)),0)),0)*AL56)+IF(OR(AM56="",AN56=""),0,MAX(AM56-MAX(N56,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A56))*持仓跟踪!$S$2:$S$157)),0)),0)*AN56))))</f>
         <v>0</v>
       </c>
-      <c r="AR56" s="26" t="str">
-        <f ca="1">IF(A56="","",IF(OR(E56="",H56=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK56="",AL56&lt;&gt;""),AND(AK56&lt;&gt;"",AL56="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM56="",AN56&lt;&gt;""),AND(AM56&lt;&gt;"",AN56="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM56&lt;&gt;"",AN56&lt;&gt;""),OR(AK56="",AL56="")),"违规：必须先完成第二批",IF(OR(H56&lt;=0,H56&lt;&gt;INT(H56),MOD(H56,100)&lt;&gt;0,AND(AL56&lt;&gt;"",OR(AL56&lt;=0,AL56&lt;&gt;INT(AL56),MOD(AL56,100)&lt;&gt;0)),AND(AN56&lt;&gt;"",OR(AN56&lt;=0,AN56&lt;&gt;INT(AN56),MOD(AN56,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL56&lt;&gt;"",AN56&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ56&gt;C56*D56,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR56" s="23" t="str">
+        <f ca="1">IF(A56="","",IF(OR(E56="",H56=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK56="",AL56&lt;&gt;""),AND(AK56&lt;&gt;"",AL56="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM56="",AN56&lt;&gt;""),AND(AM56&lt;&gt;"",AN56="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM56&lt;&gt;"",AN56&lt;&gt;""),OR(AK56="",AL56="")),"违规：必须先完成第二批",IF(OR(H56&lt;=0,H56&lt;&gt;INT(H56),MOD(H56,100)&lt;&gt;0,AND(AL56&lt;&gt;"",OR(AL56&lt;=0,AL56&lt;&gt;INT(AL56),MOD(AL56,100)&lt;&gt;0)),AND(AN56&lt;&gt;"",OR(AN56&lt;=0,AN56&lt;&gt;INT(AN56),MOD(AN56,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL56&lt;&gt;"",AN56&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ56&gt;C56*D56,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -9940,7 +9915,7 @@
         <f>IF(A57="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A57)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>27300</v>
       </c>
-      <c r="M57" s="18">
+      <c r="M57" s="17">
         <f>IF(A57="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A57)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43118</v>
       </c>
@@ -9964,7 +9939,7 @@
         <f>IF(OR(AO57="",N57="",AO57&lt;=0),"",(AO57-N57)/AO57)</f>
         <v>0.0194346289752651</v>
       </c>
-      <c r="W57" s="19">
+      <c r="W57" s="18">
         <f>IF(OR(U57="",V57="",V57&lt;=0),"",U57/V57)</f>
         <v>3.09090909090908</v>
       </c>
@@ -9978,7 +9953,7 @@
       </c>
       <c r="Z57" s="7">
         <f>IF(OR(AE57="",多次统计数据!$B$8=""),"",AE57-多次统计数据!$B$8)</f>
-        <v>-0.0631049832216061</v>
+        <v>-0.0625001811731473</v>
       </c>
       <c r="AA57" s="11">
         <f>IF(OR(I57="",M57="",M57&lt;I57),"",M57-I57)</f>
@@ -9986,7 +9961,7 @@
       </c>
       <c r="AB57" s="7">
         <f>IF(OR(A57="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC57" s="8" t="str">
         <f>IF(OR(AB57="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB57,"低于上限","达到或超过上限"))</f>
@@ -10025,135 +10000,135 @@
         <v>0</v>
       </c>
       <c r="AR57" s="8" t="str">
-        <f ca="1">IF(A57="","",IF(OR(E57="",H57=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK57="",AL57&lt;&gt;""),AND(AK57&lt;&gt;"",AL57="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM57="",AN57&lt;&gt;""),AND(AM57&lt;&gt;"",AN57="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM57&lt;&gt;"",AN57&lt;&gt;""),OR(AK57="",AL57="")),"违规：必须先完成第二批",IF(OR(H57&lt;=0,H57&lt;&gt;INT(H57),MOD(H57,100)&lt;&gt;0,AND(AL57&lt;&gt;"",OR(AL57&lt;=0,AL57&lt;&gt;INT(AL57),MOD(AL57,100)&lt;&gt;0)),AND(AN57&lt;&gt;"",OR(AN57&lt;=0,AN57&lt;&gt;INT(AN57),MOD(AN57,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL57&lt;&gt;"",AN57&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ57&gt;C57*D57,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A57="","",IF(OR(E57="",H57=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK57="",AL57&lt;&gt;""),AND(AK57&lt;&gt;"",AL57="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM57="",AN57&lt;&gt;""),AND(AM57&lt;&gt;"",AN57="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM57&lt;&gt;"",AN57&lt;&gt;""),OR(AK57="",AL57="")),"违规：必须先完成第二批",IF(OR(H57&lt;=0,H57&lt;&gt;INT(H57),MOD(H57,100)&lt;&gt;0,AND(AL57&lt;&gt;"",OR(AL57&lt;=0,AL57&lt;&gt;INT(AL57),MOD(AL57,100)&lt;&gt;0)),AND(AN57&lt;&gt;"",OR(AN57&lt;=0,AN57&lt;&gt;INT(AN57),MOD(AN57,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL57&lt;&gt;"",AN57&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ57&gt;C57*D57,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="58" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A58" s="21">
+    <row r="58" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A58" s="20">
         <v>57</v>
       </c>
-      <c r="B58" s="22" t="s">
+      <c r="B58" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C58" s="23">
+      <c r="C58" s="21">
         <v>262632</v>
       </c>
-      <c r="D58" s="24">
+      <c r="D58" s="22">
         <v>0.02</v>
       </c>
-      <c r="E58" s="23">
+      <c r="E58" s="21">
         <v>3.31</v>
       </c>
-      <c r="F58" s="25">
+      <c r="F58" s="23">
         <f>IF(OR(C58="",D58="",E58="",N58="",C58&lt;=0,D58&lt;=0,E58&lt;=N58),"",ROUNDDOWN((C58*D58)/(E58-N58)/100,0)*100)</f>
         <v>25000</v>
       </c>
-      <c r="G58" s="26" t="str">
+      <c r="G58" s="23" t="str">
         <f ca="1">IF(A58="","",IF(H58&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F58="",E58="",N58="",E58&lt;=N58,账户数据!$B$7=""),"",IF(OR(AG58="",AH58="",AI58=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A58,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F58*(E58-N58)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ58="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H58" s="21">
+      <c r="H58" s="20">
         <v>25000</v>
       </c>
-      <c r="I58" s="27">
+      <c r="I58" s="24">
         <v>43542</v>
       </c>
-      <c r="J58" s="23">
+      <c r="J58" s="21">
         <v>3.8</v>
       </c>
-      <c r="K58" s="30">
+      <c r="K58" s="25">
         <f>IF(A58="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A58)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>3.01</v>
       </c>
-      <c r="L58" s="26">
+      <c r="L58" s="23">
         <f>IF(A58="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A58)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>25000</v>
       </c>
-      <c r="M58" s="35">
+      <c r="M58" s="26">
         <f>IF(A58="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A58)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43558</v>
       </c>
-      <c r="N58" s="23">
+      <c r="N58" s="21">
         <v>3.1</v>
       </c>
-      <c r="O58" s="23"/>
-      <c r="P58" s="30" t="str">
+      <c r="O58" s="21"/>
+      <c r="P58" s="25" t="str">
         <f>IF(A58="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A58)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q58" s="21"/>
-      <c r="R58" s="21"/>
-      <c r="S58" s="21"/>
-      <c r="T58" s="21"/>
-      <c r="U58" s="31">
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20"/>
+      <c r="S58" s="20"/>
+      <c r="T58" s="20"/>
+      <c r="U58" s="27">
         <f>IF(OR(AO58="",J58="",AO58&lt;=0),"",(J58-AO58)/AO58)</f>
         <v>0.148036253776435</v>
       </c>
-      <c r="V58" s="31">
+      <c r="V58" s="27">
         <f>IF(OR(AO58="",N58="",AO58&lt;=0),"",(AO58-N58)/AO58)</f>
         <v>0.0634441087613293</v>
       </c>
-      <c r="W58" s="32">
+      <c r="W58" s="28">
         <f>IF(OR(U58="",V58="",V58&lt;=0),"",U58/V58)</f>
         <v>2.33333333333333</v>
       </c>
-      <c r="X58" s="30">
+      <c r="X58" s="25">
         <f>IF(OR(K58="",L58="",AP58=""),"",K58*L58-(E58*H58+IF(AND(AK58&lt;&gt;"",AL58&lt;&gt;""),AK58*AL58,0)+IF(AND(AM58&lt;&gt;"",AN58&lt;&gt;""),AM58*AN58,0))-IF(O58="",0,O58)-IF(P58="",0,P58))</f>
         <v>-7500</v>
       </c>
-      <c r="Y58" s="36">
+      <c r="Y58" s="27">
         <f>IF(OR(X58="",AP58=""),"",IF((E58*H58+IF(AND(AK58&lt;&gt;"",AL58&lt;&gt;""),AK58*AL58,0)+IF(AND(AM58&lt;&gt;"",AN58&lt;&gt;""),AM58*AN58,0))+IF(O58="",0,O58)&lt;=0,"",X58/((E58*H58+IF(AND(AK58&lt;&gt;"",AL58&lt;&gt;""),AK58*AL58,0)+IF(AND(AM58&lt;&gt;"",AN58&lt;&gt;""),AM58*AN58,0))+IF(O58="",0,O58))))</f>
         <v>-0.0906344410876133</v>
       </c>
-      <c r="Z58" s="36">
+      <c r="Z58" s="27">
         <f>IF(OR(AE58="",多次统计数据!$B$8=""),"",AE58-多次统计数据!$B$8)</f>
-        <v>-0.101105695368543</v>
-      </c>
-      <c r="AA58" s="37">
+        <v>-0.100500893320084</v>
+      </c>
+      <c r="AA58" s="29">
         <f>IF(OR(I58="",M58="",M58&lt;I58),"",M58-I58)</f>
         <v>16</v>
       </c>
-      <c r="AB58" s="31">
+      <c r="AB58" s="27">
         <f>IF(OR(A58="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC58" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC58" s="23" t="str">
         <f>IF(OR(AB58="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB58,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD58" s="21"/>
-      <c r="AE58" s="36">
+      <c r="AD58" s="20"/>
+      <c r="AE58" s="27">
         <f>IF(OR(X58="",C58="",C58&lt;=0),"",X58/C58)</f>
         <v>-0.0285570684455816</v>
       </c>
-      <c r="AG58" s="22" t="s">
+      <c r="AG58" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="AH58" s="21"/>
-      <c r="AI58" s="21"/>
-      <c r="AJ58" s="26" t="str">
+      <c r="AH58" s="20"/>
+      <c r="AI58" s="20"/>
+      <c r="AJ58" s="23" t="str">
         <f>IF(OR(AG58="",AH58=""),"",IF(OR(AND(AG58="短期博反弹",OR(AH58="1～3个交易日",AH58="4～10个交易日")),AND(AG58="突破冲新高",OR(AH58="4～10个交易日",AH58="11～20个交易日")),AND(AG58="趋势波段",OR(AH58="11～20个交易日",AH58="21～60个交易日",AH58="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK58" s="23"/>
-      <c r="AL58" s="34"/>
-      <c r="AM58" s="23"/>
-      <c r="AN58" s="34"/>
-      <c r="AO58" s="28">
+      <c r="AK58" s="21"/>
+      <c r="AL58" s="30"/>
+      <c r="AM58" s="21"/>
+      <c r="AN58" s="30"/>
+      <c r="AO58" s="25">
         <f>IF(OR(A58="",H58="",H58&lt;=0),"",(E58*H58+IF(AND(AK58&lt;&gt;"",AL58&lt;&gt;""),AK58*AL58,0)+IF(AND(AM58&lt;&gt;"",AN58&lt;&gt;""),AM58*AN58,0))/AP58)</f>
         <v>3.31</v>
       </c>
-      <c r="AP58" s="33">
+      <c r="AP58" s="29">
         <f>IF(OR(A58="",H58="",H58&lt;=0),"",H58+IF(AL58="",0,AL58)+IF(AN58="",0,AN58))</f>
         <v>25000</v>
       </c>
-      <c r="AQ58" s="28">
+      <c r="AQ58" s="25">
         <f>IF(A58="","",IF(M58&lt;&gt;"",0,IF(OR(H58="",N58=""),"",MAX(E58-MAX(N58,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A58))*持仓跟踪!$S$2:$S$157)),0)),0)*H58+IF(OR(AK58="",AL58=""),0,MAX(AK58-MAX(N58,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A58))*持仓跟踪!$S$2:$S$157)),0)),0)*AL58)+IF(OR(AM58="",AN58=""),0,MAX(AM58-MAX(N58,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A58))*持仓跟踪!$S$2:$S$157)),0)),0)*AN58))))</f>
         <v>0</v>
       </c>
-      <c r="AR58" s="26" t="str">
-        <f ca="1">IF(A58="","",IF(OR(E58="",H58=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK58="",AL58&lt;&gt;""),AND(AK58&lt;&gt;"",AL58="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM58="",AN58&lt;&gt;""),AND(AM58&lt;&gt;"",AN58="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM58&lt;&gt;"",AN58&lt;&gt;""),OR(AK58="",AL58="")),"违规：必须先完成第二批",IF(OR(H58&lt;=0,H58&lt;&gt;INT(H58),MOD(H58,100)&lt;&gt;0,AND(AL58&lt;&gt;"",OR(AL58&lt;=0,AL58&lt;&gt;INT(AL58),MOD(AL58,100)&lt;&gt;0)),AND(AN58&lt;&gt;"",OR(AN58&lt;=0,AN58&lt;&gt;INT(AN58),MOD(AN58,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL58&lt;&gt;"",AN58&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ58&gt;C58*D58,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR58" s="23" t="str">
+        <f ca="1">IF(A58="","",IF(OR(E58="",H58=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK58="",AL58&lt;&gt;""),AND(AK58&lt;&gt;"",AL58="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM58="",AN58&lt;&gt;""),AND(AM58&lt;&gt;"",AN58="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM58&lt;&gt;"",AN58&lt;&gt;""),OR(AK58="",AL58="")),"违规：必须先完成第二批",IF(OR(H58&lt;=0,H58&lt;&gt;INT(H58),MOD(H58,100)&lt;&gt;0,AND(AL58&lt;&gt;"",OR(AL58&lt;=0,AL58&lt;&gt;INT(AL58),MOD(AL58,100)&lt;&gt;0)),AND(AN58&lt;&gt;"",OR(AN58&lt;=0,AN58&lt;&gt;INT(AN58),MOD(AN58,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL58&lt;&gt;"",AN58&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ58&gt;C58*D58,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -10198,7 +10173,7 @@
         <f>IF(A59="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A59)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>18800</v>
       </c>
-      <c r="M59" s="18">
+      <c r="M59" s="17">
         <f>IF(A59="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A59)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43997</v>
       </c>
@@ -10222,7 +10197,7 @@
         <f>IF(OR(AO59="",N59="",AO59&lt;=0),"",(AO59-N59)/AO59)</f>
         <v>0.0632318501170959</v>
       </c>
-      <c r="W59" s="19">
+      <c r="W59" s="18">
         <f>IF(OR(U59="",V59="",V59&lt;=0),"",U59/V59)</f>
         <v>1.96296296296297</v>
       </c>
@@ -10236,7 +10211,7 @@
       </c>
       <c r="Z59" s="7">
         <f>IF(OR(AE59="",多次统计数据!$B$8=""),"",AE59-多次统计数据!$B$8)</f>
-        <v>-0.100549818463026</v>
+        <v>-0.0999450164145677</v>
       </c>
       <c r="AA59" s="11">
         <f>IF(OR(I59="",M59="",M59&lt;I59),"",M59-I59)</f>
@@ -10244,7 +10219,7 @@
       </c>
       <c r="AB59" s="7">
         <f>IF(OR(A59="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC59" s="8" t="str">
         <f>IF(OR(AB59="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB59,"低于上限","达到或超过上限"))</f>
@@ -10279,267 +10254,267 @@
         <v>0</v>
       </c>
       <c r="AR59" s="8" t="str">
-        <f ca="1">IF(A59="","",IF(OR(E59="",H59=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK59="",AL59&lt;&gt;""),AND(AK59&lt;&gt;"",AL59="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM59="",AN59&lt;&gt;""),AND(AM59&lt;&gt;"",AN59="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM59&lt;&gt;"",AN59&lt;&gt;""),OR(AK59="",AL59="")),"违规：必须先完成第二批",IF(OR(H59&lt;=0,H59&lt;&gt;INT(H59),MOD(H59,100)&lt;&gt;0,AND(AL59&lt;&gt;"",OR(AL59&lt;=0,AL59&lt;&gt;INT(AL59),MOD(AL59,100)&lt;&gt;0)),AND(AN59&lt;&gt;"",OR(AN59&lt;=0,AN59&lt;&gt;INT(AN59),MOD(AN59,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL59&lt;&gt;"",AN59&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ59&gt;C59*D59,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A59="","",IF(OR(E59="",H59=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK59="",AL59&lt;&gt;""),AND(AK59&lt;&gt;"",AL59="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM59="",AN59&lt;&gt;""),AND(AM59&lt;&gt;"",AN59="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM59&lt;&gt;"",AN59&lt;&gt;""),OR(AK59="",AL59="")),"违规：必须先完成第二批",IF(OR(H59&lt;=0,H59&lt;&gt;INT(H59),MOD(H59,100)&lt;&gt;0,AND(AL59&lt;&gt;"",OR(AL59&lt;=0,AL59&lt;&gt;INT(AL59),MOD(AL59,100)&lt;&gt;0)),AND(AN59&lt;&gt;"",OR(AN59&lt;=0,AN59&lt;&gt;INT(AN59),MOD(AN59,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL59&lt;&gt;"",AN59&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ59&gt;C59*D59,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="60" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A60" s="21">
+    <row r="60" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A60" s="20">
         <v>59</v>
       </c>
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="23">
+      <c r="C60" s="21">
         <v>247988</v>
       </c>
-      <c r="D60" s="24">
+      <c r="D60" s="22">
         <v>0.02</v>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="21">
         <v>4.77</v>
       </c>
-      <c r="F60" s="25">
+      <c r="F60" s="23">
         <f>IF(OR(C60="",D60="",E60="",N60="",C60&lt;=0,D60&lt;=0,E60&lt;=N60),"",ROUNDDOWN((C60*D60)/(E60-N60)/100,0)*100)</f>
         <v>18300</v>
       </c>
-      <c r="G60" s="26" t="str">
+      <c r="G60" s="23" t="str">
         <f ca="1">IF(A60="","",IF(H60&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F60="",E60="",N60="",E60&lt;=N60,账户数据!$B$7=""),"",IF(OR(AG60="",AH60="",AI60=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A60,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F60*(E60-N60)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ60="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H60" s="21">
+      <c r="H60" s="20">
         <v>18300</v>
       </c>
-      <c r="I60" s="27">
+      <c r="I60" s="24">
         <v>44020</v>
       </c>
-      <c r="J60" s="23">
+      <c r="J60" s="21">
         <v>5</v>
       </c>
-      <c r="K60" s="28">
+      <c r="K60" s="25">
         <f>IF(A60="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A60)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>3.96</v>
       </c>
-      <c r="L60" s="25">
+      <c r="L60" s="23">
         <f>IF(A60="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A60)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>18300</v>
       </c>
-      <c r="M60" s="29">
+      <c r="M60" s="26">
         <f>IF(A60="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A60)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>44039</v>
       </c>
-      <c r="N60" s="23">
+      <c r="N60" s="21">
         <v>4.5</v>
       </c>
-      <c r="O60" s="23"/>
-      <c r="P60" s="30" t="str">
+      <c r="O60" s="21"/>
+      <c r="P60" s="25" t="str">
         <f>IF(A60="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A60)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q60" s="21"/>
-      <c r="R60" s="21"/>
-      <c r="S60" s="21"/>
-      <c r="T60" s="21"/>
-      <c r="U60" s="31">
+      <c r="Q60" s="20"/>
+      <c r="R60" s="20"/>
+      <c r="S60" s="20"/>
+      <c r="T60" s="20"/>
+      <c r="U60" s="27">
         <f>IF(OR(AO60="",J60="",AO60&lt;=0),"",(J60-AO60)/AO60)</f>
         <v>0.0482180293501049</v>
       </c>
-      <c r="V60" s="31">
+      <c r="V60" s="27">
         <f>IF(OR(AO60="",N60="",AO60&lt;=0),"",(AO60-N60)/AO60)</f>
         <v>0.0566037735849056</v>
       </c>
-      <c r="W60" s="32">
+      <c r="W60" s="28">
         <f>IF(OR(U60="",V60="",V60&lt;=0),"",U60/V60)</f>
         <v>0.851851851851855</v>
       </c>
-      <c r="X60" s="28">
+      <c r="X60" s="25">
         <f>IF(OR(K60="",L60="",AP60=""),"",K60*L60-(E60*H60+IF(AND(AK60&lt;&gt;"",AL60&lt;&gt;""),AK60*AL60,0)+IF(AND(AM60&lt;&gt;"",AN60&lt;&gt;""),AM60*AN60,0))-IF(O60="",0,O60)-IF(P60="",0,P60))</f>
         <v>-14823</v>
       </c>
-      <c r="Y60" s="31">
+      <c r="Y60" s="27">
         <f>IF(OR(X60="",AP60=""),"",IF((E60*H60+IF(AND(AK60&lt;&gt;"",AL60&lt;&gt;""),AK60*AL60,0)+IF(AND(AM60&lt;&gt;"",AN60&lt;&gt;""),AM60*AN60,0))+IF(O60="",0,O60)&lt;=0,"",X60/((E60*H60+IF(AND(AK60&lt;&gt;"",AL60&lt;&gt;""),AK60*AL60,0)+IF(AND(AM60&lt;&gt;"",AN60&lt;&gt;""),AM60*AN60,0))+IF(O60="",0,O60))))</f>
         <v>-0.169811320754717</v>
       </c>
-      <c r="Z60" s="31">
+      <c r="Z60" s="27">
         <f>IF(OR(AE60="",多次统计数据!$B$8=""),"",AE60-多次统计数据!$B$8)</f>
-        <v>-0.132321680457809</v>
-      </c>
-      <c r="AA60" s="33">
+        <v>-0.131716878409351</v>
+      </c>
+      <c r="AA60" s="29">
         <f>IF(OR(I60="",M60="",M60&lt;I60),"",M60-I60)</f>
         <v>19</v>
       </c>
-      <c r="AB60" s="31">
+      <c r="AB60" s="27">
         <f>IF(OR(A60="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC60" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC60" s="23" t="str">
         <f>IF(OR(AB60="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB60,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD60" s="21"/>
-      <c r="AE60" s="31">
+      <c r="AD60" s="20"/>
+      <c r="AE60" s="27">
         <f>IF(OR(X60="",C60="",C60&lt;=0),"",X60/C60)</f>
         <v>-0.0597730535348484</v>
       </c>
-      <c r="AG60" s="22" t="s">
+      <c r="AG60" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="AH60" s="22" t="s">
+      <c r="AH60" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="AI60" s="21"/>
-      <c r="AJ60" s="26" t="str">
+      <c r="AI60" s="20"/>
+      <c r="AJ60" s="23" t="str">
         <f>IF(OR(AG60="",AH60=""),"",IF(OR(AND(AG60="短期博反弹",OR(AH60="1～3个交易日",AH60="4～10个交易日")),AND(AG60="突破冲新高",OR(AH60="4～10个交易日",AH60="11～20个交易日")),AND(AG60="趋势波段",OR(AH60="11～20个交易日",AH60="21～60个交易日",AH60="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v>匹配</v>
       </c>
-      <c r="AK60" s="23"/>
-      <c r="AL60" s="34"/>
-      <c r="AM60" s="23"/>
-      <c r="AN60" s="34"/>
-      <c r="AO60" s="28">
+      <c r="AK60" s="21"/>
+      <c r="AL60" s="30"/>
+      <c r="AM60" s="21"/>
+      <c r="AN60" s="30"/>
+      <c r="AO60" s="25">
         <f>IF(OR(A60="",H60="",H60&lt;=0),"",(E60*H60+IF(AND(AK60&lt;&gt;"",AL60&lt;&gt;""),AK60*AL60,0)+IF(AND(AM60&lt;&gt;"",AN60&lt;&gt;""),AM60*AN60,0))/AP60)</f>
         <v>4.77</v>
       </c>
-      <c r="AP60" s="33">
+      <c r="AP60" s="29">
         <f>IF(OR(A60="",H60="",H60&lt;=0),"",H60+IF(AL60="",0,AL60)+IF(AN60="",0,AN60))</f>
         <v>18300</v>
       </c>
-      <c r="AQ60" s="28">
+      <c r="AQ60" s="25">
         <f>IF(A60="","",IF(M60&lt;&gt;"",0,IF(OR(H60="",N60=""),"",MAX(E60-MAX(N60,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A60))*持仓跟踪!$S$2:$S$157)),0)),0)*H60+IF(OR(AK60="",AL60=""),0,MAX(AK60-MAX(N60,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A60))*持仓跟踪!$S$2:$S$157)),0)),0)*AL60)+IF(OR(AM60="",AN60=""),0,MAX(AM60-MAX(N60,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A60))*持仓跟踪!$S$2:$S$157)),0)),0)*AN60))))</f>
         <v>0</v>
       </c>
-      <c r="AR60" s="26" t="str">
-        <f ca="1">IF(A60="","",IF(OR(E60="",H60=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK60="",AL60&lt;&gt;""),AND(AK60&lt;&gt;"",AL60="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM60="",AN60&lt;&gt;""),AND(AM60&lt;&gt;"",AN60="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM60&lt;&gt;"",AN60&lt;&gt;""),OR(AK60="",AL60="")),"违规：必须先完成第二批",IF(OR(H60&lt;=0,H60&lt;&gt;INT(H60),MOD(H60,100)&lt;&gt;0,AND(AL60&lt;&gt;"",OR(AL60&lt;=0,AL60&lt;&gt;INT(AL60),MOD(AL60,100)&lt;&gt;0)),AND(AN60&lt;&gt;"",OR(AN60&lt;=0,AN60&lt;&gt;INT(AN60),MOD(AN60,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL60&lt;&gt;"",AN60&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ60&gt;C60*D60,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR60" s="23" t="str">
+        <f ca="1">IF(A60="","",IF(OR(E60="",H60=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK60="",AL60&lt;&gt;""),AND(AK60&lt;&gt;"",AL60="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM60="",AN60&lt;&gt;""),AND(AM60&lt;&gt;"",AN60="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM60&lt;&gt;"",AN60&lt;&gt;""),OR(AK60="",AL60="")),"违规：必须先完成第二批",IF(OR(H60&lt;=0,H60&lt;&gt;INT(H60),MOD(H60,100)&lt;&gt;0,AND(AL60&lt;&gt;"",OR(AL60&lt;=0,AL60&lt;&gt;INT(AL60),MOD(AL60,100)&lt;&gt;0)),AND(AN60&lt;&gt;"",OR(AN60&lt;=0,AN60&lt;&gt;INT(AN60),MOD(AN60,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL60&lt;&gt;"",AN60&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ60&gt;C60*D60,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="61" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A61" s="21">
+    <row r="61" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A61" s="20">
         <v>60</v>
       </c>
-      <c r="B61" s="22" t="s">
+      <c r="B61" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C61" s="23">
+      <c r="C61" s="21">
         <v>233165</v>
       </c>
-      <c r="D61" s="24">
+      <c r="D61" s="22">
         <v>0.02</v>
       </c>
-      <c r="E61" s="23">
+      <c r="E61" s="21">
         <v>3.89</v>
       </c>
-      <c r="F61" s="25">
+      <c r="F61" s="23">
         <f>IF(OR(C61="",D61="",E61="",N61="",C61&lt;=0,D61&lt;=0,E61&lt;=N61),"",ROUNDDOWN((C61*D61)/(E61-N61)/100,0)*100)</f>
         <v>38800</v>
       </c>
-      <c r="G61" s="26" t="str">
+      <c r="G61" s="23" t="str">
         <f ca="1">IF(A61="","",IF(H61&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F61="",E61="",N61="",E61&lt;=N61,账户数据!$B$7=""),"",IF(OR(AG61="",AH61="",AI61=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A61,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F61*(E61-N61)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ61="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H61" s="21">
+      <c r="H61" s="20">
         <v>38800</v>
       </c>
-      <c r="I61" s="27">
+      <c r="I61" s="24">
         <v>45090</v>
       </c>
-      <c r="J61" s="23">
+      <c r="J61" s="21">
         <v>4</v>
       </c>
-      <c r="K61" s="30">
+      <c r="K61" s="25">
         <f>IF(A61="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A61)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>3.63</v>
       </c>
-      <c r="L61" s="26">
+      <c r="L61" s="23">
         <f>IF(A61="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A61)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>38800</v>
       </c>
-      <c r="M61" s="35">
+      <c r="M61" s="26">
         <f>IF(A61="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A61)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45163</v>
       </c>
-      <c r="N61" s="23">
+      <c r="N61" s="21">
         <v>3.77</v>
       </c>
-      <c r="O61" s="23"/>
-      <c r="P61" s="30" t="str">
+      <c r="O61" s="21"/>
+      <c r="P61" s="25" t="str">
         <f>IF(A61="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A61)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q61" s="21"/>
-      <c r="R61" s="21"/>
-      <c r="S61" s="21"/>
-      <c r="T61" s="21"/>
-      <c r="U61" s="31">
+      <c r="Q61" s="20"/>
+      <c r="R61" s="20"/>
+      <c r="S61" s="20"/>
+      <c r="T61" s="20"/>
+      <c r="U61" s="27">
         <f>IF(OR(AO61="",J61="",AO61&lt;=0),"",(J61-AO61)/AO61)</f>
         <v>0.0282776349614396</v>
       </c>
-      <c r="V61" s="31">
+      <c r="V61" s="27">
         <f>IF(OR(AO61="",N61="",AO61&lt;=0),"",(AO61-N61)/AO61)</f>
         <v>0.0308483290488432</v>
       </c>
-      <c r="W61" s="32">
+      <c r="W61" s="28">
         <f>IF(OR(U61="",V61="",V61&lt;=0),"",U61/V61)</f>
         <v>0.916666666666665</v>
       </c>
-      <c r="X61" s="30">
+      <c r="X61" s="25">
         <f>IF(OR(K61="",L61="",AP61=""),"",K61*L61-(E61*H61+IF(AND(AK61&lt;&gt;"",AL61&lt;&gt;""),AK61*AL61,0)+IF(AND(AM61&lt;&gt;"",AN61&lt;&gt;""),AM61*AN61,0))-IF(O61="",0,O61)-IF(P61="",0,P61))</f>
         <v>-10088</v>
       </c>
-      <c r="Y61" s="36">
+      <c r="Y61" s="27">
         <f>IF(OR(X61="",AP61=""),"",IF((E61*H61+IF(AND(AK61&lt;&gt;"",AL61&lt;&gt;""),AK61*AL61,0)+IF(AND(AM61&lt;&gt;"",AN61&lt;&gt;""),AM61*AN61,0))+IF(O61="",0,O61)&lt;=0,"",X61/((E61*H61+IF(AND(AK61&lt;&gt;"",AL61&lt;&gt;""),AK61*AL61,0)+IF(AND(AM61&lt;&gt;"",AN61&lt;&gt;""),AM61*AN61,0))+IF(O61="",0,O61))))</f>
         <v>-0.0668380462724936</v>
       </c>
-      <c r="Z61" s="36">
+      <c r="Z61" s="27">
         <f>IF(OR(AE61="",多次统计数据!$B$8=""),"",AE61-多次统计数据!$B$8)</f>
-        <v>-0.115814125604152</v>
-      </c>
-      <c r="AA61" s="37">
+        <v>-0.115209323555694</v>
+      </c>
+      <c r="AA61" s="29">
         <f>IF(OR(I61="",M61="",M61&lt;I61),"",M61-I61)</f>
         <v>73</v>
       </c>
-      <c r="AB61" s="31">
+      <c r="AB61" s="27">
         <f>IF(OR(A61="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC61" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC61" s="23" t="str">
         <f>IF(OR(AB61="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB61,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD61" s="21"/>
-      <c r="AE61" s="36">
+      <c r="AD61" s="20"/>
+      <c r="AE61" s="27">
         <f>IF(OR(X61="",C61="",C61&lt;=0),"",X61/C61)</f>
         <v>-0.0432654986811914</v>
       </c>
-      <c r="AG61" s="22" t="s">
+      <c r="AG61" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="AH61" s="22" t="s">
+      <c r="AH61" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="AI61" s="21"/>
-      <c r="AJ61" s="26" t="str">
+      <c r="AI61" s="20"/>
+      <c r="AJ61" s="23" t="str">
         <f>IF(OR(AG61="",AH61=""),"",IF(OR(AND(AG61="短期博反弹",OR(AH61="1～3个交易日",AH61="4～10个交易日")),AND(AG61="突破冲新高",OR(AH61="4～10个交易日",AH61="11～20个交易日")),AND(AG61="趋势波段",OR(AH61="11～20个交易日",AH61="21～60个交易日",AH61="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v>匹配</v>
       </c>
-      <c r="AK61" s="23"/>
-      <c r="AL61" s="34"/>
-      <c r="AM61" s="23"/>
-      <c r="AN61" s="34"/>
-      <c r="AO61" s="28">
+      <c r="AK61" s="21"/>
+      <c r="AL61" s="30"/>
+      <c r="AM61" s="21"/>
+      <c r="AN61" s="30"/>
+      <c r="AO61" s="25">
         <f>IF(OR(A61="",H61="",H61&lt;=0),"",(E61*H61+IF(AND(AK61&lt;&gt;"",AL61&lt;&gt;""),AK61*AL61,0)+IF(AND(AM61&lt;&gt;"",AN61&lt;&gt;""),AM61*AN61,0))/AP61)</f>
         <v>3.89</v>
       </c>
-      <c r="AP61" s="33">
+      <c r="AP61" s="29">
         <f>IF(OR(A61="",H61="",H61&lt;=0),"",H61+IF(AL61="",0,AL61)+IF(AN61="",0,AN61))</f>
         <v>38800</v>
       </c>
-      <c r="AQ61" s="28">
+      <c r="AQ61" s="25">
         <f>IF(A61="","",IF(M61&lt;&gt;"",0,IF(OR(H61="",N61=""),"",MAX(E61-MAX(N61,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A61))*持仓跟踪!$S$2:$S$157)),0)),0)*H61+IF(OR(AK61="",AL61=""),0,MAX(AK61-MAX(N61,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A61))*持仓跟踪!$S$2:$S$157)),0)),0)*AL61)+IF(OR(AM61="",AN61=""),0,MAX(AM61-MAX(N61,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A61))*持仓跟踪!$S$2:$S$157)),0)),0)*AN61))))</f>
         <v>0</v>
       </c>
-      <c r="AR61" s="26" t="str">
-        <f ca="1">IF(A61="","",IF(OR(E61="",H61=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK61="",AL61&lt;&gt;""),AND(AK61&lt;&gt;"",AL61="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM61="",AN61&lt;&gt;""),AND(AM61&lt;&gt;"",AN61="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM61&lt;&gt;"",AN61&lt;&gt;""),OR(AK61="",AL61="")),"违规：必须先完成第二批",IF(OR(H61&lt;=0,H61&lt;&gt;INT(H61),MOD(H61,100)&lt;&gt;0,AND(AL61&lt;&gt;"",OR(AL61&lt;=0,AL61&lt;&gt;INT(AL61),MOD(AL61,100)&lt;&gt;0)),AND(AN61&lt;&gt;"",OR(AN61&lt;=0,AN61&lt;&gt;INT(AN61),MOD(AN61,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL61&lt;&gt;"",AN61&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ61&gt;C61*D61,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR61" s="23" t="str">
+        <f ca="1">IF(A61="","",IF(OR(E61="",H61=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK61="",AL61&lt;&gt;""),AND(AK61&lt;&gt;"",AL61="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM61="",AN61&lt;&gt;""),AND(AM61&lt;&gt;"",AN61="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM61&lt;&gt;"",AN61&lt;&gt;""),OR(AK61="",AL61="")),"违规：必须先完成第二批",IF(OR(H61&lt;=0,H61&lt;&gt;INT(H61),MOD(H61,100)&lt;&gt;0,AND(AL61&lt;&gt;"",OR(AL61&lt;=0,AL61&lt;&gt;INT(AL61),MOD(AL61,100)&lt;&gt;0)),AND(AN61&lt;&gt;"",OR(AN61&lt;=0,AN61&lt;&gt;INT(AN61),MOD(AN61,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL61&lt;&gt;"",AN61&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ61&gt;C61*D61,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -10584,7 +10559,7 @@
         <f>IF(A62="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A62)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>89200</v>
       </c>
-      <c r="M62" s="18">
+      <c r="M62" s="17">
         <f>IF(A62="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A62)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45777</v>
       </c>
@@ -10608,7 +10583,7 @@
         <f>IF(OR(AO62="",N62="",AO62&lt;=0),"",(AO62-N62)/AO62)</f>
         <v>0.0131578947368421</v>
       </c>
-      <c r="W62" s="19">
+      <c r="W62" s="18">
         <f>IF(OR(U62="",V62="",V62&lt;=0),"",U62/V62)</f>
         <v>4.00000000000002</v>
       </c>
@@ -10622,7 +10597,7 @@
       </c>
       <c r="Z62" s="7">
         <f>IF(OR(AE62="",多次统计数据!$B$8=""),"",AE62-多次统计数据!$B$8)</f>
-        <v>0.095393384131518</v>
+        <v>0.0959981861799768</v>
       </c>
       <c r="AA62" s="11">
         <f>IF(OR(I62="",M62="",M62&lt;I62),"",M62-I62)</f>
@@ -10630,7 +10605,7 @@
       </c>
       <c r="AB62" s="7">
         <f>IF(OR(A62="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC62" s="8" t="str">
         <f>IF(OR(AB62="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB62,"低于上限","达到或超过上限"))</f>
@@ -10665,133 +10640,133 @@
         <v>0</v>
       </c>
       <c r="AR62" s="8" t="str">
-        <f ca="1">IF(A62="","",IF(OR(E62="",H62=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK62="",AL62&lt;&gt;""),AND(AK62&lt;&gt;"",AL62="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM62="",AN62&lt;&gt;""),AND(AM62&lt;&gt;"",AN62="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM62&lt;&gt;"",AN62&lt;&gt;""),OR(AK62="",AL62="")),"违规：必须先完成第二批",IF(OR(H62&lt;=0,H62&lt;&gt;INT(H62),MOD(H62,100)&lt;&gt;0,AND(AL62&lt;&gt;"",OR(AL62&lt;=0,AL62&lt;&gt;INT(AL62),MOD(AL62,100)&lt;&gt;0)),AND(AN62&lt;&gt;"",OR(AN62&lt;=0,AN62&lt;&gt;INT(AN62),MOD(AN62,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL62&lt;&gt;"",AN62&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ62&gt;C62*D62,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A62="","",IF(OR(E62="",H62=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK62="",AL62&lt;&gt;""),AND(AK62&lt;&gt;"",AL62="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM62="",AN62&lt;&gt;""),AND(AM62&lt;&gt;"",AN62="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM62&lt;&gt;"",AN62&lt;&gt;""),OR(AK62="",AL62="")),"违规：必须先完成第二批",IF(OR(H62&lt;=0,H62&lt;&gt;INT(H62),MOD(H62,100)&lt;&gt;0,AND(AL62&lt;&gt;"",OR(AL62&lt;=0,AL62&lt;&gt;INT(AL62),MOD(AL62,100)&lt;&gt;0)),AND(AN62&lt;&gt;"",OR(AN62&lt;=0,AN62&lt;&gt;INT(AN62),MOD(AN62,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL62&lt;&gt;"",AN62&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ62&gt;C62*D62,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="63" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A63" s="21">
+    <row r="63" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A63" s="20">
         <v>62</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C63" s="23">
+      <c r="C63" s="21">
         <v>260541</v>
       </c>
-      <c r="D63" s="24">
+      <c r="D63" s="22">
         <v>0.02</v>
       </c>
-      <c r="E63" s="23">
+      <c r="E63" s="21">
         <v>4.08</v>
       </c>
-      <c r="F63" s="25">
+      <c r="F63" s="23">
         <f>IF(OR(C63="",D63="",E63="",N63="",C63&lt;=0,D63&lt;=0,E63&lt;=N63),"",ROUNDDOWN((C63*D63)/(E63-N63)/100,0)*100)</f>
         <v>65100</v>
       </c>
-      <c r="G63" s="26" t="str">
+      <c r="G63" s="23" t="str">
         <f ca="1">IF(A63="","",IF(H63&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F63="",E63="",N63="",E63&lt;=N63,账户数据!$B$7=""),"",IF(OR(AG63="",AH63="",AI63=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A63,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F63*(E63-N63)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ63="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H63" s="21">
+      <c r="H63" s="20">
         <v>65100</v>
       </c>
-      <c r="I63" s="27">
+      <c r="I63" s="24">
         <v>45483</v>
       </c>
-      <c r="J63" s="23">
+      <c r="J63" s="21">
         <v>4.2</v>
       </c>
-      <c r="K63" s="28">
+      <c r="K63" s="25">
         <f>IF(A63="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A63)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>3.87</v>
       </c>
-      <c r="L63" s="25">
+      <c r="L63" s="23">
         <f>IF(A63="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A63)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>65100</v>
       </c>
-      <c r="M63" s="29">
+      <c r="M63" s="26">
         <f>IF(A63="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A63)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45498</v>
       </c>
-      <c r="N63" s="23">
+      <c r="N63" s="21">
         <v>4</v>
       </c>
-      <c r="O63" s="23"/>
-      <c r="P63" s="30" t="str">
+      <c r="O63" s="21"/>
+      <c r="P63" s="25" t="str">
         <f>IF(A63="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A63)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q63" s="21"/>
-      <c r="R63" s="21"/>
-      <c r="S63" s="21"/>
-      <c r="T63" s="21"/>
-      <c r="U63" s="31">
+      <c r="Q63" s="20"/>
+      <c r="R63" s="20"/>
+      <c r="S63" s="20"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="27">
         <f>IF(OR(AO63="",J63="",AO63&lt;=0),"",(J63-AO63)/AO63)</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="V63" s="31">
+      <c r="V63" s="27">
         <f>IF(OR(AO63="",N63="",AO63&lt;=0),"",(AO63-N63)/AO63)</f>
         <v>0.0196078431372549</v>
       </c>
-      <c r="W63" s="32">
+      <c r="W63" s="28">
         <f>IF(OR(U63="",V63="",V63&lt;=0),"",U63/V63)</f>
         <v>1.5</v>
       </c>
-      <c r="X63" s="28">
+      <c r="X63" s="25">
         <f>IF(OR(K63="",L63="",AP63=""),"",K63*L63-(E63*H63+IF(AND(AK63&lt;&gt;"",AL63&lt;&gt;""),AK63*AL63,0)+IF(AND(AM63&lt;&gt;"",AN63&lt;&gt;""),AM63*AN63,0))-IF(O63="",0,O63)-IF(P63="",0,P63))</f>
         <v>-13671</v>
       </c>
-      <c r="Y63" s="31">
+      <c r="Y63" s="27">
         <f>IF(OR(X63="",AP63=""),"",IF((E63*H63+IF(AND(AK63&lt;&gt;"",AL63&lt;&gt;""),AK63*AL63,0)+IF(AND(AM63&lt;&gt;"",AN63&lt;&gt;""),AM63*AN63,0))+IF(O63="",0,O63)&lt;=0,"",X63/((E63*H63+IF(AND(AK63&lt;&gt;"",AL63&lt;&gt;""),AK63*AL63,0)+IF(AND(AM63&lt;&gt;"",AN63&lt;&gt;""),AM63*AN63,0))+IF(O63="",0,O63))))</f>
         <v>-0.0514705882352941</v>
       </c>
-      <c r="Z63" s="31">
+      <c r="Z63" s="27">
         <f>IF(OR(AE63="",多次统计数据!$B$8=""),"",AE63-多次统计数据!$B$8)</f>
-        <v>-0.125020214888003</v>
-      </c>
-      <c r="AA63" s="33">
+        <v>-0.124415412839544</v>
+      </c>
+      <c r="AA63" s="29">
         <f>IF(OR(I63="",M63="",M63&lt;I63),"",M63-I63)</f>
         <v>15</v>
       </c>
-      <c r="AB63" s="31">
+      <c r="AB63" s="27">
         <f>IF(OR(A63="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC63" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC63" s="23" t="str">
         <f>IF(OR(AB63="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB63,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD63" s="21"/>
-      <c r="AE63" s="31">
+      <c r="AD63" s="20"/>
+      <c r="AE63" s="27">
         <f>IF(OR(X63="",C63="",C63&lt;=0),"",X63/C63)</f>
         <v>-0.052471587965042</v>
       </c>
-      <c r="AG63" s="21"/>
-      <c r="AH63" s="21"/>
-      <c r="AI63" s="21"/>
-      <c r="AJ63" s="26" t="str">
+      <c r="AG63" s="20"/>
+      <c r="AH63" s="20"/>
+      <c r="AI63" s="20"/>
+      <c r="AJ63" s="23" t="str">
         <f>IF(OR(AG63="",AH63=""),"",IF(OR(AND(AG63="短期博反弹",OR(AH63="1～3个交易日",AH63="4～10个交易日")),AND(AG63="突破冲新高",OR(AH63="4～10个交易日",AH63="11～20个交易日")),AND(AG63="趋势波段",OR(AH63="11～20个交易日",AH63="21～60个交易日",AH63="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK63" s="23"/>
-      <c r="AL63" s="34"/>
-      <c r="AM63" s="23"/>
-      <c r="AN63" s="34"/>
-      <c r="AO63" s="28">
+      <c r="AK63" s="21"/>
+      <c r="AL63" s="30"/>
+      <c r="AM63" s="21"/>
+      <c r="AN63" s="30"/>
+      <c r="AO63" s="25">
         <f>IF(OR(A63="",H63="",H63&lt;=0),"",(E63*H63+IF(AND(AK63&lt;&gt;"",AL63&lt;&gt;""),AK63*AL63,0)+IF(AND(AM63&lt;&gt;"",AN63&lt;&gt;""),AM63*AN63,0))/AP63)</f>
         <v>4.08</v>
       </c>
-      <c r="AP63" s="33">
+      <c r="AP63" s="29">
         <f>IF(OR(A63="",H63="",H63&lt;=0),"",H63+IF(AL63="",0,AL63)+IF(AN63="",0,AN63))</f>
         <v>65100</v>
       </c>
-      <c r="AQ63" s="28">
+      <c r="AQ63" s="25">
         <f>IF(A63="","",IF(M63&lt;&gt;"",0,IF(OR(H63="",N63=""),"",MAX(E63-MAX(N63,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A63))*持仓跟踪!$S$2:$S$157)),0)),0)*H63+IF(OR(AK63="",AL63=""),0,MAX(AK63-MAX(N63,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A63))*持仓跟踪!$S$2:$S$157)),0)),0)*AL63)+IF(OR(AM63="",AN63=""),0,MAX(AM63-MAX(N63,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A63))*持仓跟踪!$S$2:$S$157)),0)),0)*AN63))))</f>
         <v>0</v>
       </c>
-      <c r="AR63" s="26" t="str">
-        <f ca="1">IF(A63="","",IF(OR(E63="",H63=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK63="",AL63&lt;&gt;""),AND(AK63&lt;&gt;"",AL63="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM63="",AN63&lt;&gt;""),AND(AM63&lt;&gt;"",AN63="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM63&lt;&gt;"",AN63&lt;&gt;""),OR(AK63="",AL63="")),"违规：必须先完成第二批",IF(OR(H63&lt;=0,H63&lt;&gt;INT(H63),MOD(H63,100)&lt;&gt;0,AND(AL63&lt;&gt;"",OR(AL63&lt;=0,AL63&lt;&gt;INT(AL63),MOD(AL63,100)&lt;&gt;0)),AND(AN63&lt;&gt;"",OR(AN63&lt;=0,AN63&lt;&gt;INT(AN63),MOD(AN63,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL63&lt;&gt;"",AN63&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ63&gt;C63*D63,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR63" s="23" t="str">
+        <f ca="1">IF(A63="","",IF(OR(E63="",H63=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK63="",AL63&lt;&gt;""),AND(AK63&lt;&gt;"",AL63="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM63="",AN63&lt;&gt;""),AND(AM63&lt;&gt;"",AN63="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM63&lt;&gt;"",AN63&lt;&gt;""),OR(AK63="",AL63="")),"违规：必须先完成第二批",IF(OR(H63&lt;=0,H63&lt;&gt;INT(H63),MOD(H63,100)&lt;&gt;0,AND(AL63&lt;&gt;"",OR(AL63&lt;=0,AL63&lt;&gt;INT(AL63),MOD(AL63,100)&lt;&gt;0)),AND(AN63&lt;&gt;"",OR(AN63&lt;=0,AN63&lt;&gt;INT(AN63),MOD(AN63,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL63&lt;&gt;"",AN63&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ63&gt;C63*D63,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -10836,7 +10811,7 @@
         <f>IF(A64="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A64)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>54800</v>
       </c>
-      <c r="M64" s="18">
+      <c r="M64" s="17">
         <f>IF(A64="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A64)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45705</v>
       </c>
@@ -10860,7 +10835,7 @@
         <f>IF(OR(AO64="",N64="",AO64&lt;=0),"",(AO64-N64)/AO64)</f>
         <v>0.020501138952164</v>
       </c>
-      <c r="W64" s="19">
+      <c r="W64" s="18">
         <f>IF(OR(U64="",V64="",V64&lt;=0),"",U64/V64)</f>
         <v>2.33333333333334</v>
       </c>
@@ -10874,7 +10849,7 @@
       </c>
       <c r="Z64" s="7">
         <f>IF(OR(AE64="",多次统计数据!$B$8=""),"",AE64-多次统计数据!$B$8)</f>
-        <v>-0.0991861284419791</v>
+        <v>-0.0985813263935203</v>
       </c>
       <c r="AA64" s="11">
         <f>IF(OR(I64="",M64="",M64&lt;I64),"",M64-I64)</f>
@@ -10882,7 +10857,7 @@
       </c>
       <c r="AB64" s="7">
         <f>IF(OR(A64="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC64" s="8" t="str">
         <f>IF(OR(AB64="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB64,"低于上限","达到或超过上限"))</f>
@@ -10917,7 +10892,7 @@
         <v>0</v>
       </c>
       <c r="AR64" s="8" t="str">
-        <f ca="1">IF(A64="","",IF(OR(E64="",H64=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK64="",AL64&lt;&gt;""),AND(AK64&lt;&gt;"",AL64="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM64="",AN64&lt;&gt;""),AND(AM64&lt;&gt;"",AN64="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM64&lt;&gt;"",AN64&lt;&gt;""),OR(AK64="",AL64="")),"违规：必须先完成第二批",IF(OR(H64&lt;=0,H64&lt;&gt;INT(H64),MOD(H64,100)&lt;&gt;0,AND(AL64&lt;&gt;"",OR(AL64&lt;=0,AL64&lt;&gt;INT(AL64),MOD(AL64,100)&lt;&gt;0)),AND(AN64&lt;&gt;"",OR(AN64&lt;=0,AN64&lt;&gt;INT(AN64),MOD(AN64,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL64&lt;&gt;"",AN64&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ64&gt;C64*D64,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A64="","",IF(OR(E64="",H64=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK64="",AL64&lt;&gt;""),AND(AK64&lt;&gt;"",AL64="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM64="",AN64&lt;&gt;""),AND(AM64&lt;&gt;"",AN64="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM64&lt;&gt;"",AN64&lt;&gt;""),OR(AK64="",AL64="")),"违规：必须先完成第二批",IF(OR(H64&lt;=0,H64&lt;&gt;INT(H64),MOD(H64,100)&lt;&gt;0,AND(AL64&lt;&gt;"",OR(AL64&lt;=0,AL64&lt;&gt;INT(AL64),MOD(AL64,100)&lt;&gt;0)),AND(AN64&lt;&gt;"",OR(AN64&lt;=0,AN64&lt;&gt;INT(AN64),MOD(AN64,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL64&lt;&gt;"",AN64&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ64&gt;C64*D64,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -10962,7 +10937,7 @@
         <f>IF(A65="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A65)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>68600</v>
       </c>
-      <c r="M65" s="18">
+      <c r="M65" s="17">
         <f>IF(A65="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A65)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45868</v>
       </c>
@@ -10986,7 +10961,7 @@
         <f>IF(OR(AO65="",N65="",AO65&lt;=0),"",(AO65-N65)/AO65)</f>
         <v>0.0176322418136021</v>
       </c>
-      <c r="W65" s="19">
+      <c r="W65" s="18">
         <f>IF(OR(U65="",V65="",V65&lt;=0),"",U65/V65)</f>
         <v>3.28571428571427</v>
       </c>
@@ -11000,7 +10975,7 @@
       </c>
       <c r="Z65" s="7">
         <f>IF(OR(AE65="",多次统计数据!$B$8=""),"",AE65-多次统计数据!$B$8)</f>
-        <v>-0.0582744461277687</v>
+        <v>-0.0576696440793099</v>
       </c>
       <c r="AA65" s="11">
         <f>IF(OR(I65="",M65="",M65&lt;I65),"",M65-I65)</f>
@@ -11008,7 +10983,7 @@
       </c>
       <c r="AB65" s="7">
         <f>IF(OR(A65="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC65" s="8" t="str">
         <f>IF(OR(AB65="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB65,"低于上限","达到或超过上限"))</f>
@@ -11043,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="AR65" s="8" t="str">
-        <f ca="1">IF(A65="","",IF(OR(E65="",H65=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK65="",AL65&lt;&gt;""),AND(AK65&lt;&gt;"",AL65="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM65="",AN65&lt;&gt;""),AND(AM65&lt;&gt;"",AN65="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM65&lt;&gt;"",AN65&lt;&gt;""),OR(AK65="",AL65="")),"违规：必须先完成第二批",IF(OR(H65&lt;=0,H65&lt;&gt;INT(H65),MOD(H65,100)&lt;&gt;0,AND(AL65&lt;&gt;"",OR(AL65&lt;=0,AL65&lt;&gt;INT(AL65),MOD(AL65,100)&lt;&gt;0)),AND(AN65&lt;&gt;"",OR(AN65&lt;=0,AN65&lt;&gt;INT(AN65),MOD(AN65,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL65&lt;&gt;"",AN65&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ65&gt;C65*D65,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A65="","",IF(OR(E65="",H65=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK65="",AL65&lt;&gt;""),AND(AK65&lt;&gt;"",AL65="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM65="",AN65&lt;&gt;""),AND(AM65&lt;&gt;"",AN65="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM65&lt;&gt;"",AN65&lt;&gt;""),OR(AK65="",AL65="")),"违规：必须先完成第二批",IF(OR(H65&lt;=0,H65&lt;&gt;INT(H65),MOD(H65,100)&lt;&gt;0,AND(AL65&lt;&gt;"",OR(AL65&lt;=0,AL65&lt;&gt;INT(AL65),MOD(AL65,100)&lt;&gt;0)),AND(AN65&lt;&gt;"",OR(AN65&lt;=0,AN65&lt;&gt;INT(AN65),MOD(AN65,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL65&lt;&gt;"",AN65&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ65&gt;C65*D65,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -11088,7 +11063,7 @@
         <f>IF(A66="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A66)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>48700</v>
       </c>
-      <c r="M66" s="18">
+      <c r="M66" s="17">
         <f>IF(A66="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A66)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>45903</v>
       </c>
@@ -11112,7 +11087,7 @@
         <f>IF(OR(AO66="",N66="",AO66&lt;=0),"",(AO66-N66)/AO66)</f>
         <v>0.0253164556962026</v>
       </c>
-      <c r="W66" s="19">
+      <c r="W66" s="18">
         <f>IF(OR(U66="",V66="",V66&lt;=0),"",U66/V66)</f>
         <v>2.5</v>
       </c>
@@ -11126,7 +11101,7 @@
       </c>
       <c r="Z66" s="7">
         <f>IF(OR(AE66="",多次统计数据!$B$8=""),"",AE66-多次统计数据!$B$8)</f>
-        <v>-0.0665541413573211</v>
+        <v>-0.0659493393088624</v>
       </c>
       <c r="AA66" s="11">
         <f>IF(OR(I66="",M66="",M66&lt;I66),"",M66-I66)</f>
@@ -11134,7 +11109,7 @@
       </c>
       <c r="AB66" s="7">
         <f>IF(OR(A66="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC66" s="8" t="str">
         <f>IF(OR(AB66="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB66,"低于上限","达到或超过上限"))</f>
@@ -11169,11 +11144,11 @@
         <v>0</v>
       </c>
       <c r="AR66" s="8" t="str">
-        <f ca="1">IF(A66="","",IF(OR(E66="",H66=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK66="",AL66&lt;&gt;""),AND(AK66&lt;&gt;"",AL66="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM66="",AN66&lt;&gt;""),AND(AM66&lt;&gt;"",AN66="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM66&lt;&gt;"",AN66&lt;&gt;""),OR(AK66="",AL66="")),"违规：必须先完成第二批",IF(OR(H66&lt;=0,H66&lt;&gt;INT(H66),MOD(H66,100)&lt;&gt;0,AND(AL66&lt;&gt;"",OR(AL66&lt;=0,AL66&lt;&gt;INT(AL66),MOD(AL66,100)&lt;&gt;0)),AND(AN66&lt;&gt;"",OR(AN66&lt;=0,AN66&lt;&gt;INT(AN66),MOD(AN66,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL66&lt;&gt;"",AN66&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ66&gt;C66*D66,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A66="","",IF(OR(E66="",H66=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK66="",AL66&lt;&gt;""),AND(AK66&lt;&gt;"",AL66="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM66="",AN66&lt;&gt;""),AND(AM66&lt;&gt;"",AN66="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM66&lt;&gt;"",AN66&lt;&gt;""),OR(AK66="",AL66="")),"违规：必须先完成第二批",IF(OR(H66&lt;=0,H66&lt;&gt;INT(H66),MOD(H66,100)&lt;&gt;0,AND(AL66&lt;&gt;"",OR(AL66&lt;=0,AL66&lt;&gt;INT(AL66),MOD(AL66,100)&lt;&gt;0)),AND(AN66&lt;&gt;"",OR(AN66&lt;=0,AN66&lt;&gt;INT(AN66),MOD(AN66,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL66&lt;&gt;"",AN66&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ66&gt;C66*D66,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="67" ht="34" spans="1:44">
+    <row r="67" ht="17" spans="1:44">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -11214,7 +11189,7 @@
         <f>IF(A67="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A67)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>32600</v>
       </c>
-      <c r="M67" s="18">
+      <c r="M67" s="17">
         <f>IF(A67="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A67)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>46171</v>
       </c>
@@ -11238,7 +11213,7 @@
         <f>IF(OR(AO67="",N67="",AO67&lt;=0),"",(AO67-N67)/AO67)</f>
         <v>0.0361445783132531</v>
       </c>
-      <c r="W67" s="19">
+      <c r="W67" s="18">
         <f>IF(OR(U67="",V67="",V67&lt;=0),"",U67/V67)</f>
         <v>2.33333333333333</v>
       </c>
@@ -11252,7 +11227,7 @@
       </c>
       <c r="Z67" s="7">
         <f>IF(OR(AE67="",多次统计数据!$B$8=""),"",AE67-多次统计数据!$B$8)</f>
-        <v>0.0471161160262407</v>
+        <v>0.0477209180746994</v>
       </c>
       <c r="AA67" s="11">
         <f>IF(OR(I67="",M67="",M67&lt;I67),"",M67-I67)</f>
@@ -11260,7 +11235,7 @@
       </c>
       <c r="AB67" s="7">
         <f>IF(OR(A67="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC67" s="8" t="str">
         <f>IF(OR(AB67="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB67,"低于上限","达到或超过上限"))</f>
@@ -11295,7 +11270,7 @@
         <v>0</v>
       </c>
       <c r="AR67" s="8" t="str">
-        <f ca="1">IF(A67="","",IF(OR(E67="",H67=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK67="",AL67&lt;&gt;""),AND(AK67&lt;&gt;"",AL67="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM67="",AN67&lt;&gt;""),AND(AM67&lt;&gt;"",AN67="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM67&lt;&gt;"",AN67&lt;&gt;""),OR(AK67="",AL67="")),"违规：必须先完成第二批",IF(OR(H67&lt;=0,H67&lt;&gt;INT(H67),MOD(H67,100)&lt;&gt;0,AND(AL67&lt;&gt;"",OR(AL67&lt;=0,AL67&lt;&gt;INT(AL67),MOD(AL67,100)&lt;&gt;0)),AND(AN67&lt;&gt;"",OR(AN67&lt;=0,AN67&lt;&gt;INT(AN67),MOD(AN67,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL67&lt;&gt;"",AN67&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ67&gt;C67*D67,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A67="","",IF(OR(E67="",H67=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK67="",AL67&lt;&gt;""),AND(AK67&lt;&gt;"",AL67="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM67="",AN67&lt;&gt;""),AND(AM67&lt;&gt;"",AN67="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM67&lt;&gt;"",AN67&lt;&gt;""),OR(AK67="",AL67="")),"违规：必须先完成第二批",IF(OR(H67&lt;=0,H67&lt;&gt;INT(H67),MOD(H67,100)&lt;&gt;0,AND(AL67&lt;&gt;"",OR(AL67&lt;=0,AL67&lt;&gt;INT(AL67),MOD(AL67,100)&lt;&gt;0)),AND(AN67&lt;&gt;"",OR(AN67&lt;=0,AN67&lt;&gt;INT(AN67),MOD(AN67,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL67&lt;&gt;"",AN67&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ67&gt;C67*D67,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -11340,7 +11315,7 @@
         <f>IF(A68="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A68)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>27400</v>
       </c>
-      <c r="M68" s="18">
+      <c r="M68" s="17">
         <f>IF(A68="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A68)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41362</v>
       </c>
@@ -11364,7 +11339,7 @@
         <f>IF(OR(AO68="",N68="",AO68&lt;=0),"",(AO68-N68)/AO68)</f>
         <v>0.0454545454545455</v>
       </c>
-      <c r="W68" s="19">
+      <c r="W68" s="18">
         <f>IF(OR(U68="",V68="",V68&lt;=0),"",U68/V68)</f>
         <v>3</v>
       </c>
@@ -11378,7 +11353,7 @@
       </c>
       <c r="Z68" s="7">
         <f>IF(OR(AE68="",多次统计数据!$B$8=""),"",AE68-多次统计数据!$B$8)</f>
-        <v>-0.128441532851383</v>
+        <v>-0.127836730802924</v>
       </c>
       <c r="AA68" s="11">
         <f>IF(OR(I68="",M68="",M68&lt;I68),"",M68-I68)</f>
@@ -11386,7 +11361,7 @@
       </c>
       <c r="AB68" s="7">
         <f>IF(OR(A68="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC68" s="8" t="str">
         <f>IF(OR(AB68="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB68,"低于上限","达到或超过上限"))</f>
@@ -11421,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="AR68" s="8" t="str">
-        <f ca="1">IF(A68="","",IF(OR(E68="",H68=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK68="",AL68&lt;&gt;""),AND(AK68&lt;&gt;"",AL68="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM68="",AN68&lt;&gt;""),AND(AM68&lt;&gt;"",AN68="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM68&lt;&gt;"",AN68&lt;&gt;""),OR(AK68="",AL68="")),"违规：必须先完成第二批",IF(OR(H68&lt;=0,H68&lt;&gt;INT(H68),MOD(H68,100)&lt;&gt;0,AND(AL68&lt;&gt;"",OR(AL68&lt;=0,AL68&lt;&gt;INT(AL68),MOD(AL68,100)&lt;&gt;0)),AND(AN68&lt;&gt;"",OR(AN68&lt;=0,AN68&lt;&gt;INT(AN68),MOD(AN68,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL68&lt;&gt;"",AN68&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ68&gt;C68*D68,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A68="","",IF(OR(E68="",H68=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK68="",AL68&lt;&gt;""),AND(AK68&lt;&gt;"",AL68="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM68="",AN68&lt;&gt;""),AND(AM68&lt;&gt;"",AN68="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM68&lt;&gt;"",AN68&lt;&gt;""),OR(AK68="",AL68="")),"违规：必须先完成第二批",IF(OR(H68&lt;=0,H68&lt;&gt;INT(H68),MOD(H68,100)&lt;&gt;0,AND(AL68&lt;&gt;"",OR(AL68&lt;=0,AL68&lt;&gt;INT(AL68),MOD(AL68,100)&lt;&gt;0)),AND(AN68&lt;&gt;"",OR(AN68&lt;=0,AN68&lt;&gt;INT(AN68),MOD(AN68,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL68&lt;&gt;"",AN68&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ68&gt;C68*D68,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -11466,7 +11441,7 @@
         <f>IF(A69="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A69)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>47100</v>
       </c>
-      <c r="M69" s="18">
+      <c r="M69" s="17">
         <f>IF(A69="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A69)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41390</v>
       </c>
@@ -11490,7 +11465,7 @@
         <f>IF(OR(AO69="",N69="",AO69&lt;=0),"",(AO69-N69)/AO69)</f>
         <v>0.0238611713665944</v>
       </c>
-      <c r="W69" s="19">
+      <c r="W69" s="18">
         <f>IF(OR(U69="",V69="",V69&lt;=0),"",U69/V69)</f>
         <v>3.54545454545453</v>
       </c>
@@ -11504,7 +11479,7 @@
       </c>
       <c r="Z69" s="7">
         <f>IF(OR(AE69="",多次统计数据!$B$8=""),"",AE69-多次统计数据!$B$8)</f>
-        <v>0.196406273320498</v>
+        <v>0.197011075368957</v>
       </c>
       <c r="AA69" s="11">
         <f>IF(OR(I69="",M69="",M69&lt;I69),"",M69-I69)</f>
@@ -11512,7 +11487,7 @@
       </c>
       <c r="AB69" s="7">
         <f>IF(OR(A69="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC69" s="8" t="str">
         <f>IF(OR(AB69="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB69,"低于上限","达到或超过上限"))</f>
@@ -11547,7 +11522,7 @@
         <v>0</v>
       </c>
       <c r="AR69" s="8" t="str">
-        <f ca="1">IF(A69="","",IF(OR(E69="",H69=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK69="",AL69&lt;&gt;""),AND(AK69&lt;&gt;"",AL69="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM69="",AN69&lt;&gt;""),AND(AM69&lt;&gt;"",AN69="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM69&lt;&gt;"",AN69&lt;&gt;""),OR(AK69="",AL69="")),"违规：必须先完成第二批",IF(OR(H69&lt;=0,H69&lt;&gt;INT(H69),MOD(H69,100)&lt;&gt;0,AND(AL69&lt;&gt;"",OR(AL69&lt;=0,AL69&lt;&gt;INT(AL69),MOD(AL69,100)&lt;&gt;0)),AND(AN69&lt;&gt;"",OR(AN69&lt;=0,AN69&lt;&gt;INT(AN69),MOD(AN69,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL69&lt;&gt;"",AN69&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ69&gt;C69*D69,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A69="","",IF(OR(E69="",H69=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK69="",AL69&lt;&gt;""),AND(AK69&lt;&gt;"",AL69="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM69="",AN69&lt;&gt;""),AND(AM69&lt;&gt;"",AN69="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM69&lt;&gt;"",AN69&lt;&gt;""),OR(AK69="",AL69="")),"违规：必须先完成第二批",IF(OR(H69&lt;=0,H69&lt;&gt;INT(H69),MOD(H69,100)&lt;&gt;0,AND(AL69&lt;&gt;"",OR(AL69&lt;=0,AL69&lt;&gt;INT(AL69),MOD(AL69,100)&lt;&gt;0)),AND(AN69&lt;&gt;"",OR(AN69&lt;=0,AN69&lt;&gt;INT(AN69),MOD(AN69,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL69&lt;&gt;"",AN69&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ69&gt;C69*D69,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -11592,7 +11567,7 @@
         <f>IF(A70="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A70)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>9200</v>
       </c>
-      <c r="M70" s="18">
+      <c r="M70" s="17">
         <f>IF(A70="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A70)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41478</v>
       </c>
@@ -11616,7 +11591,7 @@
         <f>IF(OR(AO70="",N70="",AO70&lt;=0),"",(AO70-N70)/AO70)</f>
         <v>0.0864799025578564</v>
       </c>
-      <c r="W70" s="19">
+      <c r="W70" s="18">
         <f>IF(OR(U70="",V70="",V70&lt;=0),"",U70/V70)</f>
         <v>1.11267605633803</v>
       </c>
@@ -11630,7 +11605,7 @@
       </c>
       <c r="Z70" s="7">
         <f>IF(OR(AE70="",多次统计数据!$B$8=""),"",AE70-多次统计数据!$B$8)</f>
-        <v>-0.0655553860422991</v>
+        <v>-0.0649505839938403</v>
       </c>
       <c r="AA70" s="11">
         <f>IF(OR(I70="",M70="",M70&lt;I70),"",M70-I70)</f>
@@ -11638,7 +11613,7 @@
       </c>
       <c r="AB70" s="7">
         <f>IF(OR(A70="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC70" s="8" t="str">
         <f>IF(OR(AB70="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB70,"低于上限","达到或超过上限"))</f>
@@ -11673,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="AR70" s="8" t="str">
-        <f ca="1">IF(A70="","",IF(OR(E70="",H70=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK70="",AL70&lt;&gt;""),AND(AK70&lt;&gt;"",AL70="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM70="",AN70&lt;&gt;""),AND(AM70&lt;&gt;"",AN70="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM70&lt;&gt;"",AN70&lt;&gt;""),OR(AK70="",AL70="")),"违规：必须先完成第二批",IF(OR(H70&lt;=0,H70&lt;&gt;INT(H70),MOD(H70,100)&lt;&gt;0,AND(AL70&lt;&gt;"",OR(AL70&lt;=0,AL70&lt;&gt;INT(AL70),MOD(AL70,100)&lt;&gt;0)),AND(AN70&lt;&gt;"",OR(AN70&lt;=0,AN70&lt;&gt;INT(AN70),MOD(AN70,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL70&lt;&gt;"",AN70&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ70&gt;C70*D70,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A70="","",IF(OR(E70="",H70=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK70="",AL70&lt;&gt;""),AND(AK70&lt;&gt;"",AL70="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM70="",AN70&lt;&gt;""),AND(AM70&lt;&gt;"",AN70="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM70&lt;&gt;"",AN70&lt;&gt;""),OR(AK70="",AL70="")),"违规：必须先完成第二批",IF(OR(H70&lt;=0,H70&lt;&gt;INT(H70),MOD(H70,100)&lt;&gt;0,AND(AL70&lt;&gt;"",OR(AL70&lt;=0,AL70&lt;&gt;INT(AL70),MOD(AL70,100)&lt;&gt;0)),AND(AN70&lt;&gt;"",OR(AN70&lt;=0,AN70&lt;&gt;INT(AN70),MOD(AN70,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL70&lt;&gt;"",AN70&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ70&gt;C70*D70,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -11718,7 +11693,7 @@
         <f>IF(A71="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A71)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>12000</v>
       </c>
-      <c r="M71" s="18">
+      <c r="M71" s="17">
         <f>IF(A71="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A71)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41501</v>
       </c>
@@ -11742,7 +11717,7 @@
         <f>IF(OR(AO71="",N71="",AO71&lt;=0),"",(AO71-N71)/AO71)</f>
         <v>0.0628571428571429</v>
       </c>
-      <c r="W71" s="19">
+      <c r="W71" s="18">
         <f>IF(OR(U71="",V71="",V71&lt;=0),"",U71/V71)</f>
         <v>2.27272727272727</v>
       </c>
@@ -11756,7 +11731,7 @@
       </c>
       <c r="Z71" s="7">
         <f>IF(OR(AE71="",多次统计数据!$B$8=""),"",AE71-多次统计数据!$B$8)</f>
-        <v>-0.10081043513519</v>
+        <v>-0.100205633086731</v>
       </c>
       <c r="AA71" s="11">
         <f>IF(OR(I71="",M71="",M71&lt;I71),"",M71-I71)</f>
@@ -11764,7 +11739,7 @@
       </c>
       <c r="AB71" s="7">
         <f>IF(OR(A71="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC71" s="8" t="str">
         <f>IF(OR(AB71="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB71,"低于上限","达到或超过上限"))</f>
@@ -11799,7 +11774,7 @@
         <v>0</v>
       </c>
       <c r="AR71" s="8" t="str">
-        <f ca="1">IF(A71="","",IF(OR(E71="",H71=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK71="",AL71&lt;&gt;""),AND(AK71&lt;&gt;"",AL71="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM71="",AN71&lt;&gt;""),AND(AM71&lt;&gt;"",AN71="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM71&lt;&gt;"",AN71&lt;&gt;""),OR(AK71="",AL71="")),"违规：必须先完成第二批",IF(OR(H71&lt;=0,H71&lt;&gt;INT(H71),MOD(H71,100)&lt;&gt;0,AND(AL71&lt;&gt;"",OR(AL71&lt;=0,AL71&lt;&gt;INT(AL71),MOD(AL71,100)&lt;&gt;0)),AND(AN71&lt;&gt;"",OR(AN71&lt;=0,AN71&lt;&gt;INT(AN71),MOD(AN71,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL71&lt;&gt;"",AN71&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ71&gt;C71*D71,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A71="","",IF(OR(E71="",H71=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK71="",AL71&lt;&gt;""),AND(AK71&lt;&gt;"",AL71="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM71="",AN71&lt;&gt;""),AND(AM71&lt;&gt;"",AN71="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM71&lt;&gt;"",AN71&lt;&gt;""),OR(AK71="",AL71="")),"违规：必须先完成第二批",IF(OR(H71&lt;=0,H71&lt;&gt;INT(H71),MOD(H71,100)&lt;&gt;0,AND(AL71&lt;&gt;"",OR(AL71&lt;=0,AL71&lt;&gt;INT(AL71),MOD(AL71,100)&lt;&gt;0)),AND(AN71&lt;&gt;"",OR(AN71&lt;=0,AN71&lt;&gt;INT(AN71),MOD(AN71,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL71&lt;&gt;"",AN71&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ71&gt;C71*D71,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -11844,7 +11819,7 @@
         <f>IF(A72="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A72)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>8600</v>
       </c>
-      <c r="M72" s="18">
+      <c r="M72" s="17">
         <f>IF(A72="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A72)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41516</v>
       </c>
@@ -11868,7 +11843,7 @@
         <f>IF(OR(AO72="",N72="",AO72&lt;=0),"",(AO72-N72)/AO72)</f>
         <v>0.0898058252427185</v>
       </c>
-      <c r="W72" s="19">
+      <c r="W72" s="18">
         <f>IF(OR(U72="",V72="",V72&lt;=0),"",U72/V72)</f>
         <v>2.37837837837838</v>
       </c>
@@ -11882,7 +11857,7 @@
       </c>
       <c r="Z72" s="7">
         <f>IF(OR(AE72="",多次统计数据!$B$8=""),"",AE72-多次统计数据!$B$8)</f>
-        <v>-0.103546454962075</v>
+        <v>-0.102941652913616</v>
       </c>
       <c r="AA72" s="11">
         <f>IF(OR(I72="",M72="",M72&lt;I72),"",M72-I72)</f>
@@ -11890,7 +11865,7 @@
       </c>
       <c r="AB72" s="7">
         <f>IF(OR(A72="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC72" s="8" t="str">
         <f>IF(OR(AB72="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB72,"低于上限","达到或超过上限"))</f>
@@ -11925,133 +11900,133 @@
         <v>0</v>
       </c>
       <c r="AR72" s="8" t="str">
-        <f ca="1">IF(A72="","",IF(OR(E72="",H72=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK72="",AL72&lt;&gt;""),AND(AK72&lt;&gt;"",AL72="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM72="",AN72&lt;&gt;""),AND(AM72&lt;&gt;"",AN72="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM72&lt;&gt;"",AN72&lt;&gt;""),OR(AK72="",AL72="")),"违规：必须先完成第二批",IF(OR(H72&lt;=0,H72&lt;&gt;INT(H72),MOD(H72,100)&lt;&gt;0,AND(AL72&lt;&gt;"",OR(AL72&lt;=0,AL72&lt;&gt;INT(AL72),MOD(AL72,100)&lt;&gt;0)),AND(AN72&lt;&gt;"",OR(AN72&lt;=0,AN72&lt;&gt;INT(AN72),MOD(AN72,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL72&lt;&gt;"",AN72&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ72&gt;C72*D72,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A72="","",IF(OR(E72="",H72=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK72="",AL72&lt;&gt;""),AND(AK72&lt;&gt;"",AL72="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM72="",AN72&lt;&gt;""),AND(AM72&lt;&gt;"",AN72="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM72&lt;&gt;"",AN72&lt;&gt;""),OR(AK72="",AL72="")),"违规：必须先完成第二批",IF(OR(H72&lt;=0,H72&lt;&gt;INT(H72),MOD(H72,100)&lt;&gt;0,AND(AL72&lt;&gt;"",OR(AL72&lt;=0,AL72&lt;&gt;INT(AL72),MOD(AL72,100)&lt;&gt;0)),AND(AN72&lt;&gt;"",OR(AN72&lt;=0,AN72&lt;&gt;INT(AN72),MOD(AN72,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL72&lt;&gt;"",AN72&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ72&gt;C72*D72,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="73" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A73" s="21">
+    <row r="73" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A73" s="20">
         <v>72</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C73" s="23">
+      <c r="C73" s="21">
         <v>311853</v>
       </c>
-      <c r="D73" s="24">
+      <c r="D73" s="22">
         <v>0.02</v>
       </c>
-      <c r="E73" s="23">
+      <c r="E73" s="21">
         <v>8.66</v>
       </c>
-      <c r="F73" s="25">
+      <c r="F73" s="23">
         <f>IF(OR(C73="",D73="",E73="",N73="",C73&lt;=0,D73&lt;=0,E73&lt;=N73),"",ROUNDDOWN((C73*D73)/(E73-N73)/100,0)*100)</f>
         <v>38900</v>
       </c>
-      <c r="G73" s="26" t="str">
+      <c r="G73" s="23" t="str">
         <f ca="1">IF(A73="","",IF(H73&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F73="",E73="",N73="",E73&lt;=N73,账户数据!$B$7=""),"",IF(OR(AG73="",AH73="",AI73=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A73,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F73*(E73-N73)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ73="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H73" s="21">
+      <c r="H73" s="20">
         <v>38900</v>
       </c>
-      <c r="I73" s="27">
+      <c r="I73" s="24">
         <v>41523</v>
       </c>
-      <c r="J73" s="23">
+      <c r="J73" s="21">
         <v>10</v>
       </c>
-      <c r="K73" s="30">
+      <c r="K73" s="25">
         <f>IF(A73="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A73)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>8</v>
       </c>
-      <c r="L73" s="26">
+      <c r="L73" s="23">
         <f>IF(A73="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A73)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>38900</v>
       </c>
-      <c r="M73" s="35">
+      <c r="M73" s="26">
         <f>IF(A73="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A73)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41586</v>
       </c>
-      <c r="N73" s="23">
+      <c r="N73" s="21">
         <v>8.5</v>
       </c>
-      <c r="O73" s="23"/>
-      <c r="P73" s="30" t="str">
+      <c r="O73" s="21"/>
+      <c r="P73" s="25" t="str">
         <f>IF(A73="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A73)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q73" s="21"/>
-      <c r="R73" s="21"/>
-      <c r="S73" s="21"/>
-      <c r="T73" s="21"/>
-      <c r="U73" s="31">
+      <c r="Q73" s="20"/>
+      <c r="R73" s="20"/>
+      <c r="S73" s="20"/>
+      <c r="T73" s="20"/>
+      <c r="U73" s="27">
         <f>IF(OR(AO73="",J73="",AO73&lt;=0),"",(J73-AO73)/AO73)</f>
         <v>0.15473441108545</v>
       </c>
-      <c r="V73" s="31">
+      <c r="V73" s="27">
         <f>IF(OR(AO73="",N73="",AO73&lt;=0),"",(AO73-N73)/AO73)</f>
         <v>0.0184757505773672</v>
       </c>
-      <c r="W73" s="32">
+      <c r="W73" s="28">
         <f>IF(OR(U73="",V73="",V73&lt;=0),"",U73/V73)</f>
         <v>8.37499999999999</v>
       </c>
-      <c r="X73" s="30">
+      <c r="X73" s="25">
         <f>IF(OR(K73="",L73="",AP73=""),"",K73*L73-(E73*H73+IF(AND(AK73&lt;&gt;"",AL73&lt;&gt;""),AK73*AL73,0)+IF(AND(AM73&lt;&gt;"",AN73&lt;&gt;""),AM73*AN73,0))-IF(O73="",0,O73)-IF(P73="",0,P73))</f>
         <v>-25674</v>
       </c>
-      <c r="Y73" s="36">
+      <c r="Y73" s="27">
         <f>IF(OR(X73="",AP73=""),"",IF((E73*H73+IF(AND(AK73&lt;&gt;"",AL73&lt;&gt;""),AK73*AL73,0)+IF(AND(AM73&lt;&gt;"",AN73&lt;&gt;""),AM73*AN73,0))+IF(O73="",0,O73)&lt;=0,"",X73/((E73*H73+IF(AND(AK73&lt;&gt;"",AL73&lt;&gt;""),AK73*AL73,0)+IF(AND(AM73&lt;&gt;"",AN73&lt;&gt;""),AM73*AN73,0))+IF(O73="",0,O73))))</f>
         <v>-0.0762124711316397</v>
       </c>
-      <c r="Z73" s="36">
+      <c r="Z73" s="27">
         <f>IF(OR(AE73="",多次统计数据!$B$8=""),"",AE73-多次统计数据!$B$8)</f>
-        <v>-0.154875877262063</v>
-      </c>
-      <c r="AA73" s="37">
+        <v>-0.154271075213604</v>
+      </c>
+      <c r="AA73" s="29">
         <f>IF(OR(I73="",M73="",M73&lt;I73),"",M73-I73)</f>
         <v>63</v>
       </c>
-      <c r="AB73" s="31">
+      <c r="AB73" s="27">
         <f>IF(OR(A73="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC73" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC73" s="23" t="str">
         <f>IF(OR(AB73="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB73,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD73" s="21"/>
-      <c r="AE73" s="36">
+      <c r="AD73" s="20"/>
+      <c r="AE73" s="27">
         <f>IF(OR(X73="",C73="",C73&lt;=0),"",X73/C73)</f>
         <v>-0.0823272503391021</v>
       </c>
-      <c r="AG73" s="21"/>
-      <c r="AH73" s="21"/>
-      <c r="AI73" s="21"/>
-      <c r="AJ73" s="26" t="str">
+      <c r="AG73" s="20"/>
+      <c r="AH73" s="20"/>
+      <c r="AI73" s="20"/>
+      <c r="AJ73" s="23" t="str">
         <f>IF(OR(AG73="",AH73=""),"",IF(OR(AND(AG73="短期博反弹",OR(AH73="1～3个交易日",AH73="4～10个交易日")),AND(AG73="突破冲新高",OR(AH73="4～10个交易日",AH73="11～20个交易日")),AND(AG73="趋势波段",OR(AH73="11～20个交易日",AH73="21～60个交易日",AH73="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK73" s="23"/>
-      <c r="AL73" s="34"/>
-      <c r="AM73" s="23"/>
-      <c r="AN73" s="34"/>
-      <c r="AO73" s="28">
+      <c r="AK73" s="21"/>
+      <c r="AL73" s="30"/>
+      <c r="AM73" s="21"/>
+      <c r="AN73" s="30"/>
+      <c r="AO73" s="25">
         <f>IF(OR(A73="",H73="",H73&lt;=0),"",(E73*H73+IF(AND(AK73&lt;&gt;"",AL73&lt;&gt;""),AK73*AL73,0)+IF(AND(AM73&lt;&gt;"",AN73&lt;&gt;""),AM73*AN73,0))/AP73)</f>
         <v>8.66</v>
       </c>
-      <c r="AP73" s="33">
+      <c r="AP73" s="29">
         <f>IF(OR(A73="",H73="",H73&lt;=0),"",H73+IF(AL73="",0,AL73)+IF(AN73="",0,AN73))</f>
         <v>38900</v>
       </c>
-      <c r="AQ73" s="28">
+      <c r="AQ73" s="25">
         <f>IF(A73="","",IF(M73&lt;&gt;"",0,IF(OR(H73="",N73=""),"",MAX(E73-MAX(N73,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A73))*持仓跟踪!$S$2:$S$157)),0)),0)*H73+IF(OR(AK73="",AL73=""),0,MAX(AK73-MAX(N73,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A73))*持仓跟踪!$S$2:$S$157)),0)),0)*AL73)+IF(OR(AM73="",AN73=""),0,MAX(AM73-MAX(N73,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A73))*持仓跟踪!$S$2:$S$157)),0)),0)*AN73))))</f>
         <v>0</v>
       </c>
-      <c r="AR73" s="26" t="str">
-        <f ca="1">IF(A73="","",IF(OR(E73="",H73=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK73="",AL73&lt;&gt;""),AND(AK73&lt;&gt;"",AL73="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM73="",AN73&lt;&gt;""),AND(AM73&lt;&gt;"",AN73="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM73&lt;&gt;"",AN73&lt;&gt;""),OR(AK73="",AL73="")),"违规：必须先完成第二批",IF(OR(H73&lt;=0,H73&lt;&gt;INT(H73),MOD(H73,100)&lt;&gt;0,AND(AL73&lt;&gt;"",OR(AL73&lt;=0,AL73&lt;&gt;INT(AL73),MOD(AL73,100)&lt;&gt;0)),AND(AN73&lt;&gt;"",OR(AN73&lt;=0,AN73&lt;&gt;INT(AN73),MOD(AN73,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL73&lt;&gt;"",AN73&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ73&gt;C73*D73,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR73" s="23" t="str">
+        <f ca="1">IF(A73="","",IF(OR(E73="",H73=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK73="",AL73&lt;&gt;""),AND(AK73&lt;&gt;"",AL73="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM73="",AN73&lt;&gt;""),AND(AM73&lt;&gt;"",AN73="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM73&lt;&gt;"",AN73&lt;&gt;""),OR(AK73="",AL73="")),"违规：必须先完成第二批",IF(OR(H73&lt;=0,H73&lt;&gt;INT(H73),MOD(H73,100)&lt;&gt;0,AND(AL73&lt;&gt;"",OR(AL73&lt;=0,AL73&lt;&gt;INT(AL73),MOD(AL73,100)&lt;&gt;0)),AND(AN73&lt;&gt;"",OR(AN73&lt;=0,AN73&lt;&gt;INT(AN73),MOD(AN73,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL73&lt;&gt;"",AN73&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ73&gt;C73*D73,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -12096,7 +12071,7 @@
         <f>IF(A74="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A74)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>12700</v>
       </c>
-      <c r="M74" s="18">
+      <c r="M74" s="17">
         <f>IF(A74="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A74)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41820</v>
       </c>
@@ -12120,7 +12095,7 @@
         <f>IF(OR(AO74="",N74="",AO74&lt;=0),"",(AO74-N74)/AO74)</f>
         <v>0.0376569037656903</v>
       </c>
-      <c r="W74" s="19">
+      <c r="W74" s="18">
         <f>IF(OR(U74="",V74="",V74&lt;=0),"",U74/V74)</f>
         <v>2.33333333333334</v>
       </c>
@@ -12134,7 +12109,7 @@
       </c>
       <c r="Z74" s="7">
         <f>IF(OR(AE74="",多次统计数据!$B$8=""),"",AE74-多次统计数据!$B$8)</f>
-        <v>-0.0561288337166111</v>
+        <v>-0.0555240316681523</v>
       </c>
       <c r="AA74" s="11">
         <f>IF(OR(I74="",M74="",M74&lt;I74),"",M74-I74)</f>
@@ -12142,7 +12117,7 @@
       </c>
       <c r="AB74" s="7">
         <f>IF(OR(A74="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC74" s="8" t="str">
         <f>IF(OR(AB74="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB74,"低于上限","达到或超过上限"))</f>
@@ -12177,133 +12152,133 @@
         <v>0</v>
       </c>
       <c r="AR74" s="8" t="str">
-        <f ca="1">IF(A74="","",IF(OR(E74="",H74=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK74="",AL74&lt;&gt;""),AND(AK74&lt;&gt;"",AL74="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM74="",AN74&lt;&gt;""),AND(AM74&lt;&gt;"",AN74="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM74&lt;&gt;"",AN74&lt;&gt;""),OR(AK74="",AL74="")),"违规：必须先完成第二批",IF(OR(H74&lt;=0,H74&lt;&gt;INT(H74),MOD(H74,100)&lt;&gt;0,AND(AL74&lt;&gt;"",OR(AL74&lt;=0,AL74&lt;&gt;INT(AL74),MOD(AL74,100)&lt;&gt;0)),AND(AN74&lt;&gt;"",OR(AN74&lt;=0,AN74&lt;&gt;INT(AN74),MOD(AN74,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL74&lt;&gt;"",AN74&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ74&gt;C74*D74,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A74="","",IF(OR(E74="",H74=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK74="",AL74&lt;&gt;""),AND(AK74&lt;&gt;"",AL74="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM74="",AN74&lt;&gt;""),AND(AM74&lt;&gt;"",AN74="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM74&lt;&gt;"",AN74&lt;&gt;""),OR(AK74="",AL74="")),"违规：必须先完成第二批",IF(OR(H74&lt;=0,H74&lt;&gt;INT(H74),MOD(H74,100)&lt;&gt;0,AND(AL74&lt;&gt;"",OR(AL74&lt;=0,AL74&lt;&gt;INT(AL74),MOD(AL74,100)&lt;&gt;0)),AND(AN74&lt;&gt;"",OR(AN74&lt;=0,AN74&lt;&gt;INT(AN74),MOD(AN74,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL74&lt;&gt;"",AN74&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ74&gt;C74*D74,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="75" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A75" s="21">
+    <row r="75" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A75" s="20">
         <v>74</v>
       </c>
-      <c r="B75" s="22" t="s">
+      <c r="B75" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="23">
+      <c r="C75" s="21">
         <v>290878</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="22">
         <v>0.02</v>
       </c>
-      <c r="E75" s="23">
+      <c r="E75" s="21">
         <v>12.73</v>
       </c>
-      <c r="F75" s="25">
+      <c r="F75" s="23">
         <f>IF(OR(C75="",D75="",E75="",N75="",C75&lt;=0,D75&lt;=0,E75&lt;=N75),"",ROUNDDOWN((C75*D75)/(E75-N75)/100,0)*100)</f>
         <v>13500</v>
       </c>
-      <c r="G75" s="26" t="str">
+      <c r="G75" s="23" t="str">
         <f ca="1">IF(A75="","",IF(H75&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F75="",E75="",N75="",E75&lt;=N75,账户数据!$B$7=""),"",IF(OR(AG75="",AH75="",AI75=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A75,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F75*(E75-N75)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ75="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H75" s="21">
+      <c r="H75" s="20">
         <v>13500</v>
       </c>
-      <c r="I75" s="27">
+      <c r="I75" s="24">
         <v>41834</v>
       </c>
-      <c r="J75" s="23">
+      <c r="J75" s="21">
         <v>14</v>
       </c>
-      <c r="K75" s="30">
+      <c r="K75" s="25">
         <f>IF(A75="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A75)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>13.79</v>
       </c>
-      <c r="L75" s="26">
+      <c r="L75" s="23">
         <f>IF(A75="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A75)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>13500</v>
       </c>
-      <c r="M75" s="35">
+      <c r="M75" s="26">
         <f>IF(A75="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A75)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41862</v>
       </c>
-      <c r="N75" s="23">
+      <c r="N75" s="21">
         <v>12.3</v>
       </c>
-      <c r="O75" s="23"/>
-      <c r="P75" s="30" t="str">
+      <c r="O75" s="21"/>
+      <c r="P75" s="25" t="str">
         <f>IF(A75="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A75)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q75" s="21"/>
-      <c r="R75" s="21"/>
-      <c r="S75" s="21"/>
-      <c r="T75" s="21"/>
-      <c r="U75" s="31">
+      <c r="Q75" s="20"/>
+      <c r="R75" s="20"/>
+      <c r="S75" s="20"/>
+      <c r="T75" s="20"/>
+      <c r="U75" s="27">
         <f>IF(OR(AO75="",J75="",AO75&lt;=0),"",(J75-AO75)/AO75)</f>
         <v>0.0997643362136685</v>
       </c>
-      <c r="V75" s="31">
+      <c r="V75" s="27">
         <f>IF(OR(AO75="",N75="",AO75&lt;=0),"",(AO75-N75)/AO75)</f>
         <v>0.0337784760408484</v>
       </c>
-      <c r="W75" s="32">
+      <c r="W75" s="28">
         <f>IF(OR(U75="",V75="",V75&lt;=0),"",U75/V75)</f>
         <v>2.95348837209302</v>
       </c>
-      <c r="X75" s="30">
+      <c r="X75" s="25">
         <f>IF(OR(K75="",L75="",AP75=""),"",K75*L75-(E75*H75+IF(AND(AK75&lt;&gt;"",AL75&lt;&gt;""),AK75*AL75,0)+IF(AND(AM75&lt;&gt;"",AN75&lt;&gt;""),AM75*AN75,0))-IF(O75="",0,O75)-IF(P75="",0,P75))</f>
         <v>14310</v>
       </c>
-      <c r="Y75" s="36">
+      <c r="Y75" s="27">
         <f>IF(OR(X75="",AP75=""),"",IF((E75*H75+IF(AND(AK75&lt;&gt;"",AL75&lt;&gt;""),AK75*AL75,0)+IF(AND(AM75&lt;&gt;"",AN75&lt;&gt;""),AM75*AN75,0))+IF(O75="",0,O75)&lt;=0,"",X75/((E75*H75+IF(AND(AK75&lt;&gt;"",AL75&lt;&gt;""),AK75*AL75,0)+IF(AND(AM75&lt;&gt;"",AN75&lt;&gt;""),AM75*AN75,0))+IF(O75="",0,O75))))</f>
         <v>0.0832678711704635</v>
       </c>
-      <c r="Z75" s="36">
+      <c r="Z75" s="27">
         <f>IF(OR(AE75="",多次统计数据!$B$8=""),"",AE75-多次统计数据!$B$8)</f>
-        <v>-0.0233527441129856</v>
-      </c>
-      <c r="AA75" s="37">
+        <v>-0.0227479420645269</v>
+      </c>
+      <c r="AA75" s="29">
         <f>IF(OR(I75="",M75="",M75&lt;I75),"",M75-I75)</f>
         <v>28</v>
       </c>
-      <c r="AB75" s="31">
+      <c r="AB75" s="27">
         <f>IF(OR(A75="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC75" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC75" s="23" t="str">
         <f>IF(OR(AB75="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB75,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD75" s="21"/>
-      <c r="AE75" s="36">
+      <c r="AD75" s="20"/>
+      <c r="AE75" s="27">
         <f>IF(OR(X75="",C75="",C75&lt;=0),"",X75/C75)</f>
         <v>0.0491958828099753</v>
       </c>
-      <c r="AG75" s="21"/>
-      <c r="AH75" s="21"/>
-      <c r="AI75" s="21"/>
-      <c r="AJ75" s="26" t="str">
+      <c r="AG75" s="20"/>
+      <c r="AH75" s="20"/>
+      <c r="AI75" s="20"/>
+      <c r="AJ75" s="23" t="str">
         <f>IF(OR(AG75="",AH75=""),"",IF(OR(AND(AG75="短期博反弹",OR(AH75="1～3个交易日",AH75="4～10个交易日")),AND(AG75="突破冲新高",OR(AH75="4～10个交易日",AH75="11～20个交易日")),AND(AG75="趋势波段",OR(AH75="11～20个交易日",AH75="21～60个交易日",AH75="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK75" s="23"/>
-      <c r="AL75" s="34"/>
-      <c r="AM75" s="23"/>
-      <c r="AN75" s="34"/>
-      <c r="AO75" s="28">
+      <c r="AK75" s="21"/>
+      <c r="AL75" s="30"/>
+      <c r="AM75" s="21"/>
+      <c r="AN75" s="30"/>
+      <c r="AO75" s="25">
         <f>IF(OR(A75="",H75="",H75&lt;=0),"",(E75*H75+IF(AND(AK75&lt;&gt;"",AL75&lt;&gt;""),AK75*AL75,0)+IF(AND(AM75&lt;&gt;"",AN75&lt;&gt;""),AM75*AN75,0))/AP75)</f>
         <v>12.73</v>
       </c>
-      <c r="AP75" s="33">
+      <c r="AP75" s="29">
         <f>IF(OR(A75="",H75="",H75&lt;=0),"",H75+IF(AL75="",0,AL75)+IF(AN75="",0,AN75))</f>
         <v>13500</v>
       </c>
-      <c r="AQ75" s="28">
+      <c r="AQ75" s="25">
         <f>IF(A75="","",IF(M75&lt;&gt;"",0,IF(OR(H75="",N75=""),"",MAX(E75-MAX(N75,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A75))*持仓跟踪!$S$2:$S$157)),0)),0)*H75+IF(OR(AK75="",AL75=""),0,MAX(AK75-MAX(N75,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A75))*持仓跟踪!$S$2:$S$157)),0)),0)*AL75)+IF(OR(AM75="",AN75=""),0,MAX(AM75-MAX(N75,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A75))*持仓跟踪!$S$2:$S$157)),0)),0)*AN75))))</f>
         <v>0</v>
       </c>
-      <c r="AR75" s="26" t="str">
-        <f ca="1">IF(A75="","",IF(OR(E75="",H75=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK75="",AL75&lt;&gt;""),AND(AK75&lt;&gt;"",AL75="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM75="",AN75&lt;&gt;""),AND(AM75&lt;&gt;"",AN75="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM75&lt;&gt;"",AN75&lt;&gt;""),OR(AK75="",AL75="")),"违规：必须先完成第二批",IF(OR(H75&lt;=0,H75&lt;&gt;INT(H75),MOD(H75,100)&lt;&gt;0,AND(AL75&lt;&gt;"",OR(AL75&lt;=0,AL75&lt;&gt;INT(AL75),MOD(AL75,100)&lt;&gt;0)),AND(AN75&lt;&gt;"",OR(AN75&lt;=0,AN75&lt;&gt;INT(AN75),MOD(AN75,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL75&lt;&gt;"",AN75&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ75&gt;C75*D75,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR75" s="23" t="str">
+        <f ca="1">IF(A75="","",IF(OR(E75="",H75=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK75="",AL75&lt;&gt;""),AND(AK75&lt;&gt;"",AL75="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM75="",AN75&lt;&gt;""),AND(AM75&lt;&gt;"",AN75="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM75&lt;&gt;"",AN75&lt;&gt;""),OR(AK75="",AL75="")),"违规：必须先完成第二批",IF(OR(H75&lt;=0,H75&lt;&gt;INT(H75),MOD(H75,100)&lt;&gt;0,AND(AL75&lt;&gt;"",OR(AL75&lt;=0,AL75&lt;&gt;INT(AL75),MOD(AL75,100)&lt;&gt;0)),AND(AN75&lt;&gt;"",OR(AN75&lt;=0,AN75&lt;&gt;INT(AN75),MOD(AN75,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL75&lt;&gt;"",AN75&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ75&gt;C75*D75,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -12348,7 +12323,7 @@
         <f>IF(A76="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A76)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>11700</v>
       </c>
-      <c r="M76" s="18">
+      <c r="M76" s="17">
         <f>IF(A76="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A76)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41933</v>
       </c>
@@ -12372,7 +12347,7 @@
         <f>IF(OR(AO76="",N76="",AO76&lt;=0),"",(AO76-N76)/AO76)</f>
         <v>0.0399385560675883</v>
       </c>
-      <c r="W76" s="19">
+      <c r="W76" s="18">
         <f>IF(OR(U76="",V76="",V76&lt;=0),"",U76/V76)</f>
         <v>1.88461538461539</v>
       </c>
@@ -12386,7 +12361,7 @@
       </c>
       <c r="Z76" s="7">
         <f>IF(OR(AE76="",多次统计数据!$B$8=""),"",AE76-多次统计数据!$B$8)</f>
-        <v>-0.101301395708103</v>
+        <v>-0.100696593659644</v>
       </c>
       <c r="AA76" s="11">
         <f>IF(OR(I76="",M76="",M76&lt;I76),"",M76-I76)</f>
@@ -12394,7 +12369,7 @@
       </c>
       <c r="AB76" s="7">
         <f>IF(OR(A76="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC76" s="8" t="str">
         <f>IF(OR(AB76="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB76,"低于上限","达到或超过上限"))</f>
@@ -12429,7 +12404,7 @@
         <v>0</v>
       </c>
       <c r="AR76" s="8" t="str">
-        <f ca="1">IF(A76="","",IF(OR(E76="",H76=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK76="",AL76&lt;&gt;""),AND(AK76&lt;&gt;"",AL76="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM76="",AN76&lt;&gt;""),AND(AM76&lt;&gt;"",AN76="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM76&lt;&gt;"",AN76&lt;&gt;""),OR(AK76="",AL76="")),"违规：必须先完成第二批",IF(OR(H76&lt;=0,H76&lt;&gt;INT(H76),MOD(H76,100)&lt;&gt;0,AND(AL76&lt;&gt;"",OR(AL76&lt;=0,AL76&lt;&gt;INT(AL76),MOD(AL76,100)&lt;&gt;0)),AND(AN76&lt;&gt;"",OR(AN76&lt;=0,AN76&lt;&gt;INT(AN76),MOD(AN76,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL76&lt;&gt;"",AN76&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ76&gt;C76*D76,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A76="","",IF(OR(E76="",H76=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK76="",AL76&lt;&gt;""),AND(AK76&lt;&gt;"",AL76="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM76="",AN76&lt;&gt;""),AND(AM76&lt;&gt;"",AN76="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM76&lt;&gt;"",AN76&lt;&gt;""),OR(AK76="",AL76="")),"违规：必须先完成第二批",IF(OR(H76&lt;=0,H76&lt;&gt;INT(H76),MOD(H76,100)&lt;&gt;0,AND(AL76&lt;&gt;"",OR(AL76&lt;=0,AL76&lt;&gt;INT(AL76),MOD(AL76,100)&lt;&gt;0)),AND(AN76&lt;&gt;"",OR(AN76&lt;=0,AN76&lt;&gt;INT(AN76),MOD(AN76,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL76&lt;&gt;"",AN76&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ76&gt;C76*D76,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -12474,7 +12449,7 @@
         <f>IF(A77="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A77)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>15200</v>
       </c>
-      <c r="M77" s="18">
+      <c r="M77" s="17">
         <f>IF(A77="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A77)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>41981</v>
       </c>
@@ -12498,7 +12473,7 @@
         <f>IF(OR(AO77="",N77="",AO77&lt;=0),"",(AO77-N77)/AO77)</f>
         <v>0.0358126721763086</v>
       </c>
-      <c r="W77" s="19">
+      <c r="W77" s="18">
         <f>IF(OR(U77="",V77="",V77&lt;=0),"",U77/V77)</f>
         <v>2.84615384615384</v>
       </c>
@@ -12512,7 +12487,7 @@
       </c>
       <c r="Z77" s="7">
         <f>IF(OR(AE77="",多次统计数据!$B$8=""),"",AE77-多次统计数据!$B$8)</f>
-        <v>-0.0930605477901294</v>
+        <v>-0.0924557457416706</v>
       </c>
       <c r="AA77" s="11">
         <f>IF(OR(I77="",M77="",M77&lt;I77),"",M77-I77)</f>
@@ -12520,7 +12495,7 @@
       </c>
       <c r="AB77" s="7">
         <f>IF(OR(A77="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC77" s="8" t="str">
         <f>IF(OR(AB77="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB77,"低于上限","达到或超过上限"))</f>
@@ -12555,133 +12530,133 @@
         <v>0</v>
       </c>
       <c r="AR77" s="8" t="str">
-        <f ca="1">IF(A77="","",IF(OR(E77="",H77=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK77="",AL77&lt;&gt;""),AND(AK77&lt;&gt;"",AL77="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM77="",AN77&lt;&gt;""),AND(AM77&lt;&gt;"",AN77="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM77&lt;&gt;"",AN77&lt;&gt;""),OR(AK77="",AL77="")),"违规：必须先完成第二批",IF(OR(H77&lt;=0,H77&lt;&gt;INT(H77),MOD(H77,100)&lt;&gt;0,AND(AL77&lt;&gt;"",OR(AL77&lt;=0,AL77&lt;&gt;INT(AL77),MOD(AL77,100)&lt;&gt;0)),AND(AN77&lt;&gt;"",OR(AN77&lt;=0,AN77&lt;&gt;INT(AN77),MOD(AN77,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL77&lt;&gt;"",AN77&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ77&gt;C77*D77,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A77="","",IF(OR(E77="",H77=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK77="",AL77&lt;&gt;""),AND(AK77&lt;&gt;"",AL77="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM77="",AN77&lt;&gt;""),AND(AM77&lt;&gt;"",AN77="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM77&lt;&gt;"",AN77&lt;&gt;""),OR(AK77="",AL77="")),"违规：必须先完成第二批",IF(OR(H77&lt;=0,H77&lt;&gt;INT(H77),MOD(H77,100)&lt;&gt;0,AND(AL77&lt;&gt;"",OR(AL77&lt;=0,AL77&lt;&gt;INT(AL77),MOD(AL77,100)&lt;&gt;0)),AND(AN77&lt;&gt;"",OR(AN77&lt;=0,AN77&lt;&gt;INT(AN77),MOD(AN77,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL77&lt;&gt;"",AN77&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ77&gt;C77*D77,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="78" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A78" s="21">
+    <row r="78" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A78" s="20">
         <v>77</v>
       </c>
-      <c r="B78" s="22" t="s">
+      <c r="B78" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C78" s="23">
+      <c r="C78" s="21">
         <v>290333</v>
       </c>
-      <c r="D78" s="24">
+      <c r="D78" s="22">
         <v>0.02</v>
       </c>
-      <c r="E78" s="23">
+      <c r="E78" s="21">
         <v>17.46</v>
       </c>
-      <c r="F78" s="25">
+      <c r="F78" s="23">
         <f>IF(OR(C78="",D78="",E78="",N78="",C78&lt;=0,D78&lt;=0,E78&lt;=N78),"",ROUNDDOWN((C78*D78)/(E78-N78)/100,0)*100)</f>
         <v>3900</v>
       </c>
-      <c r="G78" s="26" t="str">
+      <c r="G78" s="23" t="str">
         <f ca="1">IF(A78="","",IF(H78&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F78="",E78="",N78="",E78&lt;=N78,账户数据!$B$7=""),"",IF(OR(AG78="",AH78="",AI78=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A78,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F78*(E78-N78)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ78="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H78" s="21">
+      <c r="H78" s="20">
         <v>3900</v>
       </c>
-      <c r="I78" s="27">
+      <c r="I78" s="24">
         <v>42347</v>
       </c>
-      <c r="J78" s="23">
+      <c r="J78" s="21">
         <v>20</v>
       </c>
-      <c r="K78" s="30">
+      <c r="K78" s="25">
         <f>IF(A78="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A78)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>11.51</v>
       </c>
-      <c r="L78" s="26">
+      <c r="L78" s="23">
         <f>IF(A78="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A78)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>3900</v>
       </c>
-      <c r="M78" s="35">
+      <c r="M78" s="26">
         <f>IF(A78="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A78)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42396</v>
       </c>
-      <c r="N78" s="23">
+      <c r="N78" s="21">
         <v>16</v>
       </c>
-      <c r="O78" s="23"/>
-      <c r="P78" s="30" t="str">
+      <c r="O78" s="21"/>
+      <c r="P78" s="25" t="str">
         <f>IF(A78="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A78)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q78" s="21"/>
-      <c r="R78" s="21"/>
-      <c r="S78" s="21"/>
-      <c r="T78" s="21"/>
-      <c r="U78" s="31">
+      <c r="Q78" s="20"/>
+      <c r="R78" s="20"/>
+      <c r="S78" s="20"/>
+      <c r="T78" s="20"/>
+      <c r="U78" s="27">
         <f>IF(OR(AO78="",J78="",AO78&lt;=0),"",(J78-AO78)/AO78)</f>
         <v>0.145475372279496</v>
       </c>
-      <c r="V78" s="31">
+      <c r="V78" s="27">
         <f>IF(OR(AO78="",N78="",AO78&lt;=0),"",(AO78-N78)/AO78)</f>
         <v>0.0836197021764033</v>
       </c>
-      <c r="W78" s="32">
+      <c r="W78" s="28">
         <f>IF(OR(U78="",V78="",V78&lt;=0),"",U78/V78)</f>
         <v>1.73972602739726</v>
       </c>
-      <c r="X78" s="30">
+      <c r="X78" s="25">
         <f>IF(OR(K78="",L78="",AP78=""),"",K78*L78-(E78*H78+IF(AND(AK78&lt;&gt;"",AL78&lt;&gt;""),AK78*AL78,0)+IF(AND(AM78&lt;&gt;"",AN78&lt;&gt;""),AM78*AN78,0))-IF(O78="",0,O78)-IF(P78="",0,P78))</f>
         <v>-23205</v>
       </c>
-      <c r="Y78" s="36">
+      <c r="Y78" s="27">
         <f>IF(OR(X78="",AP78=""),"",IF((E78*H78+IF(AND(AK78&lt;&gt;"",AL78&lt;&gt;""),AK78*AL78,0)+IF(AND(AM78&lt;&gt;"",AN78&lt;&gt;""),AM78*AN78,0))+IF(O78="",0,O78)&lt;=0,"",X78/((E78*H78+IF(AND(AK78&lt;&gt;"",AL78&lt;&gt;""),AK78*AL78,0)+IF(AND(AM78&lt;&gt;"",AN78&lt;&gt;""),AM78*AN78,0))+IF(O78="",0,O78))))</f>
         <v>-0.34077892325315</v>
       </c>
-      <c r="Z78" s="36">
+      <c r="Z78" s="27">
         <f>IF(OR(AE78="",多次统计数据!$B$8=""),"",AE78-多次统计数据!$B$8)</f>
-        <v>-0.152474091820165</v>
-      </c>
-      <c r="AA78" s="37">
+        <v>-0.151869289771706</v>
+      </c>
+      <c r="AA78" s="29">
         <f>IF(OR(I78="",M78="",M78&lt;I78),"",M78-I78)</f>
         <v>49</v>
       </c>
-      <c r="AB78" s="31">
+      <c r="AB78" s="27">
         <f>IF(OR(A78="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC78" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC78" s="23" t="str">
         <f>IF(OR(AB78="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB78,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD78" s="21"/>
-      <c r="AE78" s="36">
+      <c r="AD78" s="20"/>
+      <c r="AE78" s="27">
         <f>IF(OR(X78="",C78="",C78&lt;=0),"",X78/C78)</f>
         <v>-0.0799254648972042</v>
       </c>
-      <c r="AG78" s="21"/>
-      <c r="AH78" s="21"/>
-      <c r="AI78" s="21"/>
-      <c r="AJ78" s="26" t="str">
+      <c r="AG78" s="20"/>
+      <c r="AH78" s="20"/>
+      <c r="AI78" s="20"/>
+      <c r="AJ78" s="23" t="str">
         <f>IF(OR(AG78="",AH78=""),"",IF(OR(AND(AG78="短期博反弹",OR(AH78="1～3个交易日",AH78="4～10个交易日")),AND(AG78="突破冲新高",OR(AH78="4～10个交易日",AH78="11～20个交易日")),AND(AG78="趋势波段",OR(AH78="11～20个交易日",AH78="21～60个交易日",AH78="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK78" s="23"/>
-      <c r="AL78" s="34"/>
-      <c r="AM78" s="23"/>
-      <c r="AN78" s="34"/>
-      <c r="AO78" s="28">
+      <c r="AK78" s="21"/>
+      <c r="AL78" s="30"/>
+      <c r="AM78" s="21"/>
+      <c r="AN78" s="30"/>
+      <c r="AO78" s="25">
         <f>IF(OR(A78="",H78="",H78&lt;=0),"",(E78*H78+IF(AND(AK78&lt;&gt;"",AL78&lt;&gt;""),AK78*AL78,0)+IF(AND(AM78&lt;&gt;"",AN78&lt;&gt;""),AM78*AN78,0))/AP78)</f>
         <v>17.46</v>
       </c>
-      <c r="AP78" s="33">
+      <c r="AP78" s="29">
         <f>IF(OR(A78="",H78="",H78&lt;=0),"",H78+IF(AL78="",0,AL78)+IF(AN78="",0,AN78))</f>
         <v>3900</v>
       </c>
-      <c r="AQ78" s="28">
+      <c r="AQ78" s="25">
         <f>IF(A78="","",IF(M78&lt;&gt;"",0,IF(OR(H78="",N78=""),"",MAX(E78-MAX(N78,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A78))*持仓跟踪!$S$2:$S$157)),0)),0)*H78+IF(OR(AK78="",AL78=""),0,MAX(AK78-MAX(N78,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A78))*持仓跟踪!$S$2:$S$157)),0)),0)*AL78)+IF(OR(AM78="",AN78=""),0,MAX(AM78-MAX(N78,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A78))*持仓跟踪!$S$2:$S$157)),0)),0)*AN78))))</f>
         <v>0</v>
       </c>
-      <c r="AR78" s="26" t="str">
-        <f ca="1">IF(A78="","",IF(OR(E78="",H78=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK78="",AL78&lt;&gt;""),AND(AK78&lt;&gt;"",AL78="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM78="",AN78&lt;&gt;""),AND(AM78&lt;&gt;"",AN78="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM78&lt;&gt;"",AN78&lt;&gt;""),OR(AK78="",AL78="")),"违规：必须先完成第二批",IF(OR(H78&lt;=0,H78&lt;&gt;INT(H78),MOD(H78,100)&lt;&gt;0,AND(AL78&lt;&gt;"",OR(AL78&lt;=0,AL78&lt;&gt;INT(AL78),MOD(AL78,100)&lt;&gt;0)),AND(AN78&lt;&gt;"",OR(AN78&lt;=0,AN78&lt;&gt;INT(AN78),MOD(AN78,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL78&lt;&gt;"",AN78&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ78&gt;C78*D78,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR78" s="23" t="str">
+        <f ca="1">IF(A78="","",IF(OR(E78="",H78=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK78="",AL78&lt;&gt;""),AND(AK78&lt;&gt;"",AL78="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM78="",AN78&lt;&gt;""),AND(AM78&lt;&gt;"",AN78="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM78&lt;&gt;"",AN78&lt;&gt;""),OR(AK78="",AL78="")),"违规：必须先完成第二批",IF(OR(H78&lt;=0,H78&lt;&gt;INT(H78),MOD(H78,100)&lt;&gt;0,AND(AL78&lt;&gt;"",OR(AL78&lt;=0,AL78&lt;&gt;INT(AL78),MOD(AL78,100)&lt;&gt;0)),AND(AN78&lt;&gt;"",OR(AN78&lt;=0,AN78&lt;&gt;INT(AN78),MOD(AN78,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL78&lt;&gt;"",AN78&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ78&gt;C78*D78,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -12726,7 +12701,7 @@
         <f>IF(A79="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A79)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>10900</v>
       </c>
-      <c r="M79" s="18">
+      <c r="M79" s="17">
         <f>IF(A79="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A79)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42473</v>
       </c>
@@ -12750,7 +12725,7 @@
         <f>IF(OR(AO79="",N79="",AO79&lt;=0),"",(AO79-N79)/AO79)</f>
         <v>0.0316333118140736</v>
       </c>
-      <c r="W79" s="19">
+      <c r="W79" s="18">
         <f>IF(OR(U79="",V79="",V79&lt;=0),"",U79/V79)</f>
         <v>2.06122448979592</v>
       </c>
@@ -12764,7 +12739,7 @@
       </c>
       <c r="Z79" s="7">
         <f>IF(OR(AE79="",多次统计数据!$B$8=""),"",AE79-多次统计数据!$B$8)</f>
-        <v>-0.0505142464012635</v>
+        <v>-0.0499094443528047</v>
       </c>
       <c r="AA79" s="11">
         <f>IF(OR(I79="",M79="",M79&lt;I79),"",M79-I79)</f>
@@ -12772,7 +12747,7 @@
       </c>
       <c r="AB79" s="7">
         <f>IF(OR(A79="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC79" s="8" t="str">
         <f>IF(OR(AB79="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB79,"低于上限","达到或超过上限"))</f>
@@ -12807,7 +12782,7 @@
         <v>0</v>
       </c>
       <c r="AR79" s="8" t="str">
-        <f ca="1">IF(A79="","",IF(OR(E79="",H79=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK79="",AL79&lt;&gt;""),AND(AK79&lt;&gt;"",AL79="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM79="",AN79&lt;&gt;""),AND(AM79&lt;&gt;"",AN79="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM79&lt;&gt;"",AN79&lt;&gt;""),OR(AK79="",AL79="")),"违规：必须先完成第二批",IF(OR(H79&lt;=0,H79&lt;&gt;INT(H79),MOD(H79,100)&lt;&gt;0,AND(AL79&lt;&gt;"",OR(AL79&lt;=0,AL79&lt;&gt;INT(AL79),MOD(AL79,100)&lt;&gt;0)),AND(AN79&lt;&gt;"",OR(AN79&lt;=0,AN79&lt;&gt;INT(AN79),MOD(AN79,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL79&lt;&gt;"",AN79&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ79&gt;C79*D79,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A79="","",IF(OR(E79="",H79=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK79="",AL79&lt;&gt;""),AND(AK79&lt;&gt;"",AL79="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM79="",AN79&lt;&gt;""),AND(AM79&lt;&gt;"",AN79="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM79&lt;&gt;"",AN79&lt;&gt;""),OR(AK79="",AL79="")),"违规：必须先完成第二批",IF(OR(H79&lt;=0,H79&lt;&gt;INT(H79),MOD(H79,100)&lt;&gt;0,AND(AL79&lt;&gt;"",OR(AL79&lt;=0,AL79&lt;&gt;INT(AL79),MOD(AL79,100)&lt;&gt;0)),AND(AN79&lt;&gt;"",OR(AN79&lt;=0,AN79&lt;&gt;INT(AN79),MOD(AN79,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL79&lt;&gt;"",AN79&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ79&gt;C79*D79,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -12852,7 +12827,7 @@
         <f>IF(A80="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A80)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>6200</v>
       </c>
-      <c r="M80" s="18">
+      <c r="M80" s="17">
         <f>IF(A80="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A80)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42517</v>
       </c>
@@ -12876,7 +12851,7 @@
         <f>IF(OR(AO80="",N80="",AO80&lt;=0),"",(AO80-N80)/AO80)</f>
         <v>0.0541381456129434</v>
       </c>
-      <c r="W80" s="19">
+      <c r="W80" s="18">
         <f>IF(OR(U80="",V80="",V80&lt;=0),"",U80/V80)</f>
         <v>1.06896551724138</v>
       </c>
@@ -12890,7 +12865,7 @@
       </c>
       <c r="Z80" s="7">
         <f>IF(OR(AE80="",多次统计数据!$B$8=""),"",AE80-多次统计数据!$B$8)</f>
-        <v>-0.079361464359869</v>
+        <v>-0.0787566623114102</v>
       </c>
       <c r="AA80" s="11">
         <f>IF(OR(I80="",M80="",M80&lt;I80),"",M80-I80)</f>
@@ -12898,7 +12873,7 @@
       </c>
       <c r="AB80" s="7">
         <f>IF(OR(A80="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC80" s="8" t="str">
         <f>IF(OR(AB80="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB80,"低于上限","达到或超过上限"))</f>
@@ -12933,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="AR80" s="8" t="str">
-        <f ca="1">IF(A80="","",IF(OR(E80="",H80=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK80="",AL80&lt;&gt;""),AND(AK80&lt;&gt;"",AL80="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM80="",AN80&lt;&gt;""),AND(AM80&lt;&gt;"",AN80="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM80&lt;&gt;"",AN80&lt;&gt;""),OR(AK80="",AL80="")),"违规：必须先完成第二批",IF(OR(H80&lt;=0,H80&lt;&gt;INT(H80),MOD(H80,100)&lt;&gt;0,AND(AL80&lt;&gt;"",OR(AL80&lt;=0,AL80&lt;&gt;INT(AL80),MOD(AL80,100)&lt;&gt;0)),AND(AN80&lt;&gt;"",OR(AN80&lt;=0,AN80&lt;&gt;INT(AN80),MOD(AN80,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL80&lt;&gt;"",AN80&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ80&gt;C80*D80,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A80="","",IF(OR(E80="",H80=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK80="",AL80&lt;&gt;""),AND(AK80&lt;&gt;"",AL80="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM80="",AN80&lt;&gt;""),AND(AM80&lt;&gt;"",AN80="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM80&lt;&gt;"",AN80&lt;&gt;""),OR(AK80="",AL80="")),"违规：必须先完成第二批",IF(OR(H80&lt;=0,H80&lt;&gt;INT(H80),MOD(H80,100)&lt;&gt;0,AND(AL80&lt;&gt;"",OR(AL80&lt;=0,AL80&lt;&gt;INT(AL80),MOD(AL80,100)&lt;&gt;0)),AND(AN80&lt;&gt;"",OR(AN80&lt;=0,AN80&lt;&gt;INT(AN80),MOD(AN80,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL80&lt;&gt;"",AN80&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ80&gt;C80*D80,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -12978,7 +12953,7 @@
         <f>IF(A81="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A81)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>8400</v>
       </c>
-      <c r="M81" s="18">
+      <c r="M81" s="17">
         <f>IF(A81="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A81)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42534</v>
       </c>
@@ -13002,7 +12977,7 @@
         <f>IF(OR(AO81="",N81="",AO81&lt;=0),"",(AO81-N81)/AO81)</f>
         <v>0.0389294403892944</v>
       </c>
-      <c r="W81" s="19">
+      <c r="W81" s="18">
         <f>IF(OR(U81="",V81="",V81&lt;=0),"",U81/V81)</f>
         <v>2.4375</v>
       </c>
@@ -13016,7 +12991,7 @@
       </c>
       <c r="Z81" s="7">
         <f>IF(OR(AE81="",多次统计数据!$B$8=""),"",AE81-多次统计数据!$B$8)</f>
-        <v>-0.0970218045268318</v>
+        <v>-0.0964170024783731</v>
       </c>
       <c r="AA81" s="11">
         <f>IF(OR(I81="",M81="",M81&lt;I81),"",M81-I81)</f>
@@ -13024,7 +12999,7 @@
       </c>
       <c r="AB81" s="7">
         <f>IF(OR(A81="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC81" s="8" t="str">
         <f>IF(OR(AB81="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB81,"低于上限","达到或超过上限"))</f>
@@ -13059,385 +13034,385 @@
         <v>0</v>
       </c>
       <c r="AR81" s="8" t="str">
-        <f ca="1">IF(A81="","",IF(OR(E81="",H81=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK81="",AL81&lt;&gt;""),AND(AK81&lt;&gt;"",AL81="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM81="",AN81&lt;&gt;""),AND(AM81&lt;&gt;"",AN81="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM81&lt;&gt;"",AN81&lt;&gt;""),OR(AK81="",AL81="")),"违规：必须先完成第二批",IF(OR(H81&lt;=0,H81&lt;&gt;INT(H81),MOD(H81,100)&lt;&gt;0,AND(AL81&lt;&gt;"",OR(AL81&lt;=0,AL81&lt;&gt;INT(AL81),MOD(AL81,100)&lt;&gt;0)),AND(AN81&lt;&gt;"",OR(AN81&lt;=0,AN81&lt;&gt;INT(AN81),MOD(AN81,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL81&lt;&gt;"",AN81&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ81&gt;C81*D81,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A81="","",IF(OR(E81="",H81=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK81="",AL81&lt;&gt;""),AND(AK81&lt;&gt;"",AL81="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM81="",AN81&lt;&gt;""),AND(AM81&lt;&gt;"",AN81="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM81&lt;&gt;"",AN81&lt;&gt;""),OR(AK81="",AL81="")),"违规：必须先完成第二批",IF(OR(H81&lt;=0,H81&lt;&gt;INT(H81),MOD(H81,100)&lt;&gt;0,AND(AL81&lt;&gt;"",OR(AL81&lt;=0,AL81&lt;&gt;INT(AL81),MOD(AL81,100)&lt;&gt;0)),AND(AN81&lt;&gt;"",OR(AN81&lt;=0,AN81&lt;&gt;INT(AN81),MOD(AN81,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL81&lt;&gt;"",AN81&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ81&gt;C81*D81,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="82" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A82" s="21">
+    <row r="82" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A82" s="20">
         <v>81</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B82" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C82" s="23">
+      <c r="C82" s="21">
         <v>264518</v>
       </c>
-      <c r="D82" s="24">
+      <c r="D82" s="22">
         <v>0.02</v>
       </c>
-      <c r="E82" s="23">
+      <c r="E82" s="21">
         <v>17.5</v>
       </c>
-      <c r="F82" s="25">
+      <c r="F82" s="23">
         <f>IF(OR(C82="",D82="",E82="",N82="",C82&lt;=0,D82&lt;=0,E82&lt;=N82),"",ROUNDDOWN((C82*D82)/(E82-N82)/100,0)*100)</f>
         <v>10500</v>
       </c>
-      <c r="G82" s="26" t="str">
+      <c r="G82" s="23" t="str">
         <f ca="1">IF(A82="","",IF(H82&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F82="",E82="",N82="",E82&lt;=N82,账户数据!$B$7=""),"",IF(OR(AG82="",AH82="",AI82=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A82,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F82*(E82-N82)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ82="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H82" s="21">
+      <c r="H82" s="20">
         <v>10500</v>
       </c>
-      <c r="I82" s="27">
+      <c r="I82" s="24">
         <v>42566</v>
       </c>
-      <c r="J82" s="23">
+      <c r="J82" s="21">
         <v>18.5</v>
       </c>
-      <c r="K82" s="30">
+      <c r="K82" s="25">
         <f>IF(A82="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A82)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>16.3</v>
       </c>
-      <c r="L82" s="26">
+      <c r="L82" s="23">
         <f>IF(A82="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A82)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>10500</v>
       </c>
-      <c r="M82" s="35">
+      <c r="M82" s="26">
         <f>IF(A82="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A82)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42572</v>
       </c>
-      <c r="N82" s="23">
+      <c r="N82" s="21">
         <v>17</v>
       </c>
-      <c r="O82" s="23"/>
-      <c r="P82" s="30" t="str">
+      <c r="O82" s="21"/>
+      <c r="P82" s="25" t="str">
         <f>IF(A82="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A82)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q82" s="21"/>
-      <c r="R82" s="21"/>
-      <c r="S82" s="21"/>
-      <c r="T82" s="21"/>
-      <c r="U82" s="31">
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="20"/>
+      <c r="U82" s="27">
         <f>IF(OR(AO82="",J82="",AO82&lt;=0),"",(J82-AO82)/AO82)</f>
         <v>0.0571428571428571</v>
       </c>
-      <c r="V82" s="31">
+      <c r="V82" s="27">
         <f>IF(OR(AO82="",N82="",AO82&lt;=0),"",(AO82-N82)/AO82)</f>
         <v>0.0285714285714286</v>
       </c>
-      <c r="W82" s="32">
+      <c r="W82" s="28">
         <f>IF(OR(U82="",V82="",V82&lt;=0),"",U82/V82)</f>
         <v>2</v>
       </c>
-      <c r="X82" s="30">
+      <c r="X82" s="25">
         <f>IF(OR(K82="",L82="",AP82=""),"",K82*L82-(E82*H82+IF(AND(AK82&lt;&gt;"",AL82&lt;&gt;""),AK82*AL82,0)+IF(AND(AM82&lt;&gt;"",AN82&lt;&gt;""),AM82*AN82,0))-IF(O82="",0,O82)-IF(P82="",0,P82))</f>
         <v>-12600</v>
       </c>
-      <c r="Y82" s="36">
+      <c r="Y82" s="27">
         <f>IF(OR(X82="",AP82=""),"",IF((E82*H82+IF(AND(AK82&lt;&gt;"",AL82&lt;&gt;""),AK82*AL82,0)+IF(AND(AM82&lt;&gt;"",AN82&lt;&gt;""),AM82*AN82,0))+IF(O82="",0,O82)&lt;=0,"",X82/((E82*H82+IF(AND(AK82&lt;&gt;"",AL82&lt;&gt;""),AK82*AL82,0)+IF(AND(AM82&lt;&gt;"",AN82&lt;&gt;""),AM82*AN82,0))+IF(O82="",0,O82))))</f>
         <v>-0.0685714285714286</v>
       </c>
-      <c r="Z82" s="36">
+      <c r="Z82" s="27">
         <f>IF(OR(AE82="",多次统计数据!$B$8=""),"",AE82-多次统计数据!$B$8)</f>
-        <v>-0.120182436342358</v>
-      </c>
-      <c r="AA82" s="37">
+        <v>-0.119577634293899</v>
+      </c>
+      <c r="AA82" s="29">
         <f>IF(OR(I82="",M82="",M82&lt;I82),"",M82-I82)</f>
         <v>6</v>
       </c>
-      <c r="AB82" s="31">
+      <c r="AB82" s="27">
         <f>IF(OR(A82="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC82" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC82" s="23" t="str">
         <f>IF(OR(AB82="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB82,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD82" s="21"/>
-      <c r="AE82" s="36">
+      <c r="AD82" s="20"/>
+      <c r="AE82" s="27">
         <f>IF(OR(X82="",C82="",C82&lt;=0),"",X82/C82)</f>
         <v>-0.0476338094193968</v>
       </c>
-      <c r="AG82" s="21"/>
-      <c r="AH82" s="21"/>
-      <c r="AI82" s="21"/>
-      <c r="AJ82" s="26" t="str">
+      <c r="AG82" s="20"/>
+      <c r="AH82" s="20"/>
+      <c r="AI82" s="20"/>
+      <c r="AJ82" s="23" t="str">
         <f>IF(OR(AG82="",AH82=""),"",IF(OR(AND(AG82="短期博反弹",OR(AH82="1～3个交易日",AH82="4～10个交易日")),AND(AG82="突破冲新高",OR(AH82="4～10个交易日",AH82="11～20个交易日")),AND(AG82="趋势波段",OR(AH82="11～20个交易日",AH82="21～60个交易日",AH82="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK82" s="23"/>
-      <c r="AL82" s="34"/>
-      <c r="AM82" s="23"/>
-      <c r="AN82" s="34"/>
-      <c r="AO82" s="28">
+      <c r="AK82" s="21"/>
+      <c r="AL82" s="30"/>
+      <c r="AM82" s="21"/>
+      <c r="AN82" s="30"/>
+      <c r="AO82" s="25">
         <f>IF(OR(A82="",H82="",H82&lt;=0),"",(E82*H82+IF(AND(AK82&lt;&gt;"",AL82&lt;&gt;""),AK82*AL82,0)+IF(AND(AM82&lt;&gt;"",AN82&lt;&gt;""),AM82*AN82,0))/AP82)</f>
         <v>17.5</v>
       </c>
-      <c r="AP82" s="33">
+      <c r="AP82" s="29">
         <f>IF(OR(A82="",H82="",H82&lt;=0),"",H82+IF(AL82="",0,AL82)+IF(AN82="",0,AN82))</f>
         <v>10500</v>
       </c>
-      <c r="AQ82" s="28">
+      <c r="AQ82" s="25">
         <f>IF(A82="","",IF(M82&lt;&gt;"",0,IF(OR(H82="",N82=""),"",MAX(E82-MAX(N82,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A82))*持仓跟踪!$S$2:$S$157)),0)),0)*H82+IF(OR(AK82="",AL82=""),0,MAX(AK82-MAX(N82,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A82))*持仓跟踪!$S$2:$S$157)),0)),0)*AL82)+IF(OR(AM82="",AN82=""),0,MAX(AM82-MAX(N82,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A82))*持仓跟踪!$S$2:$S$157)),0)),0)*AN82))))</f>
         <v>0</v>
       </c>
-      <c r="AR82" s="26" t="str">
-        <f ca="1">IF(A82="","",IF(OR(E82="",H82=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK82="",AL82&lt;&gt;""),AND(AK82&lt;&gt;"",AL82="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM82="",AN82&lt;&gt;""),AND(AM82&lt;&gt;"",AN82="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM82&lt;&gt;"",AN82&lt;&gt;""),OR(AK82="",AL82="")),"违规：必须先完成第二批",IF(OR(H82&lt;=0,H82&lt;&gt;INT(H82),MOD(H82,100)&lt;&gt;0,AND(AL82&lt;&gt;"",OR(AL82&lt;=0,AL82&lt;&gt;INT(AL82),MOD(AL82,100)&lt;&gt;0)),AND(AN82&lt;&gt;"",OR(AN82&lt;=0,AN82&lt;&gt;INT(AN82),MOD(AN82,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL82&lt;&gt;"",AN82&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ82&gt;C82*D82,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR82" s="23" t="str">
+        <f ca="1">IF(A82="","",IF(OR(E82="",H82=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK82="",AL82&lt;&gt;""),AND(AK82&lt;&gt;"",AL82="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM82="",AN82&lt;&gt;""),AND(AM82&lt;&gt;"",AN82="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM82&lt;&gt;"",AN82&lt;&gt;""),OR(AK82="",AL82="")),"违规：必须先完成第二批",IF(OR(H82&lt;=0,H82&lt;&gt;INT(H82),MOD(H82,100)&lt;&gt;0,AND(AL82&lt;&gt;"",OR(AL82&lt;=0,AL82&lt;&gt;INT(AL82),MOD(AL82,100)&lt;&gt;0)),AND(AN82&lt;&gt;"",OR(AN82&lt;=0,AN82&lt;&gt;INT(AN82),MOD(AN82,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL82&lt;&gt;"",AN82&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ82&gt;C82*D82,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="83" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A83" s="21">
+    <row r="83" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A83" s="20">
         <v>82</v>
       </c>
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C83" s="23">
+      <c r="C83" s="21">
         <v>251918</v>
       </c>
-      <c r="D83" s="24">
+      <c r="D83" s="22">
         <v>0.02</v>
       </c>
-      <c r="E83" s="23">
+      <c r="E83" s="21">
         <v>14.29</v>
       </c>
-      <c r="F83" s="25">
+      <c r="F83" s="23">
         <f>IF(OR(C83="",D83="",E83="",N83="",C83&lt;=0,D83&lt;=0,E83&lt;=N83),"",ROUNDDOWN((C83*D83)/(E83-N83)/100,0)*100)</f>
         <v>17300</v>
       </c>
-      <c r="G83" s="26" t="str">
+      <c r="G83" s="23" t="str">
         <f ca="1">IF(A83="","",IF(H83&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F83="",E83="",N83="",E83&lt;=N83,账户数据!$B$7=""),"",IF(OR(AG83="",AH83="",AI83=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A83,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F83*(E83-N83)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ83="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H83" s="21">
+      <c r="H83" s="20">
         <v>17300</v>
       </c>
-      <c r="I83" s="27">
+      <c r="I83" s="24">
         <v>42832</v>
       </c>
-      <c r="J83" s="23">
+      <c r="J83" s="21">
         <v>15</v>
       </c>
-      <c r="K83" s="28">
+      <c r="K83" s="25">
         <f>IF(A83="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A83)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>12.89</v>
       </c>
-      <c r="L83" s="25">
+      <c r="L83" s="23">
         <f>IF(A83="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A83)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>17300</v>
       </c>
-      <c r="M83" s="29">
+      <c r="M83" s="26">
         <f>IF(A83="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A83)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>42858</v>
       </c>
-      <c r="N83" s="23">
+      <c r="N83" s="21">
         <v>14</v>
       </c>
-      <c r="O83" s="23"/>
-      <c r="P83" s="30" t="str">
+      <c r="O83" s="21"/>
+      <c r="P83" s="25" t="str">
         <f>IF(A83="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A83)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q83" s="21"/>
-      <c r="R83" s="21"/>
-      <c r="S83" s="21"/>
-      <c r="T83" s="21"/>
-      <c r="U83" s="31">
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20"/>
+      <c r="S83" s="20"/>
+      <c r="T83" s="20"/>
+      <c r="U83" s="27">
         <f>IF(OR(AO83="",J83="",AO83&lt;=0),"",(J83-AO83)/AO83)</f>
         <v>0.0496850944716586</v>
       </c>
-      <c r="V83" s="31">
+      <c r="V83" s="27">
         <f>IF(OR(AO83="",N83="",AO83&lt;=0),"",(AO83-N83)/AO83)</f>
         <v>0.020293911826452</v>
       </c>
-      <c r="W83" s="32">
+      <c r="W83" s="28">
         <f>IF(OR(U83="",V83="",V83&lt;=0),"",U83/V83)</f>
         <v>2.44827586206898</v>
       </c>
-      <c r="X83" s="28">
+      <c r="X83" s="25">
         <f>IF(OR(K83="",L83="",AP83=""),"",K83*L83-(E83*H83+IF(AND(AK83&lt;&gt;"",AL83&lt;&gt;""),AK83*AL83,0)+IF(AND(AM83&lt;&gt;"",AN83&lt;&gt;""),AM83*AN83,0))-IF(O83="",0,O83)-IF(P83="",0,P83))</f>
         <v>-24220</v>
       </c>
-      <c r="Y83" s="31">
+      <c r="Y83" s="27">
         <f>IF(OR(X83="",AP83=""),"",IF((E83*H83+IF(AND(AK83&lt;&gt;"",AL83&lt;&gt;""),AK83*AL83,0)+IF(AND(AM83&lt;&gt;"",AN83&lt;&gt;""),AM83*AN83,0))+IF(O83="",0,O83)&lt;=0,"",X83/((E83*H83+IF(AND(AK83&lt;&gt;"",AL83&lt;&gt;""),AK83*AL83,0)+IF(AND(AM83&lt;&gt;"",AN83&lt;&gt;""),AM83*AN83,0))+IF(O83="",0,O83))))</f>
         <v>-0.0979706088173547</v>
       </c>
-      <c r="Z83" s="31">
+      <c r="Z83" s="27">
         <f>IF(OR(AE83="",多次统计数据!$B$8=""),"",AE83-多次统计数据!$B$8)</f>
-        <v>-0.168691022464367</v>
-      </c>
-      <c r="AA83" s="33">
+        <v>-0.168086220415908</v>
+      </c>
+      <c r="AA83" s="29">
         <f>IF(OR(I83="",M83="",M83&lt;I83),"",M83-I83)</f>
         <v>26</v>
       </c>
-      <c r="AB83" s="31">
+      <c r="AB83" s="27">
         <f>IF(OR(A83="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC83" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC83" s="23" t="str">
         <f>IF(OR(AB83="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB83,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD83" s="21"/>
-      <c r="AE83" s="31">
+      <c r="AD83" s="20"/>
+      <c r="AE83" s="27">
         <f>IF(OR(X83="",C83="",C83&lt;=0),"",X83/C83)</f>
         <v>-0.0961423955414062</v>
       </c>
-      <c r="AG83" s="21"/>
-      <c r="AH83" s="21"/>
-      <c r="AI83" s="21"/>
-      <c r="AJ83" s="26" t="str">
+      <c r="AG83" s="20"/>
+      <c r="AH83" s="20"/>
+      <c r="AI83" s="20"/>
+      <c r="AJ83" s="23" t="str">
         <f>IF(OR(AG83="",AH83=""),"",IF(OR(AND(AG83="短期博反弹",OR(AH83="1～3个交易日",AH83="4～10个交易日")),AND(AG83="突破冲新高",OR(AH83="4～10个交易日",AH83="11～20个交易日")),AND(AG83="趋势波段",OR(AH83="11～20个交易日",AH83="21～60个交易日",AH83="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK83" s="23"/>
-      <c r="AL83" s="34"/>
-      <c r="AM83" s="23"/>
-      <c r="AN83" s="34"/>
-      <c r="AO83" s="28">
+      <c r="AK83" s="21"/>
+      <c r="AL83" s="30"/>
+      <c r="AM83" s="21"/>
+      <c r="AN83" s="30"/>
+      <c r="AO83" s="25">
         <f>IF(OR(A83="",H83="",H83&lt;=0),"",(E83*H83+IF(AND(AK83&lt;&gt;"",AL83&lt;&gt;""),AK83*AL83,0)+IF(AND(AM83&lt;&gt;"",AN83&lt;&gt;""),AM83*AN83,0))/AP83)</f>
         <v>14.29</v>
       </c>
-      <c r="AP83" s="33">
+      <c r="AP83" s="29">
         <f>IF(OR(A83="",H83="",H83&lt;=0),"",H83+IF(AL83="",0,AL83)+IF(AN83="",0,AN83))</f>
         <v>17300</v>
       </c>
-      <c r="AQ83" s="28">
+      <c r="AQ83" s="25">
         <f>IF(A83="","",IF(M83&lt;&gt;"",0,IF(OR(H83="",N83=""),"",MAX(E83-MAX(N83,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A83))*持仓跟踪!$S$2:$S$157)),0)),0)*H83+IF(OR(AK83="",AL83=""),0,MAX(AK83-MAX(N83,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A83))*持仓跟踪!$S$2:$S$157)),0)),0)*AL83)+IF(OR(AM83="",AN83=""),0,MAX(AM83-MAX(N83,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A83))*持仓跟踪!$S$2:$S$157)),0)),0)*AN83))))</f>
         <v>0</v>
       </c>
-      <c r="AR83" s="26" t="str">
-        <f ca="1">IF(A83="","",IF(OR(E83="",H83=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK83="",AL83&lt;&gt;""),AND(AK83&lt;&gt;"",AL83="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM83="",AN83&lt;&gt;""),AND(AM83&lt;&gt;"",AN83="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM83&lt;&gt;"",AN83&lt;&gt;""),OR(AK83="",AL83="")),"违规：必须先完成第二批",IF(OR(H83&lt;=0,H83&lt;&gt;INT(H83),MOD(H83,100)&lt;&gt;0,AND(AL83&lt;&gt;"",OR(AL83&lt;=0,AL83&lt;&gt;INT(AL83),MOD(AL83,100)&lt;&gt;0)),AND(AN83&lt;&gt;"",OR(AN83&lt;=0,AN83&lt;&gt;INT(AN83),MOD(AN83,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL83&lt;&gt;"",AN83&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ83&gt;C83*D83,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR83" s="23" t="str">
+        <f ca="1">IF(A83="","",IF(OR(E83="",H83=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK83="",AL83&lt;&gt;""),AND(AK83&lt;&gt;"",AL83="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM83="",AN83&lt;&gt;""),AND(AM83&lt;&gt;"",AN83="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM83&lt;&gt;"",AN83&lt;&gt;""),OR(AK83="",AL83="")),"违规：必须先完成第二批",IF(OR(H83&lt;=0,H83&lt;&gt;INT(H83),MOD(H83,100)&lt;&gt;0,AND(AL83&lt;&gt;"",OR(AL83&lt;=0,AL83&lt;&gt;INT(AL83),MOD(AL83,100)&lt;&gt;0)),AND(AN83&lt;&gt;"",OR(AN83&lt;=0,AN83&lt;&gt;INT(AN83),MOD(AN83,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL83&lt;&gt;"",AN83&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ83&gt;C83*D83,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="84" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A84" s="21">
+    <row r="84" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A84" s="20">
         <v>83</v>
       </c>
-      <c r="B84" s="22" t="s">
+      <c r="B84" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C84" s="23">
+      <c r="C84" s="21">
         <v>227698</v>
       </c>
-      <c r="D84" s="24">
+      <c r="D84" s="22">
         <v>0.02</v>
       </c>
-      <c r="E84" s="23">
+      <c r="E84" s="21">
         <v>12.89</v>
       </c>
-      <c r="F84" s="25">
+      <c r="F84" s="23">
         <f>IF(OR(C84="",D84="",E84="",N84="",C84&lt;=0,D84&lt;=0,E84&lt;=N84),"",ROUNDDOWN((C84*D84)/(E84-N84)/100,0)*100)</f>
         <v>6100</v>
       </c>
-      <c r="G84" s="26" t="str">
+      <c r="G84" s="23" t="str">
         <f ca="1">IF(A84="","",IF(H84&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F84="",E84="",N84="",E84&lt;=N84,账户数据!$B$7=""),"",IF(OR(AG84="",AH84="",AI84=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A84,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F84*(E84-N84)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ84="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H84" s="21">
+      <c r="H84" s="20">
         <v>6100</v>
       </c>
-      <c r="I84" s="27">
+      <c r="I84" s="24">
         <v>42878</v>
       </c>
-      <c r="J84" s="23">
+      <c r="J84" s="21">
         <v>15</v>
       </c>
-      <c r="K84" s="30">
+      <c r="K84" s="25">
         <f>IF(A84="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A84)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>17.53</v>
       </c>
-      <c r="L84" s="26">
+      <c r="L84" s="23">
         <f>IF(A84="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A84)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>6100</v>
       </c>
-      <c r="M84" s="35">
+      <c r="M84" s="26">
         <f>IF(A84="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A84)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43038</v>
       </c>
-      <c r="N84" s="23">
+      <c r="N84" s="21">
         <v>12.15</v>
       </c>
-      <c r="O84" s="23"/>
-      <c r="P84" s="30" t="str">
+      <c r="O84" s="21"/>
+      <c r="P84" s="25" t="str">
         <f>IF(A84="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A84)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q84" s="21"/>
-      <c r="R84" s="21"/>
-      <c r="S84" s="21"/>
-      <c r="T84" s="21"/>
-      <c r="U84" s="31">
+      <c r="Q84" s="20"/>
+      <c r="R84" s="20"/>
+      <c r="S84" s="20"/>
+      <c r="T84" s="20"/>
+      <c r="U84" s="27">
         <f>IF(OR(AO84="",J84="",AO84&lt;=0),"",(J84-AO84)/AO84)</f>
         <v>0.163692785104732</v>
       </c>
-      <c r="V84" s="31">
+      <c r="V84" s="27">
         <f>IF(OR(AO84="",N84="",AO84&lt;=0),"",(AO84-N84)/AO84)</f>
         <v>0.0574088440651668</v>
       </c>
-      <c r="W84" s="32">
+      <c r="W84" s="28">
         <f>IF(OR(U84="",V84="",V84&lt;=0),"",U84/V84)</f>
         <v>2.85135135135135</v>
       </c>
-      <c r="X84" s="30">
+      <c r="X84" s="25">
         <f>IF(OR(K84="",L84="",AP84=""),"",K84*L84-(E84*H84+IF(AND(AK84&lt;&gt;"",AL84&lt;&gt;""),AK84*AL84,0)+IF(AND(AM84&lt;&gt;"",AN84&lt;&gt;""),AM84*AN84,0))-IF(O84="",0,O84)-IF(P84="",0,P84))</f>
         <v>28304</v>
       </c>
-      <c r="Y84" s="36">
+      <c r="Y84" s="27">
         <f>IF(OR(X84="",AP84=""),"",IF((E84*H84+IF(AND(AK84&lt;&gt;"",AL84&lt;&gt;""),AK84*AL84,0)+IF(AND(AM84&lt;&gt;"",AN84&lt;&gt;""),AM84*AN84,0))+IF(O84="",0,O84)&lt;=0,"",X84/((E84*H84+IF(AND(AK84&lt;&gt;"",AL84&lt;&gt;""),AK84*AL84,0)+IF(AND(AM84&lt;&gt;"",AN84&lt;&gt;""),AM84*AN84,0))+IF(O84="",0,O84))))</f>
         <v>0.359968968192397</v>
       </c>
-      <c r="Z84" s="36">
+      <c r="Z84" s="27">
         <f>IF(OR(AE84="",多次统计数据!$B$8=""),"",AE84-多次统计数据!$B$8)</f>
-        <v>0.0517563735601351</v>
-      </c>
-      <c r="AA84" s="37">
+        <v>0.0523611756085938</v>
+      </c>
+      <c r="AA84" s="29">
         <f>IF(OR(I84="",M84="",M84&lt;I84),"",M84-I84)</f>
         <v>160</v>
       </c>
-      <c r="AB84" s="31">
+      <c r="AB84" s="27">
         <f>IF(OR(A84="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC84" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC84" s="23" t="str">
         <f>IF(OR(AB84="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB84,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD84" s="21"/>
-      <c r="AE84" s="36">
+      <c r="AD84" s="20"/>
+      <c r="AE84" s="27">
         <f>IF(OR(X84="",C84="",C84&lt;=0),"",X84/C84)</f>
         <v>0.124305000483096</v>
       </c>
-      <c r="AG84" s="21"/>
-      <c r="AH84" s="21"/>
-      <c r="AI84" s="21"/>
-      <c r="AJ84" s="26" t="str">
+      <c r="AG84" s="20"/>
+      <c r="AH84" s="20"/>
+      <c r="AI84" s="20"/>
+      <c r="AJ84" s="23" t="str">
         <f>IF(OR(AG84="",AH84=""),"",IF(OR(AND(AG84="短期博反弹",OR(AH84="1～3个交易日",AH84="4～10个交易日")),AND(AG84="突破冲新高",OR(AH84="4～10个交易日",AH84="11～20个交易日")),AND(AG84="趋势波段",OR(AH84="11～20个交易日",AH84="21～60个交易日",AH84="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK84" s="23"/>
-      <c r="AL84" s="34"/>
-      <c r="AM84" s="23"/>
-      <c r="AN84" s="34"/>
-      <c r="AO84" s="28">
+      <c r="AK84" s="21"/>
+      <c r="AL84" s="30"/>
+      <c r="AM84" s="21"/>
+      <c r="AN84" s="30"/>
+      <c r="AO84" s="25">
         <f>IF(OR(A84="",H84="",H84&lt;=0),"",(E84*H84+IF(AND(AK84&lt;&gt;"",AL84&lt;&gt;""),AK84*AL84,0)+IF(AND(AM84&lt;&gt;"",AN84&lt;&gt;""),AM84*AN84,0))/AP84)</f>
         <v>12.89</v>
       </c>
-      <c r="AP84" s="33">
+      <c r="AP84" s="29">
         <f>IF(OR(A84="",H84="",H84&lt;=0),"",H84+IF(AL84="",0,AL84)+IF(AN84="",0,AN84))</f>
         <v>6100</v>
       </c>
-      <c r="AQ84" s="28">
+      <c r="AQ84" s="25">
         <f>IF(A84="","",IF(M84&lt;&gt;"",0,IF(OR(H84="",N84=""),"",MAX(E84-MAX(N84,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A84))*持仓跟踪!$S$2:$S$157)),0)),0)*H84+IF(OR(AK84="",AL84=""),0,MAX(AK84-MAX(N84,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A84))*持仓跟踪!$S$2:$S$157)),0)),0)*AL84)+IF(OR(AM84="",AN84=""),0,MAX(AM84-MAX(N84,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A84))*持仓跟踪!$S$2:$S$157)),0)),0)*AN84))))</f>
         <v>0</v>
       </c>
-      <c r="AR84" s="26" t="str">
-        <f ca="1">IF(A84="","",IF(OR(E84="",H84=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK84="",AL84&lt;&gt;""),AND(AK84&lt;&gt;"",AL84="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM84="",AN84&lt;&gt;""),AND(AM84&lt;&gt;"",AN84="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM84&lt;&gt;"",AN84&lt;&gt;""),OR(AK84="",AL84="")),"违规：必须先完成第二批",IF(OR(H84&lt;=0,H84&lt;&gt;INT(H84),MOD(H84,100)&lt;&gt;0,AND(AL84&lt;&gt;"",OR(AL84&lt;=0,AL84&lt;&gt;INT(AL84),MOD(AL84,100)&lt;&gt;0)),AND(AN84&lt;&gt;"",OR(AN84&lt;=0,AN84&lt;&gt;INT(AN84),MOD(AN84,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL84&lt;&gt;"",AN84&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ84&gt;C84*D84,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR84" s="23" t="str">
+        <f ca="1">IF(A84="","",IF(OR(E84="",H84=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK84="",AL84&lt;&gt;""),AND(AK84&lt;&gt;"",AL84="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM84="",AN84&lt;&gt;""),AND(AM84&lt;&gt;"",AN84="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM84&lt;&gt;"",AN84&lt;&gt;""),OR(AK84="",AL84="")),"违规：必须先完成第二批",IF(OR(H84&lt;=0,H84&lt;&gt;INT(H84),MOD(H84,100)&lt;&gt;0,AND(AL84&lt;&gt;"",OR(AL84&lt;=0,AL84&lt;&gt;INT(AL84),MOD(AL84,100)&lt;&gt;0)),AND(AN84&lt;&gt;"",OR(AN84&lt;=0,AN84&lt;&gt;INT(AN84),MOD(AN84,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL84&lt;&gt;"",AN84&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ84&gt;C84*D84,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -13482,7 +13457,7 @@
         <f>IF(A85="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A85)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>15000</v>
       </c>
-      <c r="M85" s="18">
+      <c r="M85" s="17">
         <f>IF(A85="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A85)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43117</v>
       </c>
@@ -13506,7 +13481,7 @@
         <f>IF(OR(AO85="",N85="",AO85&lt;=0),"",(AO85-N85)/AO85)</f>
         <v>0.0182403433476395</v>
       </c>
-      <c r="W85" s="19">
+      <c r="W85" s="18">
         <f>IF(OR(U85="",V85="",V85&lt;=0),"",U85/V85)</f>
         <v>4</v>
       </c>
@@ -13520,7 +13495,7 @@
       </c>
       <c r="Z85" s="7">
         <f>IF(OR(AE85="",多次统计数据!$B$8=""),"",AE85-多次统计数据!$B$8)</f>
-        <v>-0.113563931490894</v>
+        <v>-0.112959129442435</v>
       </c>
       <c r="AA85" s="11">
         <f>IF(OR(I85="",M85="",M85&lt;I85),"",M85-I85)</f>
@@ -13528,7 +13503,7 @@
       </c>
       <c r="AB85" s="7">
         <f>IF(OR(A85="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC85" s="8" t="str">
         <f>IF(OR(AB85="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB85,"低于上限","达到或超过上限"))</f>
@@ -13563,133 +13538,133 @@
         <v>0</v>
       </c>
       <c r="AR85" s="8" t="str">
-        <f ca="1">IF(A85="","",IF(OR(E85="",H85=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK85="",AL85&lt;&gt;""),AND(AK85&lt;&gt;"",AL85="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM85="",AN85&lt;&gt;""),AND(AM85&lt;&gt;"",AN85="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM85&lt;&gt;"",AN85&lt;&gt;""),OR(AK85="",AL85="")),"违规：必须先完成第二批",IF(OR(H85&lt;=0,H85&lt;&gt;INT(H85),MOD(H85,100)&lt;&gt;0,AND(AL85&lt;&gt;"",OR(AL85&lt;=0,AL85&lt;&gt;INT(AL85),MOD(AL85,100)&lt;&gt;0)),AND(AN85&lt;&gt;"",OR(AN85&lt;=0,AN85&lt;&gt;INT(AN85),MOD(AN85,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL85&lt;&gt;"",AN85&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ85&gt;C85*D85,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A85="","",IF(OR(E85="",H85=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK85="",AL85&lt;&gt;""),AND(AK85&lt;&gt;"",AL85="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM85="",AN85&lt;&gt;""),AND(AM85&lt;&gt;"",AN85="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM85&lt;&gt;"",AN85&lt;&gt;""),OR(AK85="",AL85="")),"违规：必须先完成第二批",IF(OR(H85&lt;=0,H85&lt;&gt;INT(H85),MOD(H85,100)&lt;&gt;0,AND(AL85&lt;&gt;"",OR(AL85&lt;=0,AL85&lt;&gt;INT(AL85),MOD(AL85,100)&lt;&gt;0)),AND(AN85&lt;&gt;"",OR(AN85&lt;=0,AN85&lt;&gt;INT(AN85),MOD(AN85,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL85&lt;&gt;"",AN85&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ85&gt;C85*D85,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
-    <row r="86" s="17" customFormat="1" ht="17" spans="1:44">
-      <c r="A86" s="21">
+    <row r="86" s="16" customFormat="1" ht="17" spans="1:44">
+      <c r="A86" s="20">
         <v>85</v>
       </c>
-      <c r="B86" s="22" t="s">
+      <c r="B86" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C86" s="23">
+      <c r="C86" s="21">
         <v>245502</v>
       </c>
-      <c r="D86" s="24">
+      <c r="D86" s="22">
         <v>0.02</v>
       </c>
-      <c r="E86" s="23">
+      <c r="E86" s="21">
         <v>17.18</v>
       </c>
-      <c r="F86" s="25">
+      <c r="F86" s="23">
         <f>IF(OR(C86="",D86="",E86="",N86="",C86&lt;=0,D86&lt;=0,E86&lt;=N86),"",ROUNDDOWN((C86*D86)/(E86-N86)/100,0)*100)</f>
         <v>7200</v>
       </c>
-      <c r="G86" s="26" t="str">
+      <c r="G86" s="23" t="str">
         <f ca="1">IF(A86="","",IF(H86&lt;&gt;"","已开仓",IF(账户数据!$B$23="已锁仓","禁止开仓：连续亏损达到上限",IF(账户数据!$B$23="解锁信息不完整","禁止开仓：请完整填写解锁信息",IF(OR(F86="",E86="",N86="",E86&lt;=N86,账户数据!$B$7=""),"",IF(OR(AG86="",AH86="",AI86=""),"禁止开仓：交易预期未填写完整",IF(COUNTIFS(持仓跟踪!$A$2:$A$157,"止损计划",持仓跟踪!$B$2:$B$157,A86,持仓跟踪!$AC$2:$AC$157,"计划有效")=0,"禁止开仓：请先填写止损计划",IF(账户数据!$B$9+F86*(E86-N86)&gt;=账户数据!$B$7,"禁止开仓：风险额度不足",IF(AJ86="周期与交易预期不匹配，请重新确认",IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓；周期需复核）","允许开仓（周期需复核）"),IF(账户数据!$B$23="接近锁仓","允许开仓（接近锁仓）","允许开仓"))))))))))</f>
         <v>已开仓</v>
       </c>
-      <c r="H86" s="21">
+      <c r="H86" s="20">
         <v>7200</v>
       </c>
-      <c r="I86" s="27">
+      <c r="I86" s="24">
         <v>43136</v>
       </c>
-      <c r="J86" s="23">
+      <c r="J86" s="21">
         <v>20</v>
       </c>
-      <c r="K86" s="30">
+      <c r="K86" s="25">
         <f>IF(A86="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A86)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
         <v>17.62</v>
       </c>
-      <c r="L86" s="26">
+      <c r="L86" s="23">
         <f>IF(A86="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A86)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>7200</v>
       </c>
-      <c r="M86" s="35">
+      <c r="M86" s="26">
         <f>IF(A86="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A86)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43154</v>
       </c>
-      <c r="N86" s="23">
+      <c r="N86" s="21">
         <v>16.5</v>
       </c>
-      <c r="O86" s="23"/>
-      <c r="P86" s="30" t="str">
+      <c r="O86" s="21"/>
+      <c r="P86" s="25" t="str">
         <f>IF(A86="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A86)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
         <v/>
       </c>
-      <c r="Q86" s="21"/>
-      <c r="R86" s="21"/>
-      <c r="S86" s="21"/>
-      <c r="T86" s="21"/>
-      <c r="U86" s="31">
+      <c r="Q86" s="20"/>
+      <c r="R86" s="20"/>
+      <c r="S86" s="20"/>
+      <c r="T86" s="20"/>
+      <c r="U86" s="27">
         <f>IF(OR(AO86="",J86="",AO86&lt;=0),"",(J86-AO86)/AO86)</f>
         <v>0.164144353899884</v>
       </c>
-      <c r="V86" s="31">
+      <c r="V86" s="27">
         <f>IF(OR(AO86="",N86="",AO86&lt;=0),"",(AO86-N86)/AO86)</f>
         <v>0.039580908032596</v>
       </c>
-      <c r="W86" s="32">
+      <c r="W86" s="28">
         <f>IF(OR(U86="",V86="",V86&lt;=0),"",U86/V86)</f>
         <v>4.14705882352941</v>
       </c>
-      <c r="X86" s="30">
+      <c r="X86" s="25">
         <f>IF(OR(K86="",L86="",AP86=""),"",K86*L86-(E86*H86+IF(AND(AK86&lt;&gt;"",AL86&lt;&gt;""),AK86*AL86,0)+IF(AND(AM86&lt;&gt;"",AN86&lt;&gt;""),AM86*AN86,0))-IF(O86="",0,O86)-IF(P86="",0,P86))</f>
         <v>3168</v>
       </c>
-      <c r="Y86" s="36">
+      <c r="Y86" s="27">
         <f>IF(OR(X86="",AP86=""),"",IF((E86*H86+IF(AND(AK86&lt;&gt;"",AL86&lt;&gt;""),AK86*AL86,0)+IF(AND(AM86&lt;&gt;"",AN86&lt;&gt;""),AM86*AN86,0))+IF(O86="",0,O86)&lt;=0,"",X86/((E86*H86+IF(AND(AK86&lt;&gt;"",AL86&lt;&gt;""),AK86*AL86,0)+IF(AND(AM86&lt;&gt;"",AN86&lt;&gt;""),AM86*AN86,0))+IF(O86="",0,O86))))</f>
         <v>0.0256111757857974</v>
       </c>
-      <c r="Z86" s="36">
+      <c r="Z86" s="27">
         <f>IF(OR(AE86="",多次统计数据!$B$8=""),"",AE86-多次统计数据!$B$8)</f>
-        <v>-0.0596444550628539</v>
-      </c>
-      <c r="AA86" s="37">
+        <v>-0.0590396530143951</v>
+      </c>
+      <c r="AA86" s="29">
         <f>IF(OR(I86="",M86="",M86&lt;I86),"",M86-I86)</f>
         <v>18</v>
       </c>
-      <c r="AB86" s="31">
+      <c r="AB86" s="27">
         <f>IF(OR(A86="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
-      </c>
-      <c r="AC86" s="26" t="str">
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC86" s="23" t="str">
         <f>IF(OR(AB86="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB86,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD86" s="21"/>
-      <c r="AE86" s="36">
+      <c r="AD86" s="20"/>
+      <c r="AE86" s="27">
         <f>IF(OR(X86="",C86="",C86&lt;=0),"",X86/C86)</f>
         <v>0.012904171860107</v>
       </c>
-      <c r="AG86" s="21"/>
-      <c r="AH86" s="21"/>
-      <c r="AI86" s="21"/>
-      <c r="AJ86" s="26" t="str">
+      <c r="AG86" s="20"/>
+      <c r="AH86" s="20"/>
+      <c r="AI86" s="20"/>
+      <c r="AJ86" s="23" t="str">
         <f>IF(OR(AG86="",AH86=""),"",IF(OR(AND(AG86="短期博反弹",OR(AH86="1～3个交易日",AH86="4～10个交易日")),AND(AG86="突破冲新高",OR(AH86="4～10个交易日",AH86="11～20个交易日")),AND(AG86="趋势波段",OR(AH86="11～20个交易日",AH86="21～60个交易日",AH86="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
         <v/>
       </c>
-      <c r="AK86" s="23"/>
-      <c r="AL86" s="34"/>
-      <c r="AM86" s="23"/>
-      <c r="AN86" s="34"/>
-      <c r="AO86" s="28">
+      <c r="AK86" s="21"/>
+      <c r="AL86" s="30"/>
+      <c r="AM86" s="21"/>
+      <c r="AN86" s="30"/>
+      <c r="AO86" s="25">
         <f>IF(OR(A86="",H86="",H86&lt;=0),"",(E86*H86+IF(AND(AK86&lt;&gt;"",AL86&lt;&gt;""),AK86*AL86,0)+IF(AND(AM86&lt;&gt;"",AN86&lt;&gt;""),AM86*AN86,0))/AP86)</f>
         <v>17.18</v>
       </c>
-      <c r="AP86" s="33">
+      <c r="AP86" s="29">
         <f>IF(OR(A86="",H86="",H86&lt;=0),"",H86+IF(AL86="",0,AL86)+IF(AN86="",0,AN86))</f>
         <v>7200</v>
       </c>
-      <c r="AQ86" s="28">
+      <c r="AQ86" s="25">
         <f>IF(A86="","",IF(M86&lt;&gt;"",0,IF(OR(H86="",N86=""),"",MAX(E86-MAX(N86,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A86))*持仓跟踪!$S$2:$S$157)),0)),0)*H86+IF(OR(AK86="",AL86=""),0,MAX(AK86-MAX(N86,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A86))*持仓跟踪!$S$2:$S$157)),0)),0)*AL86)+IF(OR(AM86="",AN86=""),0,MAX(AM86-MAX(N86,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A86))*持仓跟踪!$S$2:$S$157)),0)),0)*AN86))))</f>
         <v>0</v>
       </c>
-      <c r="AR86" s="26" t="str">
-        <f ca="1">IF(A86="","",IF(OR(E86="",H86=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK86="",AL86&lt;&gt;""),AND(AK86&lt;&gt;"",AL86="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM86="",AN86&lt;&gt;""),AND(AM86&lt;&gt;"",AN86="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM86&lt;&gt;"",AN86&lt;&gt;""),OR(AK86="",AL86="")),"违规：必须先完成第二批",IF(OR(H86&lt;=0,H86&lt;&gt;INT(H86),MOD(H86,100)&lt;&gt;0,AND(AL86&lt;&gt;"",OR(AL86&lt;=0,AL86&lt;&gt;INT(AL86),MOD(AL86,100)&lt;&gt;0)),AND(AN86&lt;&gt;"",OR(AN86&lt;=0,AN86&lt;&gt;INT(AN86),MOD(AN86,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL86&lt;&gt;"",AN86&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ86&gt;C86*D86,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+      <c r="AR86" s="23" t="str">
+        <f ca="1">IF(A86="","",IF(OR(E86="",H86=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK86="",AL86&lt;&gt;""),AND(AK86&lt;&gt;"",AL86="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM86="",AN86&lt;&gt;""),AND(AM86&lt;&gt;"",AN86="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM86&lt;&gt;"",AN86&lt;&gt;""),OR(AK86="",AL86="")),"违规：必须先完成第二批",IF(OR(H86&lt;=0,H86&lt;&gt;INT(H86),MOD(H86,100)&lt;&gt;0,AND(AL86&lt;&gt;"",OR(AL86&lt;=0,AL86&lt;&gt;INT(AL86),MOD(AL86,100)&lt;&gt;0)),AND(AN86&lt;&gt;"",OR(AN86&lt;=0,AN86&lt;&gt;INT(AN86),MOD(AN86,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL86&lt;&gt;"",AN86&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ86&gt;C86*D86,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -13734,7 +13709,7 @@
         <f>IF(A87="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A87)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>12700</v>
       </c>
-      <c r="M87" s="18">
+      <c r="M87" s="17">
         <f>IF(A87="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A87)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43180</v>
       </c>
@@ -13758,7 +13733,7 @@
         <f>IF(OR(AO87="",N87="",AO87&lt;=0),"",(AO87-N87)/AO87)</f>
         <v>0.0212071778140294</v>
       </c>
-      <c r="W87" s="19">
+      <c r="W87" s="18">
         <f>IF(OR(U87="",V87="",V87&lt;=0),"",U87/V87)</f>
         <v>4.12820512820512</v>
       </c>
@@ -13772,7 +13747,7 @@
       </c>
       <c r="Z87" s="7">
         <f>IF(OR(AE87="",多次统计数据!$B$8=""),"",AE87-多次统计数据!$B$8)</f>
-        <v>-0.115448856142408</v>
+        <v>-0.11484405409395</v>
       </c>
       <c r="AA87" s="11">
         <f>IF(OR(I87="",M87="",M87&lt;I87),"",M87-I87)</f>
@@ -13780,7 +13755,7 @@
       </c>
       <c r="AB87" s="7">
         <f>IF(OR(A87="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC87" s="8" t="str">
         <f>IF(OR(AB87="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB87,"低于上限","达到或超过上限"))</f>
@@ -13815,7 +13790,7 @@
         <v>0</v>
       </c>
       <c r="AR87" s="8" t="str">
-        <f ca="1">IF(A87="","",IF(OR(E87="",H87=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK87="",AL87&lt;&gt;""),AND(AK87&lt;&gt;"",AL87="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM87="",AN87&lt;&gt;""),AND(AM87&lt;&gt;"",AN87="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM87&lt;&gt;"",AN87&lt;&gt;""),OR(AK87="",AL87="")),"违规：必须先完成第二批",IF(OR(H87&lt;=0,H87&lt;&gt;INT(H87),MOD(H87,100)&lt;&gt;0,AND(AL87&lt;&gt;"",OR(AL87&lt;=0,AL87&lt;&gt;INT(AL87),MOD(AL87,100)&lt;&gt;0)),AND(AN87&lt;&gt;"",OR(AN87&lt;=0,AN87&lt;&gt;INT(AN87),MOD(AN87,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL87&lt;&gt;"",AN87&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ87&gt;C87*D87,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A87="","",IF(OR(E87="",H87=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK87="",AL87&lt;&gt;""),AND(AK87&lt;&gt;"",AL87="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM87="",AN87&lt;&gt;""),AND(AM87&lt;&gt;"",AN87="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM87&lt;&gt;"",AN87&lt;&gt;""),OR(AK87="",AL87="")),"违规：必须先完成第二批",IF(OR(H87&lt;=0,H87&lt;&gt;INT(H87),MOD(H87,100)&lt;&gt;0,AND(AL87&lt;&gt;"",OR(AL87&lt;=0,AL87&lt;&gt;INT(AL87),MOD(AL87,100)&lt;&gt;0)),AND(AN87&lt;&gt;"",OR(AN87&lt;=0,AN87&lt;&gt;INT(AN87),MOD(AN87,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL87&lt;&gt;"",AN87&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ87&gt;C87*D87,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -13860,7 +13835,7 @@
         <f>IF(A88="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A88)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Z$2:$Z$157&lt;&gt;"")),持仓跟踪!$Z$2:$Z$157),""))</f>
         <v>7600</v>
       </c>
-      <c r="M88" s="18">
+      <c r="M88" s="17">
         <f>IF(A88="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A88)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
         <v>43482</v>
       </c>
@@ -13884,7 +13859,7 @@
         <f>IF(OR(AO88="",N88="",AO88&lt;=0),"",(AO88-N88)/AO88)</f>
         <v>0.0455212922173274</v>
       </c>
-      <c r="W88" s="19">
+      <c r="W88" s="18">
         <f>IF(OR(U88="",V88="",V88&lt;=0),"",U88/V88)</f>
         <v>2.22580645161291</v>
       </c>
@@ -13898,7 +13873,7 @@
       </c>
       <c r="Z88" s="7">
         <f>IF(OR(AE88="",多次统计数据!$B$8=""),"",AE88-多次统计数据!$B$8)</f>
-        <v>-0.10639708197796</v>
+        <v>-0.105792279929502</v>
       </c>
       <c r="AA88" s="11">
         <f>IF(OR(I88="",M88="",M88&lt;I88),"",M88-I88)</f>
@@ -13906,7 +13881,7 @@
       </c>
       <c r="AB88" s="7">
         <f>IF(OR(A88="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC88" s="8" t="str">
         <f>IF(OR(AB88="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB88,"低于上限","达到或超过上限"))</f>
@@ -13941,7 +13916,7 @@
         <v>0</v>
       </c>
       <c r="AR88" s="8" t="str">
-        <f ca="1">IF(A88="","",IF(OR(E88="",H88=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK88="",AL88&lt;&gt;""),AND(AK88&lt;&gt;"",AL88="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM88="",AN88&lt;&gt;""),AND(AM88&lt;&gt;"",AN88="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM88&lt;&gt;"",AN88&lt;&gt;""),OR(AK88="",AL88="")),"违规：必须先完成第二批",IF(OR(H88&lt;=0,H88&lt;&gt;INT(H88),MOD(H88,100)&lt;&gt;0,AND(AL88&lt;&gt;"",OR(AL88&lt;=0,AL88&lt;&gt;INT(AL88),MOD(AL88,100)&lt;&gt;0)),AND(AN88&lt;&gt;"",OR(AN88&lt;=0,AN88&lt;&gt;INT(AN88),MOD(AN88,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL88&lt;&gt;"",AN88&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ88&gt;C88*D88,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$98)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <f ca="1">IF(A88="","",IF(OR(E88="",H88=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK88="",AL88&lt;&gt;""),AND(AK88&lt;&gt;"",AL88="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM88="",AN88&lt;&gt;""),AND(AM88&lt;&gt;"",AN88="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM88&lt;&gt;"",AN88&lt;&gt;""),OR(AK88="",AL88="")),"违规：必须先完成第二批",IF(OR(H88&lt;=0,H88&lt;&gt;INT(H88),MOD(H88,100)&lt;&gt;0,AND(AL88&lt;&gt;"",OR(AL88&lt;=0,AL88&lt;&gt;INT(AL88),MOD(AL88,100)&lt;&gt;0)),AND(AN88&lt;&gt;"",OR(AN88&lt;=0,AN88&lt;&gt;INT(AN88),MOD(AN88,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL88&lt;&gt;"",AN88&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ88&gt;C88*D88,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$102)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
         <v>通过</v>
       </c>
     </row>
@@ -13985,7 +13960,7 @@
         <f>IF(K89="","",H89)</f>
         <v>3400</v>
       </c>
-      <c r="M89" s="18">
+      <c r="M89" s="17">
         <v>43756</v>
       </c>
       <c r="N89" s="10">
@@ -14008,7 +13983,7 @@
         <f>IF(OR(E89="",N89="",E89&lt;=0),"",(E89-N89)/E89)</f>
         <v>0.0955137481910275</v>
       </c>
-      <c r="W89" s="19">
+      <c r="W89" s="18">
         <f>IF(OR(U89="",V89="",V89&lt;=0),"",U89/V89)</f>
         <v>1.65151515151515</v>
       </c>
@@ -14022,7 +13997,7 @@
       </c>
       <c r="Z89" s="7">
         <f>IF(OR(AE89="",多次统计数据!$B$8=""),"",AE89-多次统计数据!$B$8)</f>
-        <v>-0.115723981136559</v>
+        <v>-0.1151191790881</v>
       </c>
       <c r="AA89" s="11">
         <f>IF(OR(I89="",M89="",M89&lt;I89),"",M89-I89)</f>
@@ -14030,7 +14005,7 @@
       </c>
       <c r="AB89" s="7">
         <f>IF(OR(A89="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC89" s="8" t="str">
         <f>IF(OR(AB89="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB89,"低于上限","达到或超过上限"))</f>
@@ -14109,7 +14084,7 @@
         <f>IF(K90="","",H90)</f>
         <v>3100</v>
       </c>
-      <c r="M90" s="18">
+      <c r="M90" s="17">
         <v>43899</v>
       </c>
       <c r="N90" s="10">
@@ -14132,7 +14107,7 @@
         <f>IF(OR(E90="",N90="",E90&lt;=0),"",(E90-N90)/E90)</f>
         <v>0.0731204943357364</v>
       </c>
-      <c r="W90" s="19">
+      <c r="W90" s="18">
         <f>IF(OR(U90="",V90="",V90&lt;=0),"",U90/V90)</f>
         <v>2.52112676056338</v>
       </c>
@@ -14146,7 +14121,7 @@
       </c>
       <c r="Z90" s="7">
         <f>IF(OR(AE90="",多次统计数据!$B$8=""),"",AE90-多次统计数据!$B$8)</f>
-        <v>-0.111964115211838</v>
+        <v>-0.11135931316338</v>
       </c>
       <c r="AA90" s="11">
         <f>IF(OR(I90="",M90="",M90&lt;I90),"",M90-I90)</f>
@@ -14154,7 +14129,7 @@
       </c>
       <c r="AB90" s="7">
         <f>IF(OR(A90="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC90" s="8" t="str">
         <f>IF(OR(AB90="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB90,"低于上限","达到或超过上限"))</f>
@@ -14233,7 +14208,7 @@
         <f>IF(K91="","",H91)</f>
         <v>4700</v>
       </c>
-      <c r="M91" s="18">
+      <c r="M91" s="17">
         <v>44005</v>
       </c>
       <c r="N91" s="10">
@@ -14256,7 +14231,7 @@
         <f>IF(OR(E91="",N91="",E91&lt;=0),"",(E91-N91)/E91)</f>
         <v>0.0558343789209535</v>
       </c>
-      <c r="W91" s="19">
+      <c r="W91" s="18">
         <f>IF(OR(U91="",V91="",V91&lt;=0),"",U91/V91)</f>
         <v>4.561797752809</v>
       </c>
@@ -14270,7 +14245,7 @@
       </c>
       <c r="Z91" s="7">
         <f>IF(OR(AE91="",多次统计数据!$B$8=""),"",AE91-多次统计数据!$B$8)</f>
-        <v>0.0284175977976288</v>
+        <v>0.0290223998460876</v>
       </c>
       <c r="AA91" s="11">
         <f>IF(OR(I91="",M91="",M91&lt;I91),"",M91-I91)</f>
@@ -14278,7 +14253,7 @@
       </c>
       <c r="AB91" s="7">
         <f>IF(OR(A91="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC91" s="8" t="str">
         <f>IF(OR(AB91="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB91,"低于上限","达到或超过上限"))</f>
@@ -14357,7 +14332,7 @@
         <f>IF(K92="","",H92)</f>
         <v>2500</v>
       </c>
-      <c r="M92" s="18">
+      <c r="M92" s="17">
         <v>44062</v>
       </c>
       <c r="N92" s="10">
@@ -14380,7 +14355,7 @@
         <f>IF(OR(E92="",N92="",E92&lt;=0),"",(E92-N92)/E92)</f>
         <v>0.0719257540603248</v>
       </c>
-      <c r="W92" s="19">
+      <c r="W92" s="18">
         <f>IF(OR(U92="",V92="",V92&lt;=0),"",U92/V92)</f>
         <v>2.2258064516129</v>
       </c>
@@ -14394,7 +14369,7 @@
       </c>
       <c r="Z92" s="7">
         <f>IF(OR(AE92="",多次统计数据!$B$8=""),"",AE92-多次统计数据!$B$8)</f>
-        <v>-0.0993025680256101</v>
+        <v>-0.0986977659771514</v>
       </c>
       <c r="AA92" s="11">
         <f>IF(OR(I92="",M92="",M92&lt;I92),"",M92-I92)</f>
@@ -14402,7 +14377,7 @@
       </c>
       <c r="AB92" s="7">
         <f>IF(OR(A92="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC92" s="8" t="str">
         <f>IF(OR(AB92="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB92,"低于上限","达到或超过上限"))</f>
@@ -14481,7 +14456,7 @@
         <f>IF(K93="","",H93)</f>
         <v>700</v>
       </c>
-      <c r="M93" s="18">
+      <c r="M93" s="17">
         <v>44251</v>
       </c>
       <c r="N93" s="10">
@@ -14504,7 +14479,7 @@
         <f>IF(OR(E93="",N93="",E93&lt;=0),"",(E93-N93)/E93)</f>
         <v>0.0873136598722238</v>
       </c>
-      <c r="W93" s="19">
+      <c r="W93" s="18">
         <f>IF(OR(U93="",V93="",V93&lt;=0),"",U93/V93)</f>
         <v>0.742160278745646</v>
       </c>
@@ -14518,7 +14493,7 @@
       </c>
       <c r="Z93" s="7">
         <f>IF(OR(AE93="",多次统计数据!$B$8=""),"",AE93-多次统计数据!$B$8)</f>
-        <v>-0.0702611563443369</v>
+        <v>-0.0696563542958781</v>
       </c>
       <c r="AA93" s="11">
         <f>IF(OR(I93="",M93="",M93&lt;I93),"",M93-I93)</f>
@@ -14526,7 +14501,7 @@
       </c>
       <c r="AB93" s="7">
         <f>IF(OR(A93="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC93" s="8" t="str">
         <f>IF(OR(AB93="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB93,"低于上限","达到或超过上限"))</f>
@@ -14605,7 +14580,7 @@
         <f>IF(K94="","",H94)</f>
         <v>1800</v>
       </c>
-      <c r="M94" s="18">
+      <c r="M94" s="17">
         <v>44404</v>
       </c>
       <c r="N94" s="10">
@@ -14628,7 +14603,7 @@
         <f>IF(OR(E94="",N94="",E94&lt;=0),"",(E94-N94)/E94)</f>
         <v>0.0375659733002173</v>
       </c>
-      <c r="W94" s="19">
+      <c r="W94" s="18">
         <f>IF(OR(U94="",V94="",V94&lt;=0),"",U94/V94)</f>
         <v>2.30578512396694</v>
       </c>
@@ -14642,7 +14617,7 @@
       </c>
       <c r="Z94" s="7">
         <f>IF(OR(AE94="",多次统计数据!$B$8=""),"",AE94-多次统计数据!$B$8)</f>
-        <v>0.0223973694018807</v>
+        <v>0.0230021714503395</v>
       </c>
       <c r="AA94" s="11">
         <f>IF(OR(I94="",M94="",M94&lt;I94),"",M94-I94)</f>
@@ -14650,7 +14625,7 @@
       </c>
       <c r="AB94" s="7">
         <f>IF(OR(A94="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC94" s="8" t="str">
         <f>IF(OR(AB94="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB94,"低于上限","达到或超过上限"))</f>
@@ -14729,7 +14704,7 @@
         <f>IF(K95="","",H95)</f>
         <v>900</v>
       </c>
-      <c r="M95" s="18">
+      <c r="M95" s="17">
         <v>44441</v>
       </c>
       <c r="N95" s="10">
@@ -14752,7 +14727,7 @@
         <f>IF(OR(E95="",N95="",E95&lt;=0),"",(E95-N95)/E95)</f>
         <v>0.0594874206442511</v>
       </c>
-      <c r="W95" s="19">
+      <c r="W95" s="18">
         <f>IF(OR(U95="",V95="",V95&lt;=0),"",U95/V95)</f>
         <v>2.95256916996047</v>
       </c>
@@ -14766,7 +14741,7 @@
       </c>
       <c r="Z95" s="7">
         <f>IF(OR(AE95="",多次统计数据!$B$8=""),"",AE95-多次统计数据!$B$8)</f>
-        <v>-0.0726210571585604</v>
+        <v>-0.0720162551101017</v>
       </c>
       <c r="AA95" s="11">
         <f>IF(OR(I95="",M95="",M95&lt;I95),"",M95-I95)</f>
@@ -14774,7 +14749,7 @@
       </c>
       <c r="AB95" s="7">
         <f>IF(OR(A95="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC95" s="8" t="str">
         <f>IF(OR(AB95="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB95,"低于上限","达到或超过上限"))</f>
@@ -14853,7 +14828,7 @@
         <f>IF(K96="","",H96)</f>
         <v>1100</v>
       </c>
-      <c r="M96" s="18">
+      <c r="M96" s="17">
         <v>44452</v>
       </c>
       <c r="N96" s="10">
@@ -14876,7 +14851,7 @@
         <f>IF(OR(E96="",N96="",E96&lt;=0),"",(E96-N96)/E96)</f>
         <v>0.0492170022371365</v>
       </c>
-      <c r="W96" s="19">
+      <c r="W96" s="18">
         <f>IF(OR(U96="",V96="",V96&lt;=0),"",U96/V96)</f>
         <v>2.4090909090909</v>
       </c>
@@ -14890,7 +14865,7 @@
       </c>
       <c r="Z96" s="7">
         <f>IF(OR(AE96="",多次统计数据!$B$8=""),"",AE96-多次统计数据!$B$8)</f>
-        <v>-0.0964966021500261</v>
+        <v>-0.0958918001015673</v>
       </c>
       <c r="AA96" s="11">
         <f>IF(OR(I96="",M96="",M96&lt;I96),"",M96-I96)</f>
@@ -14898,7 +14873,7 @@
       </c>
       <c r="AB96" s="7">
         <f>IF(OR(A96="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC96" s="8" t="str">
         <f>IF(OR(AB96="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB96,"低于上限","达到或超过上限"))</f>
@@ -14977,7 +14952,7 @@
         <f>IF(K97="","",H97)</f>
         <v>700</v>
       </c>
-      <c r="M97" s="18">
+      <c r="M97" s="17">
         <v>44550</v>
       </c>
       <c r="N97" s="10">
@@ -15000,7 +14975,7 @@
         <f>IF(OR(E97="",N97="",E97&lt;=0),"",(E97-N97)/E97)</f>
         <v>0.0709197894084856</v>
       </c>
-      <c r="W97" s="19">
+      <c r="W97" s="18">
         <f>IF(OR(U97="",V97="",V97&lt;=0),"",U97/V97)</f>
         <v>1.91120815138282</v>
       </c>
@@ -15014,7 +14989,7 @@
       </c>
       <c r="Z97" s="7">
         <f>IF(OR(AE97="",多次统计数据!$B$8=""),"",AE97-多次统计数据!$B$8)</f>
-        <v>-0.100918503152625</v>
+        <v>-0.100313701104166</v>
       </c>
       <c r="AA97" s="11">
         <f>IF(OR(I97="",M97="",M97&lt;I97),"",M97-I97)</f>
@@ -15022,7 +14997,7 @@
       </c>
       <c r="AB97" s="7">
         <f>IF(OR(A97="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC97" s="8" t="str">
         <f>IF(OR(AB97="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB97,"低于上限","达到或超过上限"))</f>
@@ -15061,7 +15036,7 @@
         <v>通过</v>
       </c>
     </row>
-    <row r="98" ht="34" spans="1:44">
+    <row r="98" ht="17" spans="1:44">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -15074,31 +15049,39 @@
       <c r="D98" s="6">
         <v>0.02</v>
       </c>
-      <c r="E98" s="10"/>
-      <c r="F98" s="8" t="str">
+      <c r="E98" s="10">
+        <v>8.32</v>
+      </c>
+      <c r="F98" s="8">
         <f>IF(OR(C98="",D98="",E98="",N98="",C98&lt;=0,D98&lt;=0,E98&lt;=N98),"",ROUNDDOWN((C98*D98)/(E98-N98)/100,0)*100)</f>
-        <v/>
+        <v>2500</v>
       </c>
       <c r="G98" s="8" t="str">
         <f>IF(OR(A98="",F98="",E98="",N98="",E98&lt;=N98,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H98="",F98*(E98-N98),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H98" s="2"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="10"/>
-      <c r="K98" s="5" t="str">
-        <f>IF(A98="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A98)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$Y$2:$Y$157&lt;&gt;"")),持仓跟踪!$Y$2:$Y$157),""))</f>
-        <v/>
-      </c>
-      <c r="L98" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H98" s="2">
+        <v>2500</v>
+      </c>
+      <c r="I98" s="13">
+        <v>41495</v>
+      </c>
+      <c r="J98" s="10">
+        <v>10</v>
+      </c>
+      <c r="K98" s="5">
+        <v>8.18</v>
+      </c>
+      <c r="L98" s="8">
         <f>IF(K98="","",H98)</f>
-        <v/>
-      </c>
-      <c r="M98" s="18" t="str">
-        <f>IF(A98="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A98)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
-        <v/>
-      </c>
-      <c r="N98" s="10"/>
+        <v>2500</v>
+      </c>
+      <c r="M98" s="17">
+        <v>41586</v>
+      </c>
+      <c r="N98" s="10">
+        <v>6.5</v>
+      </c>
       <c r="O98" s="10"/>
       <c r="P98" s="5" t="str">
         <f>IF(A98="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A98)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
@@ -15108,46 +15091,46 @@
       <c r="R98" s="2"/>
       <c r="S98" s="2"/>
       <c r="T98" s="2"/>
-      <c r="U98" s="7" t="str">
+      <c r="U98" s="7">
         <f>IF(OR(E98="",J98="",E98&lt;=0),"",(J98-E98)/E98)</f>
-        <v/>
-      </c>
-      <c r="V98" s="7" t="str">
+        <v>0.201923076923077</v>
+      </c>
+      <c r="V98" s="7">
         <f>IF(OR(E98="",N98="",E98&lt;=0),"",(E98-N98)/E98)</f>
-        <v/>
-      </c>
-      <c r="W98" s="19" t="str">
+        <v>0.21875</v>
+      </c>
+      <c r="W98" s="18">
         <f>IF(OR(U98="",V98="",V98&lt;=0),"",U98/V98)</f>
-        <v/>
-      </c>
-      <c r="X98" s="5" t="str">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="X98" s="5">
         <f>IF(OR(K98="",L98="",E98="",H98=""),"",K98*L98-E98*H98-IF(O98="",0,O98)-IF(P98="",0,P98))</f>
-        <v/>
-      </c>
-      <c r="Y98" s="7" t="str">
+        <v>-350</v>
+      </c>
+      <c r="Y98" s="7">
         <f>IF(OR(X98="",E98="",H98=""),"",IF(E98*H98+IF(O98="",0,O98)&lt;=0,"",X98/(E98*H98+IF(O98="",0,O98))))</f>
-        <v/>
-      </c>
-      <c r="Z98" s="7" t="str">
+        <v>-0.0168269230769231</v>
+      </c>
+      <c r="Z98" s="7">
         <f>IF(OR(AE98="",多次统计数据!$B$8=""),"",AE98-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA98" s="11" t="str">
+        <v>-0.0734289838925999</v>
+      </c>
+      <c r="AA98" s="11">
         <f>IF(OR(I98="",M98="",M98&lt;I98),"",M98-I98)</f>
-        <v/>
+        <v>91</v>
       </c>
       <c r="AB98" s="7">
         <f>IF(OR(A98="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0530166567311223</v>
+        <v>0.0502023655767374</v>
       </c>
       <c r="AC98" s="8" t="str">
         <f>IF(OR(AB98="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB98,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
       <c r="AD98" s="2"/>
-      <c r="AE98" s="7" t="str">
+      <c r="AE98" s="7">
         <f>IF(OR(X98="",C98="",C98&lt;=0),"",X98/C98)</f>
-        <v/>
+        <v>-0.00148515901809772</v>
       </c>
       <c r="AG98" s="2"/>
       <c r="AH98" s="2"/>
@@ -15160,202 +15143,519 @@
       <c r="AL98" s="12"/>
       <c r="AM98" s="10"/>
       <c r="AN98" s="12"/>
-      <c r="AO98" s="5" t="str">
+      <c r="AO98" s="5">
         <f>IF(OR(A98="",H98="",H98&lt;=0),"",(E98*H98+IF(AND(AK98&lt;&gt;"",AL98&lt;&gt;""),AK98*AL98,0)+IF(AND(AM98&lt;&gt;"",AN98&lt;&gt;""),AM98*AN98,0))/AP98)</f>
-        <v/>
-      </c>
-      <c r="AP98" s="11" t="str">
+        <v>8.32</v>
+      </c>
+      <c r="AP98" s="11">
         <f>IF(OR(A98="",H98="",H98&lt;=0),"",H98+IF(AL98="",0,AL98)+IF(AN98="",0,AN98))</f>
-        <v/>
-      </c>
-      <c r="AQ98" s="5" t="str">
+        <v>2500</v>
+      </c>
+      <c r="AQ98" s="5">
         <f>IF(A98="","",IF(M98&lt;&gt;"",0,IF(OR(H98="",N98=""),"",MAX(E98-MAX(N98,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A98))*持仓跟踪!$S$2:$S$157)),0)),0)*H98+IF(OR(AK98="",AL98=""),0,MAX(AK98-MAX(N98,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A98))*持仓跟踪!$S$2:$S$157)),0)),0)*AL98)+IF(OR(AM98="",AN98=""),0,MAX(AM98-MAX(N98,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A98))*持仓跟踪!$S$2:$S$157)),0)),0)*AN98))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AR98" s="8" t="str">
         <f ca="1">IF(A98="","",IF(OR(E98="",H98=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK98="",AL98&lt;&gt;""),AND(AK98&lt;&gt;"",AL98="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM98="",AN98&lt;&gt;""),AND(AM98&lt;&gt;"",AN98="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM98&lt;&gt;"",AN98&lt;&gt;""),OR(AK98="",AL98="")),"违规：必须先完成第二批",IF(OR(H98&lt;=0,H98&lt;&gt;INT(H98),MOD(H98,100)&lt;&gt;0,AND(AL98&lt;&gt;"",OR(AL98&lt;=0,AL98&lt;&gt;INT(AL98),MOD(AL98,100)&lt;&gt;0)),AND(AN98&lt;&gt;"",OR(AN98&lt;=0,AN98&lt;&gt;INT(AN98),MOD(AN98,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL98&lt;&gt;"",AN98&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ98&gt;C98*D98,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$201)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
-        <v>违规：第一批价格或股数缺失</v>
-      </c>
-    </row>
-    <row r="99" spans="1:44">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="10"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="13"/>
-      <c r="J99" s="10"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="18"/>
-      <c r="N99" s="10"/>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="99" ht="17" spans="1:44">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C99" s="10">
+        <v>235315</v>
+      </c>
+      <c r="D99" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E99" s="10">
+        <v>12.91</v>
+      </c>
+      <c r="F99" s="8">
+        <f>IF(OR(C99="",D99="",E99="",N99="",C99&lt;=0,D99&lt;=0,E99&lt;=N99),"",ROUNDDOWN((C99*D99)/(E99-N99)/100,0)*100)</f>
+        <v>11400</v>
+      </c>
+      <c r="G99" s="8" t="str">
+        <f>IF(OR(A99="",F99="",E99="",N99="",E99&lt;=N99,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H99="",F99*(E99-N99),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
+        <v>允许开仓</v>
+      </c>
+      <c r="H99" s="2">
+        <v>11400</v>
+      </c>
+      <c r="I99" s="13">
+        <v>41712</v>
+      </c>
+      <c r="J99" s="10">
+        <v>20</v>
+      </c>
+      <c r="K99" s="5">
+        <v>11</v>
+      </c>
+      <c r="L99" s="8">
+        <f>IF(K99="","",H99)</f>
+        <v>11400</v>
+      </c>
+      <c r="M99" s="17">
+        <v>41768</v>
+      </c>
+      <c r="N99" s="10">
+        <v>11.68</v>
+      </c>
       <c r="O99" s="10"/>
-      <c r="P99" s="5"/>
+      <c r="P99" s="5" t="str">
+        <f>IF(A99="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A99)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
+        <v/>
+      </c>
       <c r="Q99" s="2"/>
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
       <c r="T99" s="2"/>
-      <c r="U99" s="7"/>
-      <c r="V99" s="7"/>
-      <c r="W99" s="19"/>
-      <c r="X99" s="5"/>
-      <c r="Y99" s="7"/>
-      <c r="Z99" s="7"/>
-      <c r="AA99" s="11"/>
-      <c r="AB99" s="7"/>
-      <c r="AC99" s="8"/>
+      <c r="U99" s="7">
+        <f>IF(OR(E99="",J99="",E99&lt;=0),"",(J99-E99)/E99)</f>
+        <v>0.549186676994578</v>
+      </c>
+      <c r="V99" s="7">
+        <f>IF(OR(E99="",N99="",E99&lt;=0),"",(E99-N99)/E99)</f>
+        <v>0.0952749806351666</v>
+      </c>
+      <c r="W99" s="18">
+        <f>IF(OR(U99="",V99="",V99&lt;=0),"",U99/V99)</f>
+        <v>5.76422764227642</v>
+      </c>
+      <c r="X99" s="5">
+        <f>IF(OR(K99="",L99="",E99="",H99=""),"",K99*L99-E99*H99-IF(O99="",0,O99)-IF(P99="",0,P99))</f>
+        <v>-21774</v>
+      </c>
+      <c r="Y99" s="7">
+        <f>IF(OR(X99="",E99="",H99=""),"",IF(E99*H99+IF(O99="",0,O99)&lt;=0,"",X99/(E99*H99+IF(O99="",0,O99))))</f>
+        <v>-0.147947327652982</v>
+      </c>
+      <c r="Z99" s="7">
+        <f>IF(OR(AE99="",多次统计数据!$B$8=""),"",AE99-多次统计数据!$B$8)</f>
+        <v>-0.164475112722706</v>
+      </c>
+      <c r="AA99" s="11">
+        <f>IF(OR(I99="",M99="",M99&lt;I99),"",M99-I99)</f>
+        <v>56</v>
+      </c>
+      <c r="AB99" s="7">
+        <f>IF(OR(A99="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC99" s="8" t="str">
+        <f>IF(OR(AB99="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB99,"低于上限","达到或超过上限"))</f>
+        <v>低于上限</v>
+      </c>
       <c r="AD99" s="2"/>
-      <c r="AE99" s="7"/>
+      <c r="AE99" s="7">
+        <f>IF(OR(X99="",C99="",C99&lt;=0),"",X99/C99)</f>
+        <v>-0.0925312878482035</v>
+      </c>
       <c r="AG99" s="2"/>
       <c r="AH99" s="2"/>
       <c r="AI99" s="2"/>
-      <c r="AJ99" s="8"/>
+      <c r="AJ99" s="8" t="str">
+        <f>IF(OR(AG99="",AH99=""),"",IF(OR(AND(AG99="短期博反弹",OR(AH99="1～3个交易日",AH99="4～10个交易日")),AND(AG99="突破冲新高",OR(AH99="4～10个交易日",AH99="11～20个交易日")),AND(AG99="趋势波段",OR(AH99="11～20个交易日",AH99="21～60个交易日",AH99="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
+        <v/>
+      </c>
       <c r="AK99" s="10"/>
       <c r="AL99" s="12"/>
       <c r="AM99" s="10"/>
       <c r="AN99" s="12"/>
-      <c r="AO99" s="5"/>
-      <c r="AP99" s="11"/>
-      <c r="AQ99" s="5"/>
-      <c r="AR99" s="8"/>
-    </row>
-    <row r="100" spans="1:44">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="10"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="18"/>
-      <c r="N100" s="10"/>
+      <c r="AO99" s="5">
+        <f>IF(OR(A99="",H99="",H99&lt;=0),"",(E99*H99+IF(AND(AK99&lt;&gt;"",AL99&lt;&gt;""),AK99*AL99,0)+IF(AND(AM99&lt;&gt;"",AN99&lt;&gt;""),AM99*AN99,0))/AP99)</f>
+        <v>12.91</v>
+      </c>
+      <c r="AP99" s="11">
+        <f>IF(OR(A99="",H99="",H99&lt;=0),"",H99+IF(AL99="",0,AL99)+IF(AN99="",0,AN99))</f>
+        <v>11400</v>
+      </c>
+      <c r="AQ99" s="5">
+        <f>IF(A99="","",IF(M99&lt;&gt;"",0,IF(OR(H99="",N99=""),"",MAX(E99-MAX(N99,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A99))*持仓跟踪!$S$2:$S$157)),0)),0)*H99+IF(OR(AK99="",AL99=""),0,MAX(AK99-MAX(N99,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A99))*持仓跟踪!$S$2:$S$157)),0)),0)*AL99)+IF(OR(AM99="",AN99=""),0,MAX(AM99-MAX(N99,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A99))*持仓跟踪!$S$2:$S$157)),0)),0)*AN99))))</f>
+        <v>0</v>
+      </c>
+      <c r="AR99" s="8" t="str">
+        <f ca="1">IF(A99="","",IF(OR(E99="",H99=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK99="",AL99&lt;&gt;""),AND(AK99&lt;&gt;"",AL99="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM99="",AN99&lt;&gt;""),AND(AM99&lt;&gt;"",AN99="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM99&lt;&gt;"",AN99&lt;&gt;""),OR(AK99="",AL99="")),"违规：必须先完成第二批",IF(OR(H99&lt;=0,H99&lt;&gt;INT(H99),MOD(H99,100)&lt;&gt;0,AND(AL99&lt;&gt;"",OR(AL99&lt;=0,AL99&lt;&gt;INT(AL99),MOD(AL99,100)&lt;&gt;0)),AND(AN99&lt;&gt;"",OR(AN99&lt;=0,AN99&lt;&gt;INT(AN99),MOD(AN99,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL99&lt;&gt;"",AN99&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ99&gt;C99*D99,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$201)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="100" ht="17" spans="1:44">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C100" s="10">
+        <v>213541</v>
+      </c>
+      <c r="D100" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E100" s="10">
+        <v>12.05</v>
+      </c>
+      <c r="F100" s="8">
+        <f>IF(OR(C100="",D100="",E100="",N100="",C100&lt;=0,D100&lt;=0,E100&lt;=N100),"",ROUNDDOWN((C100*D100)/(E100-N100)/100,0)*100)</f>
+        <v>6200</v>
+      </c>
+      <c r="G100" s="8" t="str">
+        <f>IF(OR(A100="",F100="",E100="",N100="",E100&lt;=N100,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H100="",F100*(E100-N100),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
+        <v>允许开仓</v>
+      </c>
+      <c r="H100" s="2">
+        <v>6200</v>
+      </c>
+      <c r="I100" s="13">
+        <v>41985</v>
+      </c>
+      <c r="J100" s="10">
+        <v>20</v>
+      </c>
+      <c r="K100" s="5">
+        <v>9.66</v>
+      </c>
+      <c r="L100" s="8">
+        <f>IF(K100="","",H100)</f>
+        <v>6200</v>
+      </c>
+      <c r="M100" s="17">
+        <v>41985</v>
+      </c>
+      <c r="N100" s="10">
+        <v>10</v>
+      </c>
       <c r="O100" s="10"/>
-      <c r="P100" s="5"/>
+      <c r="P100" s="5" t="str">
+        <f>IF(A100="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A100)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
+        <v/>
+      </c>
       <c r="Q100" s="2"/>
       <c r="R100" s="2"/>
       <c r="S100" s="2"/>
       <c r="T100" s="2"/>
-      <c r="U100" s="7"/>
-      <c r="V100" s="7"/>
-      <c r="W100" s="19"/>
-      <c r="X100" s="5"/>
-      <c r="Y100" s="7"/>
-      <c r="Z100" s="7"/>
-      <c r="AA100" s="11"/>
-      <c r="AB100" s="7"/>
-      <c r="AC100" s="8"/>
+      <c r="U100" s="7">
+        <f>IF(OR(E100="",J100="",E100&lt;=0),"",(J100-E100)/E100)</f>
+        <v>0.659751037344398</v>
+      </c>
+      <c r="V100" s="7">
+        <f>IF(OR(E100="",N100="",E100&lt;=0),"",(E100-N100)/E100)</f>
+        <v>0.170124481327801</v>
+      </c>
+      <c r="W100" s="18">
+        <f>IF(OR(U100="",V100="",V100&lt;=0),"",U100/V100)</f>
+        <v>3.8780487804878</v>
+      </c>
+      <c r="X100" s="5">
+        <f>IF(OR(K100="",L100="",E100="",H100=""),"",K100*L100-E100*H100-IF(O100="",0,O100)-IF(P100="",0,P100))</f>
+        <v>-14818</v>
+      </c>
+      <c r="Y100" s="7">
+        <f>IF(OR(X100="",E100="",H100=""),"",IF(E100*H100+IF(O100="",0,O100)&lt;=0,"",X100/(E100*H100+IF(O100="",0,O100))))</f>
+        <v>-0.198340248962656</v>
+      </c>
+      <c r="Z100" s="7">
+        <f>IF(OR(AE100="",多次统计数据!$B$8=""),"",AE100-多次统计数据!$B$8)</f>
+        <v>-0.141335651268497</v>
+      </c>
+      <c r="AA100" s="11">
+        <f>IF(OR(I100="",M100="",M100&lt;I100),"",M100-I100)</f>
+        <v>0</v>
+      </c>
+      <c r="AB100" s="7">
+        <f>IF(OR(A100="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC100" s="8" t="str">
+        <f>IF(OR(AB100="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB100,"低于上限","达到或超过上限"))</f>
+        <v>低于上限</v>
+      </c>
       <c r="AD100" s="2"/>
-      <c r="AE100" s="7"/>
+      <c r="AE100" s="7">
+        <f>IF(OR(X100="",C100="",C100&lt;=0),"",X100/C100)</f>
+        <v>-0.0693918263939946</v>
+      </c>
       <c r="AG100" s="2"/>
       <c r="AH100" s="2"/>
       <c r="AI100" s="2"/>
-      <c r="AJ100" s="8"/>
+      <c r="AJ100" s="8" t="str">
+        <f>IF(OR(AG100="",AH100=""),"",IF(OR(AND(AG100="短期博反弹",OR(AH100="1～3个交易日",AH100="4～10个交易日")),AND(AG100="突破冲新高",OR(AH100="4～10个交易日",AH100="11～20个交易日")),AND(AG100="趋势波段",OR(AH100="11～20个交易日",AH100="21～60个交易日",AH100="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
+        <v/>
+      </c>
       <c r="AK100" s="10"/>
       <c r="AL100" s="12"/>
       <c r="AM100" s="10"/>
       <c r="AN100" s="12"/>
-      <c r="AO100" s="5"/>
-      <c r="AP100" s="11"/>
-      <c r="AQ100" s="5"/>
-      <c r="AR100" s="8"/>
-    </row>
-    <row r="101" spans="1:44">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="18"/>
-      <c r="N101" s="10"/>
+      <c r="AO100" s="5">
+        <f>IF(OR(A100="",H100="",H100&lt;=0),"",(E100*H100+IF(AND(AK100&lt;&gt;"",AL100&lt;&gt;""),AK100*AL100,0)+IF(AND(AM100&lt;&gt;"",AN100&lt;&gt;""),AM100*AN100,0))/AP100)</f>
+        <v>12.05</v>
+      </c>
+      <c r="AP100" s="11">
+        <f>IF(OR(A100="",H100="",H100&lt;=0),"",H100+IF(AL100="",0,AL100)+IF(AN100="",0,AN100))</f>
+        <v>6200</v>
+      </c>
+      <c r="AQ100" s="5">
+        <f>IF(A100="","",IF(M100&lt;&gt;"",0,IF(OR(H100="",N100=""),"",MAX(E100-MAX(N100,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A100))*持仓跟踪!$S$2:$S$157)),0)),0)*H100+IF(OR(AK100="",AL100=""),0,MAX(AK100-MAX(N100,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A100))*持仓跟踪!$S$2:$S$157)),0)),0)*AL100)+IF(OR(AM100="",AN100=""),0,MAX(AM100-MAX(N100,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A100))*持仓跟踪!$S$2:$S$157)),0)),0)*AN100))))</f>
+        <v>0</v>
+      </c>
+      <c r="AR100" s="8" t="str">
+        <f ca="1">IF(A100="","",IF(OR(E100="",H100=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK100="",AL100&lt;&gt;""),AND(AK100&lt;&gt;"",AL100="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM100="",AN100&lt;&gt;""),AND(AM100&lt;&gt;"",AN100="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM100&lt;&gt;"",AN100&lt;&gt;""),OR(AK100="",AL100="")),"违规：必须先完成第二批",IF(OR(H100&lt;=0,H100&lt;&gt;INT(H100),MOD(H100,100)&lt;&gt;0,AND(AL100&lt;&gt;"",OR(AL100&lt;=0,AL100&lt;&gt;INT(AL100),MOD(AL100,100)&lt;&gt;0)),AND(AN100&lt;&gt;"",OR(AN100&lt;=0,AN100&lt;&gt;INT(AN100),MOD(AN100,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL100&lt;&gt;"",AN100&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ100&gt;C100*D100,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$201)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="101" ht="17" spans="1:44">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C101" s="10">
+        <v>198723</v>
+      </c>
+      <c r="D101" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E101" s="10">
+        <v>16.78</v>
+      </c>
+      <c r="F101" s="8">
+        <f>IF(OR(C101="",D101="",E101="",N101="",C101&lt;=0,D101&lt;=0,E101&lt;=N101),"",ROUNDDOWN((C101*D101)/(E101-N101)/100,0)*100)</f>
+        <v>4200</v>
+      </c>
+      <c r="G101" s="8" t="str">
+        <f>IF(OR(A101="",F101="",E101="",N101="",E101&lt;=N101,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H101="",F101*(E101-N101),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
+        <v>允许开仓</v>
+      </c>
+      <c r="H101" s="2">
+        <v>4200</v>
+      </c>
+      <c r="I101" s="13">
+        <v>42104</v>
+      </c>
+      <c r="J101" s="10">
+        <v>20</v>
+      </c>
+      <c r="K101" s="5">
+        <v>13.02</v>
+      </c>
+      <c r="L101" s="8">
+        <f>IF(K101="","",H101)</f>
+        <v>4200</v>
+      </c>
+      <c r="M101" s="17">
+        <v>42198</v>
+      </c>
+      <c r="N101" s="10">
+        <v>14</v>
+      </c>
       <c r="O101" s="10"/>
-      <c r="P101" s="5"/>
+      <c r="P101" s="5" t="str">
+        <f>IF(A101="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A101)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
+        <v/>
+      </c>
       <c r="Q101" s="2"/>
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
       <c r="T101" s="2"/>
-      <c r="U101" s="7"/>
-      <c r="V101" s="7"/>
-      <c r="W101" s="19"/>
-      <c r="X101" s="5"/>
-      <c r="Y101" s="7"/>
-      <c r="Z101" s="7"/>
-      <c r="AA101" s="11"/>
-      <c r="AB101" s="7"/>
-      <c r="AC101" s="8"/>
+      <c r="U101" s="7">
+        <f>IF(OR(E101="",J101="",E101&lt;=0),"",(J101-E101)/E101)</f>
+        <v>0.191895113230036</v>
+      </c>
+      <c r="V101" s="7">
+        <f>IF(OR(E101="",N101="",E101&lt;=0),"",(E101-N101)/E101)</f>
+        <v>0.165673420738975</v>
+      </c>
+      <c r="W101" s="18">
+        <f>IF(OR(U101="",V101="",V101&lt;=0),"",U101/V101)</f>
+        <v>1.15827338129496</v>
+      </c>
+      <c r="X101" s="5">
+        <f>IF(OR(K101="",L101="",E101="",H101=""),"",K101*L101-E101*H101-IF(O101="",0,O101)-IF(P101="",0,P101))</f>
+        <v>-15792</v>
+      </c>
+      <c r="Y101" s="7">
+        <f>IF(OR(X101="",E101="",H101=""),"",IF(E101*H101+IF(O101="",0,O101)&lt;=0,"",X101/(E101*H101+IF(O101="",0,O101))))</f>
+        <v>-0.224076281287247</v>
+      </c>
+      <c r="Z101" s="7">
+        <f>IF(OR(AE101="",多次统计数据!$B$8=""),"",AE101-多次统计数据!$B$8)</f>
+        <v>-0.151411224219319</v>
+      </c>
+      <c r="AA101" s="11">
+        <f>IF(OR(I101="",M101="",M101&lt;I101),"",M101-I101)</f>
+        <v>94</v>
+      </c>
+      <c r="AB101" s="7">
+        <f>IF(OR(A101="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC101" s="8" t="str">
+        <f>IF(OR(AB101="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB101,"低于上限","达到或超过上限"))</f>
+        <v>低于上限</v>
+      </c>
       <c r="AD101" s="2"/>
-      <c r="AE101" s="7"/>
+      <c r="AE101" s="7">
+        <f>IF(OR(X101="",C101="",C101&lt;=0),"",X101/C101)</f>
+        <v>-0.0794673993448167</v>
+      </c>
       <c r="AG101" s="2"/>
       <c r="AH101" s="2"/>
       <c r="AI101" s="2"/>
-      <c r="AJ101" s="8"/>
+      <c r="AJ101" s="8" t="str">
+        <f>IF(OR(AG101="",AH101=""),"",IF(OR(AND(AG101="短期博反弹",OR(AH101="1～3个交易日",AH101="4～10个交易日")),AND(AG101="突破冲新高",OR(AH101="4～10个交易日",AH101="11～20个交易日")),AND(AG101="趋势波段",OR(AH101="11～20个交易日",AH101="21～60个交易日",AH101="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
+        <v/>
+      </c>
       <c r="AK101" s="10"/>
       <c r="AL101" s="12"/>
       <c r="AM101" s="10"/>
       <c r="AN101" s="12"/>
-      <c r="AO101" s="5"/>
-      <c r="AP101" s="11"/>
-      <c r="AQ101" s="5"/>
-      <c r="AR101" s="8"/>
-    </row>
-    <row r="102" spans="1:44">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="10"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="10"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="10"/>
-      <c r="K102" s="5"/>
-      <c r="L102" s="8"/>
-      <c r="M102" s="18"/>
-      <c r="N102" s="10"/>
+      <c r="AO101" s="5">
+        <f>IF(OR(A101="",H101="",H101&lt;=0),"",(E101*H101+IF(AND(AK101&lt;&gt;"",AL101&lt;&gt;""),AK101*AL101,0)+IF(AND(AM101&lt;&gt;"",AN101&lt;&gt;""),AM101*AN101,0))/AP101)</f>
+        <v>16.78</v>
+      </c>
+      <c r="AP101" s="11">
+        <f>IF(OR(A101="",H101="",H101&lt;=0),"",H101+IF(AL101="",0,AL101)+IF(AN101="",0,AN101))</f>
+        <v>4200</v>
+      </c>
+      <c r="AQ101" s="5">
+        <f>IF(A101="","",IF(M101&lt;&gt;"",0,IF(OR(H101="",N101=""),"",MAX(E101-MAX(N101,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A101))*持仓跟踪!$S$2:$S$157)),0)),0)*H101+IF(OR(AK101="",AL101=""),0,MAX(AK101-MAX(N101,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A101))*持仓跟踪!$S$2:$S$157)),0)),0)*AL101)+IF(OR(AM101="",AN101=""),0,MAX(AM101-MAX(N101,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A101))*持仓跟踪!$S$2:$S$157)),0)),0)*AN101))))</f>
+        <v>0</v>
+      </c>
+      <c r="AR101" s="8" t="str">
+        <f ca="1">IF(A101="","",IF(OR(E101="",H101=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK101="",AL101&lt;&gt;""),AND(AK101&lt;&gt;"",AL101="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM101="",AN101&lt;&gt;""),AND(AM101&lt;&gt;"",AN101="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM101&lt;&gt;"",AN101&lt;&gt;""),OR(AK101="",AL101="")),"违规：必须先完成第二批",IF(OR(H101&lt;=0,H101&lt;&gt;INT(H101),MOD(H101,100)&lt;&gt;0,AND(AL101&lt;&gt;"",OR(AL101&lt;=0,AL101&lt;&gt;INT(AL101),MOD(AL101,100)&lt;&gt;0)),AND(AN101&lt;&gt;"",OR(AN101&lt;=0,AN101&lt;&gt;INT(AN101),MOD(AN101,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL101&lt;&gt;"",AN101&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ101&gt;C101*D101,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$201)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <v>通过</v>
+      </c>
+    </row>
+    <row r="102" ht="34" spans="1:44">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C102" s="10">
+        <v>182931</v>
+      </c>
+      <c r="D102" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="E102" s="10">
+        <v>14.53</v>
+      </c>
+      <c r="F102" s="8">
+        <f>IF(OR(C102="",D102="",E102="",N102="",C102&lt;=0,D102&lt;=0,E102&lt;=N102),"",ROUNDDOWN((C102*D102)/(E102-N102)/100,0)*100)</f>
+        <v>4300</v>
+      </c>
+      <c r="G102" s="8" t="str">
+        <f>IF(OR(A102="",F102="",E102="",N102="",E102&lt;=N102,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H102="",F102*(E102-N102),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
+        <v>允许开仓</v>
+      </c>
+      <c r="H102" s="2">
+        <v>4300</v>
+      </c>
+      <c r="I102" s="13">
+        <v>42195</v>
+      </c>
+      <c r="J102" s="10">
+        <v>16.51</v>
+      </c>
+      <c r="K102" s="5">
+        <v>16.51</v>
+      </c>
+      <c r="L102" s="8">
+        <f>IF(K102="","",H102)</f>
+        <v>4300</v>
+      </c>
+      <c r="M102" s="17" t="str">
+        <f>IF(A102="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A102)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$H$2:$H$157&lt;&gt;"")),持仓跟踪!$H$2:$H$157),""))</f>
+        <v/>
+      </c>
+      <c r="N102" s="10">
+        <v>12</v>
+      </c>
       <c r="O102" s="10"/>
-      <c r="P102" s="5"/>
+      <c r="P102" s="5" t="str">
+        <f>IF(A102="","",IFERROR(LOOKUP(2,1/((持仓跟踪!$B$2:$B$157=A102)*(持仓跟踪!$X$2:$X$157="执行卖出")*(持仓跟踪!$AA$2:$AA$157&lt;&gt;"")),持仓跟踪!$AA$2:$AA$157),""))</f>
+        <v/>
+      </c>
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
       <c r="T102" s="2"/>
-      <c r="U102" s="7"/>
-      <c r="V102" s="7"/>
-      <c r="W102" s="19"/>
-      <c r="X102" s="5"/>
-      <c r="Y102" s="7"/>
-      <c r="Z102" s="7"/>
-      <c r="AA102" s="11"/>
-      <c r="AB102" s="7"/>
-      <c r="AC102" s="8"/>
+      <c r="U102" s="7">
+        <f>IF(OR(E102="",J102="",E102&lt;=0),"",(J102-E102)/E102)</f>
+        <v>0.136269786648314</v>
+      </c>
+      <c r="V102" s="7">
+        <f>IF(OR(E102="",N102="",E102&lt;=0),"",(E102-N102)/E102)</f>
+        <v>0.174122505161734</v>
+      </c>
+      <c r="W102" s="18">
+        <f>IF(OR(U102="",V102="",V102&lt;=0),"",U102/V102)</f>
+        <v>0.782608695652175</v>
+      </c>
+      <c r="X102" s="5">
+        <f>IF(OR(K102="",L102="",E102="",H102=""),"",K102*L102-E102*H102-IF(O102="",0,O102)-IF(P102="",0,P102))</f>
+        <v>8514</v>
+      </c>
+      <c r="Y102" s="7">
+        <f>IF(OR(X102="",E102="",H102=""),"",IF(E102*H102+IF(O102="",0,O102)&lt;=0,"",X102/(E102*H102+IF(O102="",0,O102))))</f>
+        <v>0.136269786648314</v>
+      </c>
+      <c r="Z102" s="7">
+        <f>IF(OR(AE102="",多次统计数据!$B$8=""),"",AE102-多次统计数据!$B$8)</f>
+        <v>-0.0254016860352677</v>
+      </c>
+      <c r="AA102" s="11" t="str">
+        <f>IF(OR(I102="",M102="",M102&lt;I102),"",M102-I102)</f>
+        <v/>
+      </c>
+      <c r="AB102" s="7">
+        <f>IF(OR(A102="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
+        <v>0.0502023655767374</v>
+      </c>
+      <c r="AC102" s="8" t="str">
+        <f>IF(OR(AB102="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB102,"低于上限","达到或超过上限"))</f>
+        <v>低于上限</v>
+      </c>
       <c r="AD102" s="2"/>
-      <c r="AE102" s="7"/>
+      <c r="AE102" s="7">
+        <f>IF(OR(X102="",C102="",C102&lt;=0),"",X102/C102)</f>
+        <v>0.0465421388392345</v>
+      </c>
       <c r="AG102" s="2"/>
       <c r="AH102" s="2"/>
       <c r="AI102" s="2"/>
-      <c r="AJ102" s="8"/>
+      <c r="AJ102" s="8" t="str">
+        <f>IF(OR(AG102="",AH102=""),"",IF(OR(AND(AG102="短期博反弹",OR(AH102="1～3个交易日",AH102="4～10个交易日")),AND(AG102="突破冲新高",OR(AH102="4～10个交易日",AH102="11～20个交易日")),AND(AG102="趋势波段",OR(AH102="11～20个交易日",AH102="21～60个交易日",AH102="60个交易日以上"))),"匹配","周期与交易预期不匹配，请重新确认"))</f>
+        <v/>
+      </c>
       <c r="AK102" s="10"/>
       <c r="AL102" s="12"/>
       <c r="AM102" s="10"/>
       <c r="AN102" s="12"/>
-      <c r="AO102" s="5"/>
-      <c r="AP102" s="11"/>
-      <c r="AQ102" s="5"/>
-      <c r="AR102" s="8"/>
+      <c r="AO102" s="5">
+        <f>IF(OR(A102="",H102="",H102&lt;=0),"",(E102*H102+IF(AND(AK102&lt;&gt;"",AL102&lt;&gt;""),AK102*AL102,0)+IF(AND(AM102&lt;&gt;"",AN102&lt;&gt;""),AM102*AN102,0))/AP102)</f>
+        <v>14.53</v>
+      </c>
+      <c r="AP102" s="11">
+        <f>IF(OR(A102="",H102="",H102&lt;=0),"",H102+IF(AL102="",0,AL102)+IF(AN102="",0,AN102))</f>
+        <v>4300</v>
+      </c>
+      <c r="AQ102" s="5">
+        <f>IF(A102="","",IF(M102&lt;&gt;"",0,IF(OR(H102="",N102=""),"",MAX(E102-MAX(N102,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A102))*持仓跟踪!$S$2:$S$157)),0)),0)*H102+IF(OR(AK102="",AL102=""),0,MAX(AK102-MAX(N102,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A102))*持仓跟踪!$S$2:$S$157)),0)),0)*AL102)+IF(OR(AM102="",AN102=""),0,MAX(AM102-MAX(N102,IFERROR(SUMPRODUCT(MAX(((持仓跟踪!$A$2:$A$157="每日跟踪")*(持仓跟踪!$B$2:$B$157=A102))*持仓跟踪!$S$2:$S$157)),0)),0)*AN102))))</f>
+        <v>10879</v>
+      </c>
+      <c r="AR102" s="8" t="str">
+        <f ca="1">IF(A102="","",IF(OR(E102="",H102=""),"违规：第一批价格或股数缺失",IF(OR(AND(AK102="",AL102&lt;&gt;""),AND(AK102&lt;&gt;"",AL102="")),"违规：第二批价格与股数须成对填写",IF(OR(AND(AM102="",AN102&lt;&gt;""),AND(AM102&lt;&gt;"",AN102="")),"违规：第三批价格与股数须成对填写",IF(AND(OR(AM102&lt;&gt;"",AN102&lt;&gt;""),OR(AK102="",AL102="")),"违规：必须先完成第二批",IF(OR(H102&lt;=0,H102&lt;&gt;INT(H102),MOD(H102,100)&lt;&gt;0,AND(AL102&lt;&gt;"",OR(AL102&lt;=0,AL102&lt;&gt;INT(AL102),MOD(AL102,100)&lt;&gt;0)),AND(AN102&lt;&gt;"",OR(AN102&lt;=0,AN102&lt;&gt;INT(AN102),MOD(AN102,100)&lt;&gt;0))),"违规：股数须为100股整数倍",IF(AND(OR(AL102&lt;&gt;"",AN102&lt;&gt;""),OR(_LockStatus="已锁仓",_LockStatus="解锁信息不完整")),"违规：锁仓期间禁止加仓",IF(AQ102&gt;C102*D102,"违规：超过单笔风险上限",IF(SUM($AQ$2:$AQ$201)&gt;账户数据!$B$7,"违规：超过账户风险上限","通过")))))))))</f>
+        <v>通过</v>
+      </c>
     </row>
     <row r="103" spans="1:44">
       <c r="A103" s="2"/>
@@ -15370,7 +15670,7 @@
       <c r="J103" s="10"/>
       <c r="K103" s="5"/>
       <c r="L103" s="8"/>
-      <c r="M103" s="18"/>
+      <c r="M103" s="17"/>
       <c r="N103" s="10"/>
       <c r="O103" s="10"/>
       <c r="P103" s="5"/>
@@ -15380,7 +15680,7 @@
       <c r="T103" s="2"/>
       <c r="U103" s="7"/>
       <c r="V103" s="7"/>
-      <c r="W103" s="19"/>
+      <c r="W103" s="18"/>
       <c r="X103" s="5"/>
       <c r="Y103" s="7"/>
       <c r="Z103" s="7"/>
@@ -15415,7 +15715,7 @@
       <c r="J104" s="10"/>
       <c r="K104" s="5"/>
       <c r="L104" s="8"/>
-      <c r="M104" s="18"/>
+      <c r="M104" s="17"/>
       <c r="N104" s="10"/>
       <c r="O104" s="10"/>
       <c r="P104" s="5"/>
@@ -15425,7 +15725,7 @@
       <c r="T104" s="2"/>
       <c r="U104" s="7"/>
       <c r="V104" s="7"/>
-      <c r="W104" s="19"/>
+      <c r="W104" s="18"/>
       <c r="X104" s="5"/>
       <c r="Y104" s="7"/>
       <c r="Z104" s="7"/>
@@ -15460,7 +15760,7 @@
       <c r="J105" s="10"/>
       <c r="K105" s="5"/>
       <c r="L105" s="8"/>
-      <c r="M105" s="18"/>
+      <c r="M105" s="17"/>
       <c r="N105" s="10"/>
       <c r="O105" s="10"/>
       <c r="P105" s="5"/>
@@ -15470,7 +15770,7 @@
       <c r="T105" s="2"/>
       <c r="U105" s="7"/>
       <c r="V105" s="7"/>
-      <c r="W105" s="19"/>
+      <c r="W105" s="18"/>
       <c r="X105" s="5"/>
       <c r="Y105" s="7"/>
       <c r="Z105" s="7"/>
@@ -15505,7 +15805,7 @@
       <c r="J106" s="10"/>
       <c r="K106" s="5"/>
       <c r="L106" s="8"/>
-      <c r="M106" s="18"/>
+      <c r="M106" s="17"/>
       <c r="N106" s="10"/>
       <c r="O106" s="10"/>
       <c r="P106" s="5"/>
@@ -15515,7 +15815,7 @@
       <c r="T106" s="2"/>
       <c r="U106" s="7"/>
       <c r="V106" s="7"/>
-      <c r="W106" s="19"/>
+      <c r="W106" s="18"/>
       <c r="X106" s="5"/>
       <c r="Y106" s="7"/>
       <c r="Z106" s="7"/>
@@ -15550,7 +15850,7 @@
       <c r="J107" s="10"/>
       <c r="K107" s="5"/>
       <c r="L107" s="8"/>
-      <c r="M107" s="18"/>
+      <c r="M107" s="17"/>
       <c r="N107" s="10"/>
       <c r="O107" s="10"/>
       <c r="P107" s="5"/>
@@ -15560,7 +15860,7 @@
       <c r="T107" s="2"/>
       <c r="U107" s="7"/>
       <c r="V107" s="7"/>
-      <c r="W107" s="19"/>
+      <c r="W107" s="18"/>
       <c r="X107" s="5"/>
       <c r="Y107" s="7"/>
       <c r="Z107" s="7"/>
@@ -15595,7 +15895,7 @@
       <c r="J108" s="10"/>
       <c r="K108" s="5"/>
       <c r="L108" s="8"/>
-      <c r="M108" s="18"/>
+      <c r="M108" s="17"/>
       <c r="N108" s="10"/>
       <c r="O108" s="10"/>
       <c r="P108" s="5"/>
@@ -15605,7 +15905,7 @@
       <c r="T108" s="2"/>
       <c r="U108" s="7"/>
       <c r="V108" s="7"/>
-      <c r="W108" s="19"/>
+      <c r="W108" s="18"/>
       <c r="X108" s="5"/>
       <c r="Y108" s="7"/>
       <c r="Z108" s="7"/>
@@ -15640,7 +15940,7 @@
       <c r="J109" s="10"/>
       <c r="K109" s="5"/>
       <c r="L109" s="8"/>
-      <c r="M109" s="18"/>
+      <c r="M109" s="17"/>
       <c r="N109" s="10"/>
       <c r="O109" s="10"/>
       <c r="P109" s="5"/>
@@ -15650,7 +15950,7 @@
       <c r="T109" s="2"/>
       <c r="U109" s="7"/>
       <c r="V109" s="7"/>
-      <c r="W109" s="19"/>
+      <c r="W109" s="18"/>
       <c r="X109" s="5"/>
       <c r="Y109" s="7"/>
       <c r="Z109" s="7"/>
@@ -15685,7 +15985,7 @@
       <c r="J110" s="10"/>
       <c r="K110" s="5"/>
       <c r="L110" s="8"/>
-      <c r="M110" s="18"/>
+      <c r="M110" s="17"/>
       <c r="N110" s="10"/>
       <c r="O110" s="10"/>
       <c r="P110" s="5"/>
@@ -15695,7 +15995,7 @@
       <c r="T110" s="2"/>
       <c r="U110" s="7"/>
       <c r="V110" s="7"/>
-      <c r="W110" s="19"/>
+      <c r="W110" s="18"/>
       <c r="X110" s="5"/>
       <c r="Y110" s="7"/>
       <c r="Z110" s="7"/>
@@ -15730,7 +16030,7 @@
       <c r="J111" s="10"/>
       <c r="K111" s="5"/>
       <c r="L111" s="8"/>
-      <c r="M111" s="18"/>
+      <c r="M111" s="17"/>
       <c r="N111" s="10"/>
       <c r="O111" s="10"/>
       <c r="P111" s="5"/>
@@ -15740,7 +16040,7 @@
       <c r="T111" s="2"/>
       <c r="U111" s="7"/>
       <c r="V111" s="7"/>
-      <c r="W111" s="19"/>
+      <c r="W111" s="18"/>
       <c r="X111" s="5"/>
       <c r="Y111" s="7"/>
       <c r="Z111" s="7"/>
@@ -15775,7 +16075,7 @@
       <c r="J112" s="10"/>
       <c r="K112" s="5"/>
       <c r="L112" s="8"/>
-      <c r="M112" s="18"/>
+      <c r="M112" s="17"/>
       <c r="N112" s="10"/>
       <c r="O112" s="10"/>
       <c r="P112" s="5"/>
@@ -15785,7 +16085,7 @@
       <c r="T112" s="2"/>
       <c r="U112" s="7"/>
       <c r="V112" s="7"/>
-      <c r="W112" s="19"/>
+      <c r="W112" s="18"/>
       <c r="X112" s="5"/>
       <c r="Y112" s="7"/>
       <c r="Z112" s="7"/>
@@ -15820,7 +16120,7 @@
       <c r="J113" s="10"/>
       <c r="K113" s="5"/>
       <c r="L113" s="8"/>
-      <c r="M113" s="18"/>
+      <c r="M113" s="17"/>
       <c r="N113" s="10"/>
       <c r="O113" s="10"/>
       <c r="P113" s="5"/>
@@ -15830,7 +16130,7 @@
       <c r="T113" s="2"/>
       <c r="U113" s="7"/>
       <c r="V113" s="7"/>
-      <c r="W113" s="19"/>
+      <c r="W113" s="18"/>
       <c r="X113" s="5"/>
       <c r="Y113" s="7"/>
       <c r="Z113" s="7"/>
@@ -15865,7 +16165,7 @@
       <c r="J114" s="10"/>
       <c r="K114" s="5"/>
       <c r="L114" s="8"/>
-      <c r="M114" s="18"/>
+      <c r="M114" s="17"/>
       <c r="N114" s="10"/>
       <c r="O114" s="10"/>
       <c r="P114" s="5"/>
@@ -15875,7 +16175,7 @@
       <c r="T114" s="2"/>
       <c r="U114" s="7"/>
       <c r="V114" s="7"/>
-      <c r="W114" s="19"/>
+      <c r="W114" s="18"/>
       <c r="X114" s="5"/>
       <c r="Y114" s="7"/>
       <c r="Z114" s="7"/>
@@ -15910,7 +16210,7 @@
       <c r="J115" s="10"/>
       <c r="K115" s="5"/>
       <c r="L115" s="8"/>
-      <c r="M115" s="18"/>
+      <c r="M115" s="17"/>
       <c r="N115" s="10"/>
       <c r="O115" s="10"/>
       <c r="P115" s="5"/>
@@ -15920,7 +16220,7 @@
       <c r="T115" s="2"/>
       <c r="U115" s="7"/>
       <c r="V115" s="7"/>
-      <c r="W115" s="19"/>
+      <c r="W115" s="18"/>
       <c r="X115" s="5"/>
       <c r="Y115" s="7"/>
       <c r="Z115" s="7"/>
@@ -15955,7 +16255,7 @@
       <c r="J116" s="10"/>
       <c r="K116" s="5"/>
       <c r="L116" s="8"/>
-      <c r="M116" s="18"/>
+      <c r="M116" s="17"/>
       <c r="N116" s="10"/>
       <c r="O116" s="10"/>
       <c r="P116" s="5"/>
@@ -15965,7 +16265,7 @@
       <c r="T116" s="2"/>
       <c r="U116" s="7"/>
       <c r="V116" s="7"/>
-      <c r="W116" s="19"/>
+      <c r="W116" s="18"/>
       <c r="X116" s="5"/>
       <c r="Y116" s="7"/>
       <c r="Z116" s="7"/>
@@ -16000,7 +16300,7 @@
       <c r="J117" s="10"/>
       <c r="K117" s="5"/>
       <c r="L117" s="8"/>
-      <c r="M117" s="18"/>
+      <c r="M117" s="17"/>
       <c r="N117" s="10"/>
       <c r="O117" s="10"/>
       <c r="P117" s="5"/>
@@ -16010,7 +16310,7 @@
       <c r="T117" s="2"/>
       <c r="U117" s="7"/>
       <c r="V117" s="7"/>
-      <c r="W117" s="19"/>
+      <c r="W117" s="18"/>
       <c r="X117" s="5"/>
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
@@ -16045,7 +16345,7 @@
       <c r="J118" s="10"/>
       <c r="K118" s="5"/>
       <c r="L118" s="8"/>
-      <c r="M118" s="18"/>
+      <c r="M118" s="17"/>
       <c r="N118" s="10"/>
       <c r="O118" s="10"/>
       <c r="P118" s="5"/>
@@ -16055,7 +16355,7 @@
       <c r="T118" s="2"/>
       <c r="U118" s="7"/>
       <c r="V118" s="7"/>
-      <c r="W118" s="19"/>
+      <c r="W118" s="18"/>
       <c r="X118" s="5"/>
       <c r="Y118" s="7"/>
       <c r="Z118" s="7"/>
@@ -16091,9 +16391,6 @@
     <cfRule type="expression" dxfId="2" priority="270">
       <formula>$G89="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="300">
-      <formula>$G89="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W89">
     <cfRule type="cellIs" dxfId="2" priority="90" operator="lessThan">
@@ -16137,9 +16434,6 @@
     <cfRule type="expression" dxfId="2" priority="269">
       <formula>$G90="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="299">
-      <formula>$G90="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W90">
     <cfRule type="cellIs" dxfId="2" priority="89" operator="lessThan">
@@ -16183,9 +16477,6 @@
     <cfRule type="expression" dxfId="2" priority="268">
       <formula>$G91="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="298">
-      <formula>$G91="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W91">
     <cfRule type="cellIs" dxfId="2" priority="88" operator="lessThan">
@@ -16229,9 +16520,6 @@
     <cfRule type="expression" dxfId="2" priority="267">
       <formula>$G92="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="297">
-      <formula>$G92="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W92">
     <cfRule type="cellIs" dxfId="2" priority="87" operator="lessThan">
@@ -16275,9 +16563,6 @@
     <cfRule type="expression" dxfId="2" priority="266">
       <formula>$G93="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="296">
-      <formula>$G93="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W93">
     <cfRule type="cellIs" dxfId="2" priority="86" operator="lessThan">
@@ -16321,9 +16606,6 @@
     <cfRule type="expression" dxfId="2" priority="265">
       <formula>$G94="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="295">
-      <formula>$G94="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W94">
     <cfRule type="cellIs" dxfId="2" priority="85" operator="lessThan">
@@ -16367,9 +16649,6 @@
     <cfRule type="expression" dxfId="2" priority="264">
       <formula>$G95="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="294">
-      <formula>$G95="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W95">
     <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
@@ -16413,9 +16692,6 @@
     <cfRule type="expression" dxfId="2" priority="263">
       <formula>$G96="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="293">
-      <formula>$G96="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W96">
     <cfRule type="cellIs" dxfId="2" priority="83" operator="lessThan">
@@ -16459,9 +16735,6 @@
     <cfRule type="expression" dxfId="2" priority="262">
       <formula>$G97="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="292">
-      <formula>$G97="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W97">
     <cfRule type="cellIs" dxfId="2" priority="82" operator="lessThan">
@@ -16505,9 +16778,6 @@
     <cfRule type="expression" dxfId="2" priority="261">
       <formula>$G98="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="291">
-      <formula>$G98="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W98">
     <cfRule type="cellIs" dxfId="2" priority="81" operator="lessThan">
@@ -16551,9 +16821,6 @@
     <cfRule type="expression" dxfId="2" priority="260">
       <formula>$G99="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="290">
-      <formula>$G99="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W99">
     <cfRule type="cellIs" dxfId="2" priority="80" operator="lessThan">
@@ -16597,9 +16864,6 @@
     <cfRule type="expression" dxfId="2" priority="259">
       <formula>$G100="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="289">
-      <formula>$G100="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W100">
     <cfRule type="cellIs" dxfId="2" priority="79" operator="lessThan">
@@ -16643,9 +16907,6 @@
     <cfRule type="expression" dxfId="2" priority="258">
       <formula>$G101="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="288">
-      <formula>$G101="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W101">
     <cfRule type="cellIs" dxfId="2" priority="78" operator="lessThan">
@@ -16689,9 +16950,6 @@
     <cfRule type="expression" dxfId="2" priority="257">
       <formula>$G102="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="287">
-      <formula>$G102="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W102">
     <cfRule type="cellIs" dxfId="2" priority="77" operator="lessThan">
@@ -16735,9 +16993,6 @@
     <cfRule type="expression" dxfId="2" priority="256">
       <formula>$G103="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="286">
-      <formula>$G103="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W103">
     <cfRule type="cellIs" dxfId="2" priority="76" operator="lessThan">
@@ -16781,9 +17036,6 @@
     <cfRule type="expression" dxfId="2" priority="255">
       <formula>$G104="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="285">
-      <formula>$G104="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W104">
     <cfRule type="cellIs" dxfId="2" priority="75" operator="lessThan">
@@ -16827,9 +17079,6 @@
     <cfRule type="expression" dxfId="2" priority="254">
       <formula>$G105="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="284">
-      <formula>$G105="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W105">
     <cfRule type="cellIs" dxfId="2" priority="74" operator="lessThan">
@@ -16873,9 +17122,6 @@
     <cfRule type="expression" dxfId="2" priority="253">
       <formula>$G106="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="283">
-      <formula>$G106="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W106">
     <cfRule type="cellIs" dxfId="2" priority="73" operator="lessThan">
@@ -16919,9 +17165,6 @@
     <cfRule type="expression" dxfId="2" priority="252">
       <formula>$G107="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="282">
-      <formula>$G107="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W107">
     <cfRule type="cellIs" dxfId="2" priority="72" operator="lessThan">
@@ -16965,9 +17208,6 @@
     <cfRule type="expression" dxfId="2" priority="251">
       <formula>$G108="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="281">
-      <formula>$G108="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W108">
     <cfRule type="cellIs" dxfId="2" priority="71" operator="lessThan">
@@ -17011,9 +17251,6 @@
     <cfRule type="expression" dxfId="2" priority="250">
       <formula>$G109="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="280">
-      <formula>$G109="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W109">
     <cfRule type="cellIs" dxfId="2" priority="70" operator="lessThan">
@@ -17057,9 +17294,6 @@
     <cfRule type="expression" dxfId="2" priority="249">
       <formula>$G110="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="279">
-      <formula>$G110="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W110">
     <cfRule type="cellIs" dxfId="2" priority="69" operator="lessThan">
@@ -17103,9 +17337,6 @@
     <cfRule type="expression" dxfId="2" priority="248">
       <formula>$G111="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="278">
-      <formula>$G111="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W111">
     <cfRule type="cellIs" dxfId="2" priority="68" operator="lessThan">
@@ -17149,9 +17380,6 @@
     <cfRule type="expression" dxfId="2" priority="247">
       <formula>$G112="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="277">
-      <formula>$G112="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W112">
     <cfRule type="cellIs" dxfId="2" priority="67" operator="lessThan">
@@ -17195,9 +17423,6 @@
     <cfRule type="expression" dxfId="2" priority="246">
       <formula>$G113="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="276">
-      <formula>$G113="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W113">
     <cfRule type="cellIs" dxfId="2" priority="66" operator="lessThan">
@@ -17241,9 +17466,6 @@
     <cfRule type="expression" dxfId="2" priority="245">
       <formula>$G114="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="275">
-      <formula>$G114="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W114">
     <cfRule type="cellIs" dxfId="2" priority="65" operator="lessThan">
@@ -17287,9 +17509,6 @@
     <cfRule type="expression" dxfId="2" priority="244">
       <formula>$G115="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="274">
-      <formula>$G115="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W115">
     <cfRule type="cellIs" dxfId="2" priority="64" operator="lessThan">
@@ -17333,9 +17552,6 @@
     <cfRule type="expression" dxfId="2" priority="243">
       <formula>$G116="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="273">
-      <formula>$G116="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W116">
     <cfRule type="cellIs" dxfId="2" priority="63" operator="lessThan">
@@ -17379,9 +17595,6 @@
     <cfRule type="expression" dxfId="2" priority="242">
       <formula>$G117="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="272">
-      <formula>$G117="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W117">
     <cfRule type="cellIs" dxfId="2" priority="62" operator="lessThan">
@@ -17425,9 +17638,6 @@
     <cfRule type="expression" dxfId="2" priority="241">
       <formula>$G118="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="271">
-      <formula>$G118="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W118">
     <cfRule type="cellIs" dxfId="2" priority="61" operator="lessThan">
@@ -17471,9 +17681,6 @@
     <cfRule type="expression" dxfId="2" priority="433">
       <formula>$G2="允许开仓（接近锁仓）"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="434">
-      <formula>$G2="允许开仓"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W88">
     <cfRule type="cellIs" dxfId="2" priority="423" operator="lessThan">
@@ -17753,10 +17960,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="16">
-    <dataValidation type="date" operator="between" allowBlank="1" sqref="I53 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I2:I52 I54:I55 I56:I88">
-      <formula1>DATE(2000,1,1)</formula1>
-      <formula2>DATE(2100,12,31)</formula2>
-    </dataValidation>
     <dataValidation type="custom" allowBlank="1" sqref="M53">
       <formula1>OR(M53="",AND(ISNUMBER(M53),M53&gt;=#REF!))</formula1>
     </dataValidation>
@@ -17766,42 +17969,46 @@
     <dataValidation type="custom" allowBlank="1" sqref="M55">
       <formula1>OR(M55="",AND(ISNUMBER(M55),M55&gt;=I53))</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" sqref="C89 E89 J89 K89 N89 C90 E90 J90 K90 N90 C91 E91 J91 K91 N91 C92 E92 J92 K92 N92 C93 E93 J93 K93 N93 C94 E94 J94 K94 N94 C95 E95 J95 K95 N95 C96 E96 J96 K96 N96 C97 E97 J97 K97 N97 C98 E98 J98 K98 N98 C2:C88 E2:E88 N2:N88 J2:K88">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" sqref="C99 E99 J99 K99 N99 C100 E100 J100 K100 N100 C101 E101 J101 K101 N101 C102 E102 J102 K102 N102 C2:C98 E2:E98 N2:N98 J90:K98 J2:K89">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" sqref="D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D2:D88">
+    <dataValidation type="decimal" operator="between" allowBlank="1" sqref="D99 D100 D101 D102 D2:D98">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="当前禁止开仓、计划不完整或风险超限" error="请完成解锁、止损计划和交易预期，确保股数为100股整数倍，且单笔及账户风险均未超过上限" sqref="H89 H90 H91 H92 H93 H94 H95 H96 H97 H98 H2:H88">
-      <formula1>OR(H2="",AND(_LockStatus&lt;&gt;"已锁仓",_LockStatus&lt;&gt;"解锁信息不完整",AG2&lt;&gt;"",AH2&lt;&gt;"",AI2&lt;&gt;"",COUNTIFS(_TrackType,"止损计划",_TrackTradeId,A2,_TrackRule,"计划有效")&gt;0,ISNUMBER(H2),H2&gt;0,H2=INT(H2),MOD(H2,100)=0,AQ2&lt;=C2*D2,SUM($AQ$2:$AQ$98)&lt;=_AccountRiskLimit))</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="当前禁止开仓、计划不完整或风险超限" error="请完成解锁、止损计划和交易预期，确保股数为100股整数倍，且单笔及账户风险均未超过上限" sqref="H99 H100 H101 H102 H2:H98">
+      <formula1>OR(H2="",AND(_LockStatus&lt;&gt;"已锁仓",_LockStatus&lt;&gt;"解锁信息不完整",AG2&lt;&gt;"",AH2&lt;&gt;"",AI2&lt;&gt;"",COUNTIFS(_TrackType,"止损计划",_TrackTradeId,A2,_TrackRule,"计划有效")&gt;0,ISNUMBER(H2),H2&gt;0,H2=INT(H2),MOD(H2,100)=0,AQ2&lt;=C2*D2,SUM($AQ$2:$AQ$102)&lt;=_AccountRiskLimit))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" sqref="L89 L90 L91 L92 L93 L94 L95 L96 L97 L98 L2:L88">
+    <dataValidation type="date" operator="between" allowBlank="1" sqref="I99 I100 I101 I102 I2:I98">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" sqref="L99 L100 L101 L102 L2:L98">
       <formula1>OR(L2="",L2=H2)</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="O89 P89 O90 P90 O91 P91 O92 P92 O93 P93 O94 P94 O95 P95 O96 P96 O97 P97 O98 P98 O2:P88">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="O99 P99 O100 P100 O101 P101 O102 P102 O90:P98 O2:P89">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="AD89 AD90 AD91 AD92 AD93 AD94 AD95 AD96 AD97 AD98 AD2:AD88">
+    <dataValidation type="list" allowBlank="1" sqref="AD99 AD100 AD101 AD102 AD2:AD98">
       <formula1>"1-差,2-较差,3-一般,4-良好,5-优秀"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="交易预期无效" error="请从短期博反弹、突破冲新高、趋势波段中选择" sqref="AG89 AG90 AG91 AG92 AG93 AG94 AG95 AG96 AG97 AG98 AG2:AG88">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="交易预期无效" error="请从短期博反弹、突破冲新高、趋势波段中选择" sqref="AG99 AG100 AG101 AG102 AG2:AG98">
       <formula1>"短期博反弹,突破冲新高,趋势波段"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="预期持有周期无效" error="请从预设的交易日范围中选择" sqref="AH89 AH90 AH91 AH92 AH93 AH94 AH95 AH96 AH97 AH98 AH2:AH88">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="预期持有周期无效" error="请从预设的交易日范围中选择" sqref="AH99 AH100 AH101 AH102 AH2:AH98">
       <formula1>"1～3个交易日,4～10个交易日,11～20个交易日,21～60个交易日,60个交易日以上"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="第二批买入价无效" error="请填写大于0的价格；删除分仓时先删除股数" sqref="AK89 AK90 AK91 AK92 AK93 AK94 AK95 AK96 AK97 AK98 AK2:AK88">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="第二批买入价无效" error="请填写大于0的价格；删除分仓时先删除股数" sqref="AK99 AK100 AK101 AK102 AK2:AK98">
       <formula1>OR(AK2="",AND(ISNUMBER(AK2),AK2&gt;0))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="第二批加仓被阻止" error="请先填写第二批价格并确认已解锁；股数必须为100股整数倍，且加仓后不能超过单笔或账户风险上限" sqref="AL89 AL90 AL91 AL92 AL93 AL94 AL95 AL96 AL97 AL98 AL2:AL88">
-      <formula1>OR(AL2="",AND(AK2&lt;&gt;"",ISNUMBER(AL2),AL2&gt;0,AL2=INT(AL2),MOD(AL2,100)=0,_LockStatus&lt;&gt;"已锁仓",_LockStatus&lt;&gt;"解锁信息不完整",AQ2&lt;=C2*D2,SUM($AQ$2:$AQ$98)&lt;=_AccountRiskLimit))</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="第二批加仓被阻止" error="请先填写第二批价格并确认已解锁；股数必须为100股整数倍，且加仓后不能超过单笔或账户风险上限" sqref="AL99 AL100 AL101 AL102 AL2:AL98">
+      <formula1>OR(AL2="",AND(AK2&lt;&gt;"",ISNUMBER(AL2),AL2&gt;0,AL2=INT(AL2),MOD(AL2,100)=0,_LockStatus&lt;&gt;"已锁仓",_LockStatus&lt;&gt;"解锁信息不完整",AQ2&lt;=C2*D2,SUM($AQ$2:$AQ$102)&lt;=_AccountRiskLimit))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="第三批买入价无效" error="请先完整填写第二批，再填写大于0的第三批价格" sqref="AM89 AM90 AM91 AM92 AM93 AM94 AM95 AM96 AM97 AM98 AM2:AM88">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="第三批买入价无效" error="请先完整填写第二批，再填写大于0的第三批价格" sqref="AM99 AM100 AM101 AM102 AM2:AM98">
       <formula1>OR(AM2="",AND(ISNUMBER(AM2),AM2&gt;0,AND(AK2&lt;&gt;"",AL2&lt;&gt;"")))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="第三批加仓被阻止" error="请先完整填写前两批并确认已解锁；股数必须为100股整数倍，且加仓后不能超过单笔或账户风险上限" sqref="AN89 AN90 AN91 AN92 AN93 AN94 AN95 AN96 AN97 AN98 AN2:AN88">
-      <formula1>OR(AN2="",AND(AK2&lt;&gt;"",AL2&lt;&gt;"",AM2&lt;&gt;"",ISNUMBER(AN2),AN2&gt;0,AN2=INT(AN2),MOD(AN2,100)=0,_LockStatus&lt;&gt;"已锁仓",_LockStatus&lt;&gt;"解锁信息不完整",AQ2&lt;=C2*D2,SUM($AQ$2:$AQ$98)&lt;=_AccountRiskLimit))</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="第三批加仓被阻止" error="请先完整填写前两批并确认已解锁；股数必须为100股整数倍，且加仓后不能超过单笔或账户风险上限" sqref="AN99 AN100 AN101 AN102 AN2:AN98">
+      <formula1>OR(AN2="",AND(AK2&lt;&gt;"",AL2&lt;&gt;"",AM2&lt;&gt;"",ISNUMBER(AN2),AN2&gt;0,AN2=INT(AN2),MOD(AN2,100)=0,_LockStatus&lt;&gt;"已锁仓",_LockStatus&lt;&gt;"解锁信息不完整",AQ2&lt;=C2*D2,SUM($AQ$2:$AQ$102)&lt;=_AccountRiskLimit))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17845,91 +18052,91 @@
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:29">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="R1" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="S1" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="T1" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="U1" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="V1" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="W1" s="16" t="s">
+      <c r="W1" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="X1" s="16" t="s">
+      <c r="X1" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="Y1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="Z1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AA1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AB1" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AC1" s="15" t="s">
         <v>94</v>
       </c>
     </row>
@@ -30694,7 +30901,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="14" t="s">
         <v>126</v>
       </c>
     </row>
@@ -30709,7 +30916,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="14" t="s">
         <v>127</v>
       </c>
     </row>
@@ -30724,7 +30931,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="14" t="s">
         <v>128</v>
       </c>
     </row>
@@ -30739,7 +30946,7 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="15" t="s">
+      <c r="I38" s="14" t="s">
         <v>129</v>
       </c>
     </row>
@@ -30754,7 +30961,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="14" t="s">
         <v>130</v>
       </c>
     </row>
@@ -30769,7 +30976,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="14" t="s">
         <v>131</v>
       </c>
     </row>
@@ -30784,7 +30991,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="14" t="s">
         <v>132</v>
       </c>
     </row>
@@ -31654,8 +31861,10 @@
         <v>184</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="2"/>
+    <row r="100" ht="17" spans="1:9">
+      <c r="A100" s="2">
+        <v>97</v>
+      </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -31663,7 +31872,9 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
+      <c r="I100" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="2"/>
@@ -34988,169 +35199,169 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B2" s="8">
-        <f>COUNT(单次交易!M2:M98)</f>
-        <v>96</v>
+        <f>COUNT(单次交易!M2:M102)</f>
+        <v>100</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B3" s="8">
-        <f>COUNTIF(单次交易!X2:X98,"&gt;0")</f>
-        <v>42</v>
+        <f>COUNTIF(单次交易!X2:X102,"&gt;0")</f>
+        <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B4" s="8">
-        <f>COUNTIF(单次交易!X2:X98,"&lt;0")</f>
-        <v>54</v>
+        <f>COUNTIF(单次交易!X2:X102,"&lt;0")</f>
+        <v>58</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B5" s="8">
-        <f>COUNTIFS(单次交易!M2:M98,"&lt;&gt;",单次交易!X2:X98,"=0")</f>
+        <f>COUNTIFS(单次交易!M2:M102,"&lt;&gt;",单次交易!X2:X102,"=0")</f>
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B6" s="7">
         <f>IFERROR(B3/(B3+B4),"")</f>
-        <v>0.4375</v>
+        <v>0.425742574257426</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" s="7">
         <f>IFERROR(B4/(B3+B4),"")</f>
-        <v>0.5625</v>
+        <v>0.574257425742574</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B8" s="7">
-        <f>IFERROR(AVERAGEIF(单次交易!X2:X98,"&gt;0",单次交易!AE2:AE98),"")</f>
-        <v>0.072548626922961</v>
+        <f>IFERROR(AVERAGEIF(单次交易!X2:X102,"&gt;0",单次交易!AE2:AE102),"")</f>
+        <v>0.0719438248745022</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B9" s="7">
-        <f>IFERROR(-AVERAGEIF(单次交易!X2:X98,"&lt;0",单次交易!AE2:AE98),"")</f>
-        <v>0.0351041725238816</v>
+        <f>IFERROR(-AVERAGEIF(单次交易!X2:X102,"&lt;0",单次交易!AE2:AE102),"")</f>
+        <v>0.0368707067050814</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B10" s="8" t="e">
-        <f>SUMIF(单次交易!X2:X98,"&gt;0",单次交易!AA2:AA98)</f>
+        <f>SUMIF(单次交易!X2:X102,"&gt;0",单次交易!AA2:AA102)</f>
         <v>#REF!</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="8">
+        <f>SUMIF(单次交易!X2:X102,"&lt;0",单次交易!AA2:AA102)</f>
+        <v>2052</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="B11" s="8">
-        <f>SUMIF(单次交易!X2:X98,"&lt;0",单次交易!AA2:AA98)</f>
-        <v>1811</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B12" s="5">
-        <f>IFERROR(SUMPRODUCT(单次交易!AO2:AO98,单次交易!AP2:AP98)/COUNT(单次交易!AP2:AP98),"")</f>
-        <v>101087.53125</v>
+        <f>IFERROR(SUMPRODUCT(单次交易!AO2:AO102,单次交易!AP2:AP102)/COUNT(单次交易!AP2:AP102),"")</f>
+        <v>99802.396039604</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B13" s="7">
         <f>IF(OR(B6="",B7="",B8="",B9=""),"",B6*B8-B7*B9)</f>
-        <v>0.011993927234112</v>
+        <v>0.00945627208622648</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B14" s="7">
-        <f>IF(COUNT(单次交易!AE2:AE98)=0,"",EXP(SUMPRODUCT(IFERROR(LN(1+单次交易!AE2:AE98),0)))-1)</f>
-        <v>1.35733653640849</v>
+        <f>IF(COUNT(单次交易!AE2:AE102)=0,"",EXP(SUMPRODUCT(IFERROR(LN(1+单次交易!AE2:AE102),0)))-1)</f>
+        <v>0.91500771524292</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -35172,130 +35383,130 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B2" s="10">
         <v>100000</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B3" s="5">
-        <f>IF(B2="","",B2+SUM(单次交易!X2:X98))</f>
-        <v>235665</v>
+        <f>IF(B2="","",B2+SUM(单次交易!X2:X102))</f>
+        <v>191445</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B4" s="6">
         <v>0.02</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B5" s="5">
         <f>IF(B3="","",B3*B4)</f>
-        <v>4713.3</v>
+        <v>3828.9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B6" s="6">
         <v>0.06</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B7" s="5">
         <f>IF(B3="","",B3*B6)</f>
-        <v>14139.9</v>
+        <v>11486.7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B8" s="5">
-        <f ca="1">SUMIFS(单次交易!X2:X98,单次交易!X2:X98,"&lt;0",单次交易!M2:M98,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,单次交易!M2:M98,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
+        <f ca="1">SUMIFS(单次交易!X2:X102,单次交易!X2:X102,"&lt;0",单次交易!M2:M102,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,单次交易!M2:M102,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B9" s="5">
-        <f>IFERROR(SUM(单次交易!AQ2:AQ98),0)</f>
-        <v>0</v>
+        <f>IFERROR(SUM(单次交易!AQ2:AQ102),0)</f>
+        <v>10879</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B10" s="5">
         <f>IF(OR(B7="",B9=""),"",B7-B9)</f>
-        <v>14139.9</v>
+        <v>607.699999999999</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B11" s="7">
         <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
-        <v>1.35665</v>
+        <v>0.914449999999999</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -35305,129 +35516,129 @@
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B13" s="6">
         <v>0.06</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="11">
-        <f>IFERROR(LOOKUP(2,1/((单次交易!$M$2:$M$98&lt;&gt;"")*(单次交易!$X$2:$X$98&gt;0)),ROW(单次交易!$X$2:$X$98)-1),0)</f>
+        <f>IFERROR(LOOKUP(2,1/((单次交易!$M$2:$M$102&lt;&gt;"")*(单次交易!$X$2:$X$102&gt;0)),ROW(单次交易!$X$2:$X$102)-1),0)</f>
         <v>93</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B15" s="11">
-        <f>IFERROR(LOOKUP(2,1/(单次交易!$M$2:$M$98&lt;&gt;""),ROW(单次交易!$M$2:$M$98)-1),0)</f>
-        <v>96</v>
+        <f>IFERROR(LOOKUP(2,1/(单次交易!$M$2:$M$102&lt;&gt;""),ROW(单次交易!$M$2:$M$102)-1),0)</f>
+        <v>100</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B18" s="11">
         <f>MAX(B14,IF(AND(ISNUMBER(B16),B16&gt;=1,B16&lt;=B15,B17&lt;&gt;""),B16,0))</f>
         <v>93</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B19" s="5" t="e">
         <f ca="1">IF(B2="","",IF(B18=0,B2,B2+SUM(单次交易!#REF!:INDEX(单次交易!$X:$X,B18+1))))</f>
         <v>#REF!</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B20" s="5" t="e">
-        <f>IF(B18&gt;=B15,0,-SUMPRODUCT((ROW(单次交易!$X$2:$X$98)-1&gt;B18)*(单次交易!$M$2:$M$98&lt;&gt;"")*(IFERROR(单次交易!$X$2:$X$98,0)&lt;0)*IFERROR(单次交易!$X$2:$X$98,0)))</f>
-        <v>#VALUE!</v>
+        <v>251</v>
+      </c>
+      <c r="B20" s="5">
+        <f>IF(B18&gt;=B15,0,-SUMPRODUCT((ROW(单次交易!$X$2:$X$102)-1&gt;B18)*(单次交易!$M$2:$M$102&lt;&gt;"")*(IFERROR(单次交易!$X$2:$X$102,0)&lt;0)*IFERROR(单次交易!$X$2:$X$102,0)))</f>
+        <v>65584</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B21" s="7" t="e">
         <f ca="1">IF(OR(B19="",B19&lt;=0),"",B20/B19)</f>
         <v>#REF!</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" ht="17" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B22" s="7" t="e">
         <f ca="1">IF(OR(B13="",B13&lt;=0,B21=""),"",B21/B13)</f>
         <v>#REF!</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" ht="17" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B23" s="8" t="str">
         <f ca="1">IF(OR(AND(B16&lt;&gt;"",B17=""),AND(B16="",B17&lt;&gt;""),AND(B16&lt;&gt;"",OR(NOT(ISNUMBER(B16)),B16&lt;1,B16&gt;B15,B16&lt;&gt;INT(B16)))),"解锁信息不完整",IF(B22&gt;=1,"已锁仓",IF(B22&gt;=0.8,"接近锁仓","正常")))</f>
         <v>解锁信息不完整</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -35482,84 +35693,84 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B2" s="5">
         <f>账户数据!B3</f>
-        <v>235665</v>
+        <v>191445</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B3" s="6">
         <v>0.1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B4" s="5">
         <f>IF(OR(B2="",B3=""),"",B2*B3)</f>
-        <v>23566.5</v>
+        <v>19144.5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B5" s="5">
         <f>多次统计数据!B12</f>
-        <v>101087.53125</v>
+        <v>99802.396039604</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B6" s="7">
         <f>多次统计数据!B13</f>
-        <v>0.011993927234112</v>
+        <v>0.00945627208622648</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B7" s="8">
         <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -35586,57 +35797,57 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
@@ -35644,175 +35855,175 @@
         <v>77</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:3">
